--- a/Results/Ammonia/ammonia climate change results.xlsx
+++ b/Results/Ammonia/ammonia climate change results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.417550582496121</v>
+        <v>2.417532495720357</v>
       </c>
       <c r="C2" t="n">
-        <v>2.260307538569336</v>
+        <v>2.260282269662309</v>
       </c>
       <c r="D2" t="n">
-        <v>2.595330440153435</v>
+        <v>2.595310408075174</v>
       </c>
       <c r="E2" t="n">
-        <v>2.342985442775621</v>
+        <v>2.342958823808085</v>
       </c>
       <c r="F2" t="n">
-        <v>2.058498645533257</v>
+        <v>2.058476387317136</v>
       </c>
       <c r="G2" t="n">
-        <v>2.41302083569496</v>
+        <v>2.412940089071636</v>
       </c>
       <c r="H2" t="n">
-        <v>3.016476049879009</v>
+        <v>3.01645705307318</v>
       </c>
       <c r="I2" t="n">
-        <v>2.075003173506539</v>
+        <v>2.074977620092314</v>
       </c>
       <c r="J2" t="n">
-        <v>2.988202922147854</v>
+        <v>2.98816970727029</v>
       </c>
       <c r="K2" t="n">
-        <v>2.490299971400115</v>
+        <v>2.490282154802283</v>
       </c>
       <c r="L2" t="n">
-        <v>2.738957083283865</v>
+        <v>2.738938957910787</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8172994278973454</v>
+        <v>0.8172797408185825</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6085029915715012</v>
+        <v>0.6084750155201769</v>
       </c>
       <c r="D3" t="n">
-        <v>1.021783091189837</v>
+        <v>1.021761166610222</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6912782618614458</v>
+        <v>0.6912489222897964</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4067914646190794</v>
+        <v>0.4067664857988457</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8120892807418023</v>
+        <v>0.8119975218583808</v>
       </c>
       <c r="H3" t="n">
-        <v>1.506277553911232</v>
+        <v>1.506256811078456</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4231631498972777</v>
+        <v>0.4231349117099373</v>
       </c>
       <c r="J3" t="n">
-        <v>1.403904620169232</v>
+        <v>1.40386838053149</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8708668618088833</v>
+        <v>0.8708472397551937</v>
       </c>
       <c r="L3" t="n">
-        <v>1.186967716869094</v>
+        <v>1.186947981958085</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.187179812577616</v>
+        <v>0.5789019122578414</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9469497524650863</v>
+        <v>0.3688173603806966</v>
       </c>
       <c r="D4" t="n">
-        <v>1.292862404783301</v>
+        <v>0.6845833480636238</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9547228157983106</v>
+        <v>0.3701854034321411</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9547228157983106</v>
+        <v>0.3701854034321416</v>
       </c>
       <c r="G4" t="n">
-        <v>1.182248078233767</v>
+        <v>0.575777878633382</v>
       </c>
       <c r="H4" t="n">
-        <v>1.543086306964297</v>
+        <v>0.9348078501230173</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9688076784682788</v>
+        <v>0.3726201463076686</v>
       </c>
       <c r="J4" t="n">
-        <v>1.25031458973282</v>
+        <v>0.6420310520021244</v>
       </c>
       <c r="K4" t="n">
-        <v>1.111265586909805</v>
+        <v>0.5029868746801484</v>
       </c>
       <c r="L4" t="n">
-        <v>1.378179028417127</v>
+        <v>0.7699010867731888</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.67858386385338</v>
+        <v>7.529368491465444</v>
       </c>
       <c r="C5" t="n">
-        <v>20.25807679606282</v>
+        <v>3.767474817084589</v>
       </c>
       <c r="D5" t="n">
-        <v>52.92180503469119</v>
+        <v>9.771236304173193</v>
       </c>
       <c r="E5" t="n">
-        <v>20.25807689211288</v>
+        <v>3.767474913130343</v>
       </c>
       <c r="F5" t="n">
-        <v>20.25807689211288</v>
+        <v>3.767474913130343</v>
       </c>
       <c r="G5" t="n">
-        <v>42.57346547567364</v>
+        <v>7.859917809760038</v>
       </c>
       <c r="H5" t="n">
-        <v>89.02413960020668</v>
+        <v>16.33143903885966</v>
       </c>
       <c r="I5" t="n">
-        <v>20.25802437603375</v>
+        <v>3.767422404730512</v>
       </c>
       <c r="J5" t="n">
-        <v>51.16262447846517</v>
+        <v>9.426468539986146</v>
       </c>
       <c r="K5" t="n">
-        <v>33.96194681442614</v>
+        <v>6.284672104273306</v>
       </c>
       <c r="L5" t="n">
-        <v>71.93973950506121</v>
+        <v>5.513234063568357</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.882092437814935</v>
+        <v>0.6087508923831393</v>
       </c>
       <c r="C6" t="n">
-        <v>1.103647838665129</v>
+        <v>0.3963909003335196</v>
       </c>
       <c r="D6" t="n">
-        <v>1.501538299196551</v>
+        <v>0.7213048418870265</v>
       </c>
       <c r="E6" t="n">
-        <v>1.087508166160554</v>
+        <v>0.3935506228635611</v>
       </c>
       <c r="F6" t="n">
-        <v>1.137468921173301</v>
+        <v>0.4023425306113481</v>
       </c>
       <c r="G6" t="n">
-        <v>1.877160703471085</v>
+        <v>0.6980526721738542</v>
       </c>
       <c r="H6" t="n">
-        <v>2.303437400004706</v>
+        <v>1.068606222744353</v>
       </c>
       <c r="I6" t="n">
-        <v>1.663720303705597</v>
+        <v>0.4024691264329654</v>
       </c>
       <c r="J6" t="n">
-        <v>1.451781120582664</v>
+        <v>0.6774834288048043</v>
       </c>
       <c r="K6" t="n">
-        <v>1.282147564141567</v>
+        <v>0.5330577704669771</v>
       </c>
       <c r="L6" t="n">
-        <v>1.564382845232672</v>
+        <v>0.8026676189336024</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.822436838540752</v>
+        <v>0.6906997894271564</v>
       </c>
       <c r="C7" t="n">
-        <v>1.604117124460473</v>
+        <v>0.4844704358310645</v>
       </c>
       <c r="D7" t="n">
-        <v>1.925940824857355</v>
+        <v>0.7959977906679099</v>
       </c>
       <c r="E7" t="n">
-        <v>1.603157288181075</v>
+        <v>0.4843016067836916</v>
       </c>
       <c r="F7" t="n">
-        <v>1.603157288181075</v>
+        <v>0.4843016067836916</v>
       </c>
       <c r="G7" t="n">
-        <v>1.817505104196906</v>
+        <v>0.6875757558026938</v>
       </c>
       <c r="H7" t="n">
-        <v>2.17834333292744</v>
+        <v>1.046605727292331</v>
       </c>
       <c r="I7" t="n">
-        <v>1.604064704431417</v>
+        <v>0.4844180234769807</v>
       </c>
       <c r="J7" t="n">
-        <v>1.88557161569596</v>
+        <v>0.7538289291714363</v>
       </c>
       <c r="K7" t="n">
-        <v>1.746522612872941</v>
+        <v>0.6147847518494597</v>
       </c>
       <c r="L7" t="n">
-        <v>2.013436054380266</v>
+        <v>0.8816989639425007</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.126109124821605</v>
+        <v>0.7441409269139324</v>
       </c>
       <c r="C8" t="n">
-        <v>2.654167227209667</v>
+        <v>0.6692650322040856</v>
       </c>
       <c r="D8" t="n">
-        <v>3.13054156059865</v>
+        <v>1.00799140024478</v>
       </c>
       <c r="E8" t="n">
-        <v>2.449771634899752</v>
+        <v>0.6332939619722338</v>
       </c>
       <c r="F8" t="n">
-        <v>1.932112669015461</v>
+        <v>0.5421922725004463</v>
       </c>
       <c r="G8" t="n">
-        <v>2.865572134611535</v>
+        <v>0.8720213113269694</v>
       </c>
       <c r="H8" t="n">
-        <v>3.226410363342304</v>
+        <v>1.231051282816649</v>
       </c>
       <c r="I8" t="n">
-        <v>2.652131734846046</v>
+        <v>0.6688635790012569</v>
       </c>
       <c r="J8" t="n">
-        <v>2.933784940450778</v>
+        <v>0.9383002307196412</v>
       </c>
       <c r="K8" t="n">
-        <v>2.036367384654578</v>
+        <v>0.665792415021499</v>
       </c>
       <c r="L8" t="n">
-        <v>3.839085639803833</v>
+        <v>1.20298958842759</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.732725303215844</v>
+        <v>1.026853332133402</v>
       </c>
       <c r="C9" t="n">
-        <v>4.282723782233038</v>
+        <v>0.9558296459234816</v>
       </c>
       <c r="D9" t="n">
-        <v>4.606726216246665</v>
+        <v>1.267740457814876</v>
       </c>
       <c r="E9" t="n">
-        <v>5.169345400065267</v>
+        <v>1.111853972115889</v>
       </c>
       <c r="F9" t="n">
-        <v>4.282722680252481</v>
+        <v>0.9558295311501762</v>
       </c>
       <c r="G9" t="n">
-        <v>4.496111761969472</v>
+        <v>1.158934965895113</v>
       </c>
       <c r="H9" t="n">
-        <v>4.856949990700012</v>
+        <v>1.517964937384745</v>
       </c>
       <c r="I9" t="n">
-        <v>4.282671362203992</v>
+        <v>0.9557772335693995</v>
       </c>
       <c r="J9" t="n">
-        <v>4.564178273468526</v>
+        <v>1.225188139263855</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45767948811914</v>
+        <v>1.007805276723709</v>
       </c>
       <c r="L9" t="n">
-        <v>4.692042712152837</v>
+        <v>1.353058174034919</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.647293637461354</v>
+        <v>1.647275061524633</v>
       </c>
       <c r="C2" t="n">
-        <v>1.875903771955841</v>
+        <v>1.87587811887571</v>
       </c>
       <c r="D2" t="n">
-        <v>1.709240142627601</v>
+        <v>1.709220959989722</v>
       </c>
       <c r="E2" t="n">
-        <v>1.952119894929023</v>
+        <v>1.952092833140835</v>
       </c>
       <c r="F2" t="n">
-        <v>1.686469998314986</v>
+        <v>1.686447449571343</v>
       </c>
       <c r="G2" t="n">
-        <v>1.650719396353891</v>
+        <v>1.650639128318577</v>
       </c>
       <c r="H2" t="n">
-        <v>1.655962351550949</v>
+        <v>1.655941777442235</v>
       </c>
       <c r="I2" t="n">
-        <v>1.705440844212866</v>
+        <v>1.705415056793222</v>
       </c>
       <c r="J2" t="n">
-        <v>2.228263764176924</v>
+        <v>2.228229389099236</v>
       </c>
       <c r="K2" t="n">
-        <v>1.957421768943909</v>
+        <v>1.957404764038598</v>
       </c>
       <c r="L2" t="n">
-        <v>1.724419527260575</v>
+        <v>1.72439197969406</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.07137858971107494</v>
+        <v>-0.07139885166265666</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1658918654386363</v>
+        <v>0.1658634587213661</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0001272765900045894</v>
+        <v>-0.0001482363735962333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2421844796148505</v>
+        <v>0.2421546498184836</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02346541699918595</v>
+        <v>-0.02349073375100807</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.06743825734084014</v>
+        <v>-0.06752947798528464</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06135047669683783</v>
+        <v>-0.06137304514606296</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.00452430372733327</v>
+        <v>-0.004552822872325626</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5335406873642534</v>
+        <v>0.5335031687239125</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2592320198962697</v>
+        <v>0.2592133350308409</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01732382041862147</v>
+        <v>0.0172932365250339</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4757081630435882</v>
+        <v>0.08120478279237679</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4790378801318814</v>
+        <v>0.1102786302578028</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5125327354688334</v>
+        <v>0.1180289945594927</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4823631693965851</v>
+        <v>0.1108639206133964</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4823631693965851</v>
+        <v>0.1108639206133966</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4763236810495027</v>
+        <v>0.08295451059608276</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4808660917765892</v>
+        <v>0.08636150861579606</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5007953849861002</v>
+        <v>0.1141084124894316</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5704889716564955</v>
+        <v>0.1759798230353766</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5567693201160305</v>
+        <v>0.1622659638269827</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5215190025137937</v>
+        <v>0.1270102729236882</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.964712509544063</v>
+        <v>-0.3483312367845494</v>
       </c>
       <c r="C5" t="n">
-        <v>1.046218978489251</v>
+        <v>0.2100153496440155</v>
       </c>
       <c r="D5" t="n">
-        <v>1.238244891931491</v>
+        <v>0.2457255643541448</v>
       </c>
       <c r="E5" t="n">
-        <v>1.046219143038826</v>
+        <v>0.2100155141881107</v>
       </c>
       <c r="F5" t="n">
-        <v>1.046219143038821</v>
+        <v>0.2100155141881107</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.795833672016502</v>
+        <v>-0.3175274569934982</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.711603884146703</v>
+        <v>-0.2995592229228925</v>
       </c>
       <c r="I5" t="n">
-        <v>1.046220656245816</v>
+        <v>0.210017034975326</v>
       </c>
       <c r="J5" t="n">
-        <v>6.808151087630462</v>
+        <v>1.27368979358499</v>
       </c>
       <c r="K5" t="n">
-        <v>4.798330675772625</v>
+        <v>0.9087584540552797</v>
       </c>
       <c r="L5" t="n">
-        <v>1.640886795630335</v>
+        <v>0.4376182268273607</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6829090989784778</v>
+        <v>0.1176465208691679</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5103842135845171</v>
+        <v>0.1157909080324929</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5272713384737922</v>
+        <v>0.1569385484653947</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5063008672941702</v>
+        <v>0.1150725716950624</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5129047670053999</v>
+        <v>0.1162338461396985</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6835246169843932</v>
+        <v>0.08507298590353617</v>
       </c>
       <c r="H6" t="n">
-        <v>0.72901045106072</v>
+        <v>0.1300144385249259</v>
       </c>
       <c r="I6" t="n">
-        <v>0.512859273137092</v>
+        <v>0.1162268877968846</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8011777290592561</v>
+        <v>0.2165547627245805</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5812965757123338</v>
+        <v>0.1665790072628791</v>
       </c>
       <c r="L6" t="n">
-        <v>0.535935355506643</v>
+        <v>0.1295428918097125</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8059490510941736</v>
+        <v>0.1393207774839751</v>
       </c>
       <c r="C7" t="n">
-        <v>0.831034595280122</v>
+        <v>0.1722227218497178</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8408815300194181</v>
+        <v>0.1758119808521386</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8249212242346169</v>
+        <v>0.1711469292301149</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8249212242346171</v>
+        <v>0.1711469292301149</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8065645691000878</v>
+        <v>0.1410705052876806</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8111069798271738</v>
+        <v>0.1444775033073944</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8310362730366849</v>
+        <v>0.1722244071810291</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9007298597070816</v>
+        <v>0.2340958177269747</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8870102081666155</v>
+        <v>0.2203819585185806</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8517598905643795</v>
+        <v>0.1851262676152866</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8739476864825967</v>
+        <v>0.1512838790191039</v>
       </c>
       <c r="C8" t="n">
-        <v>1.218664186854071</v>
+        <v>0.2404328493795895</v>
       </c>
       <c r="D8" t="n">
-        <v>1.300774998402154</v>
+        <v>0.2567388601898822</v>
       </c>
       <c r="E8" t="n">
-        <v>1.130160241999355</v>
+        <v>0.2248584884515391</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9067543993241267</v>
+        <v>0.1855446445889162</v>
       </c>
       <c r="G8" t="n">
-        <v>1.197585223954237</v>
+        <v>0.2098774376097499</v>
       </c>
       <c r="H8" t="n">
-        <v>1.202127634682576</v>
+        <v>0.2132844356296831</v>
       </c>
       <c r="I8" t="n">
-        <v>1.222056927890836</v>
+        <v>0.241031339503098</v>
       </c>
       <c r="J8" t="n">
-        <v>1.291813997663435</v>
+        <v>0.3029139214940336</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9490085436965371</v>
+        <v>0.2312891567119145</v>
       </c>
       <c r="L8" t="n">
-        <v>1.580204055443337</v>
+        <v>0.3133113344035779</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.33092949238584</v>
+        <v>0.23168155500101</v>
       </c>
       <c r="C9" t="n">
-        <v>1.622992171547724</v>
+        <v>0.3115593667671088</v>
       </c>
       <c r="D9" t="n">
-        <v>1.634731186259055</v>
+        <v>0.315481631777647</v>
       </c>
       <c r="E9" t="n">
-        <v>1.931078186770382</v>
+        <v>0.3657686682497905</v>
       </c>
       <c r="F9" t="n">
-        <v>1.622992264072929</v>
+        <v>0.3115595186465068</v>
       </c>
       <c r="G9" t="n">
-        <v>1.598522145367693</v>
+        <v>0.2804071502050711</v>
       </c>
       <c r="H9" t="n">
-        <v>1.603064556094781</v>
+        <v>0.2838141482247854</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6229938493043</v>
+        <v>0.3115610520984207</v>
       </c>
       <c r="J9" t="n">
-        <v>1.692687435974689</v>
+        <v>0.3734324626443654</v>
       </c>
       <c r="K9" t="n">
-        <v>1.524280178239231</v>
+        <v>0.3325006003701622</v>
       </c>
       <c r="L9" t="n">
-        <v>1.643717466831984</v>
+        <v>0.3244629125326774</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.013009959808053</v>
+        <v>2.012949001975416</v>
       </c>
       <c r="C2" t="n">
-        <v>1.890469841819948</v>
+        <v>1.890434589269223</v>
       </c>
       <c r="D2" t="n">
-        <v>2.326339740257336</v>
+        <v>2.32631413506825</v>
       </c>
       <c r="E2" t="n">
-        <v>1.890865728773785</v>
+        <v>1.890843677354061</v>
       </c>
       <c r="F2" t="n">
-        <v>1.890865728773785</v>
+        <v>1.890843677354061</v>
       </c>
       <c r="G2" t="n">
-        <v>2.21661821245746</v>
+        <v>2.216529554116152</v>
       </c>
       <c r="H2" t="n">
-        <v>2.451317823432309</v>
+        <v>2.451291557522031</v>
       </c>
       <c r="I2" t="n">
-        <v>2.033472200036116</v>
+        <v>2.033443653673401</v>
       </c>
       <c r="J2" t="n">
-        <v>2.602527199639058</v>
+        <v>2.602490923726529</v>
       </c>
       <c r="K2" t="n">
-        <v>2.241109390821014</v>
+        <v>2.241087818605637</v>
       </c>
       <c r="L2" t="n">
-        <v>2.150717660322409</v>
+        <v>2.150631894798239</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3373650638756383</v>
+        <v>0.337296307751906</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2243715582921787</v>
+        <v>0.2243311864139246</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6977592174607954</v>
+        <v>0.6977311242004282</v>
       </c>
       <c r="E3" t="n">
-        <v>0.218295118976688</v>
+        <v>0.2182701390614692</v>
       </c>
       <c r="F3" t="n">
-        <v>0.218295118976688</v>
+        <v>0.2182701390614692</v>
       </c>
       <c r="G3" t="n">
-        <v>0.571556731744928</v>
+        <v>0.5714561142980832</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8416010645576594</v>
+        <v>0.8415722031430007</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3608422701511121</v>
+        <v>0.360810834827306</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9856508795586738</v>
+        <v>0.9856110467004702</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5844587531392959</v>
+        <v>0.5844347565995028</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4957586834435468</v>
+        <v>0.4956613928719871</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8345891666089033</v>
+        <v>0.2717088660387958</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8511045668981588</v>
+        <v>0.3059842886618993</v>
       </c>
       <c r="D4" t="n">
-        <v>1.020850444176966</v>
+        <v>0.4579911592554217</v>
       </c>
       <c r="E4" t="n">
-        <v>0.819308853026752</v>
+        <v>0.2790652765223112</v>
       </c>
       <c r="F4" t="n">
-        <v>0.819308853026752</v>
+        <v>0.2790652765223111</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9533219081541882</v>
+        <v>0.392323445308644</v>
       </c>
       <c r="H4" t="n">
-        <v>1.095099645669073</v>
+        <v>0.5322399521988312</v>
       </c>
       <c r="I4" t="n">
-        <v>0.831536993064891</v>
+        <v>0.2811908101570385</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0671708263593</v>
+        <v>0.5043073112760426</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9097605663855169</v>
+        <v>0.346901533747647</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9164659618545002</v>
+        <v>0.353570909376294</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.32246117491027</v>
+        <v>2.117174724905365</v>
       </c>
       <c r="C5" t="n">
-        <v>15.04100623034964</v>
+        <v>2.803190179074978</v>
       </c>
       <c r="D5" t="n">
-        <v>29.01947296333251</v>
+        <v>5.385715332933976</v>
       </c>
       <c r="E5" t="n">
-        <v>12.24093031851055</v>
+        <v>2.289206276250162</v>
       </c>
       <c r="F5" t="n">
-        <v>12.24093031851055</v>
+        <v>2.289206276250162</v>
       </c>
       <c r="G5" t="n">
-        <v>23.35668071369964</v>
+        <v>4.334627976681535</v>
       </c>
       <c r="H5" t="n">
-        <v>40.94260421856198</v>
+        <v>7.54535501183231</v>
       </c>
       <c r="I5" t="n">
-        <v>12.24089911449961</v>
+        <v>2.289175080594552</v>
       </c>
       <c r="J5" t="n">
-        <v>35.24936972994723</v>
+        <v>6.520263865221573</v>
       </c>
       <c r="K5" t="n">
-        <v>18.32146074355159</v>
+        <v>3.411331521851606</v>
       </c>
       <c r="L5" t="n">
-        <v>21.7414210063097</v>
+        <v>4.018025470065643</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.343539781416235</v>
+        <v>0.2912345392229802</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9658597967137917</v>
+        <v>0.326175982751076</v>
       </c>
       <c r="D6" t="n">
-        <v>1.151874837186359</v>
+        <v>0.4810461636064197</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9082199527502582</v>
+        <v>0.2947089586384521</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9411627459221822</v>
+        <v>0.3005056299320089</v>
       </c>
       <c r="G6" t="n">
-        <v>1.462272522961522</v>
+        <v>0.4818687273643255</v>
       </c>
       <c r="H6" t="n">
-        <v>1.683625876011968</v>
+        <v>0.6357980130154181</v>
       </c>
       <c r="I6" t="n">
-        <v>1.340487607872224</v>
+        <v>0.3707360922127199</v>
       </c>
       <c r="J6" t="n">
-        <v>1.610138310450412</v>
+        <v>0.599841287715084</v>
       </c>
       <c r="K6" t="n">
-        <v>1.020164190242965</v>
+        <v>0.3663284947691112</v>
       </c>
       <c r="L6" t="n">
-        <v>1.030202983747678</v>
+        <v>0.3735833027833538</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.35858467884564</v>
+        <v>0.3639249677058116</v>
       </c>
       <c r="C7" t="n">
-        <v>1.395719397875417</v>
+        <v>0.4018284287688955</v>
       </c>
       <c r="D7" t="n">
-        <v>1.542844542007597</v>
+        <v>0.5498550120070861</v>
       </c>
       <c r="E7" t="n">
-        <v>1.354196556039401</v>
+        <v>0.3731975109773112</v>
       </c>
       <c r="F7" t="n">
-        <v>1.354196556039401</v>
+        <v>0.3731975109773112</v>
       </c>
       <c r="G7" t="n">
-        <v>1.477317420390923</v>
+        <v>0.4845395469756603</v>
       </c>
       <c r="H7" t="n">
-        <v>1.619095157905805</v>
+        <v>0.6244560538658483</v>
       </c>
       <c r="I7" t="n">
-        <v>1.355532505301623</v>
+        <v>0.3734069118240548</v>
       </c>
       <c r="J7" t="n">
-        <v>1.591166338596034</v>
+        <v>0.5965234129430595</v>
       </c>
       <c r="K7" t="n">
-        <v>1.433756078622246</v>
+        <v>0.4391176354146629</v>
       </c>
       <c r="L7" t="n">
-        <v>1.440461474091227</v>
+        <v>0.4457870110433109</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.595198287520497</v>
+        <v>0.4055633098254287</v>
       </c>
       <c r="C8" t="n">
-        <v>2.246388480037657</v>
+        <v>0.5515313344433043</v>
       </c>
       <c r="D8" t="n">
-        <v>2.521219672579467</v>
+        <v>0.7220322508348168</v>
       </c>
       <c r="E8" t="n">
-        <v>2.037967006693675</v>
+        <v>0.4935287543915602</v>
       </c>
       <c r="F8" t="n">
-        <v>1.611977665088419</v>
+        <v>0.418561031842371</v>
       </c>
       <c r="G8" t="n">
-        <v>2.326641606848852</v>
+        <v>0.6340057313660538</v>
       </c>
       <c r="H8" t="n">
-        <v>2.468419344366281</v>
+        <v>0.7739222382566924</v>
       </c>
       <c r="I8" t="n">
-        <v>2.204856691759547</v>
+        <v>0.5228730962144497</v>
       </c>
       <c r="J8" t="n">
-        <v>2.440610939685201</v>
+        <v>0.7460107884966762</v>
       </c>
       <c r="K8" t="n">
-        <v>1.658988273794405</v>
+        <v>0.4787530200132466</v>
       </c>
       <c r="L8" t="n">
-        <v>2.929813092563038</v>
+        <v>0.7078883930140445</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.520158677692982</v>
+        <v>0.5683150781329588</v>
       </c>
       <c r="C9" t="n">
-        <v>3.079780144282379</v>
+        <v>0.6981607832255404</v>
       </c>
       <c r="D9" t="n">
-        <v>3.228906905436387</v>
+        <v>0.8465396510327013</v>
       </c>
       <c r="E9" t="n">
-        <v>3.64256253164042</v>
+        <v>0.7758697648747702</v>
       </c>
       <c r="F9" t="n">
-        <v>3.039623867387783</v>
+        <v>0.6697703584073291</v>
       </c>
       <c r="G9" t="n">
-        <v>3.161378166797889</v>
+        <v>0.780871901432306</v>
       </c>
       <c r="H9" t="n">
-        <v>3.303155904312766</v>
+        <v>0.920788408322492</v>
       </c>
       <c r="I9" t="n">
-        <v>3.039593251708584</v>
+        <v>0.6697392662807011</v>
       </c>
       <c r="J9" t="n">
-        <v>3.275227085002997</v>
+        <v>0.8928557673997042</v>
       </c>
       <c r="K9" t="n">
-        <v>2.45991269378346</v>
+        <v>0.682178307591337</v>
       </c>
       <c r="L9" t="n">
-        <v>3.124522220498196</v>
+        <v>0.7421193654999562</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.918732002971964</v>
+        <v>1.918673162503669</v>
       </c>
       <c r="C2" t="n">
-        <v>1.810071308345806</v>
+        <v>1.810038882944796</v>
       </c>
       <c r="D2" t="n">
-        <v>2.170862197380161</v>
+        <v>2.170838572322022</v>
       </c>
       <c r="E2" t="n">
-        <v>1.790849787114238</v>
+        <v>1.790828821456111</v>
       </c>
       <c r="F2" t="n">
-        <v>1.790849787114238</v>
+        <v>1.790828821456111</v>
       </c>
       <c r="G2" t="n">
-        <v>2.078011817506707</v>
+        <v>2.077934394918358</v>
       </c>
       <c r="H2" t="n">
-        <v>2.163942979549193</v>
+        <v>2.163918706261138</v>
       </c>
       <c r="I2" t="n">
-        <v>1.936608781518226</v>
+        <v>1.936582435319951</v>
       </c>
       <c r="J2" t="n">
-        <v>2.46160856057848</v>
+        <v>2.461574826031056</v>
       </c>
       <c r="K2" t="n">
-        <v>2.068477940928962</v>
+        <v>2.068458162942938</v>
       </c>
       <c r="L2" t="n">
-        <v>1.993784332060419</v>
+        <v>1.993717974580946</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2288582963152569</v>
+        <v>0.2287919303901574</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1321458607409808</v>
+        <v>0.1321088460423486</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5188602484971079</v>
+        <v>0.5188343875885394</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1036622537283273</v>
+        <v>0.1036386446158163</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1036622537283273</v>
+        <v>0.1036386446158163</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4120630777443894</v>
+        <v>0.4119753385319539</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5109886355553936</v>
+        <v>0.5109620214301936</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2493677445172961</v>
+        <v>0.249338790541932</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8241011536954473</v>
+        <v>0.8240644027693366</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3866632037306813</v>
+        <v>0.3866412856197821</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3151842529406332</v>
+        <v>0.3151092401742807</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7273668667009932</v>
+        <v>0.2056075355907849</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7496068371410362</v>
+        <v>0.2487437216041616</v>
       </c>
       <c r="D4" t="n">
-        <v>0.877247583614056</v>
+        <v>0.3555091865729855</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7101010040476498</v>
+        <v>0.2113487901267434</v>
       </c>
       <c r="F4" t="n">
-        <v>0.71010100404765</v>
+        <v>0.2113487901267434</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8198266187992639</v>
+        <v>0.2998899496358416</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8731231136258454</v>
+        <v>0.3513843176250855</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7232805089736449</v>
+        <v>0.2136465520400435</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9346109719012559</v>
+        <v>0.4128694858529284</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7592609268401792</v>
+        <v>0.2375229086411648</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7719962892417743</v>
+        <v>0.2502324833034464</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.821779188085369</v>
+        <v>1.10184960952881</v>
       </c>
       <c r="C5" t="n">
-        <v>10.26244403495043</v>
+        <v>1.92281864285185</v>
       </c>
       <c r="D5" t="n">
-        <v>19.39856902803043</v>
+        <v>3.615232931471907</v>
       </c>
       <c r="E5" t="n">
-        <v>6.649118128927421</v>
+        <v>1.256559764499314</v>
       </c>
       <c r="F5" t="n">
-        <v>6.649118128927421</v>
+        <v>1.256559764499314</v>
       </c>
       <c r="G5" t="n">
-        <v>14.73831535412954</v>
+        <v>2.74898717808195</v>
       </c>
       <c r="H5" t="n">
-        <v>21.46772371195352</v>
+        <v>3.975994029891739</v>
       </c>
       <c r="I5" t="n">
-        <v>6.649092657076922</v>
+        <v>1.256534299770538</v>
       </c>
       <c r="J5" t="n">
-        <v>25.94325311134437</v>
+        <v>4.814308051331484</v>
       </c>
       <c r="K5" t="n">
-        <v>8.589573173837065</v>
+        <v>1.615635007428448</v>
       </c>
       <c r="L5" t="n">
-        <v>11.15230556481317</v>
+        <v>2.076663263989072</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.151681701360216</v>
+        <v>0.2802593387844198</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8501789829733222</v>
+        <v>0.2664395487583278</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9811359853819932</v>
+        <v>0.4348429162221968</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7820138686321286</v>
+        <v>0.2240011085477641</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8097277922945807</v>
+        <v>0.2288776795310206</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9074244698462464</v>
+        <v>0.3153023881622551</v>
       </c>
       <c r="H6" t="n">
-        <v>1.374937988689519</v>
+        <v>0.4396828693513493</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8108783600206405</v>
+        <v>0.2290589905664554</v>
       </c>
       <c r="J6" t="n">
-        <v>1.042965577730454</v>
+        <v>0.4319349025509732</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8428255114798933</v>
+        <v>0.2522264889767015</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8608247222885567</v>
+        <v>0.2658614926783915</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.181119893290129</v>
+        <v>0.2854615836516428</v>
       </c>
       <c r="C7" t="n">
-        <v>1.227948375110307</v>
+        <v>0.332924419010112</v>
       </c>
       <c r="D7" t="n">
-        <v>1.329107068131331</v>
+        <v>0.4350299712315477</v>
       </c>
       <c r="E7" t="n">
-        <v>1.174996856259187</v>
+        <v>0.2931631548269211</v>
       </c>
       <c r="F7" t="n">
-        <v>1.174996856259187</v>
+        <v>0.2931631548269211</v>
       </c>
       <c r="G7" t="n">
-        <v>1.273579645388399</v>
+        <v>0.3797439976966993</v>
       </c>
       <c r="H7" t="n">
-        <v>1.326876140214984</v>
+        <v>0.4312383656859433</v>
       </c>
       <c r="I7" t="n">
-        <v>1.177033535562784</v>
+        <v>0.2935006001009001</v>
       </c>
       <c r="J7" t="n">
-        <v>1.388363998490395</v>
+        <v>0.4927235339137833</v>
       </c>
       <c r="K7" t="n">
-        <v>1.213013953429319</v>
+        <v>0.3173769567020215</v>
       </c>
       <c r="L7" t="n">
-        <v>1.225749315830913</v>
+        <v>0.3300865313643044</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.377405286154999</v>
+        <v>0.3200028256463498</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9538498210258</v>
+        <v>0.4606697639174655</v>
       </c>
       <c r="D8" t="n">
-        <v>2.166085353932952</v>
+        <v>0.5823230832320369</v>
       </c>
       <c r="E8" t="n">
-        <v>1.757681456269437</v>
+        <v>0.395704586675811</v>
       </c>
       <c r="F8" t="n">
-        <v>1.39001512932469</v>
+        <v>0.3310011075743794</v>
       </c>
       <c r="G8" t="n">
-        <v>1.998954286776541</v>
+        <v>0.5073965993184052</v>
       </c>
       <c r="H8" t="n">
-        <v>2.052250781607035</v>
+        <v>0.5588909673083309</v>
       </c>
       <c r="I8" t="n">
-        <v>1.902408176950936</v>
+        <v>0.4211532017226073</v>
       </c>
       <c r="J8" t="n">
-        <v>2.113842620496426</v>
+        <v>0.6203944344835994</v>
       </c>
       <c r="K8" t="n">
-        <v>1.399471241917366</v>
+        <v>0.3501886073968937</v>
       </c>
       <c r="L8" t="n">
-        <v>2.503801918491043</v>
+        <v>0.5550017338676924</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.020930568284784</v>
+        <v>0.4332300749808077</v>
       </c>
       <c r="C9" t="n">
-        <v>2.476017003788319</v>
+        <v>0.5525334949380802</v>
       </c>
       <c r="D9" t="n">
-        <v>2.579069446448784</v>
+        <v>0.6549723470800988</v>
       </c>
       <c r="E9" t="n">
-        <v>2.896248388129063</v>
+        <v>0.5960376045858418</v>
       </c>
       <c r="F9" t="n">
-        <v>2.425127269945186</v>
+        <v>0.5131350763223352</v>
       </c>
       <c r="G9" t="n">
-        <v>2.521648274066405</v>
+        <v>0.5993530736246672</v>
       </c>
       <c r="H9" t="n">
-        <v>2.574944768892989</v>
+        <v>0.6508474416139124</v>
       </c>
       <c r="I9" t="n">
-        <v>2.425102164240794</v>
+        <v>0.5131096760288691</v>
       </c>
       <c r="J9" t="n">
-        <v>2.636432627168407</v>
+        <v>0.7123326098417508</v>
       </c>
       <c r="K9" t="n">
-        <v>2.224536407692601</v>
+        <v>0.4953613311331476</v>
       </c>
       <c r="L9" t="n">
-        <v>2.473817944508928</v>
+        <v>0.5496956072922715</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.862737746356834</v>
+        <v>1.862681699198182</v>
       </c>
       <c r="C2" t="n">
-        <v>1.742364079875181</v>
+        <v>1.742333893256048</v>
       </c>
       <c r="D2" t="n">
-        <v>2.055196821810732</v>
+        <v>2.055175826399793</v>
       </c>
       <c r="E2" t="n">
-        <v>1.716257958334542</v>
+        <v>1.716238692461513</v>
       </c>
       <c r="F2" t="n">
-        <v>1.716257958334542</v>
+        <v>1.716238692461513</v>
       </c>
       <c r="G2" t="n">
-        <v>1.983627594774379</v>
+        <v>1.983557847762921</v>
       </c>
       <c r="H2" t="n">
-        <v>2.01282081892044</v>
+        <v>2.012799159964814</v>
       </c>
       <c r="I2" t="n">
-        <v>1.864716462264282</v>
+        <v>1.864693023111936</v>
       </c>
       <c r="J2" t="n">
-        <v>2.324869357380389</v>
+        <v>2.324836738065973</v>
       </c>
       <c r="K2" t="n">
-        <v>1.979919564972631</v>
+        <v>1.979902445853203</v>
       </c>
       <c r="L2" t="n">
-        <v>1.905649057169949</v>
+        <v>1.905596745361046</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1645480462981246</v>
+        <v>0.1644847277382107</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05497793850279746</v>
+        <v>0.05494358359281587</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3859158508474809</v>
+        <v>0.3858928490583851</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01836637367263689</v>
+        <v>0.01834473535561394</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01836637367263689</v>
+        <v>0.01834473535561394</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3035964142349585</v>
+        <v>0.3035173380064015</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3372594846906281</v>
+        <v>0.3372357121341439</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1667744990758861</v>
+        <v>0.1667487217361121</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6677978780958668</v>
+        <v>0.6677625720168453</v>
       </c>
       <c r="K3" t="n">
-        <v>0.284870737516856</v>
+        <v>0.2848517056751455</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2139034978764081</v>
+        <v>0.2138444748153683</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6646403078804647</v>
+        <v>0.1648270122482857</v>
       </c>
       <c r="C4" t="n">
-        <v>0.677561843093748</v>
+        <v>0.2026091855643073</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7790490730549942</v>
+        <v>0.2792566142015632</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6379302726754567</v>
+        <v>0.1611185802171346</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6379302726754567</v>
+        <v>0.1611185802171346</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7343230020756529</v>
+        <v>0.2362988887080601</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7538595435589822</v>
+        <v>0.2540666778183355</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6513823980279327</v>
+        <v>0.1634668736156359</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8273691794754268</v>
+        <v>0.3275740279344936</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6770705795428987</v>
+        <v>0.1772784913405836</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6901578010108228</v>
+        <v>0.1903467183424422</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.754419564306725</v>
+        <v>0.5322587712122083</v>
       </c>
       <c r="C5" t="n">
-        <v>6.779524764573189</v>
+        <v>1.276386234215392</v>
       </c>
       <c r="D5" t="n">
-        <v>13.16325697037629</v>
+        <v>2.458851877558129</v>
       </c>
       <c r="E5" t="n">
-        <v>2.766473378882519</v>
+        <v>0.5356923076614618</v>
       </c>
       <c r="F5" t="n">
-        <v>2.766473378882519</v>
+        <v>0.5356923076614618</v>
       </c>
       <c r="G5" t="n">
-        <v>9.514547440415688</v>
+        <v>1.781114643813604</v>
       </c>
       <c r="H5" t="n">
-        <v>12.21816274292098</v>
+        <v>2.271747863636939</v>
       </c>
       <c r="I5" t="n">
-        <v>2.766451017340962</v>
+        <v>0.5356699525912088</v>
       </c>
       <c r="J5" t="n">
-        <v>18.50563413560998</v>
+        <v>3.438876572210528</v>
       </c>
       <c r="K5" t="n">
-        <v>3.805573871686265</v>
+        <v>0.7278755981733965</v>
       </c>
       <c r="L5" t="n">
-        <v>5.690997399207849</v>
+        <v>1.070120436663175</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.051724394140476</v>
+        <v>0.1781462586575107</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7726800154360921</v>
+        <v>0.2193451176565615</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8684361922716032</v>
+        <v>0.2949849434370141</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6997724043388908</v>
+        <v>0.1719984743296476</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7257583922475909</v>
+        <v>0.1765709810324999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8100271841056543</v>
+        <v>0.3043984448485127</v>
       </c>
       <c r="H6" t="n">
-        <v>1.210331705780088</v>
+        <v>0.3343851507296239</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7270865800579354</v>
+        <v>0.2315664297560886</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9219622128583334</v>
+        <v>0.4014313336007402</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7488045737210115</v>
+        <v>0.18989992284448</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7662598302914836</v>
+        <v>0.203736014323156</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.089461338476108</v>
+        <v>0.2395891709118411</v>
       </c>
       <c r="C7" t="n">
-        <v>1.131884567321779</v>
+        <v>0.2825626585655372</v>
       </c>
       <c r="D7" t="n">
-        <v>1.201977312377052</v>
+        <v>0.353685641589742</v>
       </c>
       <c r="E7" t="n">
-        <v>1.07385216818526</v>
+        <v>0.2378336675038976</v>
       </c>
       <c r="F7" t="n">
-        <v>1.07385216818526</v>
+        <v>0.2378336675038976</v>
       </c>
       <c r="G7" t="n">
-        <v>1.159144032671297</v>
+        <v>0.311061047371616</v>
       </c>
       <c r="H7" t="n">
-        <v>1.178680574154621</v>
+        <v>0.3288288364818908</v>
       </c>
       <c r="I7" t="n">
-        <v>1.076203428623577</v>
+        <v>0.2382290322791917</v>
       </c>
       <c r="J7" t="n">
-        <v>1.252190210071066</v>
+        <v>0.402336186598049</v>
       </c>
       <c r="K7" t="n">
-        <v>1.101891610138544</v>
+        <v>0.2520406500041391</v>
       </c>
       <c r="L7" t="n">
-        <v>1.114978831606472</v>
+        <v>0.2651088770059979</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.264546258381059</v>
+        <v>0.2703992434979442</v>
       </c>
       <c r="C8" t="n">
-        <v>1.8015195319147</v>
+        <v>0.4004053568112422</v>
       </c>
       <c r="D8" t="n">
-        <v>1.975786815513698</v>
+        <v>0.4898613205207109</v>
       </c>
       <c r="E8" t="n">
-        <v>1.610121411221501</v>
+        <v>0.3322062046579319</v>
       </c>
       <c r="F8" t="n">
-        <v>1.266693349525586</v>
+        <v>0.2717685664780896</v>
       </c>
       <c r="G8" t="n">
-        <v>1.828558328268697</v>
+        <v>0.4288648735213336</v>
       </c>
       <c r="H8" t="n">
-        <v>1.848094869754686</v>
+        <v>0.4466326626320772</v>
       </c>
       <c r="I8" t="n">
-        <v>1.745617724220984</v>
+        <v>0.3560328584289092</v>
       </c>
       <c r="J8" t="n">
-        <v>1.921701654882775</v>
+        <v>0.5201571093946987</v>
       </c>
       <c r="K8" t="n">
-        <v>1.267794108160879</v>
+        <v>0.2812347689656905</v>
       </c>
       <c r="L8" t="n">
-        <v>2.300761494637341</v>
+        <v>0.4737849529418533</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.758904342195814</v>
+        <v>0.3573772632016987</v>
       </c>
       <c r="C9" t="n">
-        <v>2.153203248981073</v>
+        <v>0.4622692729649848</v>
       </c>
       <c r="D9" t="n">
-        <v>2.225188964336135</v>
+        <v>0.5337254187546778</v>
       </c>
       <c r="E9" t="n">
-        <v>2.503601360491514</v>
+        <v>0.4894106312056536</v>
       </c>
       <c r="F9" t="n">
-        <v>2.097544196191203</v>
+        <v>0.4179579532374035</v>
       </c>
       <c r="G9" t="n">
-        <v>2.180462714330592</v>
+        <v>0.4907676617710626</v>
       </c>
       <c r="H9" t="n">
-        <v>2.199999255813917</v>
+        <v>0.5085354508813387</v>
       </c>
       <c r="I9" t="n">
-        <v>2.097522110282869</v>
+        <v>0.4179356466786396</v>
       </c>
       <c r="J9" t="n">
-        <v>2.273508891730367</v>
+        <v>0.5820428009974964</v>
       </c>
       <c r="K9" t="n">
-        <v>1.911060619095727</v>
+        <v>0.3537807844889515</v>
       </c>
       <c r="L9" t="n">
-        <v>2.13629751326576</v>
+        <v>0.4448154914054451</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.857732006990683</v>
+        <v>1.857669888974999</v>
       </c>
       <c r="C2" t="n">
-        <v>1.662926645964887</v>
+        <v>1.662887812695352</v>
       </c>
       <c r="D2" t="n">
-        <v>2.08541194766949</v>
+        <v>2.085385774488753</v>
       </c>
       <c r="E2" t="n">
-        <v>1.748775859172818</v>
+        <v>1.748753364572875</v>
       </c>
       <c r="F2" t="n">
-        <v>1.748775859172818</v>
+        <v>1.748753364572875</v>
       </c>
       <c r="G2" t="n">
-        <v>2.051896026290029</v>
+        <v>2.051809296826287</v>
       </c>
       <c r="H2" t="n">
-        <v>2.287019166908513</v>
+        <v>2.286992166142077</v>
       </c>
       <c r="I2" t="n">
-        <v>1.886117143035468</v>
+        <v>1.886087508377361</v>
       </c>
       <c r="J2" t="n">
-        <v>2.533556220611462</v>
+        <v>2.533519691462541</v>
       </c>
       <c r="K2" t="n">
-        <v>2.112502680953579</v>
+        <v>2.112480830150555</v>
       </c>
       <c r="L2" t="n">
-        <v>2.056689316885874</v>
+        <v>2.056599874455842</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1590456442426732</v>
+        <v>0.1589755462264479</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03774471219854912</v>
+        <v>-0.03778931718694173</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4209247397809263</v>
+        <v>0.4208959857708394</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05435412533679267</v>
+        <v>0.05432853126187655</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05435412533679256</v>
+        <v>0.05432853126187644</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3823744873923481</v>
+        <v>0.3822760811126097</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6528999487863217</v>
+        <v>0.6528702347679654</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1916494774588039</v>
+        <v>0.1916167804773819</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9057567339190291</v>
+        <v>0.9057164613475718</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4365418684066868</v>
+        <v>0.4365175014556734</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3878837588770593</v>
+        <v>0.3877822319947709</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6876410221662181</v>
+        <v>0.1750228028066893</v>
       </c>
       <c r="C4" t="n">
-        <v>0.658721427678706</v>
+        <v>0.1636908799278192</v>
       </c>
       <c r="D4" t="n">
-        <v>0.822987099282298</v>
+        <v>0.3103902476040329</v>
       </c>
       <c r="E4" t="n">
-        <v>0.678721019178409</v>
+        <v>0.1873803975326692</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6787210191784085</v>
+        <v>0.1873803975326692</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8008207015262907</v>
+        <v>0.2900357809689783</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9427881347798214</v>
+        <v>0.4301907759912294</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6896868551295616</v>
+        <v>0.1892858367871117</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9681818902832037</v>
+        <v>0.4555804375430823</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7775793286146404</v>
+        <v>0.2649827329183842</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8059053255827834</v>
+        <v>0.293270859643926</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.351402170466474</v>
+        <v>0.6434410118693334</v>
       </c>
       <c r="C5" t="n">
-        <v>2.548816034160759</v>
+        <v>0.4960944626985883</v>
       </c>
       <c r="D5" t="n">
-        <v>16.35328806292294</v>
+        <v>3.043691879840276</v>
       </c>
       <c r="E5" t="n">
-        <v>4.89539524185412</v>
+        <v>0.9294475058436427</v>
       </c>
       <c r="F5" t="n">
-        <v>4.89539524185412</v>
+        <v>0.9294475058436427</v>
       </c>
       <c r="G5" t="n">
-        <v>14.8368646675823</v>
+        <v>2.759720836974955</v>
       </c>
       <c r="H5" t="n">
-        <v>31.60721625518253</v>
+        <v>5.827084812092123</v>
       </c>
       <c r="I5" t="n">
-        <v>4.895366506220813</v>
+        <v>0.9294187781525026</v>
       </c>
       <c r="J5" t="n">
-        <v>32.01087940287525</v>
+        <v>5.91898029924357</v>
       </c>
       <c r="K5" t="n">
-        <v>11.99805903001349</v>
+        <v>2.239760034886209</v>
       </c>
       <c r="L5" t="n">
-        <v>16.89696275144164</v>
+        <v>3.124525720100188</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.101614639103162</v>
+        <v>0.1874121843723473</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7252101689711193</v>
+        <v>0.1753876265121948</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9043355687592193</v>
+        <v>0.3247034318940485</v>
       </c>
       <c r="E6" t="n">
-        <v>0.730336629386604</v>
+        <v>0.1964600732656266</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7591247971809819</v>
+        <v>0.201525576999041</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8712446469848141</v>
+        <v>0.3024251625346361</v>
       </c>
       <c r="H6" t="n">
-        <v>1.428445084146772</v>
+        <v>0.5156439943273476</v>
       </c>
       <c r="I6" t="n">
-        <v>1.103660472066504</v>
+        <v>0.2016752183527696</v>
       </c>
       <c r="J6" t="n">
-        <v>1.412432959143639</v>
+        <v>0.5337404688381825</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8498421656282772</v>
+        <v>0.2776968964372155</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8803293432602234</v>
+        <v>0.3063641701635074</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.16187573753102</v>
+        <v>0.2584811491274651</v>
       </c>
       <c r="C7" t="n">
-        <v>1.153346868162861</v>
+        <v>0.2507370893893628</v>
       </c>
       <c r="D7" t="n">
-        <v>1.295220368987533</v>
+        <v>0.3934963395113203</v>
       </c>
       <c r="E7" t="n">
-        <v>1.162801360510574</v>
+        <v>0.2725707135124734</v>
       </c>
       <c r="F7" t="n">
-        <v>1.162801360510574</v>
+        <v>0.2725707135124734</v>
       </c>
       <c r="G7" t="n">
-        <v>1.275055416891094</v>
+        <v>0.3734941272897541</v>
       </c>
       <c r="H7" t="n">
-        <v>1.417022850144623</v>
+        <v>0.5136491223120042</v>
       </c>
       <c r="I7" t="n">
-        <v>1.163921570494365</v>
+        <v>0.2727441831078875</v>
       </c>
       <c r="J7" t="n">
-        <v>1.442416605648008</v>
+        <v>0.5390387838638573</v>
       </c>
       <c r="K7" t="n">
-        <v>1.251814043979443</v>
+        <v>0.3484410792391599</v>
       </c>
       <c r="L7" t="n">
-        <v>1.280140040947585</v>
+        <v>0.3767292059647017</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.36088635442286</v>
+        <v>0.2935015661358944</v>
       </c>
       <c r="C8" t="n">
-        <v>1.898706041535255</v>
+        <v>0.3819058940547396</v>
       </c>
       <c r="D8" t="n">
-        <v>2.154010078330076</v>
+        <v>0.544627043314484</v>
       </c>
       <c r="E8" t="n">
-        <v>1.759593473212457</v>
+        <v>0.3775941508248024</v>
       </c>
       <c r="F8" t="n">
-        <v>1.380739057486581</v>
+        <v>0.3109220052600991</v>
       </c>
       <c r="G8" t="n">
-        <v>2.018874165414325</v>
+        <v>0.5043918025945241</v>
       </c>
       <c r="H8" t="n">
-        <v>2.16084159866996</v>
+        <v>0.6445467976171464</v>
       </c>
       <c r="I8" t="n">
-        <v>1.907740319017593</v>
+        <v>0.4036418584126579</v>
       </c>
       <c r="J8" t="n">
-        <v>2.18634242409931</v>
+        <v>0.6699553017125449</v>
       </c>
       <c r="K8" t="n">
-        <v>1.440704570161225</v>
+        <v>0.3816805269583007</v>
       </c>
       <c r="L8" t="n">
-        <v>2.593056438636122</v>
+        <v>0.6077786946087345</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.122840831537677</v>
+        <v>0.4275645768024522</v>
       </c>
       <c r="C9" t="n">
-        <v>2.562163899207537</v>
+        <v>0.4986272200361258</v>
       </c>
       <c r="D9" t="n">
-        <v>2.706038964808735</v>
+        <v>0.6417387455272374</v>
       </c>
       <c r="E9" t="n">
-        <v>3.089578476642628</v>
+        <v>0.6116042177347079</v>
       </c>
       <c r="F9" t="n">
-        <v>2.572766851127661</v>
+        <v>0.5206629559162109</v>
       </c>
       <c r="G9" t="n">
-        <v>2.683872447935771</v>
+        <v>0.6213842579365166</v>
       </c>
       <c r="H9" t="n">
-        <v>2.825839881189301</v>
+        <v>0.7615392529587669</v>
       </c>
       <c r="I9" t="n">
-        <v>2.572738601539044</v>
+        <v>0.5206343137546499</v>
       </c>
       <c r="J9" t="n">
-        <v>2.851233636692683</v>
+        <v>0.7869289145106211</v>
       </c>
       <c r="K9" t="n">
-        <v>2.096705514132709</v>
+        <v>0.4970994984664767</v>
       </c>
       <c r="L9" t="n">
-        <v>2.688957071992266</v>
+        <v>0.6246193366114644</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.80968704942914</v>
+        <v>1.809631880761028</v>
       </c>
       <c r="C2" t="n">
-        <v>1.63295259139287</v>
+        <v>1.632919615881746</v>
       </c>
       <c r="D2" t="n">
-        <v>1.821263595835139</v>
+        <v>1.821239589495943</v>
       </c>
       <c r="E2" t="n">
-        <v>1.687390490138732</v>
+        <v>1.687369481973676</v>
       </c>
       <c r="F2" t="n">
-        <v>1.687390490138732</v>
+        <v>1.687369481973676</v>
       </c>
       <c r="G2" t="n">
-        <v>1.842328287404839</v>
+        <v>1.842258094813199</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83432806226667</v>
+        <v>1.834303083137102</v>
       </c>
       <c r="I2" t="n">
-        <v>1.820054188484994</v>
+        <v>1.82002709612629</v>
       </c>
       <c r="J2" t="n">
-        <v>2.189546381061001</v>
+        <v>2.189512066182915</v>
       </c>
       <c r="K2" t="n">
-        <v>1.926410470478005</v>
+        <v>1.926389959424368</v>
       </c>
       <c r="L2" t="n">
-        <v>1.847457512281852</v>
+        <v>1.847398257236651</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1036135931552407</v>
+        <v>0.1035514352149267</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.07358526185106933</v>
+        <v>-0.07362309580510977</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1169290195965031</v>
+        <v>0.1169027047896996</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01712208383004032</v>
+        <v>-0.01714586306366849</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01712208383004026</v>
+        <v>-0.01714586306366849</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1411577784393708</v>
+        <v>0.1410783398748049</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1320344826766791</v>
+        <v>0.1320070415232633</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1155652311100543</v>
+        <v>0.1155353980785205</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5100971848717153</v>
+        <v>0.5100595359768387</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2225930365781663</v>
+        <v>0.222570273004375</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1470512516532873</v>
+        <v>0.1469843929033253</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.602366368533261</v>
+        <v>0.1400994484985325</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5865767036568168</v>
+        <v>0.1360083398021307</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6092481348317444</v>
+        <v>0.146999739481097</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5887860913234945</v>
+        <v>0.1428170332287296</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5887860913234882</v>
+        <v>0.1428170332287296</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6198281868539517</v>
+        <v>0.1591525749069662</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6170235209753138</v>
+        <v>0.1547745356012858</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5956380729796917</v>
+        <v>0.1440147678201046</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7077341524267741</v>
+        <v>0.2454816983776127</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6112947698189108</v>
+        <v>0.1490465958850828</v>
       </c>
       <c r="L4" t="n">
-        <v>0.62480329274461</v>
+        <v>0.1625339376320591</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.587732871667171</v>
+        <v>0.3131941850741929</v>
       </c>
       <c r="C5" t="n">
-        <v>1.390258953542206</v>
+        <v>0.2772644332010148</v>
       </c>
       <c r="D5" t="n">
-        <v>2.144357068923374</v>
+        <v>0.417155032359611</v>
       </c>
       <c r="E5" t="n">
-        <v>2.082991579819203</v>
+        <v>0.4057426935909302</v>
       </c>
       <c r="F5" t="n">
-        <v>2.082991579819203</v>
+        <v>0.4057426935909302</v>
       </c>
       <c r="G5" t="n">
-        <v>3.378667402731062</v>
+        <v>0.6442311540434063</v>
       </c>
       <c r="H5" t="n">
-        <v>3.173785888583419</v>
+        <v>0.6047268654950843</v>
       </c>
       <c r="I5" t="n">
-        <v>2.082982557788903</v>
+        <v>0.4057336775905358</v>
       </c>
       <c r="J5" t="n">
-        <v>11.76003387973569</v>
+        <v>2.190592869347692</v>
       </c>
       <c r="K5" t="n">
-        <v>2.340165089393714</v>
+        <v>0.4533073466431569</v>
       </c>
       <c r="L5" t="n">
-        <v>4.053967952965663</v>
+        <v>0.7656513185570044</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6409656533428943</v>
+        <v>0.1468883110529031</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6302703899757164</v>
+        <v>0.1436936700887384</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9281944264259383</v>
+        <v>0.1536834695497766</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6196053183389094</v>
+        <v>0.1482369651291698</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6340354925700156</v>
+        <v>0.1507757100641954</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6584274716635847</v>
+        <v>0.2122518811672773</v>
       </c>
       <c r="H6" t="n">
-        <v>0.973466647400846</v>
+        <v>0.2174883001563768</v>
       </c>
       <c r="I6" t="n">
-        <v>0.634237357789325</v>
+        <v>0.1971140740804155</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7591319202145104</v>
+        <v>0.2545228800661223</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6487541830862852</v>
+        <v>0.1556357253264699</v>
       </c>
       <c r="L6" t="n">
-        <v>0.664296431436727</v>
+        <v>0.1694801175472094</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9845068597611286</v>
+        <v>0.2073500358250863</v>
       </c>
       <c r="C7" t="n">
-        <v>0.982419158459539</v>
+        <v>0.2056696406139909</v>
       </c>
       <c r="D7" t="n">
-        <v>0.989493810572088</v>
+        <v>0.2139168392875244</v>
       </c>
       <c r="E7" t="n">
-        <v>0.976336143766242</v>
+        <v>0.2110189397807543</v>
       </c>
       <c r="F7" t="n">
-        <v>0.976336143766242</v>
+        <v>0.2110189397807543</v>
       </c>
       <c r="G7" t="n">
-        <v>1.00196867808182</v>
+        <v>0.2264031622335203</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9991640122031811</v>
+        <v>0.2220251229278402</v>
       </c>
       <c r="I7" t="n">
-        <v>0.977778564207552</v>
+        <v>0.2112653551466585</v>
       </c>
       <c r="J7" t="n">
-        <v>1.089874643654641</v>
+        <v>0.312732285704167</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9934352610467782</v>
+        <v>0.2162971832116369</v>
       </c>
       <c r="L7" t="n">
-        <v>1.006943783972478</v>
+        <v>0.2297845249586131</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.119054792046086</v>
+        <v>0.2310258984243546</v>
       </c>
       <c r="C8" t="n">
-        <v>1.540831533487643</v>
+        <v>0.3039378706789127</v>
       </c>
       <c r="D8" t="n">
-        <v>1.636373771147587</v>
+        <v>0.3277537282179133</v>
       </c>
       <c r="E8" t="n">
-        <v>1.419936952344234</v>
+        <v>0.2890824412472923</v>
       </c>
       <c r="F8" t="n">
-        <v>1.126001249842712</v>
+        <v>0.2373551688117279</v>
       </c>
       <c r="G8" t="n">
-        <v>1.559289177326668</v>
+        <v>0.3244792021989104</v>
       </c>
       <c r="H8" t="n">
-        <v>1.556484511449562</v>
+        <v>0.3201011628934994</v>
       </c>
       <c r="I8" t="n">
-        <v>1.535099063452409</v>
+        <v>0.3093413951120486</v>
       </c>
       <c r="J8" t="n">
-        <v>1.647278229436275</v>
+        <v>0.4108229473682072</v>
       </c>
       <c r="K8" t="n">
-        <v>1.120129975882438</v>
+        <v>0.2385910243251598</v>
       </c>
       <c r="L8" t="n">
-        <v>2.005885580719165</v>
+        <v>0.4055777713621139</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.614237883805717</v>
+        <v>0.3181458019348796</v>
       </c>
       <c r="C9" t="n">
-        <v>1.933108743402291</v>
+        <v>0.372941782472088</v>
       </c>
       <c r="D9" t="n">
-        <v>1.942078311685858</v>
+        <v>0.3815224863704528</v>
       </c>
       <c r="E9" t="n">
-        <v>2.298856442514119</v>
+        <v>0.4437190350704227</v>
       </c>
       <c r="F9" t="n">
-        <v>1.928477016350268</v>
+        <v>0.3785464857568714</v>
       </c>
       <c r="G9" t="n">
-        <v>1.952658263024571</v>
+        <v>0.3936753040916181</v>
       </c>
       <c r="H9" t="n">
-        <v>1.949853597145932</v>
+        <v>0.3892972647859378</v>
       </c>
       <c r="I9" t="n">
-        <v>1.928468149150312</v>
+        <v>0.3785374970047558</v>
       </c>
       <c r="J9" t="n">
-        <v>2.040564228597393</v>
+        <v>0.4800044275622641</v>
       </c>
       <c r="K9" t="n">
-        <v>1.758160237650686</v>
+        <v>0.3124554824165297</v>
       </c>
       <c r="L9" t="n">
-        <v>1.957633368915231</v>
+        <v>0.3970566668167108</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.79853964540701</v>
+        <v>1.798493002408477</v>
       </c>
       <c r="C2" t="n">
-        <v>1.626135120366836</v>
+        <v>1.626108370559576</v>
       </c>
       <c r="D2" t="n">
-        <v>1.802744215160499</v>
+        <v>1.802723419503491</v>
       </c>
       <c r="E2" t="n">
-        <v>1.675195974757532</v>
+        <v>1.675177735926609</v>
       </c>
       <c r="F2" t="n">
-        <v>1.675195974757532</v>
+        <v>1.675177735926609</v>
       </c>
       <c r="G2" t="n">
-        <v>1.805047020393455</v>
+        <v>1.80499333830527</v>
       </c>
       <c r="H2" t="n">
-        <v>1.804045375726903</v>
+        <v>1.804023776868294</v>
       </c>
       <c r="I2" t="n">
-        <v>1.804731737275113</v>
+        <v>1.804708905118809</v>
       </c>
       <c r="J2" t="n">
-        <v>2.023349658744497</v>
+        <v>2.023316249869617</v>
       </c>
       <c r="K2" t="n">
-        <v>1.903435918295755</v>
+        <v>1.903418731680445</v>
       </c>
       <c r="L2" t="n">
-        <v>1.800814430862327</v>
+        <v>1.800776645564077</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08989457202587196</v>
+        <v>0.08984186433728425</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.08275333258622231</v>
+        <v>-0.08278406680503536</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09473069821638402</v>
+        <v>0.09470772032481106</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.03251606884288013</v>
+        <v>-0.03253679520638332</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.03251606884288007</v>
+        <v>-0.03253679520638332</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09737940125895013</v>
+        <v>0.09731859715911893</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09629608587970621</v>
+        <v>0.09627217699822822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0970372428493292</v>
+        <v>0.09701195120209792</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3189463461541457</v>
+        <v>0.3189098007743111</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1942590098742792</v>
+        <v>0.1942396991241649</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09250504250756776</v>
+        <v>0.09246252243548377</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5597260667948939</v>
+        <v>0.1286422355170546</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5480395758917884</v>
+        <v>0.1259803665249626</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5622255053506093</v>
+        <v>0.1311570392220622</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5418013992709766</v>
+        <v>0.1285452497021861</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5418013992709767</v>
+        <v>0.1285452497021861</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5616998039585445</v>
+        <v>0.1321729714578064</v>
       </c>
       <c r="H4" t="n">
-        <v>0.563005769269119</v>
+        <v>0.1319368169715793</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5508041105143441</v>
+        <v>0.130123948538875</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5765131975136922</v>
+        <v>0.1454409547785501</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5576212841861322</v>
+        <v>0.1265530479923538</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5610625333839075</v>
+        <v>0.1299839611283952</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.366789337179989</v>
+        <v>0.2704106943178512</v>
       </c>
       <c r="C5" t="n">
-        <v>1.249822763657132</v>
+        <v>0.2493538995606455</v>
       </c>
       <c r="D5" t="n">
-        <v>1.524663615690869</v>
+        <v>0.3005252504432028</v>
       </c>
       <c r="E5" t="n">
-        <v>1.633648926298402</v>
+        <v>0.3206689176762605</v>
       </c>
       <c r="F5" t="n">
-        <v>1.633648926298402</v>
+        <v>0.3206689176762605</v>
       </c>
       <c r="G5" t="n">
-        <v>1.685510584915869</v>
+        <v>0.3296199230942819</v>
       </c>
       <c r="H5" t="n">
-        <v>1.746872705677877</v>
+        <v>0.3402647878850563</v>
       </c>
       <c r="I5" t="n">
-        <v>1.633642940413033</v>
+        <v>0.3206629361503497</v>
       </c>
       <c r="J5" t="n">
-        <v>2.963074676918205</v>
+        <v>0.5653900855831345</v>
       </c>
       <c r="K5" t="n">
-        <v>1.104235479752202</v>
+        <v>0.2227398533017904</v>
       </c>
       <c r="L5" t="n">
-        <v>1.566829657895101</v>
+        <v>0.3067876542152247</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8168728125630087</v>
+        <v>0.1738739347221751</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5753575783283187</v>
+        <v>0.13078367040667</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5856065473748937</v>
+        <v>0.1352684032285355</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5628987244800832</v>
+        <v>0.132254149887597</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5730565036623086</v>
+        <v>0.1340410764734632</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8188465497266593</v>
+        <v>0.177404670662924</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8627430681418288</v>
+        <v>0.1846709878814866</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5733639463854096</v>
+        <v>0.1340901024965765</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8550277803146019</v>
+        <v>0.1944344875377227</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5781961292647076</v>
+        <v>0.1301705718958291</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5841150971777135</v>
+        <v>0.134036877852359</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9119222658455064</v>
+        <v>0.1906229166991065</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9107967672231558</v>
+        <v>0.1898188970708869</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9125266588411889</v>
+        <v>0.1928041923666511</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9005640494405419</v>
+        <v>0.1916808321567145</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9005640494405419</v>
+        <v>0.1916808321567145</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9138960030091565</v>
+        <v>0.1941536526398557</v>
       </c>
       <c r="H7" t="n">
-        <v>0.915201968319732</v>
+        <v>0.193917498153631</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9030003095649568</v>
+        <v>0.1921046297209267</v>
       </c>
       <c r="J7" t="n">
-        <v>0.928709396564305</v>
+        <v>0.2074216359606016</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9098174832367455</v>
+        <v>0.1885337291744054</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9132587324345212</v>
+        <v>0.1919646423104469</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.017474083974218</v>
+        <v>0.2091956852254686</v>
       </c>
       <c r="C8" t="n">
-        <v>1.387492184461709</v>
+        <v>0.2737054367995164</v>
       </c>
       <c r="D8" t="n">
-        <v>1.467913964243745</v>
+        <v>0.2905388857120152</v>
       </c>
       <c r="E8" t="n">
-        <v>1.277697212027721</v>
+        <v>0.258046419428792</v>
       </c>
       <c r="F8" t="n">
-        <v>1.019992102577525</v>
+        <v>0.2126955559131647</v>
       </c>
       <c r="G8" t="n">
-        <v>1.390457076797925</v>
+        <v>0.2780164956745592</v>
       </c>
       <c r="H8" t="n">
-        <v>1.391763042109365</v>
+        <v>0.2777803411884867</v>
       </c>
       <c r="I8" t="n">
-        <v>1.379561383353724</v>
+        <v>0.2759674727556308</v>
       </c>
       <c r="J8" t="n">
-        <v>1.405343384132509</v>
+        <v>0.2912973103358196</v>
       </c>
       <c r="K8" t="n">
-        <v>1.008477613979802</v>
+        <v>0.205893701049382</v>
       </c>
       <c r="L8" t="n">
-        <v>1.777369996894087</v>
+        <v>0.3440284276089846</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.459763315673215</v>
+        <v>0.2870114225428336</v>
       </c>
       <c r="C9" t="n">
-        <v>1.742438199163896</v>
+        <v>0.3361454687683461</v>
       </c>
       <c r="D9" t="n">
-        <v>1.746063184925366</v>
+        <v>0.3394643006332699</v>
       </c>
       <c r="E9" t="n">
-        <v>2.06214721741573</v>
+        <v>0.3960646285802484</v>
       </c>
       <c r="F9" t="n">
-        <v>1.734647585541456</v>
+        <v>0.3384371579733432</v>
       </c>
       <c r="G9" t="n">
-        <v>1.745537434949895</v>
+        <v>0.3404802243373144</v>
       </c>
       <c r="H9" t="n">
-        <v>1.74684340026047</v>
+        <v>0.3402440698510878</v>
       </c>
       <c r="I9" t="n">
-        <v>1.734641741505696</v>
+        <v>0.3384312014183836</v>
       </c>
       <c r="J9" t="n">
-        <v>1.760350828505043</v>
+        <v>0.3537482076580603</v>
       </c>
       <c r="K9" t="n">
-        <v>1.57702387964508</v>
+        <v>0.3047520912159844</v>
       </c>
       <c r="L9" t="n">
-        <v>1.744900164375258</v>
+        <v>0.3382912140079041</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.815334249200267</v>
+        <v>1.815271393145943</v>
       </c>
       <c r="C2" t="n">
-        <v>1.633275992691764</v>
+        <v>1.633235210572502</v>
       </c>
       <c r="D2" t="n">
-        <v>1.861170418447103</v>
+        <v>1.861143178330362</v>
       </c>
       <c r="E2" t="n">
-        <v>1.700937032432325</v>
+        <v>1.700913969103602</v>
       </c>
       <c r="F2" t="n">
-        <v>1.700937032432325</v>
+        <v>1.700913969103603</v>
       </c>
       <c r="G2" t="n">
-        <v>1.904974385923986</v>
+        <v>1.904883083040554</v>
       </c>
       <c r="H2" t="n">
-        <v>2.180558017647578</v>
+        <v>2.180529639087054</v>
       </c>
       <c r="I2" t="n">
-        <v>1.825878870941772</v>
+        <v>1.825847920816785</v>
       </c>
       <c r="J2" t="n">
-        <v>2.184175735402626</v>
+        <v>2.18413641938901</v>
       </c>
       <c r="K2" t="n">
-        <v>1.968830084893558</v>
+        <v>1.968807119002412</v>
       </c>
       <c r="L2" t="n">
-        <v>1.983038809002181</v>
+        <v>1.982944484945887</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1114983350685422</v>
+        <v>0.1114273940341189</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.07192592276280899</v>
+        <v>-0.07197262587367917</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1642194246362599</v>
+        <v>0.164189449307875</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.001312047926249727</v>
+        <v>-0.00133840237004927</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.001312047926249726</v>
+        <v>-0.001338402370051123</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2146030611992004</v>
+        <v>0.21449940041856</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5316604886849184</v>
+        <v>0.531629195550098</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1236278693236438</v>
+        <v>0.1235936687794148</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5038050398099168</v>
+        <v>0.5037614371952043</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2717746747571898</v>
+        <v>0.2717490239202126</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3043841109827753</v>
+        <v>0.304276975147841</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6438420328207112</v>
+        <v>0.1535273773949929</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6223773184916512</v>
+        <v>0.1455026109928975</v>
       </c>
       <c r="D4" t="n">
-        <v>0.671089693194709</v>
+        <v>0.1807962099347073</v>
       </c>
       <c r="E4" t="n">
-        <v>0.628300322191203</v>
+        <v>0.1559868670216269</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6283003221912032</v>
+        <v>0.1559868670216269</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6950750833838164</v>
+        <v>0.2064362148770171</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8608961541152609</v>
+        <v>0.3706019781861535</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6365010223030548</v>
+        <v>0.1574153857486674</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7367076399089583</v>
+        <v>0.2464080168926474</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6706764566657767</v>
+        <v>0.1803831723370167</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7435054999774374</v>
+        <v>0.2531721347034621</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.123989196190348</v>
+        <v>0.4136350695088457</v>
       </c>
       <c r="C5" t="n">
-        <v>1.561875916815387</v>
+        <v>0.3106036098669464</v>
       </c>
       <c r="D5" t="n">
-        <v>4.674962191048606</v>
+        <v>0.8854484816432814</v>
       </c>
       <c r="E5" t="n">
-        <v>2.650025892724226</v>
+        <v>0.5117424848435362</v>
       </c>
       <c r="F5" t="n">
-        <v>2.650025892724226</v>
+        <v>0.5117424848435362</v>
       </c>
       <c r="G5" t="n">
-        <v>7.399903087011004</v>
+        <v>1.385793093835984</v>
       </c>
       <c r="H5" t="n">
-        <v>26.0719528987132</v>
+        <v>4.807701402125002</v>
       </c>
       <c r="I5" t="n">
-        <v>2.650009068682446</v>
+        <v>0.5117256691925095</v>
       </c>
       <c r="J5" t="n">
-        <v>11.59379245409843</v>
+        <v>2.157114830456458</v>
       </c>
       <c r="K5" t="n">
-        <v>4.652163641607683</v>
+        <v>0.8810988773225928</v>
       </c>
       <c r="L5" t="n">
-        <v>13.43477311882774</v>
+        <v>2.486022026966975</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9990369681365208</v>
+        <v>0.1615823968789414</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6693231881898158</v>
+        <v>0.1537597000280791</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7156012490582877</v>
+        <v>0.1886260645674192</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6614375229572176</v>
+        <v>0.1618142497890045</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6816851662097975</v>
+        <v>0.1653765647152099</v>
       </c>
       <c r="G6" t="n">
-        <v>1.050270018699626</v>
+        <v>0.2689203934284624</v>
       </c>
       <c r="H6" t="n">
-        <v>1.286488947073939</v>
+        <v>0.4454835680499876</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6822983826464066</v>
+        <v>0.2198995643001114</v>
       </c>
       <c r="J6" t="n">
-        <v>1.120452698544868</v>
+        <v>0.3139186059548267</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7143890851645731</v>
+        <v>0.1880724675943879</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7927278555346384</v>
+        <v>0.2618298578780887</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.079192107467535</v>
+        <v>0.2301418430300905</v>
       </c>
       <c r="C7" t="n">
-        <v>1.073371850420273</v>
+        <v>0.2248695029806619</v>
       </c>
       <c r="D7" t="n">
-        <v>1.104438558004518</v>
+        <v>0.2570584626459494</v>
       </c>
       <c r="E7" t="n">
-        <v>1.070690119348459</v>
+        <v>0.2338394047308196</v>
       </c>
       <c r="F7" t="n">
-        <v>1.070690119348459</v>
+        <v>0.2338394047308196</v>
       </c>
       <c r="G7" t="n">
-        <v>1.13042515803064</v>
+        <v>0.2830506805121142</v>
       </c>
       <c r="H7" t="n">
-        <v>1.296246228762087</v>
+        <v>0.4472164438212498</v>
       </c>
       <c r="I7" t="n">
-        <v>1.071851096949879</v>
+        <v>0.2340298513837643</v>
       </c>
       <c r="J7" t="n">
-        <v>1.172057714555781</v>
+        <v>0.323022482527746</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1060265313126</v>
+        <v>0.256997637972114</v>
       </c>
       <c r="L7" t="n">
-        <v>1.178855574624263</v>
+        <v>0.3297866003385599</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.249012096489024</v>
+        <v>0.2600245062453863</v>
       </c>
       <c r="C8" t="n">
-        <v>1.737915842074869</v>
+        <v>0.3418143243772092</v>
       </c>
       <c r="D8" t="n">
-        <v>1.871753925023031</v>
+        <v>0.3920890913636638</v>
       </c>
       <c r="E8" t="n">
-        <v>1.600808352086901</v>
+        <v>0.3271278006460827</v>
       </c>
       <c r="F8" t="n">
-        <v>1.257813472595802</v>
+        <v>0.2667671530236573</v>
       </c>
       <c r="G8" t="n">
-        <v>1.793466628104059</v>
+        <v>0.3997310305199757</v>
       </c>
       <c r="H8" t="n">
-        <v>1.959287698837793</v>
+        <v>0.5638967938295145</v>
       </c>
       <c r="I8" t="n">
-        <v>1.734892567023299</v>
+        <v>0.350710201391625</v>
       </c>
       <c r="J8" t="n">
-        <v>1.83519611633019</v>
+        <v>0.4397198906884701</v>
       </c>
       <c r="K8" t="n">
-        <v>1.266684678140714</v>
+        <v>0.2852679895998321</v>
       </c>
       <c r="L8" t="n">
-        <v>2.357108123753391</v>
+        <v>0.5371343920331841</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.891035875682837</v>
+        <v>0.3729792854711594</v>
       </c>
       <c r="C9" t="n">
-        <v>2.277447019258852</v>
+        <v>0.43672417573546</v>
       </c>
       <c r="D9" t="n">
-        <v>2.310514875677111</v>
+        <v>0.4692653375776811</v>
       </c>
       <c r="E9" t="n">
-        <v>2.728569186205619</v>
+        <v>0.5255456504781443</v>
       </c>
       <c r="F9" t="n">
-        <v>2.275942635310747</v>
+        <v>0.4459012598081256</v>
       </c>
       <c r="G9" t="n">
-        <v>2.334500326869219</v>
+        <v>0.4949053532669114</v>
       </c>
       <c r="H9" t="n">
-        <v>2.500321397600663</v>
+        <v>0.6590711165760491</v>
       </c>
       <c r="I9" t="n">
-        <v>2.275926265788458</v>
+        <v>0.4458845241385628</v>
       </c>
       <c r="J9" t="n">
-        <v>2.376132883394357</v>
+        <v>0.5348771552825438</v>
       </c>
       <c r="K9" t="n">
-        <v>2.073621019928735</v>
+        <v>0.4288634519114481</v>
       </c>
       <c r="L9" t="n">
-        <v>2.382930743462839</v>
+        <v>0.5416412730933577</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.761845969904711</v>
+        <v>1.761789061737333</v>
       </c>
       <c r="C2" t="n">
-        <v>1.612606060690956</v>
+        <v>1.612570296546791</v>
       </c>
       <c r="D2" t="n">
-        <v>1.774777398032009</v>
+        <v>1.774749782159887</v>
       </c>
       <c r="E2" t="n">
-        <v>1.649420895241991</v>
+        <v>1.649397594105904</v>
       </c>
       <c r="F2" t="n">
-        <v>1.649420895241991</v>
+        <v>1.649397594105904</v>
       </c>
       <c r="G2" t="n">
-        <v>1.769838093316022</v>
+        <v>1.769764336322213</v>
       </c>
       <c r="H2" t="n">
-        <v>1.775037483594989</v>
+        <v>1.775008822334143</v>
       </c>
       <c r="I2" t="n">
-        <v>1.760959050767031</v>
+        <v>1.760928475197803</v>
       </c>
       <c r="J2" t="n">
-        <v>1.996389072932506</v>
+        <v>1.996352909749373</v>
       </c>
       <c r="K2" t="n">
-        <v>1.856421480288281</v>
+        <v>1.856395481460133</v>
       </c>
       <c r="L2" t="n">
-        <v>1.776854027911046</v>
+        <v>1.776788183325254</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04991154475825257</v>
+        <v>0.04984718297168332</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.09860876615555113</v>
+        <v>-0.0986500062476207</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06478536584191247</v>
+        <v>0.06475469626276736</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06264330858141533</v>
+        <v>-0.06267010704489885</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.06264330858141515</v>
+        <v>-0.06267010704489903</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05910414224463771</v>
+        <v>0.05902040081744741</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06515678222547208</v>
+        <v>0.06512490281346497</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04891035551142721</v>
+        <v>0.04887631352683098</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2856496192011891</v>
+        <v>0.285609109075901</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1421929368632623</v>
+        <v>0.1421638906122732</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06716759115743132</v>
+        <v>0.067092950176452</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5583564623995831</v>
+        <v>0.1244740123583564</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5496005331253822</v>
+        <v>0.1254650350560514</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5660436484701703</v>
+        <v>0.1321786114572534</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5380337103741611</v>
+        <v>0.1204905861108787</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5380337103741613</v>
+        <v>0.1204905861108787</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5612303828774861</v>
+        <v>0.1288846349984657</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5662036481018734</v>
+        <v>0.1323379779286731</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5453504138423123</v>
+        <v>0.1217716247888581</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5630856638658092</v>
+        <v>0.129215508764381</v>
       </c>
       <c r="K4" t="n">
-        <v>0.549277293317191</v>
+        <v>0.1154122811744711</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5672595353757397</v>
+        <v>0.1333717678062634</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9182844395781991</v>
+        <v>0.1875106296531445</v>
       </c>
       <c r="C5" t="n">
-        <v>1.162956212170811</v>
+        <v>0.2332325810992497</v>
       </c>
       <c r="D5" t="n">
-        <v>1.566482162602475</v>
+        <v>0.3082325780361742</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8039751661089898</v>
+        <v>0.1672436530379449</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8039751661089898</v>
+        <v>0.1672436530379449</v>
       </c>
       <c r="G5" t="n">
-        <v>1.321167646674127</v>
+        <v>0.262157601139292</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7297745197532</v>
+        <v>0.3370885757969858</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8039679955433392</v>
+        <v>0.1672364885158376</v>
       </c>
       <c r="J5" t="n">
-        <v>1.33871716071822</v>
+        <v>0.2656159303055388</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02391544639100451</v>
+        <v>0.02292568501072786</v>
       </c>
       <c r="L5" t="n">
-        <v>1.867761345229272</v>
+        <v>0.3618124852254788</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8153295649267518</v>
+        <v>0.1280091107550954</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5757849294368835</v>
+        <v>0.1300686827367933</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5875972096726745</v>
+        <v>0.1359670673657242</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5542537240895589</v>
+        <v>0.1233410273280627</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5650902984207598</v>
+        <v>0.1252472893110389</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5813424919139949</v>
+        <v>0.1324197333952045</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8777625302283092</v>
+        <v>0.1871520484470288</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5654625228788152</v>
+        <v>0.1669720222447192</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5910590595570233</v>
+        <v>0.1785464032477549</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5652654704359805</v>
+        <v>0.1182224407780695</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5881452784985411</v>
+        <v>0.1370430101235675</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9118140382130433</v>
+        <v>0.1866763702937314</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9145014137717505</v>
+        <v>0.1896805379325174</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9176066322673673</v>
+        <v>0.1940475211910544</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8969925076069314</v>
+        <v>0.1836603863923274</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8969925076069314</v>
+        <v>0.1836603863923274</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9146879586909386</v>
+        <v>0.1910869929338407</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9196612239153389</v>
+        <v>0.1945403358640485</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8988079896557719</v>
+        <v>0.1839739827242334</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9165432396792712</v>
+        <v>0.1914178666997563</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9027348691306566</v>
+        <v>0.1776146391098462</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9207171111892016</v>
+        <v>0.1955741257416382</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.019086891818458</v>
+        <v>0.2055517884933432</v>
       </c>
       <c r="C8" t="n">
-        <v>1.398149021942409</v>
+        <v>0.2747900772660233</v>
       </c>
       <c r="D8" t="n">
-        <v>1.480314880738286</v>
+        <v>0.2930700802934297</v>
       </c>
       <c r="E8" t="n">
-        <v>1.279127088509748</v>
+        <v>0.2509057538172555</v>
       </c>
       <c r="F8" t="n">
-        <v>1.018038384118599</v>
+        <v>0.204959597017445</v>
       </c>
       <c r="G8" t="n">
-        <v>1.397608599387114</v>
+        <v>0.2760685626734936</v>
       </c>
       <c r="H8" t="n">
-        <v>1.402581864614479</v>
+        <v>0.2795219056042232</v>
       </c>
       <c r="I8" t="n">
-        <v>1.381728630351943</v>
+        <v>0.2689555524638854</v>
       </c>
       <c r="J8" t="n">
-        <v>1.399537705702608</v>
+        <v>0.2764124281524777</v>
       </c>
       <c r="K8" t="n">
-        <v>1.00302987225411</v>
+        <v>0.1952621016093677</v>
       </c>
       <c r="L8" t="n">
-        <v>1.796033276451131</v>
+        <v>0.3496090984348166</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.501993355239485</v>
+        <v>0.2905110045444027</v>
       </c>
       <c r="C9" t="n">
-        <v>1.801732959814735</v>
+        <v>0.3457840051751475</v>
       </c>
       <c r="D9" t="n">
-        <v>1.806732810940198</v>
+        <v>0.3504844437677835</v>
       </c>
       <c r="E9" t="n">
-        <v>2.12883852923918</v>
+        <v>0.4004017129336617</v>
       </c>
       <c r="F9" t="n">
-        <v>1.786046556264839</v>
+        <v>0.3400845880910531</v>
       </c>
       <c r="G9" t="n">
-        <v>1.80191950473393</v>
+        <v>0.3471904601764708</v>
       </c>
       <c r="H9" t="n">
-        <v>1.80689276995832</v>
+        <v>0.3506438031066785</v>
       </c>
       <c r="I9" t="n">
-        <v>1.786039535698755</v>
+        <v>0.3400774499668641</v>
       </c>
       <c r="J9" t="n">
-        <v>1.803774785722256</v>
+        <v>0.3475213339423863</v>
       </c>
       <c r="K9" t="n">
-        <v>1.415924624680339</v>
+        <v>0.3034333422413</v>
       </c>
       <c r="L9" t="n">
-        <v>1.807948657232187</v>
+        <v>0.3516775929842689</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.755741944065333</v>
+        <v>1.755689942545452</v>
       </c>
       <c r="C2" t="n">
-        <v>1.601554500964475</v>
+        <v>1.601521792816436</v>
       </c>
       <c r="D2" t="n">
-        <v>1.762474545065422</v>
+        <v>1.762449026585559</v>
       </c>
       <c r="E2" t="n">
-        <v>1.645225887790647</v>
+        <v>1.645206474292302</v>
       </c>
       <c r="F2" t="n">
-        <v>1.645225887790647</v>
+        <v>1.645206474292302</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758688698596226</v>
+        <v>1.758628358034176</v>
       </c>
       <c r="H2" t="n">
-        <v>1.763745326122629</v>
+        <v>1.763718917639655</v>
       </c>
       <c r="I2" t="n">
-        <v>1.752619288912023</v>
+        <v>1.752591612504664</v>
       </c>
       <c r="J2" t="n">
-        <v>1.971320696472516</v>
+        <v>1.971286981459949</v>
       </c>
       <c r="K2" t="n">
-        <v>1.861637251975216</v>
+        <v>1.861616473108458</v>
       </c>
       <c r="L2" t="n">
-        <v>1.765369766236381</v>
+        <v>1.765323789386076</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03634564887594515</v>
+        <v>0.03628522474175202</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1172127821876404</v>
+        <v>-0.1172518579708849</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04408953468014322</v>
+        <v>0.04405957152791506</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0746370874649757</v>
+        <v>-0.07466126905765523</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0746370874649757</v>
+        <v>-0.0746612690576554</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03973502700483461</v>
+        <v>0.03966501124471946</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04561188532918038</v>
+        <v>0.04558089151126139</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03280354086937896</v>
+        <v>0.03277112332635923</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2518035758757355</v>
+        <v>0.2517644077716089</v>
       </c>
       <c r="K3" t="n">
-        <v>0.140019121024024</v>
+        <v>0.1399939048163874</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04741358062000363</v>
+        <v>0.04736008544651001</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5060362794446854</v>
+        <v>0.1129621639317357</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5012007586190167</v>
+        <v>0.114325784635968</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5100385254547348</v>
+        <v>0.1169801529868931</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4895154856199965</v>
+        <v>0.1085480537880132</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4895154856199971</v>
+        <v>0.1085480537880132</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5060831111834245</v>
+        <v>0.1144088943564476</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5107984394875473</v>
+        <v>0.1177395288265601</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4928173363853032</v>
+        <v>0.1091228778900011</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5055581025723699</v>
+        <v>0.1124957391994089</v>
       </c>
       <c r="K4" t="n">
-        <v>0.49724317459773</v>
+        <v>0.1041848311448715</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5117400177655251</v>
+        <v>0.1186694774507095</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8654486064487081</v>
+        <v>0.1759383609957696</v>
       </c>
       <c r="C5" t="n">
-        <v>1.073436990221014</v>
+        <v>0.2148917187865159</v>
       </c>
       <c r="D5" t="n">
-        <v>1.174560783580486</v>
+        <v>0.2339156602958863</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6277334463952448</v>
+        <v>0.132832321450441</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6277334463952448</v>
+        <v>0.132832321450441</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9833404476673343</v>
+        <v>0.1980439786905366</v>
       </c>
       <c r="H5" t="n">
-        <v>1.351552645067103</v>
+        <v>0.2656792801083414</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6277267403524962</v>
+        <v>0.1328256200137025</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7800996108757579</v>
+        <v>0.1607262630706832</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.003099722764951962</v>
+        <v>0.01610444955151241</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47029303273969</v>
+        <v>0.2871259101135146</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7086339046397017</v>
+        <v>0.1134052381138815</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5066516758397607</v>
+        <v>0.1152804550181281</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5127277347793822</v>
+        <v>0.1174497001271539</v>
       </c>
       <c r="E6" t="n">
-        <v>0.48882957824936</v>
+        <v>0.1084231193739386</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4951827064692237</v>
+        <v>0.1095404142890824</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7086807363784419</v>
+        <v>0.150039953449285</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7570475922896337</v>
+        <v>0.1610596694790197</v>
       </c>
       <c r="I6" t="n">
-        <v>0.49536006376881</v>
+        <v>0.1447539369828388</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7274367728441019</v>
+        <v>0.1137951930997304</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4953690782270668</v>
+        <v>0.1038512755750543</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5151247427652806</v>
+        <v>0.1192607688333665</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8305815633530123</v>
+        <v>0.1700762607627902</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8329632910773364</v>
+        <v>0.1727092706700979</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8326880070254934</v>
+        <v>0.1737605885906811</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8164545586001856</v>
+        <v>0.1660827134473562</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8164545586001856</v>
+        <v>0.1660827134473562</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8306283950917517</v>
+        <v>0.1715229911875021</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8353437233958738</v>
+        <v>0.1748536256576146</v>
       </c>
       <c r="I7" t="n">
-        <v>0.817362620293629</v>
+        <v>0.166236974721056</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8301033864806953</v>
+        <v>0.1696098360304634</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8217884585060572</v>
+        <v>0.1612989279759263</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8362853016738511</v>
+        <v>0.1757835742817642</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9034355414758107</v>
+        <v>0.1828942473684822</v>
       </c>
       <c r="C8" t="n">
-        <v>1.22275380509981</v>
+        <v>0.2413006242602119</v>
       </c>
       <c r="D8" t="n">
-        <v>1.288180320166859</v>
+        <v>0.2539138710113842</v>
       </c>
       <c r="E8" t="n">
-        <v>1.120223557246841</v>
+        <v>0.2195362906674807</v>
       </c>
       <c r="F8" t="n">
-        <v>0.900804716919961</v>
+        <v>0.1809237754539005</v>
       </c>
       <c r="G8" t="n">
-        <v>1.218834572941776</v>
+        <v>0.2398354682662817</v>
       </c>
       <c r="H8" t="n">
-        <v>1.223549901248759</v>
+        <v>0.2431661027368972</v>
       </c>
       <c r="I8" t="n">
-        <v>1.205568798143656</v>
+        <v>0.2345494517998351</v>
       </c>
       <c r="J8" t="n">
-        <v>1.218371540228755</v>
+        <v>0.23793321939399</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8887846076027138</v>
+        <v>0.1730860759276764</v>
       </c>
       <c r="L8" t="n">
-        <v>1.55390322161043</v>
+        <v>0.3020646870598032</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.360245997149164</v>
+        <v>0.2632651780267204</v>
       </c>
       <c r="C9" t="n">
-        <v>1.626219132591581</v>
+        <v>0.3122793495400631</v>
       </c>
       <c r="D9" t="n">
-        <v>1.627839660515867</v>
+        <v>0.3136643303664527</v>
       </c>
       <c r="E9" t="n">
-        <v>1.914803889566263</v>
+        <v>0.3593366014807444</v>
       </c>
       <c r="F9" t="n">
-        <v>1.610625021879879</v>
+        <v>0.3058137293331533</v>
       </c>
       <c r="G9" t="n">
-        <v>1.623884236606013</v>
+        <v>0.3110930700574678</v>
       </c>
       <c r="H9" t="n">
-        <v>1.628599564910133</v>
+        <v>0.3144237045275799</v>
       </c>
       <c r="I9" t="n">
-        <v>1.61061846180789</v>
+        <v>0.3058070535910209</v>
       </c>
       <c r="J9" t="n">
-        <v>1.623359227994956</v>
+        <v>0.3091799149004293</v>
       </c>
       <c r="K9" t="n">
-        <v>1.456122124456165</v>
+        <v>0.2729052914377921</v>
       </c>
       <c r="L9" t="n">
-        <v>1.629541143188112</v>
+        <v>0.3153536531517295</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.286223826813761</v>
+        <v>2.286205568760193</v>
       </c>
       <c r="C2" t="n">
-        <v>2.147011826610232</v>
+        <v>2.146985490116145</v>
       </c>
       <c r="D2" t="n">
-        <v>2.560871451734382</v>
+        <v>2.560851088530468</v>
       </c>
       <c r="E2" t="n">
-        <v>2.229288359570275</v>
+        <v>2.229260655294425</v>
       </c>
       <c r="F2" t="n">
-        <v>1.946246436437535</v>
+        <v>1.946223147069402</v>
       </c>
       <c r="G2" t="n">
-        <v>2.380178336869399</v>
+        <v>2.380092676391155</v>
       </c>
       <c r="H2" t="n">
-        <v>2.91897797569088</v>
+        <v>2.918958293759395</v>
       </c>
       <c r="I2" t="n">
-        <v>1.966310543580527</v>
+        <v>1.966283911648517</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98385986724915</v>
+        <v>2.98382705535547</v>
       </c>
       <c r="K2" t="n">
-        <v>2.385962538572221</v>
+        <v>2.385944456013952</v>
       </c>
       <c r="L2" t="n">
-        <v>2.703657919899088</v>
+        <v>2.703639414112748</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6660052819000941</v>
+        <v>0.6659853943713567</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4786330203144152</v>
+        <v>0.4786038120948014</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9819069436429114</v>
+        <v>0.9818846347551972</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5610098802163436</v>
+        <v>0.5609792899897252</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2779679570836024</v>
+        <v>0.277941781764702</v>
       </c>
       <c r="G3" t="n">
-        <v>0.774072431082197</v>
+        <v>0.7739750168027139</v>
       </c>
       <c r="H3" t="n">
-        <v>1.393885535791454</v>
+        <v>1.393864001640239</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2978420456059599</v>
+        <v>0.29781256633244</v>
       </c>
       <c r="J3" t="n">
-        <v>1.399538222702694</v>
+        <v>1.399502455272448</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7515334091540696</v>
+        <v>0.7515134729868089</v>
       </c>
       <c r="L3" t="n">
-        <v>1.146125239958197</v>
+        <v>1.146105063831632</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.056141905618509</v>
+        <v>0.4916564766964479</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8278344559253429</v>
+        <v>0.294744584969775</v>
       </c>
       <c r="D4" t="n">
-        <v>1.219408280826741</v>
+        <v>0.6549216004820025</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8346358984831455</v>
+        <v>0.2959416176569436</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8346358984831459</v>
+        <v>0.2959416176569436</v>
       </c>
       <c r="G4" t="n">
-        <v>1.109607254834105</v>
+        <v>0.5470483593641615</v>
       </c>
       <c r="H4" t="n">
-        <v>1.432172723286751</v>
+        <v>0.8676864313792821</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8502530435445297</v>
+        <v>0.2986375842659498</v>
       </c>
       <c r="J4" t="n">
-        <v>1.198206955626228</v>
+        <v>0.6337162787028882</v>
       </c>
       <c r="K4" t="n">
-        <v>0.999902303379428</v>
+        <v>0.4354159874286191</v>
       </c>
       <c r="L4" t="n">
-        <v>1.304224530067591</v>
+        <v>0.7397389342536576</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.81295697779462</v>
+        <v>5.728838108406053</v>
       </c>
       <c r="C5" t="n">
-        <v>12.70441527356532</v>
+        <v>2.384922802844446</v>
       </c>
       <c r="D5" t="n">
-        <v>47.41913343165936</v>
+        <v>8.786034687389416</v>
       </c>
       <c r="E5" t="n">
-        <v>12.70441536570833</v>
+        <v>2.384922894982266</v>
       </c>
       <c r="F5" t="n">
-        <v>12.70441536570833</v>
+        <v>2.384922894982266</v>
       </c>
       <c r="G5" t="n">
-        <v>37.91195577252969</v>
+        <v>7.023552200776308</v>
       </c>
       <c r="H5" t="n">
-        <v>76.9158931738734</v>
+        <v>14.1527850301928</v>
       </c>
       <c r="I5" t="n">
-        <v>12.70435255803161</v>
+        <v>2.384860095512415</v>
       </c>
       <c r="J5" t="n">
-        <v>48.35020654415553</v>
+        <v>8.93235613492911</v>
       </c>
       <c r="K5" t="n">
-        <v>26.22723159668113</v>
+        <v>4.875393762942648</v>
       </c>
       <c r="L5" t="n">
-        <v>27.30426099375147</v>
+        <v>5.314573710786076</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.673043012808741</v>
+        <v>0.6002027132421526</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9537961815201215</v>
+        <v>0.3169087909580069</v>
       </c>
       <c r="D6" t="n">
-        <v>1.399188787213816</v>
+        <v>0.6865588290356067</v>
       </c>
       <c r="E6" t="n">
-        <v>0.939894122348248</v>
+        <v>0.3144623158867504</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9908918923144031</v>
+        <v>0.3234367595999895</v>
       </c>
       <c r="G6" t="n">
-        <v>1.253665850434382</v>
+        <v>0.655594595909866</v>
       </c>
       <c r="H6" t="n">
-        <v>1.595709726722372</v>
+        <v>0.9865198639182898</v>
       </c>
       <c r="I6" t="n">
-        <v>1.467154150734764</v>
+        <v>0.4071838208116556</v>
       </c>
       <c r="J6" t="n">
-        <v>1.843531965405959</v>
+        <v>0.7472650150277235</v>
       </c>
       <c r="K6" t="n">
-        <v>1.139190722153101</v>
+        <v>0.4599266719199539</v>
       </c>
       <c r="L6" t="n">
-        <v>1.463455853218726</v>
+        <v>0.7677585618056805</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.623181667031411</v>
+        <v>0.5914483547037377</v>
       </c>
       <c r="C7" t="n">
-        <v>1.417355520491142</v>
+        <v>0.3984921696052694</v>
       </c>
       <c r="D7" t="n">
-        <v>1.784410441722376</v>
+        <v>0.7543548608662141</v>
       </c>
       <c r="E7" t="n">
-        <v>1.416634412336221</v>
+        <v>0.3983653552295679</v>
       </c>
       <c r="F7" t="n">
-        <v>1.416634412336221</v>
+        <v>0.3983653552295679</v>
       </c>
       <c r="G7" t="n">
-        <v>1.67664701624701</v>
+        <v>0.6468402373714524</v>
       </c>
       <c r="H7" t="n">
-        <v>1.999212484699653</v>
+        <v>0.9674783093865726</v>
       </c>
       <c r="I7" t="n">
-        <v>1.417292804957434</v>
+        <v>0.3984294622732414</v>
       </c>
       <c r="J7" t="n">
-        <v>1.765246717039131</v>
+        <v>0.7335081567101788</v>
       </c>
       <c r="K7" t="n">
-        <v>1.566942064792332</v>
+        <v>0.5352078654359091</v>
       </c>
       <c r="L7" t="n">
-        <v>1.871264291480495</v>
+        <v>0.8395308122609483</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.888887759668036</v>
+        <v>0.6382075083552805</v>
       </c>
       <c r="C8" t="n">
-        <v>2.345843213512914</v>
+        <v>0.5618920590009975</v>
       </c>
       <c r="D8" t="n">
-        <v>2.849933212444632</v>
+        <v>0.9418710674008745</v>
       </c>
       <c r="E8" t="n">
-        <v>2.164354984189487</v>
+        <v>0.5299526240438875</v>
       </c>
       <c r="F8" t="n">
-        <v>1.704792236328147</v>
+        <v>0.4490757231180476</v>
       </c>
       <c r="G8" t="n">
-        <v>2.603118233428704</v>
+        <v>0.809885205190117</v>
       </c>
       <c r="H8" t="n">
-        <v>2.925683701881906</v>
+        <v>1.130523277205337</v>
       </c>
       <c r="I8" t="n">
-        <v>2.343764022139131</v>
+        <v>0.5614744300919057</v>
       </c>
       <c r="J8" t="n">
-        <v>2.691847793036982</v>
+        <v>0.8965759779416538</v>
       </c>
       <c r="K8" t="n">
-        <v>1.820374106041033</v>
+        <v>0.5798069503947297</v>
       </c>
       <c r="L8" t="n">
-        <v>3.487959933102914</v>
+        <v>1.124046036563536</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.124925521309742</v>
+        <v>0.8557071490601952</v>
       </c>
       <c r="C9" t="n">
-        <v>3.548532075531125</v>
+        <v>0.7735153749328123</v>
       </c>
       <c r="D9" t="n">
-        <v>3.917624785456665</v>
+        <v>1.129736716936857</v>
       </c>
       <c r="E9" t="n">
-        <v>4.274882998086973</v>
+        <v>0.9013350445950563</v>
       </c>
       <c r="F9" t="n">
-        <v>3.548531103478018</v>
+        <v>0.7735152797977252</v>
       </c>
       <c r="G9" t="n">
-        <v>3.807823571286996</v>
+        <v>1.021863442698996</v>
       </c>
       <c r="H9" t="n">
-        <v>4.130389039739633</v>
+        <v>1.342501514714117</v>
       </c>
       <c r="I9" t="n">
-        <v>3.548469359997422</v>
+        <v>0.7734526676007852</v>
       </c>
       <c r="J9" t="n">
-        <v>3.896423272079113</v>
+        <v>1.108531362037724</v>
       </c>
       <c r="K9" t="n">
-        <v>3.333422920184604</v>
+        <v>0.8460537499715551</v>
       </c>
       <c r="L9" t="n">
-        <v>4.002440846520481</v>
+        <v>1.214554017588491</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.176135249316751</v>
+        <v>2.176117687405591</v>
       </c>
       <c r="C2" t="n">
-        <v>2.216659534323355</v>
+        <v>2.216634081724805</v>
       </c>
       <c r="D2" t="n">
-        <v>2.517839907603118</v>
+        <v>2.517820338492498</v>
       </c>
       <c r="E2" t="n">
-        <v>2.297614899737884</v>
+        <v>2.297588067143454</v>
       </c>
       <c r="F2" t="n">
-        <v>2.018301721488042</v>
+        <v>2.018279326913102</v>
       </c>
       <c r="G2" t="n">
-        <v>2.364550440566831</v>
+        <v>2.364475380583007</v>
       </c>
       <c r="H2" t="n">
-        <v>2.78803013293318</v>
+        <v>2.78801144245662</v>
       </c>
       <c r="I2" t="n">
-        <v>2.036898239664712</v>
+        <v>2.036872675601885</v>
       </c>
       <c r="J2" t="n">
-        <v>2.866635907182533</v>
+        <v>2.866601919110268</v>
       </c>
       <c r="K2" t="n">
-        <v>2.387657297714581</v>
+        <v>2.387639610123838</v>
       </c>
       <c r="L2" t="n">
-        <v>2.646225764600609</v>
+        <v>2.646204453579052</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5386875179553309</v>
+        <v>0.5386684303834464</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5581964285180828</v>
+        <v>0.558168263194051</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9317186588913727</v>
+        <v>0.9316972626243166</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6392477370133792</v>
+        <v>0.6392181778709253</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3599345587635376</v>
+        <v>0.3599094376405726</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7554040179822054</v>
+        <v>0.755318795716069</v>
       </c>
       <c r="H3" t="n">
-        <v>1.242568534100086</v>
+        <v>1.242548140158596</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3783643264376539</v>
+        <v>0.3783360689928885</v>
       </c>
       <c r="J3" t="n">
-        <v>1.265224860879464</v>
+        <v>1.265187779257378</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7532207297710009</v>
+        <v>0.7532012755414695</v>
       </c>
       <c r="L3" t="n">
-        <v>1.079377761583898</v>
+        <v>1.079354358996122</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.963673665371383</v>
+        <v>0.4219466610678292</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8427099973376838</v>
+        <v>0.3324338785751925</v>
       </c>
       <c r="D4" t="n">
-        <v>1.16680260546801</v>
+        <v>0.6250744079694351</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8487607265644104</v>
+        <v>0.3334988150736706</v>
       </c>
       <c r="F4" t="n">
-        <v>0.848760726564411</v>
+        <v>0.3334988150736706</v>
       </c>
       <c r="G4" t="n">
-        <v>1.073460782829899</v>
+        <v>0.533527026021458</v>
       </c>
       <c r="H4" t="n">
-        <v>1.327330838304558</v>
+        <v>0.7856031488249076</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8662846211829445</v>
+        <v>0.3365401903084095</v>
       </c>
       <c r="J4" t="n">
-        <v>1.106291925236588</v>
+        <v>0.564558715878003</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9755906018522728</v>
+        <v>0.433862643857447</v>
       </c>
       <c r="L4" t="n">
-        <v>1.243066997685116</v>
+        <v>0.7013377485805979</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.50882194073966</v>
+        <v>4.38987792213342</v>
       </c>
       <c r="C5" t="n">
-        <v>15.35807410718633</v>
+        <v>2.887050333414729</v>
       </c>
       <c r="D5" t="n">
-        <v>41.35420670644139</v>
+        <v>7.698023567541498</v>
       </c>
       <c r="E5" t="n">
-        <v>15.35807422592167</v>
+        <v>2.887050452145108</v>
       </c>
       <c r="F5" t="n">
-        <v>15.35807422592167</v>
+        <v>2.887050452145108</v>
       </c>
       <c r="G5" t="n">
-        <v>34.18091636660559</v>
+        <v>6.359881448102306</v>
       </c>
       <c r="H5" t="n">
-        <v>64.02966262467037</v>
+        <v>11.82118444979243</v>
       </c>
       <c r="I5" t="n">
-        <v>15.35802320057185</v>
+        <v>2.886999433696303</v>
       </c>
       <c r="J5" t="n">
-        <v>38.989710017751</v>
+        <v>7.231921036045617</v>
       </c>
       <c r="K5" t="n">
-        <v>23.35141651749698</v>
+        <v>4.371977988238935</v>
       </c>
       <c r="L5" t="n">
-        <v>57.72263097434833</v>
+        <v>5.58729182586978</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.10056289568841</v>
+        <v>0.520474000036185</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9726446514119769</v>
+        <v>0.355297759168299</v>
       </c>
       <c r="D6" t="n">
-        <v>1.332339449473755</v>
+        <v>0.6542050874515988</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9604043495110481</v>
+        <v>0.3531437576738697</v>
       </c>
       <c r="F6" t="n">
-        <v>1.001430376476685</v>
+        <v>0.3603633798062493</v>
       </c>
       <c r="G6" t="n">
-        <v>1.210350013146927</v>
+        <v>0.6320543649898138</v>
       </c>
       <c r="H6" t="n">
-        <v>1.939058178557814</v>
+        <v>0.8932470425555816</v>
       </c>
       <c r="I6" t="n">
-        <v>1.003173851499976</v>
+        <v>0.4350675292767657</v>
       </c>
       <c r="J6" t="n">
-        <v>1.267695941157918</v>
+        <v>0.667626661140962</v>
       </c>
       <c r="K6" t="n">
-        <v>1.108742836257874</v>
+        <v>0.4572936894565077</v>
       </c>
       <c r="L6" t="n">
-        <v>1.393100629869033</v>
+        <v>0.7277390964332232</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.469559782120502</v>
+        <v>0.5109763248700082</v>
       </c>
       <c r="C7" t="n">
-        <v>1.372221644546532</v>
+        <v>0.4256207538290188</v>
       </c>
       <c r="D7" t="n">
-        <v>1.67079186915553</v>
+        <v>0.7137702256939351</v>
       </c>
       <c r="E7" t="n">
-        <v>1.369829706783308</v>
+        <v>0.4251998930850301</v>
       </c>
       <c r="F7" t="n">
-        <v>1.369829706783308</v>
+        <v>0.4251998930850301</v>
       </c>
       <c r="G7" t="n">
-        <v>1.579346899579021</v>
+        <v>0.6225566898236359</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83321695505368</v>
+        <v>0.8746328126270836</v>
       </c>
       <c r="I7" t="n">
-        <v>1.372170737932067</v>
+        <v>0.4255698541105863</v>
       </c>
       <c r="J7" t="n">
-        <v>1.612178041985718</v>
+        <v>0.6535883796801798</v>
       </c>
       <c r="K7" t="n">
-        <v>1.481476718601395</v>
+        <v>0.5228923076596249</v>
       </c>
       <c r="L7" t="n">
-        <v>1.748953114434239</v>
+        <v>0.7903674123827755</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.698418363279424</v>
+        <v>0.5512509774683519</v>
       </c>
       <c r="C8" t="n">
-        <v>2.182775606405854</v>
+        <v>0.5682660202380376</v>
       </c>
       <c r="D8" t="n">
-        <v>2.603589653469804</v>
+        <v>0.877928768976424</v>
       </c>
       <c r="E8" t="n">
-        <v>2.02320299413958</v>
+        <v>0.5401834675545377</v>
       </c>
       <c r="F8" t="n">
-        <v>1.61921665279397</v>
+        <v>0.4690872817672976</v>
       </c>
       <c r="G8" t="n">
-        <v>2.389676108302708</v>
+        <v>0.7651623798065252</v>
       </c>
       <c r="H8" t="n">
-        <v>2.643546163778413</v>
+        <v>1.017238502610157</v>
       </c>
       <c r="I8" t="n">
-        <v>2.182499946655753</v>
+        <v>0.5681755440934767</v>
       </c>
       <c r="J8" t="n">
-        <v>2.422621526012666</v>
+        <v>0.7962141805848841</v>
       </c>
       <c r="K8" t="n">
-        <v>1.699534184353406</v>
+        <v>0.5612661087065705</v>
       </c>
       <c r="L8" t="n">
-        <v>3.16667701512341</v>
+        <v>1.039866427641617</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.725371879214756</v>
+        <v>0.7319606823625557</v>
       </c>
       <c r="C9" t="n">
-        <v>3.165129887543609</v>
+        <v>0.7411212066714414</v>
       </c>
       <c r="D9" t="n">
-        <v>3.4655971867667</v>
+        <v>1.029604563601114</v>
       </c>
       <c r="E9" t="n">
-        <v>3.784926697710508</v>
+        <v>0.850190741793735</v>
       </c>
       <c r="F9" t="n">
-        <v>3.165129147925938</v>
+        <v>0.7411211743454956</v>
       </c>
       <c r="G9" t="n">
-        <v>3.372255142576098</v>
+        <v>0.9380571426660556</v>
       </c>
       <c r="H9" t="n">
-        <v>3.626125198050763</v>
+        <v>1.190133265469505</v>
       </c>
       <c r="I9" t="n">
-        <v>3.165078980929143</v>
+        <v>0.7410703069530097</v>
       </c>
       <c r="J9" t="n">
-        <v>3.405086284982799</v>
+        <v>0.9690888325226023</v>
       </c>
       <c r="K9" t="n">
-        <v>2.59808498516223</v>
+        <v>0.7193801152885962</v>
       </c>
       <c r="L9" t="n">
-        <v>3.541861357431327</v>
+        <v>1.105867865225198</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.129237184026317</v>
+        <v>2.129220234444134</v>
       </c>
       <c r="C2" t="n">
-        <v>2.372686588611679</v>
+        <v>2.372662684939566</v>
       </c>
       <c r="D2" t="n">
-        <v>2.434636770104547</v>
+        <v>2.434617882316285</v>
       </c>
       <c r="E2" t="n">
-        <v>2.452548572258072</v>
+        <v>2.452523286716999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.176169981268623</v>
+        <v>2.176149125744001</v>
       </c>
       <c r="G2" t="n">
-        <v>2.322311599990903</v>
+        <v>2.322245248700793</v>
       </c>
       <c r="H2" t="n">
-        <v>2.640682051079748</v>
+        <v>2.64066413192152</v>
       </c>
       <c r="I2" t="n">
-        <v>2.189808540832233</v>
+        <v>2.18978463625973</v>
       </c>
       <c r="J2" t="n">
-        <v>2.85416351336473</v>
+        <v>2.854132211096895</v>
       </c>
       <c r="K2" t="n">
-        <v>2.339888961758481</v>
+        <v>2.339872031736644</v>
       </c>
       <c r="L2" t="n">
-        <v>2.573839805208011</v>
+        <v>2.573818182095583</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4839368849613787</v>
+        <v>0.4839184970474865</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7363924730867315</v>
+        <v>0.7363661010091156</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8352096722850109</v>
+        <v>0.8351890550326287</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8163455550676968</v>
+        <v>0.8163177874222258</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5399669640782466</v>
+        <v>0.5399436264492301</v>
       </c>
       <c r="G3" t="n">
-        <v>0.706012458565428</v>
+        <v>0.7059372484538927</v>
       </c>
       <c r="H3" t="n">
-        <v>1.072273824968711</v>
+        <v>1.072254314336443</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5535117291894867</v>
+        <v>0.5534853713464835</v>
       </c>
       <c r="J3" t="n">
-        <v>1.25050353822466</v>
+        <v>1.250469560146778</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6978589584457511</v>
+        <v>0.6978403912396988</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9953120759020558</v>
+        <v>0.9952883103222209</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9484071932344351</v>
+        <v>0.3970507846149912</v>
       </c>
       <c r="C4" t="n">
-        <v>0.94955774507677</v>
+        <v>0.4269166526332355</v>
       </c>
       <c r="D4" t="n">
-        <v>1.129954306279729</v>
+        <v>0.5785967454789079</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9554681364891338</v>
+        <v>0.4279569152472142</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9554681364891346</v>
+        <v>0.4279569152472141</v>
       </c>
       <c r="G4" t="n">
-        <v>1.061360395858922</v>
+        <v>0.5114754334070679</v>
       </c>
       <c r="H4" t="n">
-        <v>1.252375155632493</v>
+        <v>0.7010181582157602</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9723717062369557</v>
+        <v>0.4309110758789668</v>
       </c>
       <c r="J4" t="n">
-        <v>1.113202332653382</v>
+        <v>0.5618410266077278</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9613496680671877</v>
+        <v>0.4099924724719849</v>
       </c>
       <c r="L4" t="n">
-        <v>1.212654127983736</v>
+        <v>0.6612949274582831</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.39883926457443</v>
+        <v>3.820312444557175</v>
       </c>
       <c r="C5" t="n">
-        <v>22.82691998131513</v>
+        <v>4.277255714809649</v>
       </c>
       <c r="D5" t="n">
-        <v>35.74908773924032</v>
+        <v>6.671531724637199</v>
       </c>
       <c r="E5" t="n">
-        <v>22.82692012678767</v>
+        <v>4.27725586027762</v>
       </c>
       <c r="F5" t="n">
-        <v>22.82692012678767</v>
+        <v>4.27725586027762</v>
       </c>
       <c r="G5" t="n">
-        <v>31.15010705159843</v>
+        <v>5.8066263351438</v>
       </c>
       <c r="H5" t="n">
-        <v>52.7542158671215</v>
+        <v>9.765315241160584</v>
       </c>
       <c r="I5" t="n">
-        <v>22.82689569899916</v>
+        <v>4.277231438423374</v>
       </c>
       <c r="J5" t="n">
-        <v>38.53940942920926</v>
+        <v>7.148757153270938</v>
       </c>
       <c r="K5" t="n">
-        <v>19.99909137971892</v>
+        <v>3.760608526331237</v>
       </c>
       <c r="L5" t="n">
-        <v>52.38910868155202</v>
+        <v>9.668283665091383</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.093262165982087</v>
+        <v>0.4225407264533841</v>
       </c>
       <c r="C6" t="n">
-        <v>1.105872980359796</v>
+        <v>0.4544236407453509</v>
       </c>
       <c r="D6" t="n">
-        <v>1.697988007919131</v>
+        <v>0.678545395719057</v>
       </c>
       <c r="E6" t="n">
-        <v>1.09340390407087</v>
+        <v>0.4522293915342281</v>
       </c>
       <c r="F6" t="n">
-        <v>1.120699558362602</v>
+        <v>0.4570325559594766</v>
       </c>
       <c r="G6" t="n">
-        <v>1.206215368606583</v>
+        <v>0.5369653752454594</v>
       </c>
       <c r="H6" t="n">
-        <v>1.853617120116129</v>
+        <v>0.8068171500765636</v>
       </c>
       <c r="I6" t="n">
-        <v>1.522018892028049</v>
+        <v>0.5276239334187881</v>
       </c>
       <c r="J6" t="n">
-        <v>1.689521457705277</v>
+        <v>0.5918736899561408</v>
       </c>
       <c r="K6" t="n">
-        <v>1.099677129907108</v>
+        <v>0.4343344329980623</v>
       </c>
       <c r="L6" t="n">
-        <v>1.370694171613984</v>
+        <v>0.6891055658541287</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.44305554527451</v>
+        <v>0.4841028675641496</v>
       </c>
       <c r="C7" t="n">
-        <v>1.467044340592764</v>
+        <v>0.5179874352143826</v>
       </c>
       <c r="D7" t="n">
-        <v>1.622706550401791</v>
+        <v>0.6653151134927577</v>
       </c>
       <c r="E7" t="n">
-        <v>1.462885421277156</v>
+        <v>0.5172556046463984</v>
       </c>
       <c r="F7" t="n">
-        <v>1.462885421277156</v>
+        <v>0.5172556046463984</v>
       </c>
       <c r="G7" t="n">
-        <v>1.556008747899012</v>
+        <v>0.598527516356223</v>
       </c>
       <c r="H7" t="n">
-        <v>1.747023507672592</v>
+        <v>0.7880702411649173</v>
       </c>
       <c r="I7" t="n">
-        <v>1.467020058277035</v>
+        <v>0.5179631588281249</v>
       </c>
       <c r="J7" t="n">
-        <v>1.607850684693481</v>
+        <v>0.6488931095568838</v>
       </c>
       <c r="K7" t="n">
-        <v>1.455998020107279</v>
+        <v>0.4970445554211428</v>
       </c>
       <c r="L7" t="n">
-        <v>1.707302480023839</v>
+        <v>0.7483470104074414</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.65545266896916</v>
+        <v>0.5214805868969439</v>
       </c>
       <c r="C8" t="n">
-        <v>2.236968713662549</v>
+        <v>0.653482559027058</v>
       </c>
       <c r="D8" t="n">
-        <v>2.51190945924699</v>
+        <v>0.8218017063805086</v>
       </c>
       <c r="E8" t="n">
-        <v>2.083722587894396</v>
+        <v>0.6265133851027103</v>
       </c>
       <c r="F8" t="n">
-        <v>1.695811014516308</v>
+        <v>0.5582460919360651</v>
       </c>
       <c r="G8" t="n">
-        <v>2.327403706290592</v>
+        <v>0.7342814462012456</v>
       </c>
       <c r="H8" t="n">
-        <v>2.518418466065387</v>
+        <v>0.9238241710101545</v>
       </c>
       <c r="I8" t="n">
-        <v>2.238415016668613</v>
+        <v>0.6537170886731476</v>
       </c>
       <c r="J8" t="n">
-        <v>2.379355501899008</v>
+        <v>0.7846663730972062</v>
       </c>
       <c r="K8" t="n">
-        <v>1.658011472054385</v>
+        <v>0.5325948861410981</v>
       </c>
       <c r="L8" t="n">
-        <v>3.062617419142072</v>
+        <v>0.9868631181728958</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.584212372189334</v>
+        <v>0.6849126401768055</v>
       </c>
       <c r="C9" t="n">
-        <v>3.108359974752074</v>
+        <v>0.8068137322802468</v>
       </c>
       <c r="D9" t="n">
-        <v>3.26591849224951</v>
+        <v>0.954475160646411</v>
       </c>
       <c r="E9" t="n">
-        <v>3.685532091685193</v>
+        <v>0.9083829598066018</v>
       </c>
       <c r="F9" t="n">
-        <v>3.108359426138143</v>
+        <v>0.8068137555994548</v>
       </c>
       <c r="G9" t="n">
-        <v>3.19732438205831</v>
+        <v>0.8873538134220893</v>
       </c>
       <c r="H9" t="n">
-        <v>3.388339141831901</v>
+        <v>1.076896538230782</v>
       </c>
       <c r="I9" t="n">
-        <v>3.108335692436348</v>
+        <v>0.8067894558939899</v>
       </c>
       <c r="J9" t="n">
-        <v>3.249166318852788</v>
+        <v>0.9377194066227513</v>
       </c>
       <c r="K9" t="n">
-        <v>2.807519761096619</v>
+        <v>0.734873747336256</v>
       </c>
       <c r="L9" t="n">
-        <v>3.348618114183148</v>
+        <v>1.037173307473307</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.810465397396474</v>
+        <v>1.810443934644813</v>
       </c>
       <c r="C2" t="n">
-        <v>1.970855965607606</v>
+        <v>1.970826601504824</v>
       </c>
       <c r="D2" t="n">
-        <v>1.952116688564297</v>
+        <v>1.952095002463761</v>
       </c>
       <c r="E2" t="n">
-        <v>2.049644794123683</v>
+        <v>2.049613937651615</v>
       </c>
       <c r="F2" t="n">
-        <v>1.776948177178135</v>
+        <v>1.77692210767934</v>
       </c>
       <c r="G2" t="n">
-        <v>1.906103601632076</v>
+        <v>1.905967710444639</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0804030589052</v>
+        <v>2.080378690190619</v>
       </c>
       <c r="I2" t="n">
-        <v>1.796604534219642</v>
+        <v>1.796574335944758</v>
       </c>
       <c r="J2" t="n">
-        <v>2.776515626702239</v>
+        <v>2.776473031886667</v>
       </c>
       <c r="K2" t="n">
-        <v>2.060955042329834</v>
+        <v>2.060934040796444</v>
       </c>
       <c r="L2" t="n">
-        <v>1.961943782114371</v>
+        <v>1.961885794205762</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1170729687395937</v>
+        <v>0.1170493840227557</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2752941498628545</v>
+        <v>0.2752613703126192</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2800012965591562</v>
+        <v>0.2799774549448457</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3541710264196517</v>
+        <v>0.3541367383823411</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08147440947410221</v>
+        <v>0.08144490841006458</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2270767150048576</v>
+        <v>0.2269215138830993</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4276227718914424</v>
+        <v>0.4275958326705818</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1009979142158944</v>
+        <v>0.1009643515038052</v>
       </c>
       <c r="J3" t="n">
-        <v>1.162480084705739</v>
+        <v>1.162433062578894</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3784264587029561</v>
+        <v>0.3784030712579093</v>
       </c>
       <c r="L3" t="n">
-        <v>0.291299800601231</v>
+        <v>0.2912341997280409</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6426112672253761</v>
+        <v>0.1888863925186443</v>
       </c>
       <c r="C4" t="n">
-        <v>0.591630995379695</v>
+        <v>0.1731228161019223</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7268169575502821</v>
+        <v>0.2730919500721075</v>
       </c>
       <c r="E4" t="n">
-        <v>0.597563079954514</v>
+        <v>0.1741668713375777</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5975630799545141</v>
+        <v>0.1741668713375778</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6977075592292787</v>
+        <v>0.2453621114530172</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8030448680478564</v>
+        <v>0.3493182385888094</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6227427600626687</v>
+        <v>0.1785799174251631</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9566729259350784</v>
+        <v>0.5029389276242135</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6856058620699268</v>
+        <v>0.2318799427724521</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7326363829111231</v>
+        <v>0.2788897714444103</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.932940849056062</v>
+        <v>1.119962118866142</v>
       </c>
       <c r="C5" t="n">
-        <v>5.131009330703125</v>
+        <v>0.9719453171276442</v>
       </c>
       <c r="D5" t="n">
-        <v>13.02228283479947</v>
+        <v>2.437065282605707</v>
       </c>
       <c r="E5" t="n">
-        <v>5.131009506581002</v>
+        <v>0.971945492996898</v>
       </c>
       <c r="F5" t="n">
-        <v>5.131009506581002</v>
+        <v>0.971945492996898</v>
       </c>
       <c r="G5" t="n">
-        <v>11.25056035589252</v>
+        <v>2.101541144753115</v>
       </c>
       <c r="H5" t="n">
-        <v>22.0630497642981</v>
+        <v>4.091019723123632</v>
       </c>
       <c r="I5" t="n">
-        <v>5.130988469571785</v>
+        <v>0.9719244705794469</v>
       </c>
       <c r="J5" t="n">
-        <v>38.88806075880424</v>
+        <v>7.178677465882924</v>
       </c>
       <c r="K5" t="n">
-        <v>9.700323732999347</v>
+        <v>1.818430771329816</v>
       </c>
       <c r="L5" t="n">
-        <v>11.26630121271552</v>
+        <v>3.088316392894016</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7109134156208975</v>
+        <v>0.2009013821731444</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6743852565350529</v>
+        <v>0.1876818879055167</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8027742375109256</v>
+        <v>0.3394042173478161</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6658055376766037</v>
+        <v>0.1861722399222042</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6898706308798518</v>
+        <v>0.1904058967205206</v>
       </c>
       <c r="G6" t="n">
-        <v>1.055370112069042</v>
+        <v>0.257377101107516</v>
       </c>
       <c r="H6" t="n">
-        <v>1.223870072921988</v>
+        <v>0.4233576425058969</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9804053129024304</v>
+        <v>0.1905949070796631</v>
       </c>
       <c r="J6" t="n">
-        <v>1.344051940142938</v>
+        <v>0.5710854540727565</v>
       </c>
       <c r="K6" t="n">
-        <v>0.757087520286201</v>
+        <v>0.2444563223355649</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8061035323971221</v>
+        <v>0.2918138672139479</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.065363764106988</v>
+        <v>0.263282057790092</v>
       </c>
       <c r="C7" t="n">
-        <v>1.045516118075619</v>
+        <v>0.2529964292448031</v>
       </c>
       <c r="D7" t="n">
-        <v>1.147539332398385</v>
+        <v>0.3471303139351389</v>
       </c>
       <c r="E7" t="n">
-        <v>1.039151068228377</v>
+        <v>0.2518763689884214</v>
       </c>
       <c r="F7" t="n">
-        <v>1.039151068228377</v>
+        <v>0.2518763689884214</v>
       </c>
       <c r="G7" t="n">
-        <v>1.120460056110889</v>
+        <v>0.3197577767244619</v>
       </c>
       <c r="H7" t="n">
-        <v>1.22579736492947</v>
+        <v>0.4237139038602519</v>
       </c>
       <c r="I7" t="n">
-        <v>1.045495256944281</v>
+        <v>0.2529755826966085</v>
       </c>
       <c r="J7" t="n">
-        <v>1.379425422816691</v>
+        <v>0.5773345928956579</v>
       </c>
       <c r="K7" t="n">
-        <v>1.108358358951542</v>
+        <v>0.306275608043898</v>
       </c>
       <c r="L7" t="n">
-        <v>1.155388879792735</v>
+        <v>0.3532854367158524</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.204866011114413</v>
+        <v>0.2878275765433436</v>
       </c>
       <c r="C8" t="n">
-        <v>1.634083975279665</v>
+        <v>0.3565661394168457</v>
       </c>
       <c r="D8" t="n">
-        <v>1.83539714945945</v>
+        <v>0.4681726547058942</v>
       </c>
       <c r="E8" t="n">
-        <v>1.510135897482674</v>
+        <v>0.334754535001196</v>
       </c>
       <c r="F8" t="n">
-        <v>1.196775903978037</v>
+        <v>0.2796110845127713</v>
       </c>
       <c r="G8" t="n">
-        <v>1.712459507981879</v>
+        <v>0.4239314081899944</v>
       </c>
       <c r="H8" t="n">
-        <v>1.817796816801502</v>
+        <v>0.5278875353259713</v>
       </c>
       <c r="I8" t="n">
-        <v>1.637494708815268</v>
+        <v>0.3571492141621417</v>
       </c>
       <c r="J8" t="n">
-        <v>1.971513803172254</v>
+        <v>0.68152387353497</v>
       </c>
       <c r="K8" t="n">
-        <v>1.23945523807461</v>
+        <v>0.3293419937238637</v>
       </c>
       <c r="L8" t="n">
-        <v>2.220059499189754</v>
+        <v>0.5406372902766095</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.021648217836437</v>
+        <v>0.4315307336556233</v>
       </c>
       <c r="C9" t="n">
-        <v>2.424636787837387</v>
+        <v>0.4956453501311408</v>
       </c>
       <c r="D9" t="n">
-        <v>2.528690192066961</v>
+        <v>0.5901365481642196</v>
       </c>
       <c r="E9" t="n">
-        <v>2.912580537677139</v>
+        <v>0.5815017513782195</v>
       </c>
       <c r="F9" t="n">
-        <v>2.42463655161972</v>
+        <v>0.4956454535007576</v>
       </c>
       <c r="G9" t="n">
-        <v>2.499580725872658</v>
+        <v>0.5624066976108004</v>
       </c>
       <c r="H9" t="n">
-        <v>2.60491803469123</v>
+        <v>0.6663628247465901</v>
       </c>
       <c r="I9" t="n">
-        <v>2.424615926706049</v>
+        <v>0.4956245035829454</v>
       </c>
       <c r="J9" t="n">
-        <v>2.758546092578452</v>
+        <v>0.8199835137819983</v>
       </c>
       <c r="K9" t="n">
-        <v>1.955052739139731</v>
+        <v>0.5058167397924022</v>
       </c>
       <c r="L9" t="n">
-        <v>2.534509549554499</v>
+        <v>0.5959343576021905</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.519117394412334</v>
+        <v>1.519095717291455</v>
       </c>
       <c r="C2" t="n">
-        <v>1.832263402922336</v>
+        <v>1.832235047809663</v>
       </c>
       <c r="D2" t="n">
-        <v>1.719672428864667</v>
+        <v>1.719651655934331</v>
       </c>
       <c r="E2" t="n">
-        <v>1.90757203534675</v>
+        <v>1.907542236856705</v>
       </c>
       <c r="F2" t="n">
-        <v>1.644741785817553</v>
+        <v>1.644716614053522</v>
       </c>
       <c r="G2" t="n">
-        <v>1.630147699785251</v>
+        <v>1.630043710779226</v>
       </c>
       <c r="H2" t="n">
-        <v>1.674473976990773</v>
+        <v>1.674452200521798</v>
       </c>
       <c r="I2" t="n">
-        <v>1.665503680113887</v>
+        <v>1.665474923315409</v>
       </c>
       <c r="J2" t="n">
-        <v>2.145217109664214</v>
+        <v>2.145177251138701</v>
       </c>
       <c r="K2" t="n">
-        <v>1.765790659127575</v>
+        <v>1.765769333240115</v>
       </c>
       <c r="L2" t="n">
-        <v>1.691552671069918</v>
+        <v>1.691511040307103</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.2195862560481775</v>
+        <v>-0.219610083076058</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1154724317106298</v>
+        <v>0.1154408798114985</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01109357842223208</v>
+        <v>0.01107079140077928</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1908595259781131</v>
+        <v>0.1908265159117861</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.07197072355108447</v>
+        <v>-0.07199910689139859</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.09187840501086293</v>
+        <v>-0.09199690775750866</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.04083871583752414</v>
+        <v>-0.04086266715133324</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05129929194226186</v>
+        <v>-0.05133121171338295</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4383867296359442</v>
+        <v>0.4383428880126544</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0395789682029995</v>
+        <v>0.03955528682125942</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.02125723470517014</v>
+        <v>-0.02130401606989039</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3742538942737315</v>
+        <v>0.000922669561065223</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4245161015477722</v>
+        <v>0.08147991958212751</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4934753640179486</v>
+        <v>0.1201446768082451</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4277338688833418</v>
+        <v>0.08204629367968092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4277338688833417</v>
+        <v>0.08204629367968092</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4387958421570235</v>
+        <v>0.0666194653032092</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4666025337142946</v>
+        <v>0.09327122956840576</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4515358322907366</v>
+        <v>0.08623358279456379</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5003950850602694</v>
+        <v>0.1270566053384921</v>
       </c>
       <c r="K4" t="n">
-        <v>0.423691891371334</v>
+        <v>0.05035985302944828</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4767238723728122</v>
+        <v>0.1033807668192359</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-8.571640721464293</v>
+        <v>-1.573593086621444</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.7521264710885891</v>
+        <v>-0.1257105725584299</v>
       </c>
       <c r="D5" t="n">
-        <v>1.87777201185239</v>
+        <v>0.3637474255214855</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7521262833323368</v>
+        <v>-0.1257103848088172</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7521262833323408</v>
+        <v>-0.1257103848088172</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.527492565564041</v>
+        <v>-0.4562007344557928</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2522762698636836</v>
+        <v>-0.03329837636192745</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7521273791682255</v>
+        <v>-0.1257114702240374</v>
       </c>
       <c r="J5" t="n">
-        <v>2.629920241887685</v>
+        <v>0.5016982098905052</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.904395909681226</v>
+        <v>-0.711433755857187</v>
       </c>
       <c r="L5" t="n">
-        <v>3.41954570061667</v>
+        <v>0.6209723335709769</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3665408548720834</v>
+        <v>0.03111513206489314</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4445831484454525</v>
+        <v>0.08500674815964866</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4972528249706357</v>
+        <v>0.120804452639633</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4421782470531066</v>
+        <v>0.0845838520635659</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4478822555597325</v>
+        <v>0.08558647391762053</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4310828027553782</v>
+        <v>0.06525676672298215</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6825483069594469</v>
+        <v>0.0928365856388296</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4438227928890968</v>
+        <v>0.0848708842143356</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5055145967195387</v>
+        <v>0.1616230025977938</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4162374178878711</v>
+        <v>0.04904389328749172</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4761464692537246</v>
+        <v>0.103274008615345</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6878496542940616</v>
+        <v>0.05610846575527616</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7651325003907075</v>
+        <v>0.1414202766543824</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8051806211836858</v>
+        <v>0.1749977445630113</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7576379558345909</v>
+        <v>0.1401014220501703</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7576379558345916</v>
+        <v>0.1401014220501703</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7523916021773585</v>
+        <v>0.1218052614974231</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7801982937346263</v>
+        <v>0.1484570257626192</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7651315923110691</v>
+        <v>0.1414193789887774</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8139908450806005</v>
+        <v>0.1822424015327052</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7372876513916657</v>
+        <v>0.1055456492236615</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7903196323931448</v>
+        <v>0.1585665630134485</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7400505671612054</v>
+        <v>0.06529047118904961</v>
       </c>
       <c r="C8" t="n">
-        <v>1.108846107075029</v>
+        <v>0.2018995030815409</v>
       </c>
       <c r="D8" t="n">
-        <v>1.216929675110991</v>
+        <v>0.2474493077055986</v>
       </c>
       <c r="E8" t="n">
-        <v>1.027810574188273</v>
+        <v>0.187639873597703</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8233805031165931</v>
+        <v>0.1516664562162183</v>
       </c>
       <c r="G8" t="n">
-        <v>1.100824517718059</v>
+        <v>0.1831150589446081</v>
       </c>
       <c r="H8" t="n">
-        <v>1.128631209274938</v>
+        <v>0.209766823209737</v>
       </c>
       <c r="I8" t="n">
-        <v>1.113564507851767</v>
+        <v>0.2027291764359626</v>
       </c>
       <c r="J8" t="n">
-        <v>1.16248197881168</v>
+        <v>0.2435624436046921</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7839859027066374</v>
+        <v>0.1137593541553831</v>
       </c>
       <c r="L8" t="n">
-        <v>1.448191645365072</v>
+        <v>0.2743281980951089</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.22368822069494</v>
+        <v>0.1503730132372212</v>
       </c>
       <c r="C9" t="n">
-        <v>1.563659601754262</v>
+        <v>0.2819036494401754</v>
       </c>
       <c r="D9" t="n">
-        <v>1.605598171775334</v>
+        <v>0.3158138363376357</v>
       </c>
       <c r="E9" t="n">
-        <v>1.866796615691739</v>
+        <v>0.3352393511064178</v>
       </c>
       <c r="F9" t="n">
-        <v>1.563659689677074</v>
+        <v>0.2819038196350271</v>
       </c>
       <c r="G9" t="n">
-        <v>1.550918703540911</v>
+        <v>0.2622886342832159</v>
       </c>
       <c r="H9" t="n">
-        <v>1.578725395098192</v>
+        <v>0.2889403985484118</v>
       </c>
       <c r="I9" t="n">
-        <v>1.563658693674623</v>
+        <v>0.2819027517745711</v>
       </c>
       <c r="J9" t="n">
-        <v>1.612517946444166</v>
+        <v>0.3227257743184989</v>
       </c>
       <c r="K9" t="n">
-        <v>1.377436904054167</v>
+        <v>0.2181631765368023</v>
       </c>
       <c r="L9" t="n">
-        <v>1.588846733756697</v>
+        <v>0.2990499357992429</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.362805020098652</v>
+        <v>1.362783569984746</v>
       </c>
       <c r="C2" t="n">
-        <v>1.793014871129964</v>
+        <v>1.792990037009649</v>
       </c>
       <c r="D2" t="n">
-        <v>1.700631432759878</v>
+        <v>1.700613251676883</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8669031148641</v>
+        <v>1.866876897582817</v>
       </c>
       <c r="F2" t="n">
-        <v>1.607980043205141</v>
+        <v>1.607958261903061</v>
       </c>
       <c r="G2" t="n">
-        <v>1.577316838004807</v>
+        <v>1.577247635959622</v>
       </c>
       <c r="H2" t="n">
-        <v>1.68180840730329</v>
+        <v>1.681789287415434</v>
       </c>
       <c r="I2" t="n">
-        <v>1.629829915553491</v>
+        <v>1.629805063883332</v>
       </c>
       <c r="J2" t="n">
-        <v>1.989891029080968</v>
+        <v>1.989858147862351</v>
       </c>
       <c r="K2" t="n">
-        <v>1.668752015657374</v>
+        <v>1.668732874590248</v>
       </c>
       <c r="L2" t="n">
-        <v>1.692762573248508</v>
+        <v>1.692734749032898</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.4005726550221544</v>
+        <v>-0.4005962305182142</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06966537289115361</v>
+        <v>0.06963791728936415</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01200229993118657</v>
+        <v>-0.01202211536452219</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1436361000525597</v>
+        <v>0.1436072474116285</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1152869716063996</v>
+        <v>-0.1153113882681275</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.153839628440865</v>
+        <v>-0.1539181285496789</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.03360396597020503</v>
+        <v>-0.03362486875098571</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09356461522616245</v>
+        <v>-0.09359207219989793</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2599939817599058</v>
+        <v>0.2599581728259672</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0722172767801621</v>
+        <v>-0.07223839190497791</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.02106331946355718</v>
+        <v>-0.02109422853115504</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2506492532967254</v>
+        <v>-0.09678223111199635</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3677082230671948</v>
+        <v>0.05462178268385295</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4514727407044196</v>
+        <v>0.1040431995960576</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3704101450735121</v>
+        <v>0.05509741188138201</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3704101450735121</v>
+        <v>0.05509741188138204</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3767326534198196</v>
+        <v>0.03045506244566123</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4402648234972103</v>
+        <v>0.09283471149825803</v>
       </c>
       <c r="I4" t="n">
-        <v>0.399803243193081</v>
+        <v>0.0602708647416034</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3831516981876147</v>
+        <v>0.0357170384768434</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3393323421964732</v>
+        <v>-0.008098543332749855</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4467447424186508</v>
+        <v>0.09930945585030278</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-16.31699275762495</v>
+        <v>-3.012740823100416</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.36983897461566</v>
+        <v>-0.4272711524536976</v>
       </c>
       <c r="D5" t="n">
-        <v>1.208604532973777</v>
+        <v>0.2372727715506271</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.369838757945181</v>
+        <v>-0.4272709357879455</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.369838757945181</v>
+        <v>-0.4272709357879455</v>
       </c>
       <c r="G5" t="n">
-        <v>-5.125813377513681</v>
+        <v>-0.938475806218015</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2585525588728794</v>
+        <v>0.06081537467285045</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.369837518078451</v>
+        <v>-0.4272696897278917</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.029560762880518</v>
+        <v>-0.9170280556762611</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.917729880532776</v>
+        <v>-1.461385048771893</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.706555205307232</v>
+        <v>0.1711975005187633</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2251418612051242</v>
+        <v>-0.1012760660347557</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3767346625712612</v>
+        <v>0.05620588224120782</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5988347586194042</v>
+        <v>0.1023632362030092</v>
       </c>
       <c r="E6" t="n">
-        <v>0.376223515477162</v>
+        <v>0.05611629270457829</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3789497535585503</v>
+        <v>0.05659522234460615</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3512252613282199</v>
+        <v>0.05362198439481435</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6121154383650945</v>
+        <v>0.1230607076643654</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3742958511014807</v>
+        <v>0.05577702981884108</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3681007763725224</v>
+        <v>0.06319694825870642</v>
       </c>
       <c r="K6" t="n">
-        <v>0.311101963446044</v>
+        <v>-0.01307083809949591</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4301574615168965</v>
+        <v>0.09638560883679104</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5440428775973616</v>
+        <v>-0.04515094594151513</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6931954109565049</v>
+        <v>0.1119006871862767</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7429770612737517</v>
+        <v>0.1553419673673523</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6838954207284644</v>
+        <v>0.1102640888518755</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6838954207284644</v>
+        <v>0.1102640888518755</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6701262777204562</v>
+        <v>0.08208634761614031</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7336584477978471</v>
+        <v>0.1444659966687329</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6931968674937179</v>
+        <v>0.1119021499120825</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6765453224882514</v>
+        <v>0.08734832364732328</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6327259664971088</v>
+        <v>0.04353274183772793</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7401383667192851</v>
+        <v>0.1509407410207854</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5763972986355359</v>
+        <v>-0.03946082708928343</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9813518058609367</v>
+        <v>0.1626045188166483</v>
       </c>
       <c r="D8" t="n">
-        <v>1.093857512425064</v>
+        <v>0.2170836683629184</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9097930153599092</v>
+        <v>0.1500123867109583</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7294422015014532</v>
+        <v>0.1182758180774035</v>
       </c>
       <c r="G8" t="n">
-        <v>0.964736894497064</v>
+        <v>0.1339261033626204</v>
       </c>
       <c r="H8" t="n">
-        <v>1.028269064573297</v>
+        <v>0.1963057524150081</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9878074842703271</v>
+        <v>0.1637419056585623</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9712074803814079</v>
+        <v>0.1391971491654806</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6602088440273027</v>
+        <v>0.04836560748617753</v>
       </c>
       <c r="L8" t="n">
-        <v>1.308697509710506</v>
+        <v>0.250987651518836</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9978655574319607</v>
+        <v>0.03468752440925457</v>
       </c>
       <c r="C9" t="n">
-        <v>1.377725354830168</v>
+        <v>0.2323320780174348</v>
       </c>
       <c r="D9" t="n">
-        <v>1.429396173629347</v>
+        <v>0.2761058517852116</v>
       </c>
       <c r="E9" t="n">
-        <v>1.643956607384929</v>
+        <v>0.2791756193271743</v>
       </c>
       <c r="F9" t="n">
-        <v>1.377725465284635</v>
+        <v>0.2323322759988297</v>
       </c>
       <c r="G9" t="n">
-        <v>1.354656221594118</v>
+        <v>0.2025177384472989</v>
       </c>
       <c r="H9" t="n">
-        <v>1.418188391671514</v>
+        <v>0.2648973874998938</v>
       </c>
       <c r="I9" t="n">
-        <v>1.377726811367379</v>
+        <v>0.2323335407432402</v>
       </c>
       <c r="J9" t="n">
-        <v>1.361075266361917</v>
+        <v>0.2077797144784785</v>
       </c>
       <c r="K9" t="n">
-        <v>1.183583158643834</v>
+        <v>0.1394902018268631</v>
       </c>
       <c r="L9" t="n">
-        <v>1.424668310592953</v>
+        <v>0.2713721318519406</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.079818506608463</v>
+        <v>2.079799342961004</v>
       </c>
       <c r="C2" t="n">
-        <v>2.10492256509844</v>
+        <v>2.104895348232169</v>
       </c>
       <c r="D2" t="n">
-        <v>2.508917385295411</v>
+        <v>2.508896425263523</v>
       </c>
       <c r="E2" t="n">
-        <v>2.185748143982644</v>
+        <v>2.185719535513427</v>
       </c>
       <c r="F2" t="n">
-        <v>1.906954243115027</v>
+        <v>1.906930121259921</v>
       </c>
       <c r="G2" t="n">
-        <v>2.263045050136158</v>
+        <v>2.262949382451287</v>
       </c>
       <c r="H2" t="n">
-        <v>2.847566898398051</v>
+        <v>2.847546144232633</v>
       </c>
       <c r="I2" t="n">
-        <v>1.927283716217219</v>
+        <v>1.927256102815506</v>
       </c>
       <c r="J2" t="n">
-        <v>2.845030741530935</v>
+        <v>2.844993532639096</v>
       </c>
       <c r="K2" t="n">
-        <v>2.285203955677895</v>
+        <v>2.285185044286695</v>
       </c>
       <c r="L2" t="n">
-        <v>2.571484341455575</v>
+        <v>2.571451666785259</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4277933671021732</v>
+        <v>0.4277724450772955</v>
       </c>
       <c r="C3" t="n">
-        <v>0.429885783063931</v>
+        <v>0.4298555546453545</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9213459651570988</v>
+        <v>0.9213229769180064</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5108062644022076</v>
+        <v>0.5107746299094831</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2320123635345903</v>
+        <v>0.2319852156559767</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6385418474231711</v>
+        <v>0.6384329299075047</v>
       </c>
       <c r="H3" t="n">
-        <v>1.310932386270468</v>
+        <v>1.310909625344856</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2521791237414646</v>
+        <v>0.2521485279496183</v>
       </c>
       <c r="J3" t="n">
-        <v>1.240462493767687</v>
+        <v>1.240421678524661</v>
       </c>
       <c r="K3" t="n">
-        <v>0.635713096911862</v>
+        <v>0.6356921991299727</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9932962921902281</v>
+        <v>0.9932598261398884</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8965560010974505</v>
+        <v>0.3633650461324335</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7672839335322461</v>
+        <v>0.2658766287739884</v>
       </c>
       <c r="D4" t="n">
-        <v>1.151637102014976</v>
+        <v>0.6184450791755364</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7736478143746784</v>
+        <v>0.2669966593109325</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7736478143746787</v>
+        <v>0.2669966593109326</v>
       </c>
       <c r="G4" t="n">
-        <v>1.00325135414765</v>
+        <v>0.4718483975857544</v>
       </c>
       <c r="H4" t="n">
-        <v>1.35282397347131</v>
+        <v>0.8196320543556742</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7912112855631989</v>
+        <v>0.2700439377806333</v>
       </c>
       <c r="J4" t="n">
-        <v>1.084370704587677</v>
+        <v>0.5511724361085956</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9065856336399574</v>
+        <v>0.3733937762929457</v>
       </c>
       <c r="L4" t="n">
-        <v>1.188764813442907</v>
+        <v>0.6555658076823135</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.62294203268427</v>
+        <v>3.659187682777365</v>
       </c>
       <c r="C5" t="n">
-        <v>10.99996460166211</v>
+        <v>2.066724512317081</v>
       </c>
       <c r="D5" t="n">
-        <v>42.92608364104127</v>
+        <v>7.970707778380603</v>
       </c>
       <c r="E5" t="n">
-        <v>10.99996471187912</v>
+        <v>2.066724622528555</v>
       </c>
       <c r="F5" t="n">
-        <v>10.99996471187911</v>
+        <v>2.066724622528555</v>
       </c>
       <c r="G5" t="n">
-        <v>30.61956197406584</v>
+        <v>5.683536634090198</v>
       </c>
       <c r="H5" t="n">
-        <v>66.90047128702004</v>
+        <v>12.35597430378459</v>
       </c>
       <c r="I5" t="n">
-        <v>10.99991259993977</v>
+        <v>2.066672520030282</v>
       </c>
       <c r="J5" t="n">
-        <v>40.92599337758435</v>
+        <v>7.563145309087061</v>
       </c>
       <c r="K5" t="n">
-        <v>20.746777962818</v>
+        <v>3.865231663440279</v>
       </c>
       <c r="L5" t="n">
-        <v>56.81802870257923</v>
+        <v>10.44613279740828</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.020774167021365</v>
+        <v>0.3852219786366321</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8819735219238298</v>
+        <v>0.2860568009602307</v>
       </c>
       <c r="D6" t="n">
-        <v>1.315380425759434</v>
+        <v>0.6472596784942232</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8697907141551521</v>
+        <v>0.2839129361905249</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9133697773238719</v>
+        <v>0.2915815670400552</v>
       </c>
       <c r="G6" t="n">
-        <v>1.556059319205138</v>
+        <v>0.569113557855614</v>
       </c>
       <c r="H6" t="n">
-        <v>1.96209956283913</v>
+        <v>0.9268415202055329</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9154294514871132</v>
+        <v>0.3673090980504938</v>
       </c>
       <c r="J6" t="n">
-        <v>1.664498717747587</v>
+        <v>0.6532457284550185</v>
       </c>
       <c r="K6" t="n">
-        <v>1.026680112780622</v>
+        <v>0.3945262372730166</v>
       </c>
       <c r="L6" t="n">
-        <v>1.327465065088353</v>
+        <v>0.6799717178272987</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.417688239396256</v>
+        <v>0.4550768567253369</v>
       </c>
       <c r="C7" t="n">
-        <v>1.312395525584348</v>
+        <v>0.3618077406603352</v>
       </c>
       <c r="D7" t="n">
-        <v>1.670733629704487</v>
+        <v>0.7097986047723592</v>
       </c>
       <c r="E7" t="n">
-        <v>1.310378170085813</v>
+        <v>0.361452802176502</v>
       </c>
       <c r="F7" t="n">
-        <v>1.310378170085813</v>
+        <v>0.361452802176502</v>
       </c>
       <c r="G7" t="n">
-        <v>1.524383592446455</v>
+        <v>0.5635602081786564</v>
       </c>
       <c r="H7" t="n">
-        <v>1.873956211770116</v>
+        <v>0.9113438649485766</v>
       </c>
       <c r="I7" t="n">
-        <v>1.312343523862005</v>
+        <v>0.3617557483735362</v>
       </c>
       <c r="J7" t="n">
-        <v>1.605502942886484</v>
+        <v>0.6428842467014986</v>
       </c>
       <c r="K7" t="n">
-        <v>1.427717871938764</v>
+        <v>0.465105586885849</v>
       </c>
       <c r="L7" t="n">
-        <v>1.709897051741712</v>
+        <v>0.7472776182752147</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.643327305015442</v>
+        <v>0.4947838630544741</v>
       </c>
       <c r="C8" t="n">
-        <v>2.133106494686746</v>
+        <v>0.5062380670507399</v>
       </c>
       <c r="D8" t="n">
-        <v>2.615953172902204</v>
+        <v>0.8761404776235472</v>
       </c>
       <c r="E8" t="n">
-        <v>1.96992684387866</v>
+        <v>0.4775210960867988</v>
       </c>
       <c r="F8" t="n">
-        <v>1.556884313749927</v>
+        <v>0.4048321073952499</v>
       </c>
       <c r="G8" t="n">
-        <v>2.344333251868234</v>
+        <v>0.7078565218301056</v>
       </c>
       <c r="H8" t="n">
-        <v>2.693905871192499</v>
+        <v>1.055640178600131</v>
       </c>
       <c r="I8" t="n">
-        <v>2.132293183283783</v>
+        <v>0.506052062024985</v>
       </c>
       <c r="J8" t="n">
-        <v>2.425569400992229</v>
+        <v>0.787201115082373</v>
       </c>
       <c r="K8" t="n">
-        <v>1.642317313187318</v>
+        <v>0.5028697931403072</v>
       </c>
       <c r="L8" t="n">
-        <v>3.150653821490752</v>
+        <v>1.000826208980063</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.789586292289617</v>
+        <v>0.696480926227648</v>
       </c>
       <c r="C9" t="n">
-        <v>3.259973080458682</v>
+        <v>0.7045150179206279</v>
       </c>
       <c r="D9" t="n">
-        <v>3.620346935419635</v>
+        <v>1.05286417410998</v>
       </c>
       <c r="E9" t="n">
-        <v>3.924293900559856</v>
+        <v>0.8214166656373596</v>
       </c>
       <c r="F9" t="n">
-        <v>3.259972178361116</v>
+        <v>0.7045149499930712</v>
       </c>
       <c r="G9" t="n">
-        <v>3.471961147320788</v>
+        <v>0.906267485438949</v>
       </c>
       <c r="H9" t="n">
-        <v>3.821533766644445</v>
+        <v>1.254051142208869</v>
       </c>
       <c r="I9" t="n">
-        <v>3.259921078736339</v>
+        <v>0.7044630256338282</v>
       </c>
       <c r="J9" t="n">
-        <v>3.553080497760816</v>
+        <v>0.9855915239617909</v>
       </c>
       <c r="K9" t="n">
-        <v>3.028211894512743</v>
+        <v>0.7491173907011202</v>
       </c>
       <c r="L9" t="n">
-        <v>3.657474606616046</v>
+        <v>1.089984895535508</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.665861008826957</v>
+        <v>1.665841599340925</v>
       </c>
       <c r="C2" t="n">
-        <v>1.964232203691559</v>
+        <v>1.964205172574246</v>
       </c>
       <c r="D2" t="n">
-        <v>2.269297721806143</v>
+        <v>2.269276188458</v>
       </c>
       <c r="E2" t="n">
-        <v>2.042148600184218</v>
+        <v>2.042120147716313</v>
       </c>
       <c r="F2" t="n">
-        <v>1.771715117838038</v>
+        <v>1.77169122734203</v>
       </c>
       <c r="G2" t="n">
-        <v>1.884094822437527</v>
+        <v>1.884004147060415</v>
       </c>
       <c r="H2" t="n">
-        <v>1.742610872945435</v>
+        <v>1.742589633076878</v>
       </c>
       <c r="I2" t="n">
-        <v>1.791194427372087</v>
+        <v>1.791167147229218</v>
       </c>
       <c r="J2" t="n">
-        <v>2.42093410137349</v>
+        <v>2.420895623740377</v>
       </c>
       <c r="K2" t="n">
-        <v>2.00935736875088</v>
+        <v>2.009339366366796</v>
       </c>
       <c r="L2" t="n">
-        <v>2.21699683996105</v>
+        <v>2.216963490070399</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04947257339044424</v>
+        <v>-0.04949378088385099</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2676454317923163</v>
+        <v>0.2676154364435694</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6446046480741362</v>
+        <v>0.6445809976993456</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3456411976573458</v>
+        <v>0.3456097663985519</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07520771531116544</v>
+        <v>0.07518084602426967</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2015415192600096</v>
+        <v>0.2014383412291763</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03887688941493157</v>
+        <v>0.0388535675074867</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09462303600596735</v>
+        <v>0.09459281890681341</v>
       </c>
       <c r="J3" t="n">
-        <v>0.754237670929516</v>
+        <v>0.7541954397075498</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3190820013359033</v>
+        <v>0.3190621624346058</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5844288768589132</v>
+        <v>0.5843916319255029</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5428889606505466</v>
+        <v>0.100694943990486</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5859253268656853</v>
+        <v>0.1696588219899305</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9016065167341166</v>
+        <v>0.4594112375280323</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5900768426775719</v>
+        <v>0.1703894969714238</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5900768426775719</v>
+        <v>0.1703894969714239</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6708981545783537</v>
+        <v>0.2300803626196627</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5885534736618503</v>
+        <v>0.1463583515398396</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6059759412014409</v>
+        <v>0.1731713928260276</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7353746440449841</v>
+        <v>0.2931728880041513</v>
       </c>
       <c r="K4" t="n">
-        <v>0.642058986546764</v>
+        <v>0.1998648174807344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8704287614984999</v>
+        <v>0.4282264402944668</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.843388414680779</v>
+        <v>-0.3193136444043859</v>
       </c>
       <c r="C5" t="n">
-        <v>4.600505492882926</v>
+        <v>0.876130121798387</v>
       </c>
       <c r="D5" t="n">
-        <v>27.8830275368008</v>
+        <v>5.208096955390201</v>
       </c>
       <c r="E5" t="n">
-        <v>4.600505625864408</v>
+        <v>0.8761302547736752</v>
       </c>
       <c r="F5" t="n">
-        <v>4.600505625864407</v>
+        <v>0.8761302547736752</v>
       </c>
       <c r="G5" t="n">
-        <v>9.503535654559514</v>
+        <v>1.783960622613748</v>
       </c>
       <c r="H5" t="n">
-        <v>2.38621473046344</v>
+        <v>0.4626995115440451</v>
       </c>
       <c r="I5" t="n">
-        <v>4.600486865443108</v>
+        <v>0.8761115031551275</v>
       </c>
       <c r="J5" t="n">
-        <v>16.44354249083863</v>
+        <v>3.057656101243097</v>
       </c>
       <c r="K5" t="n">
-        <v>6.615443647823319</v>
+        <v>1.251153727691565</v>
       </c>
       <c r="L5" t="n">
-        <v>31.57084013371099</v>
+        <v>1.022566157499854</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5928237991438007</v>
+        <v>0.1577180478945755</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6449546230781196</v>
+        <v>0.1800431434387065</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9967616625164363</v>
+        <v>0.4761546040589429</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6380718478403252</v>
+        <v>0.1788320878804759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6567858800115817</v>
+        <v>0.1821246204049355</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9950442670890856</v>
+        <v>0.2388639048632233</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9534531384404443</v>
+        <v>0.2105595035533632</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9301220537121722</v>
+        <v>0.2301944967301171</v>
       </c>
       <c r="J6" t="n">
-        <v>1.084517673851753</v>
+        <v>0.3048118954955491</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6932611600483903</v>
+        <v>0.2088725481309613</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9315890587202217</v>
+        <v>0.4389857570384992</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9281728196498217</v>
+        <v>0.1684980981368126</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9912784276405489</v>
+        <v>0.240993165615615</v>
       </c>
       <c r="D7" t="n">
-        <v>1.284996437945607</v>
+        <v>0.5268810586842482</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9872687828611224</v>
+        <v>0.2402876071994071</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9872687828611226</v>
+        <v>0.2402876071994071</v>
       </c>
       <c r="G7" t="n">
-        <v>1.056182013577633</v>
+        <v>0.2978835167659897</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9738373326611353</v>
+        <v>0.2141615056861665</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9912598002007204</v>
+        <v>0.2409745469723541</v>
       </c>
       <c r="J7" t="n">
-        <v>1.120658503044264</v>
+        <v>0.3609760421504773</v>
       </c>
       <c r="K7" t="n">
-        <v>1.027342845546048</v>
+        <v>0.2676679716270608</v>
       </c>
       <c r="L7" t="n">
-        <v>1.255712620497779</v>
+        <v>0.4960295944407935</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.048311317654731</v>
+        <v>0.1896374805716613</v>
       </c>
       <c r="C8" t="n">
-        <v>1.516047419861696</v>
+        <v>0.3333389692794477</v>
       </c>
       <c r="D8" t="n">
-        <v>1.897204700400265</v>
+        <v>0.6346143699083149</v>
       </c>
       <c r="E8" t="n">
-        <v>1.404635997753609</v>
+        <v>0.3137330101877993</v>
       </c>
       <c r="F8" t="n">
-        <v>1.12302414388766</v>
+        <v>0.2641752738650841</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58231146854349</v>
+        <v>0.3904687354326865</v>
       </c>
       <c r="H8" t="n">
-        <v>1.499966787627897</v>
+        <v>0.3067467243530233</v>
       </c>
       <c r="I8" t="n">
-        <v>1.517389255166578</v>
+        <v>0.333559765639051</v>
       </c>
       <c r="J8" t="n">
-        <v>1.646867746754086</v>
+        <v>0.4535753019514341</v>
       </c>
       <c r="K8" t="n">
-        <v>1.139939853094975</v>
+        <v>0.2874802109745482</v>
       </c>
       <c r="L8" t="n">
-        <v>2.20593357832669</v>
+        <v>0.6632459632387164</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.720830719740764</v>
+        <v>0.3079649438204245</v>
       </c>
       <c r="C9" t="n">
-        <v>2.14663369815592</v>
+        <v>0.4442810748492687</v>
       </c>
       <c r="D9" t="n">
-        <v>2.442245938895381</v>
+        <v>0.7305023524059324</v>
       </c>
       <c r="E9" t="n">
-        <v>2.565179026528968</v>
+        <v>0.5179293831310607</v>
       </c>
       <c r="F9" t="n">
-        <v>2.146633715778953</v>
+        <v>0.4442811875380469</v>
       </c>
       <c r="G9" t="n">
-        <v>2.21153728409301</v>
+        <v>0.5011714259996428</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1291926031765</v>
+        <v>0.4174494149198203</v>
       </c>
       <c r="I9" t="n">
-        <v>2.14661507071609</v>
+        <v>0.4442624562060075</v>
       </c>
       <c r="J9" t="n">
-        <v>2.276013773559634</v>
+        <v>0.5642639513841307</v>
       </c>
       <c r="K9" t="n">
-        <v>1.972549958301038</v>
+        <v>0.3905937564845108</v>
       </c>
       <c r="L9" t="n">
-        <v>2.411067891013148</v>
+        <v>0.6993175036744468</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia climate change results.xlsx
+++ b/Results/Ammonia/ammonia climate change results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.417532495720357</v>
+        <v>2.701627450228377</v>
       </c>
       <c r="C2" t="n">
-        <v>2.260282269662309</v>
+        <v>2.83734037322328</v>
       </c>
       <c r="D2" t="n">
-        <v>2.595310408075174</v>
+        <v>2.710983548660236</v>
       </c>
       <c r="E2" t="n">
-        <v>2.342958823808085</v>
+        <v>2.90669340249095</v>
       </c>
       <c r="F2" t="n">
-        <v>2.058476387317136</v>
+        <v>2.669865718519153</v>
       </c>
       <c r="G2" t="n">
-        <v>2.412940089071636</v>
+        <v>2.70138576098771</v>
       </c>
       <c r="H2" t="n">
-        <v>3.01645705307318</v>
+        <v>2.733005169467742</v>
       </c>
       <c r="I2" t="n">
-        <v>2.074977620092314</v>
+        <v>2.683598432065438</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98816970727029</v>
+        <v>3.093802866594949</v>
       </c>
       <c r="K2" t="n">
-        <v>2.490282154802283</v>
+        <v>2.861758700790735</v>
       </c>
       <c r="L2" t="n">
-        <v>2.738938957910787</v>
+        <v>2.718688840305117</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8172797408185825</v>
+        <v>1.981130591932112</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6084750155201769</v>
+        <v>2.107255941103475</v>
       </c>
       <c r="D3" t="n">
-        <v>1.021761166610222</v>
+        <v>2.048096785600916</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6912489222897964</v>
+        <v>2.221278060133789</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4067664857988457</v>
+        <v>1.830372206859595</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8119975218583808</v>
+        <v>1.980054957643558</v>
       </c>
       <c r="H3" t="n">
-        <v>1.506256811078456</v>
+        <v>2.208629862926373</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4231349117099373</v>
+        <v>1.853031476170677</v>
       </c>
       <c r="J3" t="n">
-        <v>1.40386838053149</v>
+        <v>2.660203580568928</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8708472397551937</v>
+        <v>2.209061464258442</v>
       </c>
       <c r="L3" t="n">
-        <v>1.186947981958085</v>
+        <v>2.105016105902504</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5789019122578414</v>
+        <v>0.5789019122578445</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3688173603806966</v>
+        <v>0.3688173603806959</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6845833480636238</v>
+        <v>0.6845833480636242</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3701854034321411</v>
+        <v>0.3701854034321417</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3701854034321416</v>
+        <v>0.3701854034321417</v>
       </c>
       <c r="G4" t="n">
-        <v>0.575777878633382</v>
+        <v>0.575777878633384</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9348078501230173</v>
+        <v>0.9348078501230165</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3726201463076686</v>
+        <v>0.372620146307669</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6420310520021244</v>
+        <v>0.642031052002125</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5029868746801484</v>
+        <v>0.5029868746801486</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7699010867731888</v>
+        <v>0.7699010867731884</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.529368491465444</v>
+        <v>7.529368491465479</v>
       </c>
       <c r="C5" t="n">
-        <v>3.767474817084589</v>
+        <v>3.767474817084591</v>
       </c>
       <c r="D5" t="n">
-        <v>9.771236304173193</v>
+        <v>9.771236304173216</v>
       </c>
       <c r="E5" t="n">
-        <v>3.767474913130343</v>
+        <v>3.767474913130348</v>
       </c>
       <c r="F5" t="n">
-        <v>3.767474913130343</v>
+        <v>3.767474913130348</v>
       </c>
       <c r="G5" t="n">
-        <v>7.859917809760038</v>
+        <v>7.859917809760037</v>
       </c>
       <c r="H5" t="n">
-        <v>16.33143903885966</v>
+        <v>16.33143903885964</v>
       </c>
       <c r="I5" t="n">
-        <v>3.767422404730512</v>
+        <v>3.767422404730511</v>
       </c>
       <c r="J5" t="n">
-        <v>9.426468539986146</v>
+        <v>9.426468539986159</v>
       </c>
       <c r="K5" t="n">
-        <v>6.284672104273306</v>
+        <v>6.284672104273318</v>
       </c>
       <c r="L5" t="n">
-        <v>5.513234063568357</v>
+        <v>13.18871138282453</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6087508923831393</v>
+        <v>0.6087508923831407</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3963909003335196</v>
+        <v>0.396390900333502</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7213048418870265</v>
+        <v>0.7213059152040134</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3935506228635611</v>
+        <v>0.3935506228635685</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4023425306113481</v>
+        <v>0.4023425306113482</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6980526721738542</v>
+        <v>0.6980526721738546</v>
       </c>
       <c r="H6" t="n">
-        <v>1.068606222744353</v>
+        <v>1.06860622274435</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4024691264329654</v>
+        <v>0.4948949398481409</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6774834288048043</v>
+        <v>0.7699466346340202</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5330577704669771</v>
+        <v>0.5330577704669706</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8026676189336024</v>
+        <v>0.8026676189336015</v>
       </c>
     </row>
     <row r="7">
@@ -715,25 +715,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6906997894271564</v>
+        <v>0.6906997894271558</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4844704358310645</v>
+        <v>0.4844704358310642</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7959977906679099</v>
+        <v>0.7959977906679093</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4843016067836916</v>
+        <v>0.4843016067836914</v>
       </c>
       <c r="F7" t="n">
         <v>0.4843016067836916</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6875757558026938</v>
+        <v>0.687575755802694</v>
       </c>
       <c r="H7" t="n">
-        <v>1.046605727292331</v>
+        <v>1.04660572729233</v>
       </c>
       <c r="I7" t="n">
         <v>0.4844180234769807</v>
@@ -745,7 +745,7 @@
         <v>0.6147847518494597</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8816989639425007</v>
+        <v>0.8816989639425005</v>
       </c>
     </row>
     <row r="8">
@@ -758,34 +758,34 @@
         <v>0.7441409269139324</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6692650322040856</v>
+        <v>0.6692650322057873</v>
       </c>
       <c r="D8" t="n">
-        <v>1.00799140024478</v>
+        <v>1.007991400244779</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6332939619722338</v>
+        <v>0.6332939619722314</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5421922725004463</v>
+        <v>0.5421922725004458</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8720213113269694</v>
+        <v>0.8720213113269696</v>
       </c>
       <c r="H8" t="n">
-        <v>1.231051282816649</v>
+        <v>1.231051282816647</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6688635790012569</v>
+        <v>0.6688635790012559</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9383002307196412</v>
+        <v>0.9383002307196416</v>
       </c>
       <c r="K8" t="n">
-        <v>0.665792415021499</v>
+        <v>0.6657924150214991</v>
       </c>
       <c r="L8" t="n">
-        <v>1.20298958842759</v>
+        <v>1.202989588427589</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.026853332133402</v>
+        <v>1.0268533321334</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9558296459234816</v>
+        <v>0.9558296459234806</v>
       </c>
       <c r="D9" t="n">
-        <v>1.267740457814876</v>
+        <v>1.267740457814875</v>
       </c>
       <c r="E9" t="n">
-        <v>1.111853972115889</v>
+        <v>1.111853972115888</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9558295311501762</v>
+        <v>0.9558295311501767</v>
       </c>
       <c r="G9" t="n">
-        <v>1.158934965895113</v>
+        <v>1.158934965895111</v>
       </c>
       <c r="H9" t="n">
         <v>1.517964937384745</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9557772335693995</v>
+        <v>0.9557772335693985</v>
       </c>
       <c r="J9" t="n">
-        <v>1.225188139263855</v>
+        <v>1.225188139263854</v>
       </c>
       <c r="K9" t="n">
-        <v>1.007805276723709</v>
+        <v>0.9158958867476189</v>
       </c>
       <c r="L9" t="n">
-        <v>1.353058174034919</v>
+        <v>1.353058174034917</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.647275061524633</v>
+        <v>2.578331691369865</v>
       </c>
       <c r="C2" t="n">
-        <v>1.87587811887571</v>
+        <v>2.723217706734868</v>
       </c>
       <c r="D2" t="n">
-        <v>1.709220959989722</v>
+        <v>2.581591780971618</v>
       </c>
       <c r="E2" t="n">
-        <v>1.952092833140835</v>
+        <v>2.78672118936657</v>
       </c>
       <c r="F2" t="n">
-        <v>1.686447449571343</v>
+        <v>2.565572330135129</v>
       </c>
       <c r="G2" t="n">
-        <v>1.650639128318577</v>
+        <v>2.578508735523657</v>
       </c>
       <c r="H2" t="n">
-        <v>1.655941777442235</v>
+        <v>2.578518196931482</v>
       </c>
       <c r="I2" t="n">
-        <v>1.705415056793222</v>
+        <v>2.581392425257333</v>
       </c>
       <c r="J2" t="n">
-        <v>2.228229389099236</v>
+        <v>2.937585290835076</v>
       </c>
       <c r="K2" t="n">
-        <v>1.957404764038598</v>
+        <v>2.730147411103144</v>
       </c>
       <c r="L2" t="n">
-        <v>1.72439197969406</v>
+        <v>2.582493617898285</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.07139885166265666</v>
+        <v>1.647006490459605</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1658634587213661</v>
+        <v>1.902889821489649</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0001482363735962333</v>
+        <v>1.670163458160134</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2421546498184836</v>
+        <v>2.007673725396782</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02349073375100807</v>
+        <v>1.642649009051314</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.06752947798528464</v>
+        <v>1.648261735304907</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06137304514606296</v>
+        <v>1.64991286668676</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.004552822872325626</v>
+        <v>1.668751814027777</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5335031687239125</v>
+        <v>2.285949270494085</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2592133350308409</v>
+        <v>1.936637905743854</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0172932365250339</v>
+        <v>1.676008767377105</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08120478279237679</v>
+        <v>0.08120478279237449</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1102786302578028</v>
+        <v>0.1102786302578023</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1180289945594927</v>
+        <v>0.1180289945594943</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1108639206133964</v>
+        <v>0.1108639206133957</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1108639206133966</v>
+        <v>0.1108639206133952</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08295451059608276</v>
+        <v>0.08295451059608216</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08636150861579606</v>
+        <v>0.08636150861579582</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1141084124894316</v>
+        <v>0.1141084124894318</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1759798230353766</v>
+        <v>0.1759798230353798</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1622659638269827</v>
+        <v>0.162265963826986</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1270102729236882</v>
+        <v>0.1270102729236889</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3483312367845494</v>
+        <v>-0.3483312367845479</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2100153496440155</v>
+        <v>0.2100153496440141</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2457255643541448</v>
+        <v>0.2457255643541441</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2100155141881107</v>
+        <v>0.2100155141881088</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2100155141881107</v>
+        <v>0.2100155141881088</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3175274569934982</v>
+        <v>-0.3175274569935118</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2995592229228925</v>
+        <v>-0.2995592229228963</v>
       </c>
       <c r="I5" t="n">
-        <v>0.210017034975326</v>
+        <v>0.2100170349753266</v>
       </c>
       <c r="J5" t="n">
-        <v>1.27368979358499</v>
+        <v>1.27368979358496</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9087584540552797</v>
+        <v>0.908758454055278</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4376182268273607</v>
+        <v>0.4376182268273604</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1176465208691679</v>
+        <v>0.08332325809983081</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1157909080324929</v>
+        <v>0.115790908032476</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1569385484653947</v>
+        <v>0.1569385484653934</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1150725716950624</v>
+        <v>0.1150725716950482</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1162338461396985</v>
+        <v>0.1162338461396996</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08507298590353617</v>
+        <v>0.1193962486728746</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1300144385249259</v>
+        <v>0.1300144385249296</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1162268877968846</v>
+        <v>0.1162268877968851</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2165547627245805</v>
+        <v>0.1798658792216587</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1665790072628791</v>
+        <v>0.1665790072628875</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1295428918097125</v>
+        <v>0.1295428918097128</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1393207774839751</v>
+        <v>0.1393207774839743</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1722227218497178</v>
+        <v>0.172222721849716</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1758119808521386</v>
+        <v>0.175811980852138</v>
       </c>
       <c r="E7" t="n">
         <v>0.1711469292301149</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1711469292301149</v>
+        <v>0.1711469292301153</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1410705052876806</v>
+        <v>0.1410705052876807</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1444775033073944</v>
+        <v>0.1444775033073948</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1722244071810291</v>
+        <v>0.1722244071810298</v>
       </c>
       <c r="J7" t="n">
         <v>0.2340958177269747</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2203819585185806</v>
+        <v>0.2203819585185813</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1851262676152866</v>
+        <v>0.1851262676152872</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1512838790191039</v>
+        <v>0.151283879019102</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2404328493795895</v>
+        <v>0.2404328493794221</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2567388601898822</v>
+        <v>0.2567388601898848</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2248584884515391</v>
+        <v>0.2248584884515349</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1855446445889162</v>
+        <v>0.1855446445889146</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2098774376097499</v>
+        <v>0.2098774376097486</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2132844356296831</v>
+        <v>0.2132844356296834</v>
       </c>
       <c r="I8" t="n">
-        <v>0.241031339503098</v>
+        <v>0.2410313395030986</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3029139214940336</v>
+        <v>0.3029139214940372</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2312891567119145</v>
+        <v>0.2312891567119136</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3133113344035779</v>
+        <v>0.3133113344035793</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.23168155500101</v>
+        <v>0.2316815550010083</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3115593667671088</v>
+        <v>0.3115593667671089</v>
       </c>
       <c r="D9" t="n">
-        <v>0.315481631777647</v>
+        <v>0.3154816317776473</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3657686682497905</v>
+        <v>0.3657686682497909</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3115595186465068</v>
+        <v>0.3115595186465063</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2804071502050711</v>
+        <v>0.28040715020507</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2838141482247854</v>
+        <v>0.2838141482247857</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3115610520984207</v>
+        <v>0.3115610520984208</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3734324626443654</v>
+        <v>0.3734324626443639</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3325006003701622</v>
+        <v>0.3325006003701637</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3244629125326774</v>
+        <v>0.3244629125326788</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.012949001975416</v>
+        <v>2.732138720834095</v>
       </c>
       <c r="C2" t="n">
-        <v>1.890434589269223</v>
+        <v>2.579879115583296</v>
       </c>
       <c r="D2" t="n">
-        <v>2.32631413506825</v>
+        <v>2.748630505395486</v>
       </c>
       <c r="E2" t="n">
-        <v>1.890843677354061</v>
+        <v>2.614536725433025</v>
       </c>
       <c r="F2" t="n">
-        <v>1.890843677354061</v>
+        <v>2.614503434333101</v>
       </c>
       <c r="G2" t="n">
-        <v>2.216529554116152</v>
+        <v>2.742852760949717</v>
       </c>
       <c r="H2" t="n">
-        <v>2.451291557522031</v>
+        <v>2.754931696360715</v>
       </c>
       <c r="I2" t="n">
-        <v>2.033443653673401</v>
+        <v>2.733217563363371</v>
       </c>
       <c r="J2" t="n">
-        <v>2.602490923726529</v>
+        <v>2.917759407449681</v>
       </c>
       <c r="K2" t="n">
-        <v>2.241087818605637</v>
+        <v>2.823405374087699</v>
       </c>
       <c r="L2" t="n">
-        <v>2.150631894798239</v>
+        <v>2.73929494621522</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.337296307751906</v>
+        <v>1.914155444096471</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2243311864139246</v>
+        <v>1.681554793091684</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6977311242004282</v>
+        <v>2.031493456531066</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2182701390614692</v>
+        <v>1.725843052819118</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2182701390614692</v>
+        <v>1.725809761719193</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5714561142980832</v>
+        <v>1.990557743927718</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8415722031430007</v>
+        <v>2.079556259547428</v>
       </c>
       <c r="I3" t="n">
-        <v>0.360810834827306</v>
+        <v>1.92175985179727</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9856110467004702</v>
+        <v>2.333665725875396</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5844347565995028</v>
+        <v>2.101136684283349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4956613928719871</v>
+        <v>1.966477656876335</v>
       </c>
     </row>
     <row r="4">
@@ -1390,31 +1390,31 @@
         <v>0.2717088660387958</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3059842886618993</v>
+        <v>0.305984288661899</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4579911592554217</v>
+        <v>0.4579911592554218</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2790652765223112</v>
+        <v>0.279065276522311</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2790652765223111</v>
+        <v>0.279065276522311</v>
       </c>
       <c r="G4" t="n">
-        <v>0.392323445308644</v>
+        <v>0.3923234453086445</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5322399521988312</v>
+        <v>0.5322399521988316</v>
       </c>
       <c r="I4" t="n">
         <v>0.2811908101570385</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5043073112760426</v>
+        <v>0.5043073112760428</v>
       </c>
       <c r="K4" t="n">
-        <v>0.346901533747647</v>
+        <v>0.3469015337476469</v>
       </c>
       <c r="L4" t="n">
         <v>0.353570909376294</v>
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.117174724905365</v>
+        <v>2.117174724905368</v>
       </c>
       <c r="C5" t="n">
-        <v>2.803190179074978</v>
+        <v>2.80319017907498</v>
       </c>
       <c r="D5" t="n">
         <v>5.385715332933976</v>
       </c>
       <c r="E5" t="n">
-        <v>2.289206276250162</v>
+        <v>2.289206276250158</v>
       </c>
       <c r="F5" t="n">
-        <v>2.289206276250162</v>
+        <v>2.289206276250158</v>
       </c>
       <c r="G5" t="n">
-        <v>4.334627976681535</v>
+        <v>4.334627976681533</v>
       </c>
       <c r="H5" t="n">
-        <v>7.54535501183231</v>
+        <v>7.545355011832307</v>
       </c>
       <c r="I5" t="n">
-        <v>2.289175080594552</v>
+        <v>2.289175080594545</v>
       </c>
       <c r="J5" t="n">
-        <v>6.520263865221573</v>
+        <v>6.520263865221561</v>
       </c>
       <c r="K5" t="n">
-        <v>3.411331521851606</v>
+        <v>3.411331521851603</v>
       </c>
       <c r="L5" t="n">
-        <v>4.018025470065643</v>
+        <v>4.018025470065636</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2912345392229802</v>
+        <v>0.3612541480944762</v>
       </c>
       <c r="C6" t="n">
-        <v>0.326175982751076</v>
+        <v>0.3261759827510846</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4810461636064197</v>
+        <v>0.4810473268733408</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2947089586384521</v>
+        <v>0.2947089586384519</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3005056299320089</v>
+        <v>0.3005056299320087</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4818687273643255</v>
+        <v>0.4118491184928277</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6357980130154181</v>
+        <v>0.6357980130154178</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3707360922127199</v>
+        <v>0.3007164833412229</v>
       </c>
       <c r="J6" t="n">
-        <v>0.599841287715084</v>
+        <v>0.5998412877150842</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3663284947691112</v>
+        <v>0.3663284947691113</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3735833027833538</v>
+        <v>0.3735833027833539</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3639249677058116</v>
+        <v>0.363924967705812</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4018284287688955</v>
+        <v>0.4018284287688952</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5498550120070861</v>
+        <v>0.5498550120070865</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3731975109773112</v>
+        <v>0.3731975109773109</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3731975109773112</v>
+        <v>0.3731975109773109</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4845395469756603</v>
+        <v>0.4845395469756599</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6244560538658483</v>
+        <v>0.6244560538658481</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3734069118240548</v>
+        <v>0.3734069118240549</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5965234129430595</v>
+        <v>0.5965234129430597</v>
       </c>
       <c r="K7" t="n">
         <v>0.4391176354146629</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4457870110433109</v>
+        <v>0.4457870110433106</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4055633098254287</v>
+        <v>0.4055633098254295</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5515313344433043</v>
+        <v>0.5515313344433046</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7220322508348168</v>
+        <v>0.7220322508348174</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4935287543915602</v>
+        <v>0.4935287543915604</v>
       </c>
       <c r="F8" t="n">
-        <v>0.418561031842371</v>
+        <v>0.4185610318423714</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6340057313660538</v>
+        <v>0.6340057313660551</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7739222382566924</v>
+        <v>0.7739222382566925</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5228730962144497</v>
+        <v>0.5228730962144498</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7460107884966762</v>
+        <v>0.7460107884966761</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4787530200132466</v>
+        <v>0.4787530200132474</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7078883930140445</v>
+        <v>0.7078883930140452</v>
       </c>
     </row>
     <row r="9">
@@ -1590,34 +1590,34 @@
         <v>0.5683150781329588</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6981607832255404</v>
+        <v>0.6981607832255401</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8465396510327013</v>
+        <v>0.846539651032702</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7758697648747702</v>
+        <v>0.7758697648747704</v>
       </c>
       <c r="F9" t="n">
         <v>0.6697703584073291</v>
       </c>
       <c r="G9" t="n">
-        <v>0.780871901432306</v>
+        <v>0.7808719014323059</v>
       </c>
       <c r="H9" t="n">
-        <v>0.920788408322492</v>
+        <v>0.9207884083224921</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6697392662807011</v>
+        <v>0.6697392662807012</v>
       </c>
       <c r="J9" t="n">
         <v>0.8928557673997042</v>
       </c>
       <c r="K9" t="n">
-        <v>0.682178307591337</v>
+        <v>0.6821783075913366</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7421193654999562</v>
+        <v>0.7421193654999569</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.918673162503669</v>
+        <v>2.716921612499278</v>
       </c>
       <c r="C2" t="n">
-        <v>1.810038882944796</v>
+        <v>2.563798772351846</v>
       </c>
       <c r="D2" t="n">
-        <v>2.170838572322022</v>
+        <v>2.730192577177174</v>
       </c>
       <c r="E2" t="n">
-        <v>1.790828821456111</v>
+        <v>2.596556914096581</v>
       </c>
       <c r="F2" t="n">
-        <v>1.790828821456111</v>
+        <v>2.596523587250838</v>
       </c>
       <c r="G2" t="n">
-        <v>2.077934394918358</v>
+        <v>2.725303214842976</v>
       </c>
       <c r="H2" t="n">
-        <v>2.163918706261138</v>
+        <v>2.72950479366677</v>
       </c>
       <c r="I2" t="n">
-        <v>1.936582435319951</v>
+        <v>2.717864476369286</v>
       </c>
       <c r="J2" t="n">
-        <v>2.461574826031056</v>
+        <v>2.896953885475868</v>
       </c>
       <c r="K2" t="n">
-        <v>2.068458162942938</v>
+        <v>2.799735141695066</v>
       </c>
       <c r="L2" t="n">
-        <v>1.993717974580946</v>
+        <v>2.72079289732783</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2287919303901574</v>
+        <v>1.874084681686236</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1321088460423486</v>
+        <v>1.644619152738857</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5188343875885394</v>
+        <v>1.968534166135465</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1036386446158163</v>
+        <v>1.680501563769299</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1036386446158163</v>
+        <v>1.680468236923556</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4119753385319539</v>
+        <v>1.933852614785587</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5109620214301936</v>
+        <v>1.966442185616711</v>
       </c>
       <c r="I3" t="n">
-        <v>0.249338790541932</v>
+        <v>1.880753996326838</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8240644027693366</v>
+        <v>2.27202109959656</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3866412856197821</v>
+        <v>2.026187510343072</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3151092401742807</v>
+        <v>1.902559640250751</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2056075355907849</v>
+        <v>0.2056075355907861</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2487437216041616</v>
+        <v>0.2487437216041619</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3555091865729855</v>
+        <v>0.3555091865729861</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2113487901267434</v>
+        <v>0.2113487901267435</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2113487901267434</v>
+        <v>0.2113487901267436</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2998899496358416</v>
+        <v>0.2998899496358422</v>
       </c>
       <c r="H4" t="n">
         <v>0.3513843176250855</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2136465520400435</v>
+        <v>0.2136465520400437</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4128694858529284</v>
+        <v>0.4128694858529288</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2375229086411648</v>
+        <v>0.2375229086411655</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2502324833034464</v>
+        <v>0.2502324833034467</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.10184960952881</v>
+        <v>1.101849609528812</v>
       </c>
       <c r="C5" t="n">
-        <v>1.92281864285185</v>
+        <v>1.922818642851855</v>
       </c>
       <c r="D5" t="n">
-        <v>3.615232931471907</v>
+        <v>3.61523293147191</v>
       </c>
       <c r="E5" t="n">
-        <v>1.256559764499314</v>
+        <v>1.256559764499315</v>
       </c>
       <c r="F5" t="n">
-        <v>1.256559764499314</v>
+        <v>1.256559764499315</v>
       </c>
       <c r="G5" t="n">
-        <v>2.74898717808195</v>
+        <v>2.748987178081966</v>
       </c>
       <c r="H5" t="n">
-        <v>3.975994029891739</v>
+        <v>3.975994029891742</v>
       </c>
       <c r="I5" t="n">
-        <v>1.256534299770538</v>
+        <v>1.256534299770539</v>
       </c>
       <c r="J5" t="n">
         <v>4.814308051331484</v>
       </c>
       <c r="K5" t="n">
-        <v>1.615635007428448</v>
+        <v>1.615635007428447</v>
       </c>
       <c r="L5" t="n">
-        <v>2.076663263989072</v>
+        <v>2.076663263989071</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2802593387844198</v>
+        <v>0.2802593387844196</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2664395487583278</v>
+        <v>0.2664395487582935</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4348429162221968</v>
+        <v>0.4348429162221993</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2240011085477641</v>
+        <v>0.2240011085477642</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2288776795310206</v>
+        <v>0.2288776795310205</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3153023881622551</v>
+        <v>0.3745417528294753</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4396828693513493</v>
+        <v>0.43968286935135</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2290589905664554</v>
+        <v>0.2290589905664557</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4319349025509732</v>
+        <v>0.4319349025509759</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2522264889767015</v>
+        <v>0.2522264889767</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2658614926783915</v>
+        <v>0.2658614926783929</v>
       </c>
     </row>
     <row r="7">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2854615836516428</v>
+        <v>0.2854615836516433</v>
       </c>
       <c r="C7" t="n">
-        <v>0.332924419010112</v>
+        <v>0.3329244190101123</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4350299712315477</v>
+        <v>0.4350299712315485</v>
       </c>
       <c r="E7" t="n">
         <v>0.2931631548269211</v>
@@ -1918,22 +1918,22 @@
         <v>0.2931631548269211</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3797439976966993</v>
+        <v>0.3797439976966998</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4312383656859433</v>
+        <v>0.4312383656859424</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2935006001009001</v>
+        <v>0.2935006001009003</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4927235339137833</v>
+        <v>0.4927235339137853</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3173769567020215</v>
+        <v>0.3173769567020222</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3300865313643044</v>
+        <v>0.3300865313643038</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3200028256463498</v>
+        <v>0.3200028256463495</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4606697639174655</v>
+        <v>0.4606697639162173</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5823230832320369</v>
+        <v>0.5823230832320376</v>
       </c>
       <c r="E8" t="n">
-        <v>0.395704586675811</v>
+        <v>0.3957045866758111</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3310011075743794</v>
+        <v>0.3310011075743795</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5073965993184052</v>
+        <v>0.5073965993184059</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5588909673083309</v>
+        <v>0.5588909673083331</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4211532017226073</v>
+        <v>0.4211532017226072</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6203944344835994</v>
+        <v>0.6203944344835987</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3501886073968937</v>
+        <v>0.3501886073968951</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5550017338676924</v>
+        <v>0.5550017338676919</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4332300749808077</v>
+        <v>0.4332300749808082</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5525334949380802</v>
+        <v>0.5525334949380806</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6549723470800988</v>
+        <v>0.6549723470800999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5960376045858418</v>
+        <v>0.5960376045858423</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5131350763223352</v>
+        <v>0.5131350763223355</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5993530736246672</v>
+        <v>0.5993530736246684</v>
       </c>
       <c r="H9" t="n">
         <v>0.6508474416139124</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5131096760288691</v>
+        <v>0.5131096760288697</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7123326098417508</v>
+        <v>0.7123326098417538</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4953613311331476</v>
+        <v>0.4953613311331489</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5496956072922715</v>
+        <v>0.5496956072922733</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.862681699198182</v>
+        <v>2.710640647671781</v>
       </c>
       <c r="C2" t="n">
-        <v>1.742333893256048</v>
+        <v>2.553739862219772</v>
       </c>
       <c r="D2" t="n">
-        <v>2.055175826399793</v>
+        <v>2.720771231262272</v>
       </c>
       <c r="E2" t="n">
-        <v>1.716238692461513</v>
+        <v>2.58719122723382</v>
       </c>
       <c r="F2" t="n">
-        <v>1.716238692461513</v>
+        <v>2.587157896465126</v>
       </c>
       <c r="G2" t="n">
-        <v>1.983557847762921</v>
+        <v>2.717002119291374</v>
       </c>
       <c r="H2" t="n">
-        <v>2.012799159964814</v>
+        <v>2.71821109816561</v>
       </c>
       <c r="I2" t="n">
-        <v>1.864693023111936</v>
+        <v>2.710746814679716</v>
       </c>
       <c r="J2" t="n">
-        <v>2.324836738065973</v>
+        <v>2.881851490222042</v>
       </c>
       <c r="K2" t="n">
-        <v>1.979902445853203</v>
+        <v>2.791879193920008</v>
       </c>
       <c r="L2" t="n">
-        <v>1.905596745361046</v>
+        <v>2.712842870157776</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1644847277382107</v>
+        <v>1.8529551512009</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05494358359281587</v>
+        <v>1.615022712047572</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3858928490583851</v>
+        <v>1.925069907279844</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01834473535561394</v>
+        <v>1.649720473515041</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01834473535561394</v>
+        <v>1.649687142746346</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3035173380064015</v>
+        <v>1.898315518402883</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3372357121341439</v>
+        <v>1.909322243866945</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1667487217361121</v>
+        <v>1.853683463498561</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6677625720168453</v>
+        <v>2.214672903200109</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2848517056751455</v>
+        <v>1.993054620492243</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2138444748153683</v>
+        <v>1.869189664433098</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1648270122482857</v>
+        <v>0.1648270122482856</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2026091855643073</v>
+        <v>0.202609185564307</v>
       </c>
       <c r="D4" t="n">
         <v>0.2792566142015632</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1611185802171346</v>
+        <v>0.1611185802171345</v>
       </c>
       <c r="F4" t="n">
         <v>0.1611185802171346</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2362988887080601</v>
+        <v>0.2362988887080603</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2540666778183355</v>
+        <v>0.2540666778183353</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1634668736156359</v>
+        <v>0.1634668736156358</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3275740279344936</v>
+        <v>0.3275740279344935</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1772784913405836</v>
+        <v>0.1772784913405835</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1903467183424422</v>
+        <v>0.190346718342442</v>
       </c>
     </row>
     <row r="5">
@@ -2219,34 +2219,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5322587712122083</v>
+        <v>0.5322587712122091</v>
       </c>
       <c r="C5" t="n">
-        <v>1.276386234215392</v>
+        <v>1.276386234215393</v>
       </c>
       <c r="D5" t="n">
-        <v>2.458851877558129</v>
+        <v>2.458851877558132</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5356923076614618</v>
+        <v>0.5356923076614614</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5356923076614618</v>
+        <v>0.5356923076614614</v>
       </c>
       <c r="G5" t="n">
-        <v>1.781114643813604</v>
+        <v>1.7811146438136</v>
       </c>
       <c r="H5" t="n">
-        <v>2.271747863636939</v>
+        <v>2.271747863636937</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5356699525912088</v>
+        <v>0.5356699525912094</v>
       </c>
       <c r="J5" t="n">
-        <v>3.438876572210528</v>
+        <v>3.438876572210527</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7278755981733965</v>
+        <v>0.7278755981733938</v>
       </c>
       <c r="L5" t="n">
         <v>1.070120436663175</v>
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1781462586575107</v>
+        <v>0.1781462586575106</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2193451176565615</v>
+        <v>0.2193451176565651</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2949849434370141</v>
+        <v>0.2949837465925787</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1719984743296476</v>
+        <v>0.1719984743296438</v>
       </c>
       <c r="F6" t="n">
         <v>0.1765709810324999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3043984448485127</v>
+        <v>0.3043984448485126</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3343851507296239</v>
+        <v>0.3343851507296247</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2315664297560886</v>
+        <v>0.2315664297560885</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4014313336007402</v>
+        <v>0.4014313336007401</v>
       </c>
       <c r="K6" t="n">
-        <v>0.18989992284448</v>
+        <v>0.189899922844478</v>
       </c>
       <c r="L6" t="n">
-        <v>0.203736014323156</v>
+        <v>0.2037360143231537</v>
       </c>
     </row>
     <row r="7">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2395891709118411</v>
+        <v>0.239589170911841</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2825626585655372</v>
+        <v>0.2825626585655373</v>
       </c>
       <c r="D7" t="n">
         <v>0.353685641589742</v>
@@ -2314,22 +2314,22 @@
         <v>0.2378336675038976</v>
       </c>
       <c r="G7" t="n">
-        <v>0.311061047371616</v>
+        <v>0.3110610473716157</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3288288364818908</v>
+        <v>0.328828836481891</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2382290322791917</v>
+        <v>0.2382290322791915</v>
       </c>
       <c r="J7" t="n">
-        <v>0.402336186598049</v>
+        <v>0.4023361865980492</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2520406500041391</v>
+        <v>0.252040650004139</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2651088770059979</v>
+        <v>0.2651088770059976</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2703992434979442</v>
+        <v>0.2703992434979441</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4004053568112422</v>
+        <v>0.4004053568123031</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4898613205207109</v>
+        <v>0.4898613205207111</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3322062046579319</v>
+        <v>0.3322062046579313</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2717685664780896</v>
+        <v>0.2717685664780897</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4288648735213336</v>
+        <v>0.4288648735213333</v>
       </c>
       <c r="H8" t="n">
         <v>0.4466326626320772</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3560328584289092</v>
+        <v>0.3560328584289094</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5201571093946987</v>
+        <v>0.5201571093946983</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2812347689656905</v>
+        <v>0.2812347689656903</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4737849529418533</v>
+        <v>0.4737849529418532</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3573772632016987</v>
+        <v>0.3573772632016988</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4622692729649848</v>
+        <v>0.4622692729649849</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5337254187546778</v>
+        <v>0.533725418754678</v>
       </c>
       <c r="E9" t="n">
         <v>0.4894106312056536</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4179579532374035</v>
+        <v>0.4179579532374034</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4907676617710626</v>
+        <v>0.4907676617710631</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5085354508813387</v>
+        <v>0.5085354508813392</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4179356466786396</v>
+        <v>0.4179356466786392</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5820428009974964</v>
+        <v>0.5820428009974967</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3537807844889515</v>
+        <v>0.3944159140856938</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4448154914054451</v>
+        <v>0.4448154914054454</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.857669888974999</v>
+        <v>2.696351467626154</v>
       </c>
       <c r="C2" t="n">
-        <v>1.662887812695352</v>
+        <v>2.543904712413931</v>
       </c>
       <c r="D2" t="n">
-        <v>2.085385774488753</v>
+        <v>2.708335702400564</v>
       </c>
       <c r="E2" t="n">
-        <v>1.748753364572875</v>
+        <v>2.583547873583396</v>
       </c>
       <c r="F2" t="n">
-        <v>1.748753364572875</v>
+        <v>2.583514484312825</v>
       </c>
       <c r="G2" t="n">
-        <v>2.051809296826287</v>
+        <v>2.706568639069444</v>
       </c>
       <c r="H2" t="n">
-        <v>2.286992166142077</v>
+        <v>2.718713463937498</v>
       </c>
       <c r="I2" t="n">
-        <v>1.886087508377361</v>
+        <v>2.697847373797753</v>
       </c>
       <c r="J2" t="n">
-        <v>2.533519691462541</v>
+        <v>2.890904825157736</v>
       </c>
       <c r="K2" t="n">
-        <v>2.112480830150555</v>
+        <v>2.790449178907025</v>
       </c>
       <c r="L2" t="n">
-        <v>2.056599874455842</v>
+        <v>2.706812412488986</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1589755462264479</v>
+        <v>1.836966938368599</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03778931718694173</v>
+        <v>1.58186979864411</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4208959857708394</v>
+        <v>1.922279839620896</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05432853126187655</v>
+        <v>1.658911438163719</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05432853126187644</v>
+        <v>1.658878048893149</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3822760811126097</v>
+        <v>1.909829097870338</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6528702347679654</v>
+        <v>1.998758432912308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1916167804773819</v>
+        <v>1.847595841741117</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9057164613475718</v>
+        <v>2.294479375410507</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4365175014556734</v>
+        <v>2.035843809923911</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3877822319947709</v>
+        <v>1.912185513679936</v>
       </c>
     </row>
     <row r="4">
@@ -2575,13 +2575,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1750228028066893</v>
+        <v>0.1750228028066895</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1636908799278192</v>
+        <v>0.1636908799278193</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3103902476040329</v>
+        <v>0.310390247604033</v>
       </c>
       <c r="E4" t="n">
         <v>0.1873803975326692</v>
@@ -2590,22 +2590,22 @@
         <v>0.1873803975326692</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2900357809689783</v>
+        <v>0.2900357809689784</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4301907759912294</v>
+        <v>0.4301907759912297</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1892858367871117</v>
+        <v>0.1892858367871116</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4555804375430823</v>
+        <v>0.4555804375430818</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2649827329183842</v>
+        <v>0.2649827329183843</v>
       </c>
       <c r="L4" t="n">
-        <v>0.293270859643926</v>
+        <v>0.2932708596439262</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6434410118693334</v>
+        <v>0.6434410118693328</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4960944626985883</v>
+        <v>0.4960944626985882</v>
       </c>
       <c r="D5" t="n">
-        <v>3.043691879840276</v>
+        <v>3.043691879840273</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9294475058436427</v>
+        <v>0.9294475058436402</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9294475058436427</v>
+        <v>0.9294475058436402</v>
       </c>
       <c r="G5" t="n">
-        <v>2.759720836974955</v>
+        <v>2.759720836974957</v>
       </c>
       <c r="H5" t="n">
-        <v>5.827084812092123</v>
+        <v>5.827084812092125</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9294187781525026</v>
+        <v>0.9294187781524996</v>
       </c>
       <c r="J5" t="n">
         <v>5.91898029924357</v>
       </c>
       <c r="K5" t="n">
-        <v>2.239760034886209</v>
+        <v>2.239760034886215</v>
       </c>
       <c r="L5" t="n">
-        <v>3.124525720100188</v>
+        <v>3.124525720100187</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1874121843723473</v>
+        <v>0.1874121843723472</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1753876265121948</v>
+        <v>0.1753876265121798</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3247034318940485</v>
+        <v>0.3247022374715754</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1964600732656266</v>
+        <v>0.1964600732656029</v>
       </c>
       <c r="F6" t="n">
-        <v>0.201525576999041</v>
+        <v>0.2015255769990408</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3024251625346361</v>
+        <v>0.3024251625346357</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5156439943273476</v>
+        <v>0.5156439943273478</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2016752183527696</v>
+        <v>0.2621154874137155</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5337404688381825</v>
+        <v>0.4718404984803671</v>
       </c>
       <c r="K6" t="n">
         <v>0.2776968964372155</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3063641701635074</v>
+        <v>0.3063641701635079</v>
       </c>
     </row>
     <row r="7">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2584811491274651</v>
+        <v>0.2584811491274653</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2507370893893628</v>
+        <v>0.2507370893893633</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3934963395113203</v>
+        <v>0.3934963395113206</v>
       </c>
       <c r="E7" t="n">
         <v>0.2725707135124734</v>
@@ -2710,22 +2710,22 @@
         <v>0.2725707135124734</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3734941272897541</v>
+        <v>0.3734941272897543</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5136491223120042</v>
+        <v>0.5136491223120049</v>
       </c>
       <c r="I7" t="n">
         <v>0.2727441831078875</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5390387838638573</v>
+        <v>0.5390387838638576</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3484410792391599</v>
+        <v>0.3484410792391605</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3767292059647017</v>
+        <v>0.3767292059647021</v>
       </c>
     </row>
     <row r="8">
@@ -2735,22 +2735,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2935015661358944</v>
+        <v>0.2935015661358948</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3819058940547396</v>
+        <v>0.3819058940562411</v>
       </c>
       <c r="D8" t="n">
-        <v>0.544627043314484</v>
+        <v>0.5446270433144847</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3775941508248024</v>
+        <v>0.377594150824803</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3109220052600991</v>
+        <v>0.3109220052600994</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5043918025945241</v>
+        <v>0.5043918025945243</v>
       </c>
       <c r="H8" t="n">
         <v>0.6445467976171464</v>
@@ -2759,13 +2759,13 @@
         <v>0.4036418584126579</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6699553017125449</v>
+        <v>0.6699553017125448</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3816805269583007</v>
+        <v>0.3816805269583011</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6077786946087345</v>
+        <v>0.6077786946087351</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4275645768024522</v>
+        <v>0.4275645768024521</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4986272200361258</v>
+        <v>0.4986272200361259</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6417387455272374</v>
+        <v>0.6417387455272373</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6116042177347079</v>
+        <v>0.611604217734708</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5206629559162109</v>
+        <v>0.52066295591621</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6213842579365166</v>
+        <v>0.6213842579365165</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7615392529587669</v>
+        <v>0.7615392529587673</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5206343137546499</v>
+        <v>0.5206343137546501</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7869289145106211</v>
+        <v>0.7869289145106205</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4970994984664767</v>
+        <v>0.5506703055001454</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6246193366114644</v>
+        <v>0.6246193366114648</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.809631880761028</v>
+        <v>2.668724763730048</v>
       </c>
       <c r="C2" t="n">
-        <v>1.632919615881746</v>
+        <v>2.523589258744617</v>
       </c>
       <c r="D2" t="n">
-        <v>1.821239589495943</v>
+        <v>2.669335654386002</v>
       </c>
       <c r="E2" t="n">
-        <v>1.687369481973676</v>
+        <v>2.558850747757798</v>
       </c>
       <c r="F2" t="n">
-        <v>1.687369481973676</v>
+        <v>2.558817225517998</v>
       </c>
       <c r="G2" t="n">
-        <v>1.842258094813199</v>
+        <v>2.670441816574735</v>
       </c>
       <c r="H2" t="n">
-        <v>1.834303083137102</v>
+        <v>2.669707149480625</v>
       </c>
       <c r="I2" t="n">
-        <v>1.82002709612629</v>
+        <v>2.669273127317123</v>
       </c>
       <c r="J2" t="n">
-        <v>2.189512066182915</v>
+        <v>2.846697062373321</v>
       </c>
       <c r="K2" t="n">
-        <v>1.926389959424368</v>
+        <v>2.754174780407543</v>
       </c>
       <c r="L2" t="n">
-        <v>1.847398257236651</v>
+        <v>2.670742289686927</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1035514352149267</v>
+        <v>1.802220081397163</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.07362309580510977</v>
+        <v>1.561968276122748</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1169027047896996</v>
+        <v>1.806545145903839</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01714586306366849</v>
+        <v>1.623821234294428</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01714586306366849</v>
+        <v>1.623787712054628</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1410783398748049</v>
+        <v>1.814452288503936</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1320070415232633</v>
+        <v>1.811237445953508</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1155353980785205</v>
+        <v>1.806105349411575</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5100595359768387</v>
+        <v>2.14720773753771</v>
       </c>
       <c r="K3" t="n">
-        <v>0.222570273004375</v>
+        <v>1.947581746445444</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1469843929033253</v>
+        <v>1.816534132071645</v>
       </c>
     </row>
     <row r="4">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1400994484985325</v>
+        <v>0.1400994484985328</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1360083398021307</v>
+        <v>0.1360083398021308</v>
       </c>
       <c r="D4" t="n">
-        <v>0.146999739481097</v>
+        <v>0.1469997394810972</v>
       </c>
       <c r="E4" t="n">
         <v>0.1428170332287296</v>
@@ -2986,22 +2986,22 @@
         <v>0.1428170332287296</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1591525749069662</v>
+        <v>0.1591525749069663</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1547745356012858</v>
+        <v>0.1547745356012862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1440147678201046</v>
+        <v>0.1440147678201043</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2454816983776127</v>
+        <v>0.2454816983776131</v>
       </c>
       <c r="K4" t="n">
         <v>0.1490465958850828</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1625339376320591</v>
+        <v>0.1625339376320593</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3131941850741929</v>
+        <v>0.3131941850741933</v>
       </c>
       <c r="C5" t="n">
         <v>0.2772644332010148</v>
       </c>
       <c r="D5" t="n">
-        <v>0.417155032359611</v>
+        <v>0.4171550323596112</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4057426935909302</v>
+        <v>0.4057426935909301</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4057426935909302</v>
+        <v>0.4057426935909301</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6442311540434063</v>
+        <v>0.6442311540433995</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6047268654950843</v>
+        <v>0.6047268654950828</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4057336775905358</v>
+        <v>0.4057336775905366</v>
       </c>
       <c r="J5" t="n">
-        <v>2.190592869347692</v>
+        <v>2.190592869347693</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4533073466431569</v>
+        <v>0.453307346643156</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7656513185570044</v>
+        <v>0.7656513185570049</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1468883110529031</v>
+        <v>0.1468883110529033</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1436936700887384</v>
+        <v>0.1436936700887354</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1536834695497766</v>
+        <v>0.2031087469644644</v>
       </c>
       <c r="E6" t="n">
         <v>0.1482369651291698</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1507757100641954</v>
+        <v>0.1507757100641955</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2122518811672773</v>
+        <v>0.1659414374613366</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2174883001563768</v>
+        <v>0.2174883001563769</v>
       </c>
       <c r="I6" t="n">
         <v>0.1971140740804155</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2545228800661223</v>
+        <v>0.3029719014194364</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1556357253264699</v>
+        <v>0.1556357253264697</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1694801175472094</v>
+        <v>0.1694801175472095</v>
       </c>
     </row>
     <row r="7">
@@ -3094,34 +3094,34 @@
         <v>0.2073500358250863</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2056696406139909</v>
+        <v>0.2056696406139912</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2139168392875244</v>
+        <v>0.2139168392875242</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2110189397807543</v>
+        <v>0.2110189397807544</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2110189397807543</v>
+        <v>0.2110189397807544</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2264031622335203</v>
+        <v>0.2264031622335205</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2220251229278402</v>
+        <v>0.2220251229278401</v>
       </c>
       <c r="I7" t="n">
         <v>0.2112653551466585</v>
       </c>
       <c r="J7" t="n">
-        <v>0.312732285704167</v>
+        <v>0.3127322857041671</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2162971832116369</v>
+        <v>0.2162971832116367</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2297845249586131</v>
+        <v>0.2297845249586133</v>
       </c>
     </row>
     <row r="8">
@@ -3131,16 +3131,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2310258984243546</v>
+        <v>0.2310258984243551</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3039378706789127</v>
+        <v>0.3039378706779037</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3277537282179133</v>
+        <v>0.3277537282179132</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2890824412472923</v>
+        <v>0.2890824412472918</v>
       </c>
       <c r="F8" t="n">
         <v>0.2373551688117279</v>
@@ -3149,19 +3149,19 @@
         <v>0.3244792021989104</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3201011628934994</v>
+        <v>0.3201011628934995</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3093413951120486</v>
+        <v>0.3093413951120489</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4108229473682072</v>
+        <v>0.4108229473682077</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2385910243251598</v>
+        <v>0.2385910243251597</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4055777713621139</v>
+        <v>0.4055777713621138</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3181458019348796</v>
+        <v>0.3181458019348795</v>
       </c>
       <c r="C9" t="n">
-        <v>0.372941782472088</v>
+        <v>0.3729417824720875</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3815224863704528</v>
+        <v>0.3815224863704527</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4437190350704227</v>
+        <v>0.4437190350704228</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3785464857568714</v>
+        <v>0.3785464857568716</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3936753040916181</v>
+        <v>0.3936753040916179</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3892972647859378</v>
+        <v>0.3892972647859373</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3785374970047558</v>
+        <v>0.3785374970047559</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4800044275622641</v>
+        <v>0.480004427562264</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3124554824165297</v>
+        <v>0.3508466986078541</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3970566668167108</v>
+        <v>0.3970566668167109</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.798493002408477</v>
+        <v>2.65918238864179</v>
       </c>
       <c r="C2" t="n">
-        <v>1.626108370559576</v>
+        <v>2.516551516923005</v>
       </c>
       <c r="D2" t="n">
-        <v>1.802723419503491</v>
+        <v>2.659405027091219</v>
       </c>
       <c r="E2" t="n">
-        <v>1.675177735926609</v>
+        <v>2.551693935410417</v>
       </c>
       <c r="F2" t="n">
-        <v>1.675177735926609</v>
+        <v>2.551660309154605</v>
       </c>
       <c r="G2" t="n">
-        <v>1.80499333830527</v>
+        <v>2.659524488409336</v>
       </c>
       <c r="H2" t="n">
-        <v>1.804023776868294</v>
+        <v>2.659175160290216</v>
       </c>
       <c r="I2" t="n">
-        <v>1.804708905118809</v>
+        <v>2.659510547208884</v>
       </c>
       <c r="J2" t="n">
-        <v>2.023316249869617</v>
+        <v>2.824283759730192</v>
       </c>
       <c r="K2" t="n">
-        <v>1.903418731680445</v>
+        <v>2.749259719553034</v>
       </c>
       <c r="L2" t="n">
-        <v>1.800776645564077</v>
+        <v>2.659333790657549</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08984186433728425</v>
+        <v>1.791375412062975</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.08278406680503536</v>
+        <v>1.55564660732573</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09470772032481106</v>
+        <v>1.79293667626653</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.03253679520638332</v>
+        <v>1.615709850469603</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.03253679520638332</v>
+        <v>1.61567622421379</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09731859715911893</v>
+        <v>1.79380001095959</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09627217699822822</v>
+        <v>1.793180549064799</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09701195120209792</v>
+        <v>1.793692252413304</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3189098007743111</v>
+        <v>2.072060711516901</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1942396991241649</v>
+        <v>1.939029102648854</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09246252243548377</v>
+        <v>1.792280203675552</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1286422355170546</v>
+        <v>0.1286422355170527</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1259803665249626</v>
+        <v>0.1259803665249627</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1311570392220622</v>
+        <v>0.1311570392220613</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1285452497021861</v>
+        <v>0.1285452497021863</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1285452497021861</v>
+        <v>0.1285452497021863</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1321729714578064</v>
+        <v>0.1321729714578227</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1319368169715793</v>
+        <v>0.1319368169715807</v>
       </c>
       <c r="I4" t="n">
-        <v>0.130123948538875</v>
+        <v>0.1301239485388715</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1454409547785501</v>
+        <v>0.1454409547785495</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1265530479923538</v>
+        <v>0.1265530479923536</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1299839611283952</v>
+        <v>0.1299839611283968</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2704106943178512</v>
+        <v>0.2704106943178555</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2493538995606455</v>
+        <v>0.2493538995606449</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3005252504432028</v>
+        <v>0.3005252504432027</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3206689176762605</v>
+        <v>0.3206689176762603</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3206689176762605</v>
+        <v>0.3206689176762603</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3296199230942819</v>
+        <v>0.3296199230942624</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3402647878850563</v>
+        <v>0.3402647878850544</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3206629361503497</v>
+        <v>0.3206629361503473</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5653900855831345</v>
+        <v>0.5653900855831347</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2227398533017904</v>
+        <v>0.2227398533017923</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3067876542152247</v>
+        <v>0.3067876542152243</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1738739347221751</v>
+        <v>0.1738739347221765</v>
       </c>
       <c r="C6" t="n">
-        <v>0.13078367040667</v>
+        <v>0.1307836704066637</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1352684032285355</v>
+        <v>0.1352684032285383</v>
       </c>
       <c r="E6" t="n">
-        <v>0.132254149887597</v>
+        <v>0.1322541498876076</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1340410764734632</v>
+        <v>0.1340410764734633</v>
       </c>
       <c r="G6" t="n">
-        <v>0.177404670662924</v>
+        <v>0.1774046706629271</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1846709878814866</v>
+        <v>0.1360070952518803</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1340901024965765</v>
+        <v>0.1753556477439951</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1944344875377227</v>
+        <v>0.1508532520459896</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1301705718958291</v>
+        <v>0.130170571895827</v>
       </c>
       <c r="L6" t="n">
-        <v>0.134036877852359</v>
+        <v>0.1340368778523599</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1906229166991065</v>
+        <v>0.1906229166991071</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1898188970708869</v>
+        <v>0.1898188970708866</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1928041923666511</v>
+        <v>0.1928041923666527</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1916808321567145</v>
+        <v>0.1916808321567146</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1916808321567145</v>
+        <v>0.1916808321567146</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1941536526398557</v>
+        <v>0.1941536526398556</v>
       </c>
       <c r="H7" t="n">
-        <v>0.193917498153631</v>
+        <v>0.1939174981536319</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1921046297209267</v>
+        <v>0.1921046297209266</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2074216359606016</v>
+        <v>0.2074216359606023</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1885337291744054</v>
+        <v>0.188533729174408</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1919646423104469</v>
+        <v>0.1919646423104479</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2091956852254686</v>
+        <v>0.2091956852254691</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2737054367995164</v>
+        <v>0.2737054368000653</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2905388857120152</v>
+        <v>0.2905388857120154</v>
       </c>
       <c r="E8" t="n">
-        <v>0.258046419428792</v>
+        <v>0.2580464194287915</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2126955559131647</v>
+        <v>0.2126955559131645</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2780164956745592</v>
+        <v>0.2780164956745606</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2777803411884867</v>
+        <v>0.277780341188487</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2759674727556308</v>
+        <v>0.2759674727556306</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2912973103358196</v>
+        <v>0.2912973103358228</v>
       </c>
       <c r="K8" t="n">
-        <v>0.205893701049382</v>
+        <v>0.205893701049385</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3440284276089846</v>
+        <v>0.3440284276089851</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2870114225428336</v>
+        <v>0.2870114225428326</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3361454687683461</v>
+        <v>0.3361454687683438</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3394643006332699</v>
+        <v>0.3394643006332719</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3960646285802484</v>
+        <v>0.3960646285802478</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3384371579733432</v>
+        <v>0.3384371579733424</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3404802243373144</v>
+        <v>0.3404802243373147</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3402440698510878</v>
+        <v>0.3402440698510879</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3384312014183836</v>
+        <v>0.3384312014183837</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3537482076580603</v>
+        <v>0.35374820765806</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3047520912159844</v>
+        <v>0.3059259929826915</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3382912140079041</v>
+        <v>0.3382912140079049</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.815271393145943</v>
+        <v>2.669537695904298</v>
       </c>
       <c r="C2" t="n">
-        <v>1.633235210572502</v>
+        <v>2.524600626140154</v>
       </c>
       <c r="D2" t="n">
-        <v>1.861143178330362</v>
+        <v>2.671951836849842</v>
       </c>
       <c r="E2" t="n">
-        <v>1.700913969103602</v>
+        <v>2.56610622995118</v>
       </c>
       <c r="F2" t="n">
-        <v>1.700913969103603</v>
+        <v>2.566072758248604</v>
       </c>
       <c r="G2" t="n">
-        <v>1.904883083040554</v>
+        <v>2.674253781160294</v>
       </c>
       <c r="H2" t="n">
-        <v>2.180529639087054</v>
+        <v>2.688589290427755</v>
       </c>
       <c r="I2" t="n">
-        <v>1.825847920816785</v>
+        <v>2.670095353790204</v>
       </c>
       <c r="J2" t="n">
-        <v>2.18413641938901</v>
+        <v>2.854739493578245</v>
       </c>
       <c r="K2" t="n">
-        <v>1.968807119002412</v>
+        <v>2.76210978975725</v>
       </c>
       <c r="L2" t="n">
-        <v>1.982944484945887</v>
+        <v>2.678432662390561</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1114273940341189</v>
+        <v>1.801068738391172</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.07197262587367917</v>
+        <v>1.559462189149482</v>
       </c>
       <c r="D3" t="n">
-        <v>0.164189449307875</v>
+        <v>1.818233045078902</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.00133840237004927</v>
+        <v>1.633353015954029</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.001338402370051123</v>
+        <v>1.633319544251456</v>
       </c>
       <c r="G3" t="n">
-        <v>0.21449940041856</v>
+        <v>1.834692530302356</v>
       </c>
       <c r="H3" t="n">
-        <v>0.531629195550098</v>
+        <v>1.938706018553496</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1235936687794148</v>
+        <v>1.805018122141576</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5037614371952043</v>
+        <v>2.15191779992142</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2717490239202126</v>
+        <v>1.966860737958236</v>
       </c>
       <c r="L3" t="n">
-        <v>0.304276975147841</v>
+        <v>1.864499820629071</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1535273773949929</v>
+        <v>0.153527377394995</v>
       </c>
       <c r="C4" t="n">
         <v>0.1455026109928975</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1807962099347073</v>
+        <v>0.1807962099347094</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1559868670216269</v>
+        <v>0.1559868670216271</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1559868670216269</v>
+        <v>0.1559868670216271</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2064362148770171</v>
+        <v>0.2064362148770183</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3706019781861535</v>
+        <v>0.3706019781861548</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1574153857486674</v>
+        <v>0.1574153857486677</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2464080168926474</v>
+        <v>0.2464080168926493</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1803831723370167</v>
+        <v>0.1803831723370181</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2531721347034621</v>
+        <v>0.2531721347034626</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4136350695088457</v>
+        <v>0.4136350695088464</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3106036098669464</v>
+        <v>0.3106036098669467</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8854484816432814</v>
+        <v>0.8854484816432826</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5117424848435362</v>
+        <v>0.5117424848435472</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5117424848435362</v>
+        <v>0.5117424848435473</v>
       </c>
       <c r="G5" t="n">
-        <v>1.385793093835984</v>
+        <v>1.385793093835999</v>
       </c>
       <c r="H5" t="n">
-        <v>4.807701402125002</v>
+        <v>4.807701402125008</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5117256691925095</v>
+        <v>0.5117256691925196</v>
       </c>
       <c r="J5" t="n">
-        <v>2.157114830456458</v>
+        <v>2.157114830456456</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8810988773225928</v>
+        <v>0.8810988773225937</v>
       </c>
       <c r="L5" t="n">
-        <v>2.486022026966975</v>
+        <v>2.486022026966982</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1615823968789414</v>
+        <v>0.1615823968789442</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1537597000280791</v>
+        <v>0.1537597000280754</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1886260645674192</v>
+        <v>0.1886260645674199</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1618142497890045</v>
+        <v>0.1618142497890046</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1653765647152099</v>
+        <v>0.1653765647152101</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2689203934284624</v>
+        <v>0.2144912343609672</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4454835680499876</v>
+        <v>0.4454835680499867</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2198995643001114</v>
+        <v>0.1654704052326175</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3139186059548267</v>
+        <v>0.2569214303532773</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1880724675943879</v>
+        <v>0.1880724675943885</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2618298578780887</v>
+        <v>0.2618298578780888</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2301418430300905</v>
+        <v>0.2301418430300917</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2248695029806619</v>
+        <v>0.2248695029806621</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2570584626459494</v>
+        <v>0.2570584626459488</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2338394047308196</v>
+        <v>0.2338394047308199</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2338394047308196</v>
+        <v>0.2338394047308199</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2830506805121142</v>
+        <v>0.2830506805121155</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4472164438212498</v>
+        <v>0.4472164438212524</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2340298513837643</v>
+        <v>0.2340298513837646</v>
       </c>
       <c r="J7" t="n">
-        <v>0.323022482527746</v>
+        <v>0.3230224825277474</v>
       </c>
       <c r="K7" t="n">
-        <v>0.256997637972114</v>
+        <v>0.2569976379721145</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3297866003385599</v>
+        <v>0.3297866003385604</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2600245062453863</v>
+        <v>0.2600245062453864</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3418143243772092</v>
+        <v>0.3418143243757924</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3920890913636638</v>
+        <v>0.3920890913636658</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3271278006460827</v>
+        <v>0.3271278006460832</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2667671530236573</v>
+        <v>0.2667671530236577</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3997310305199757</v>
+        <v>0.3997310305199762</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5638967938295145</v>
+        <v>0.5638967938295143</v>
       </c>
       <c r="I8" t="n">
-        <v>0.350710201391625</v>
+        <v>0.3507102013916258</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4397198906884701</v>
+        <v>0.4397198906884744</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2852679895998321</v>
+        <v>0.2852679895998313</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5371343920331841</v>
+        <v>0.5371343920331867</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3729792854711594</v>
+        <v>0.3729792854711616</v>
       </c>
       <c r="C9" t="n">
-        <v>0.43672417573546</v>
+        <v>0.4367241757354599</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4692653375776811</v>
+        <v>0.4692653375776836</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5255456504781443</v>
+        <v>0.5255456504781444</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4459012598081256</v>
+        <v>0.4459012598081255</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4949053532669114</v>
+        <v>0.4949053532669138</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6590711165760491</v>
+        <v>0.6590711165760509</v>
       </c>
       <c r="I9" t="n">
         <v>0.4458845241385628</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5348771552825438</v>
+        <v>0.5348771552825453</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4288634519114481</v>
+        <v>0.4288634519114504</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5416412730933577</v>
+        <v>0.5416412730933594</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.761789061737333</v>
+        <v>2.623976826307904</v>
       </c>
       <c r="C2" t="n">
-        <v>1.612570296546791</v>
+        <v>2.495638970720225</v>
       </c>
       <c r="D2" t="n">
-        <v>1.774749782159887</v>
+        <v>2.62465892328168</v>
       </c>
       <c r="E2" t="n">
-        <v>1.649397594105904</v>
+        <v>2.531096372349804</v>
       </c>
       <c r="F2" t="n">
-        <v>1.649397594105904</v>
+        <v>2.531062768403281</v>
       </c>
       <c r="G2" t="n">
-        <v>1.769764336322213</v>
+        <v>2.624396549169136</v>
       </c>
       <c r="H2" t="n">
-        <v>1.775008822334143</v>
+        <v>2.62437993448968</v>
       </c>
       <c r="I2" t="n">
-        <v>1.760928475197803</v>
+        <v>2.62393274197334</v>
       </c>
       <c r="J2" t="n">
-        <v>1.996352909749373</v>
+        <v>2.813001260517243</v>
       </c>
       <c r="K2" t="n">
-        <v>1.856395481460133</v>
+        <v>2.714610463502833</v>
       </c>
       <c r="L2" t="n">
-        <v>1.776788183325254</v>
+        <v>2.624806481536969</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04984718297168332</v>
+        <v>1.748976218939165</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0986500062476207</v>
+        <v>1.538685459937586</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06475469626276736</v>
+        <v>1.753814379315137</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06267010704489885</v>
+        <v>1.59538882768105</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.06267010704489903</v>
+        <v>1.595355223734528</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05902040081744741</v>
+        <v>1.751954677230468</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06512490281346497</v>
+        <v>1.753672220861714</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04887631352683098</v>
+        <v>1.748643713153985</v>
       </c>
       <c r="J3" t="n">
-        <v>0.285609109075901</v>
+        <v>2.063287558116062</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1421638906122732</v>
+        <v>1.894173893574779</v>
       </c>
       <c r="L3" t="n">
-        <v>0.067092950176452</v>
+        <v>1.75467287299967</v>
       </c>
     </row>
     <row r="4">
@@ -4159,34 +4159,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1244740123583564</v>
+        <v>0.1244740123583563</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1254650350560514</v>
+        <v>0.1254650350560515</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1321786114572534</v>
+        <v>0.1321786114572533</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1204905861108787</v>
+        <v>0.1204905861108784</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1204905861108787</v>
+        <v>0.1204905861108784</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1288846349984657</v>
+        <v>0.1288846349984648</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1323379779286731</v>
+        <v>0.1323379779286728</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1217716247888581</v>
+        <v>0.1217716247888579</v>
       </c>
       <c r="J4" t="n">
-        <v>0.129215508764381</v>
+        <v>0.1292155087643806</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1154122811744711</v>
+        <v>0.1154122811744709</v>
       </c>
       <c r="L4" t="n">
         <v>0.1333717678062634</v>
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1875106296531445</v>
+        <v>0.1875106296531441</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2332325810992497</v>
+        <v>0.2332325810992492</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3082325780361742</v>
+        <v>0.308232578036173</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1672436530379449</v>
+        <v>0.1672436530379453</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1672436530379449</v>
+        <v>0.1672436530379453</v>
       </c>
       <c r="G5" t="n">
-        <v>0.262157601139292</v>
+        <v>0.2621576011392783</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3370885757969858</v>
+        <v>0.3370885757969852</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1672364885158376</v>
+        <v>0.1672364885158375</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2656159303055388</v>
+        <v>0.2656159303055378</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02292568501072786</v>
+        <v>0.0229256850107275</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3618124852254788</v>
+        <v>0.361812485225479</v>
       </c>
     </row>
     <row r="6">
@@ -4239,34 +4239,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1280091107550954</v>
+        <v>0.1696744098142167</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1300686827367933</v>
+        <v>0.1300686827367908</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1359670673657242</v>
+        <v>0.1359682383637946</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1233410273280627</v>
+        <v>0.1233410273280624</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1252472893110389</v>
+        <v>0.1252472893110385</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1324197333952045</v>
+        <v>0.1324197333952042</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1871520484470288</v>
+        <v>0.1871520484470276</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1669720222447192</v>
+        <v>0.1669720222447185</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1785464032477549</v>
+        <v>0.1341339658613367</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1182224407780695</v>
+        <v>0.1182224407780675</v>
       </c>
       <c r="L6" t="n">
         <v>0.1370430101235675</v>
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1866763702937314</v>
+        <v>0.186676370293731</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1896805379325174</v>
+        <v>0.1896805379325171</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1940475211910544</v>
+        <v>0.1940475211910541</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1836603863923274</v>
+        <v>0.1836603863923269</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1836603863923274</v>
+        <v>0.183660386392327</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1910869929338407</v>
+        <v>0.1910869929338398</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1945403358640485</v>
+        <v>0.1945403358640475</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1839739827242334</v>
+        <v>0.1839739827242328</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1914178666997563</v>
+        <v>0.1914178666997556</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1776146391098462</v>
+        <v>0.1776146391098456</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1955741257416382</v>
+        <v>0.1955741257416377</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2055517884933432</v>
+        <v>0.205551788493343</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2747900772660233</v>
+        <v>0.274790077266022</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2930700802934297</v>
+        <v>0.2930700802934285</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2509057538172555</v>
+        <v>0.2509057538172546</v>
       </c>
       <c r="F8" t="n">
-        <v>0.204959597017445</v>
+        <v>0.2049595970174451</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2760685626734936</v>
+        <v>0.2760685626734925</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2795219056042232</v>
+        <v>0.2795219056042218</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2689555524638854</v>
+        <v>0.2689555524638846</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2764124281524777</v>
+        <v>0.2764124281524773</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1952621016093677</v>
+        <v>0.1952621016093671</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3496090984348166</v>
+        <v>0.3496090984348156</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2905110045444027</v>
+        <v>0.2905110045444019</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3457840051751475</v>
+        <v>0.3457840051751468</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3504844437677835</v>
+        <v>0.350484443767783</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4004017129336617</v>
+        <v>0.4004017129336608</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3400845880910531</v>
+        <v>0.3400845880910521</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3471904601764708</v>
+        <v>0.3471904601764692</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3506438031066785</v>
+        <v>0.3506438031066773</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3400774499668641</v>
+        <v>0.340077449966863</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3475213339423863</v>
+        <v>0.3475213339423853</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3034333422413</v>
+        <v>0.2679023138133176</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3516775929842689</v>
+        <v>0.3516775929842679</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.755689942545452</v>
+        <v>2.595464378300613</v>
       </c>
       <c r="C2" t="n">
-        <v>1.601521792816436</v>
+        <v>2.463530286422067</v>
       </c>
       <c r="D2" t="n">
-        <v>1.762449026585559</v>
+        <v>2.595820095469023</v>
       </c>
       <c r="E2" t="n">
-        <v>1.645206474292302</v>
+        <v>2.505922112338837</v>
       </c>
       <c r="F2" t="n">
-        <v>1.645206474292302</v>
+        <v>2.505888334286863</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758628358034176</v>
+        <v>2.595619021271621</v>
       </c>
       <c r="H2" t="n">
-        <v>1.763718917639655</v>
+        <v>2.595604217868233</v>
       </c>
       <c r="I2" t="n">
-        <v>1.752591612504664</v>
+        <v>2.595302148240609</v>
       </c>
       <c r="J2" t="n">
-        <v>1.971286981459949</v>
+        <v>2.77553257435705</v>
       </c>
       <c r="K2" t="n">
-        <v>1.861616473108458</v>
+        <v>2.695147488922819</v>
       </c>
       <c r="L2" t="n">
-        <v>1.765323789386076</v>
+        <v>2.596016148526422</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03628522474175202</v>
+        <v>1.741848429743404</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1172518579708849</v>
+        <v>1.525418185216179</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04405957152791506</v>
+        <v>1.744361946480439</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.07466126905765523</v>
+        <v>1.593124511841937</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0746612690576554</v>
+        <v>1.593090733789963</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03966501124471946</v>
+        <v>1.742935743904813</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04558089151126139</v>
+        <v>1.744594029166684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03277112332635923</v>
+        <v>1.740673805770705</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2517644077716089</v>
+        <v>2.038843967746542</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1399939048163874</v>
+        <v>1.902121514915916</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04736008544651001</v>
+        <v>1.745520865859977</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1129621639317357</v>
+        <v>0.1129621639317344</v>
       </c>
       <c r="C4" t="n">
         <v>0.114325784635968</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1169801529868931</v>
+        <v>0.1169801529868915</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1085480537880132</v>
+        <v>0.108548053788013</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1085480537880132</v>
+        <v>0.108548053788013</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1144088943564476</v>
+        <v>0.1144088943564471</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1177395288265601</v>
+        <v>0.1177395288265596</v>
       </c>
       <c r="I4" t="n">
         <v>0.1091228778900011</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1124957391994089</v>
+        <v>0.1124957391994071</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1041848311448715</v>
+        <v>0.1041848311448697</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1186694774507095</v>
+        <v>0.118669477450708</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1759383609957696</v>
+        <v>0.1759383609957674</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2148917187865159</v>
+        <v>0.2148917187865158</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2339156602958863</v>
+        <v>0.233915660295884</v>
       </c>
       <c r="E5" t="n">
-        <v>0.132832321450441</v>
+        <v>0.1328323214504421</v>
       </c>
       <c r="F5" t="n">
-        <v>0.132832321450441</v>
+        <v>0.1328323214504421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1980439786905366</v>
+        <v>0.1980439786905346</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2656792801083414</v>
+        <v>0.2656792801083386</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1328256200137025</v>
+        <v>0.1328256200137016</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1607262630706832</v>
+        <v>0.1607262630706824</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01610444955151241</v>
+        <v>0.01610444955151166</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2871259101135146</v>
+        <v>0.2871259101135135</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1134052381138815</v>
+        <v>0.14859322302457</v>
       </c>
       <c r="C6" t="n">
         <v>0.1152804550181281</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1174497001271539</v>
+        <v>0.1174485903465446</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1084231193739386</v>
+        <v>0.1084231193739385</v>
       </c>
       <c r="F6" t="n">
         <v>0.1095404142890824</v>
       </c>
       <c r="G6" t="n">
-        <v>0.150039953449285</v>
+        <v>0.1148519685385911</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1610596694790197</v>
+        <v>0.1610596694790183</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1447539369828388</v>
+        <v>0.1095659520721471</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1137951930997304</v>
+        <v>0.1515213000345344</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1038512755750543</v>
+        <v>0.1038512755750512</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1192607688333665</v>
+        <v>0.1192607688333735</v>
       </c>
     </row>
     <row r="7">
@@ -4675,13 +4675,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1700762607627902</v>
+        <v>0.1700762607627879</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1727092706700979</v>
+        <v>0.1727092706700977</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1737605885906811</v>
+        <v>0.1737605885906801</v>
       </c>
       <c r="E7" t="n">
         <v>0.1660827134473562</v>
@@ -4690,22 +4690,22 @@
         <v>0.1660827134473562</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1715229911875021</v>
+        <v>0.1715229911875009</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1748536256576146</v>
+        <v>0.1748536256576125</v>
       </c>
       <c r="I7" t="n">
         <v>0.166236974721056</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1696098360304634</v>
+        <v>0.1696098360304623</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1612989279759263</v>
+        <v>0.1612989279759236</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1757835742817642</v>
+        <v>0.1757835742817626</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1828942473684822</v>
+        <v>0.1828942473684801</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2413006242602119</v>
+        <v>0.2413006242601293</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2539138710113842</v>
+        <v>0.2539138710113827</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2195362906674807</v>
+        <v>0.2195362906674805</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1809237754539005</v>
+        <v>0.1809237754539006</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2398354682662817</v>
+        <v>0.2398354682662806</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2431661027368972</v>
+        <v>0.243166102736896</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2345494517998351</v>
+        <v>0.2345494517998349</v>
       </c>
       <c r="J8" t="n">
-        <v>0.23793321939399</v>
+        <v>0.2379332193939876</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1730860759276764</v>
+        <v>0.1730860759276742</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3020646870598032</v>
+        <v>0.3020646870598013</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2632651780267204</v>
+        <v>0.2632651780267195</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3122793495400631</v>
+        <v>0.3122793495400629</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3136643303664527</v>
+        <v>0.3136643303664507</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3593366014807444</v>
+        <v>0.3593366014807443</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3058137293331533</v>
+        <v>0.3058137293331527</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3110930700574678</v>
+        <v>0.3110930700574659</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3144237045275799</v>
+        <v>0.3144237045275786</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3058070535910209</v>
+        <v>0.3058070535910206</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3091799149004293</v>
+        <v>0.3091799149004276</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2729052914377921</v>
+        <v>0.2729052914377898</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3153536531517295</v>
+        <v>0.3153536531517276</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.286205568760193</v>
+        <v>2.686934287548747</v>
       </c>
       <c r="C2" t="n">
-        <v>2.146985490116145</v>
+        <v>2.820058017619532</v>
       </c>
       <c r="D2" t="n">
-        <v>2.560851088530468</v>
+        <v>2.701388335764315</v>
       </c>
       <c r="E2" t="n">
-        <v>2.229260655294425</v>
+        <v>2.88904484284104</v>
       </c>
       <c r="F2" t="n">
-        <v>1.946223147069402</v>
+        <v>2.653419851931613</v>
       </c>
       <c r="G2" t="n">
-        <v>2.380092676391155</v>
+        <v>2.691875379548547</v>
       </c>
       <c r="H2" t="n">
-        <v>2.918958293759395</v>
+        <v>2.720065743901251</v>
       </c>
       <c r="I2" t="n">
-        <v>1.966283911648517</v>
+        <v>2.67009510891313</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98382705535547</v>
+        <v>3.081275331464451</v>
       </c>
       <c r="K2" t="n">
-        <v>2.385944456013952</v>
+        <v>2.843723727670013</v>
       </c>
       <c r="L2" t="n">
-        <v>2.703639414112748</v>
+        <v>2.70905385912181</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6659853943713567</v>
+        <v>1.9276678363416</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4786038120948014</v>
+        <v>2.055931996598146</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9818846347551972</v>
+        <v>2.030773507954851</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5609792899897252</v>
+        <v>2.169348997388225</v>
       </c>
       <c r="F3" t="n">
-        <v>0.277941781764702</v>
+        <v>1.780428422930139</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7739750168027139</v>
+        <v>1.963363919298775</v>
       </c>
       <c r="H3" t="n">
-        <v>1.393864001640239</v>
+        <v>2.167466582293684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.29781256633244</v>
+        <v>1.807944711884148</v>
       </c>
       <c r="J3" t="n">
-        <v>1.399502455272448</v>
+        <v>2.648530840106591</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7515134729868089</v>
+        <v>2.159538195585017</v>
       </c>
       <c r="L3" t="n">
-        <v>1.146105063831632</v>
+        <v>2.087456643786711</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4916564766964479</v>
+        <v>0.4916564766964483</v>
       </c>
       <c r="C4" t="n">
-        <v>0.294744584969775</v>
+        <v>0.2947445849697746</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6549216004820025</v>
+        <v>0.6549216004820012</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2959416176569436</v>
+        <v>0.2959416176569434</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2959416176569436</v>
+        <v>0.2959416176569434</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5470483593641615</v>
+        <v>0.5470483593641623</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8676864313792821</v>
+        <v>0.8676864313792811</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2986375842659498</v>
+        <v>0.2986375842659497</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6337162787028882</v>
+        <v>0.6337162787028884</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4354159874286191</v>
+        <v>0.435415987428618</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7397389342536576</v>
+        <v>0.7397389342536564</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.728838108406053</v>
+        <v>5.728838108406091</v>
       </c>
       <c r="C5" t="n">
-        <v>2.384922802844446</v>
+        <v>2.384922802844441</v>
       </c>
       <c r="D5" t="n">
-        <v>8.786034687389416</v>
+        <v>8.786034687389414</v>
       </c>
       <c r="E5" t="n">
-        <v>2.384922894982266</v>
+        <v>2.38492289498226</v>
       </c>
       <c r="F5" t="n">
-        <v>2.384922894982266</v>
+        <v>2.38492289498226</v>
       </c>
       <c r="G5" t="n">
-        <v>7.023552200776308</v>
+        <v>7.023552200776319</v>
       </c>
       <c r="H5" t="n">
         <v>14.1527850301928</v>
       </c>
       <c r="I5" t="n">
-        <v>2.384860095512415</v>
+        <v>2.384860095512413</v>
       </c>
       <c r="J5" t="n">
-        <v>8.93235613492911</v>
+        <v>8.932356134929107</v>
       </c>
       <c r="K5" t="n">
-        <v>4.875393762942648</v>
+        <v>4.875393762942671</v>
       </c>
       <c r="L5" t="n">
-        <v>5.314573710786076</v>
+        <v>5.31457371078608</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6002027132421526</v>
+        <v>0.5170055327739945</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3169087909580069</v>
+        <v>0.316908790958003</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6865588290356067</v>
+        <v>0.6865597953073743</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3144623158867504</v>
+        <v>0.3144623158867499</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3234367595999895</v>
+        <v>0.3234367595999892</v>
       </c>
       <c r="G6" t="n">
-        <v>0.655594595909866</v>
+        <v>0.5723974154417073</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9865198639182898</v>
+        <v>0.9865198639182891</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4071838208116556</v>
+        <v>0.4071838208116552</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7472650150277235</v>
+        <v>0.6641570341248252</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4599266719199539</v>
+        <v>0.4599266719199459</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7677585618056805</v>
+        <v>0.7677585618056791</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5914483547037377</v>
+        <v>0.5914483547037391</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3984921696052694</v>
+        <v>0.3984921696052691</v>
       </c>
       <c r="D7" t="n">
         <v>0.7543548608662141</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3983653552295679</v>
+        <v>0.3983653552295674</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3983653552295679</v>
+        <v>0.3983653552295674</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6468402373714524</v>
+        <v>0.6468402373714527</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9674783093865726</v>
+        <v>0.9674783093865733</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3984294622732414</v>
+        <v>0.3984294622732415</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7335081567101788</v>
+        <v>0.7335081567101804</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5352078654359091</v>
+        <v>0.5352078654359101</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8395308122609483</v>
+        <v>0.8395308122609484</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6382075083552805</v>
+        <v>0.6382075083552815</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5618920590009975</v>
+        <v>0.561892059002426</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9418710674008745</v>
+        <v>0.9418710674008735</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5299526240438875</v>
+        <v>0.5299526240438871</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4490757231180476</v>
+        <v>0.4490757231180468</v>
       </c>
       <c r="G8" t="n">
-        <v>0.809885205190117</v>
+        <v>0.8098852051901169</v>
       </c>
       <c r="H8" t="n">
-        <v>1.130523277205337</v>
+        <v>1.130523277205336</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5614744300919057</v>
+        <v>0.5614744300919056</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8965759779416538</v>
+        <v>0.8965759779416537</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5798069503947297</v>
+        <v>0.579806950394729</v>
       </c>
       <c r="L8" t="n">
-        <v>1.124046036563536</v>
+        <v>1.124046036563535</v>
       </c>
     </row>
     <row r="9">
@@ -5151,34 +5151,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8557071490601952</v>
+        <v>0.8557071490601948</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7735153749328123</v>
+        <v>0.7735153749328118</v>
       </c>
       <c r="D9" t="n">
         <v>1.129736716936857</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9013350445950563</v>
+        <v>0.9013350445950572</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7735152797977252</v>
+        <v>0.7735152797977251</v>
       </c>
       <c r="G9" t="n">
         <v>1.021863442698996</v>
       </c>
       <c r="H9" t="n">
-        <v>1.342501514714117</v>
+        <v>1.342501514714119</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7734526676007852</v>
+        <v>0.7734526676007849</v>
       </c>
       <c r="J9" t="n">
-        <v>1.108531362037724</v>
+        <v>1.108531362037725</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8460537499715551</v>
+        <v>0.8460537499715547</v>
       </c>
       <c r="L9" t="n">
         <v>1.214554017588491</v>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.176117687405591</v>
+        <v>2.677540858698026</v>
       </c>
       <c r="C2" t="n">
-        <v>2.216634081724805</v>
+        <v>2.819396791007936</v>
       </c>
       <c r="D2" t="n">
-        <v>2.517820338492498</v>
+        <v>2.695523990548602</v>
       </c>
       <c r="E2" t="n">
-        <v>2.297588067143454</v>
+        <v>2.887268655880266</v>
       </c>
       <c r="F2" t="n">
-        <v>2.018279326913102</v>
+        <v>2.654747326578678</v>
       </c>
       <c r="G2" t="n">
-        <v>2.364475380583007</v>
+        <v>2.687453749981444</v>
       </c>
       <c r="H2" t="n">
-        <v>2.78801144245662</v>
+        <v>2.709515283955625</v>
       </c>
       <c r="I2" t="n">
-        <v>2.036872675601885</v>
+        <v>2.670210905841658</v>
       </c>
       <c r="J2" t="n">
-        <v>2.866601919110268</v>
+        <v>3.065216687523667</v>
       </c>
       <c r="K2" t="n">
-        <v>2.387639610123838</v>
+        <v>2.837975227838602</v>
       </c>
       <c r="L2" t="n">
-        <v>2.646204453579052</v>
+        <v>2.702404225394152</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5386684303834464</v>
+        <v>1.884687346343044</v>
       </c>
       <c r="C3" t="n">
-        <v>0.558168263194051</v>
+        <v>2.078975347896578</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9316972626243166</v>
+        <v>2.012484857946837</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6392181778709253</v>
+        <v>2.19058547580215</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3599094376405726</v>
+        <v>1.806788096225939</v>
       </c>
       <c r="G3" t="n">
-        <v>0.755318795716069</v>
+        <v>1.955416864035832</v>
       </c>
       <c r="H3" t="n">
-        <v>1.242548140158596</v>
+        <v>2.11617221818801</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3783360689928885</v>
+        <v>1.83230383694076</v>
       </c>
       <c r="J3" t="n">
-        <v>1.265187779257378</v>
+        <v>2.594502932221465</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7532012755414695</v>
+        <v>2.154860181778954</v>
       </c>
       <c r="L3" t="n">
-        <v>1.079354358996122</v>
+        <v>2.063877953950011</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4219466610678292</v>
+        <v>0.4219466610678299</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3324338785751925</v>
+        <v>0.3324338785751926</v>
       </c>
       <c r="D4" t="n">
         <v>0.6250744079694351</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3334988150736706</v>
+        <v>0.3334988150736709</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3334988150736706</v>
+        <v>0.3334988150736707</v>
       </c>
       <c r="G4" t="n">
-        <v>0.533527026021458</v>
+        <v>0.5335270260214586</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7856031488249076</v>
+        <v>0.7856031488249061</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3365401903084095</v>
+        <v>0.3365401903084098</v>
       </c>
       <c r="J4" t="n">
-        <v>0.564558715878003</v>
+        <v>0.5645587158780025</v>
       </c>
       <c r="K4" t="n">
-        <v>0.433862643857447</v>
+        <v>0.4338626438574468</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7013377485805979</v>
+        <v>0.7013377485805973</v>
       </c>
     </row>
     <row r="5">
@@ -5390,34 +5390,34 @@
         <v>4.38987792213342</v>
       </c>
       <c r="C5" t="n">
-        <v>2.887050333414729</v>
+        <v>2.887050333414725</v>
       </c>
       <c r="D5" t="n">
-        <v>7.698023567541498</v>
+        <v>7.698023567541529</v>
       </c>
       <c r="E5" t="n">
-        <v>2.887050452145108</v>
+        <v>2.887050452145104</v>
       </c>
       <c r="F5" t="n">
-        <v>2.887050452145108</v>
+        <v>2.887050452145103</v>
       </c>
       <c r="G5" t="n">
-        <v>6.359881448102306</v>
+        <v>6.35988144810227</v>
       </c>
       <c r="H5" t="n">
-        <v>11.82118444979243</v>
+        <v>11.82118444979241</v>
       </c>
       <c r="I5" t="n">
-        <v>2.886999433696303</v>
+        <v>2.886999433696298</v>
       </c>
       <c r="J5" t="n">
-        <v>7.231921036045617</v>
+        <v>7.231921036045616</v>
       </c>
       <c r="K5" t="n">
-        <v>4.371977988238935</v>
+        <v>4.371977988238946</v>
       </c>
       <c r="L5" t="n">
-        <v>5.58729182586978</v>
+        <v>5.587291825869785</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.520474000036185</v>
+        <v>0.446034477052856</v>
       </c>
       <c r="C6" t="n">
-        <v>0.355297759168299</v>
+        <v>0.355297759168289</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6542050874515988</v>
+        <v>0.654205087451611</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3531437576738697</v>
+        <v>0.3531437576738701</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3603633798062493</v>
+        <v>0.3603633798062495</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6320543649898138</v>
+        <v>0.5576148420064871</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8932470425555816</v>
+        <v>0.893247042555579</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4350675292767657</v>
+        <v>0.435067529276765</v>
       </c>
       <c r="J6" t="n">
-        <v>0.667626661140962</v>
+        <v>0.592960921276532</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4572936894565077</v>
+        <v>0.4572936894565061</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7277390964332232</v>
+        <v>0.7277390964332219</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5109763248700082</v>
+        <v>0.5109763248700067</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4256207538290188</v>
+        <v>0.4256207538290192</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7137702256939351</v>
+        <v>0.7137702256939359</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4251998930850301</v>
+        <v>0.4251998930850299</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4251998930850301</v>
+        <v>0.4251998930850299</v>
       </c>
       <c r="G7" t="n">
         <v>0.6225566898236359</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8746328126270836</v>
+        <v>0.8746328126270811</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4255698541105863</v>
+        <v>0.4255698541105862</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6535883796801798</v>
+        <v>0.6535883796801799</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5228923076596249</v>
+        <v>0.5228923076596242</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7903674123827755</v>
+        <v>0.7903674123827746</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5512509774683519</v>
+        <v>0.5512509774683513</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5682660202380376</v>
+        <v>0.5682660202380381</v>
       </c>
       <c r="D8" t="n">
-        <v>0.877928768976424</v>
+        <v>0.8779287689764238</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5401834675545377</v>
+        <v>0.5401834675545383</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4690872817672976</v>
+        <v>0.4690872817672977</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7651623798065252</v>
+        <v>0.7651623798065263</v>
       </c>
       <c r="H8" t="n">
-        <v>1.017238502610157</v>
+        <v>1.017238502610156</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5681755440934767</v>
+        <v>0.5681755440934765</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7962141805848841</v>
+        <v>0.796214180584885</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5612661087065705</v>
+        <v>0.561266108706569</v>
       </c>
       <c r="L8" t="n">
-        <v>1.039866427641617</v>
+        <v>1.039866427641616</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7319606823625557</v>
+        <v>0.7319606823625547</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7411212066714414</v>
+        <v>0.7411212066714417</v>
       </c>
       <c r="D9" t="n">
-        <v>1.029604563601114</v>
+        <v>1.029604563601112</v>
       </c>
       <c r="E9" t="n">
-        <v>0.850190741793735</v>
+        <v>0.850190741793734</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7411211743454956</v>
+        <v>0.7411211743454943</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9380571426660556</v>
+        <v>0.9380571426660567</v>
       </c>
       <c r="H9" t="n">
-        <v>1.190133265469505</v>
+        <v>1.190133265469504</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7410703069530097</v>
+        <v>0.7410703069530085</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9690888325226023</v>
+        <v>0.9690888325226015</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7193801152885962</v>
+        <v>0.7836297800607964</v>
       </c>
       <c r="L9" t="n">
-        <v>1.105867865225198</v>
+        <v>1.105867865225196</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.129220234444134</v>
+        <v>2.672548747768353</v>
       </c>
       <c r="C2" t="n">
-        <v>2.372662684939566</v>
+        <v>2.827513501778669</v>
       </c>
       <c r="D2" t="n">
-        <v>2.434617882316285</v>
+        <v>2.68862121940728</v>
       </c>
       <c r="E2" t="n">
-        <v>2.452523286716999</v>
+        <v>2.894454818326931</v>
       </c>
       <c r="F2" t="n">
-        <v>2.176149125744001</v>
+        <v>2.664376071892174</v>
       </c>
       <c r="G2" t="n">
-        <v>2.322245248700793</v>
+        <v>2.682707270890122</v>
       </c>
       <c r="H2" t="n">
-        <v>2.64066413192152</v>
+        <v>2.69918973442744</v>
       </c>
       <c r="I2" t="n">
-        <v>2.18978463625973</v>
+        <v>2.675735792770583</v>
       </c>
       <c r="J2" t="n">
-        <v>2.854132211096895</v>
+        <v>3.059790373589618</v>
       </c>
       <c r="K2" t="n">
-        <v>2.339872031736644</v>
+        <v>2.830913448587098</v>
       </c>
       <c r="L2" t="n">
-        <v>2.573818182095583</v>
+        <v>2.696057071397113</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4839184970474865</v>
+        <v>1.866038690783476</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7363661010091156</v>
+        <v>2.139324185681286</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8351890550326287</v>
+        <v>1.980054581855267</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8163177874222258</v>
+        <v>2.249466053120692</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5399436264492301</v>
+        <v>1.869700650137066</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7059372484538927</v>
+        <v>1.938457941471321</v>
       </c>
       <c r="H3" t="n">
-        <v>1.072254314336443</v>
+        <v>2.058928911812995</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5534853713464835</v>
+        <v>1.888441991925283</v>
       </c>
       <c r="J3" t="n">
-        <v>1.250469560146778</v>
+        <v>2.586091474321867</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6978403912396988</v>
+        <v>2.133177685119538</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9952883103222209</v>
+        <v>2.035382309228057</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3970507846149912</v>
+        <v>0.3970507846149934</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4269166526332355</v>
+        <v>0.426916652633236</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5785967454789079</v>
+        <v>0.5785967454789107</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4279569152472142</v>
+        <v>0.4279569152472154</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4279569152472141</v>
+        <v>0.4279569152472151</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5114754334070679</v>
+        <v>0.5114754334070675</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7010181582157602</v>
+        <v>0.7010181582157634</v>
       </c>
       <c r="I4" t="n">
         <v>0.4309110758789668</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5618410266077278</v>
+        <v>0.5618410266077306</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4099924724719849</v>
+        <v>0.4099924724719875</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6612949274582831</v>
+        <v>0.6612949274582871</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.820312444557175</v>
+        <v>3.820312444557182</v>
       </c>
       <c r="C5" t="n">
-        <v>4.277255714809649</v>
+        <v>4.277255714809653</v>
       </c>
       <c r="D5" t="n">
-        <v>6.671531724637199</v>
+        <v>6.67153172463721</v>
       </c>
       <c r="E5" t="n">
-        <v>4.27725586027762</v>
+        <v>4.27725586027763</v>
       </c>
       <c r="F5" t="n">
-        <v>4.27725586027762</v>
+        <v>4.27725586027763</v>
       </c>
       <c r="G5" t="n">
-        <v>5.8066263351438</v>
+        <v>5.806626335143803</v>
       </c>
       <c r="H5" t="n">
         <v>9.765315241160584</v>
       </c>
       <c r="I5" t="n">
-        <v>4.277231438423374</v>
+        <v>4.277231438423386</v>
       </c>
       <c r="J5" t="n">
-        <v>7.148757153270938</v>
+        <v>7.148757153270935</v>
       </c>
       <c r="K5" t="n">
-        <v>3.760608526331237</v>
+        <v>3.760608526331235</v>
       </c>
       <c r="L5" t="n">
-        <v>9.668283665091383</v>
+        <v>4.00228524828069</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4225407264533841</v>
+        <v>0.4225407264533855</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4544236407453509</v>
+        <v>0.4544236407453739</v>
       </c>
       <c r="D6" t="n">
-        <v>0.678545395719057</v>
+        <v>0.6079309347244696</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4522293915342281</v>
+        <v>0.4522293915342204</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4570325559594766</v>
+        <v>0.4570325559594756</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5369653752454594</v>
+        <v>0.6081882909468859</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8068171500765636</v>
+        <v>0.8068171500765629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5276239334187881</v>
+        <v>0.4564010177173597</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5918736899561408</v>
+        <v>0.6632478143737033</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4343344329980623</v>
+        <v>0.4343344329980637</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6891055658541287</v>
+        <v>0.6891055658541316</v>
       </c>
     </row>
     <row r="7">
@@ -5863,34 +5863,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4841028675641496</v>
+        <v>0.4841028675641504</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5179874352143826</v>
+        <v>0.5179874352143817</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6653151134927577</v>
+        <v>0.6653151134927544</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5172556046463984</v>
+        <v>0.5172556046463987</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5172556046463984</v>
+        <v>0.5172556046463987</v>
       </c>
       <c r="G7" t="n">
-        <v>0.598527516356223</v>
+        <v>0.5985275163562236</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7880702411649173</v>
+        <v>0.7880702411649186</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5179631588281249</v>
+        <v>0.5179631588281248</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6488931095568838</v>
+        <v>0.6488931095568851</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4970445554211428</v>
+        <v>0.497044555421143</v>
       </c>
       <c r="L7" t="n">
         <v>0.7483470104074414</v>
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5214805868969439</v>
+        <v>0.5214805868969483</v>
       </c>
       <c r="C8" t="n">
-        <v>0.653482559027058</v>
+        <v>0.6534825590270589</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8218017063805086</v>
+        <v>0.8218017063805098</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6265133851027103</v>
+        <v>0.6265133851027097</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5582460919360651</v>
+        <v>0.5582460919360646</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7342814462012456</v>
+        <v>0.7342814462012486</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9238241710101545</v>
+        <v>0.9238241710101559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6537170886731476</v>
+        <v>0.6537170886731474</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7846663730972062</v>
+        <v>0.7846663730972091</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5325948861410981</v>
+        <v>0.5325948861410987</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9868631181728958</v>
+        <v>0.9868631181729003</v>
       </c>
     </row>
     <row r="9">
@@ -5943,16 +5943,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6849126401768055</v>
+        <v>0.6849126401768031</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8068137322802468</v>
+        <v>0.8068137322802473</v>
       </c>
       <c r="D9" t="n">
-        <v>0.954475160646411</v>
+        <v>0.9544751606464131</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9083829598066018</v>
+        <v>0.9083829598066009</v>
       </c>
       <c r="F9" t="n">
         <v>0.8068137555994548</v>
@@ -5961,19 +5961,19 @@
         <v>0.8873538134220893</v>
       </c>
       <c r="H9" t="n">
-        <v>1.076896538230782</v>
+        <v>1.076896538230787</v>
       </c>
       <c r="I9" t="n">
         <v>0.8067894558939899</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9377194066227513</v>
+        <v>0.9377194066227555</v>
       </c>
       <c r="K9" t="n">
-        <v>0.734873747336256</v>
+        <v>0.7348737473362572</v>
       </c>
       <c r="L9" t="n">
-        <v>1.037173307473307</v>
+        <v>1.037173307473312</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.810443934644813</v>
+        <v>2.612336578531737</v>
       </c>
       <c r="C2" t="n">
-        <v>1.970826601504824</v>
+        <v>2.756445728322899</v>
       </c>
       <c r="D2" t="n">
-        <v>1.952095002463761</v>
+        <v>2.619791392889366</v>
       </c>
       <c r="E2" t="n">
-        <v>2.049613937651615</v>
+        <v>2.82224259191282</v>
       </c>
       <c r="F2" t="n">
-        <v>1.77692210767934</v>
+        <v>2.595228696526114</v>
       </c>
       <c r="G2" t="n">
-        <v>1.905967710444639</v>
+        <v>2.617363805126579</v>
       </c>
       <c r="H2" t="n">
-        <v>2.080378690190619</v>
+        <v>2.626298110720708</v>
       </c>
       <c r="I2" t="n">
-        <v>1.796574335944758</v>
+        <v>2.61160688182765</v>
       </c>
       <c r="J2" t="n">
-        <v>2.776473031886667</v>
+        <v>3.004491546813064</v>
       </c>
       <c r="K2" t="n">
-        <v>2.060934040796444</v>
+        <v>2.764442878837718</v>
       </c>
       <c r="L2" t="n">
-        <v>1.961885794205762</v>
+        <v>2.620348954304859</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1170493840227557</v>
+        <v>1.722541234510321</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2752613703126192</v>
+        <v>1.956610200816029</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2799774549448457</v>
+        <v>1.775252061936073</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3541367383823411</v>
+        <v>2.065032871177562</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08144490841006458</v>
+        <v>1.690326701835006</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2269215138830993</v>
+        <v>1.758255749172082</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4275958326705818</v>
+        <v>1.823556454680994</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1009643515038052</v>
+        <v>1.717351100470953</v>
       </c>
       <c r="J3" t="n">
-        <v>1.162433062578894</v>
+        <v>2.52262153675077</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3784030712579093</v>
+        <v>1.994297324970364</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2912341997280409</v>
+        <v>1.779933577545251</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1888863925186443</v>
+        <v>0.1888863925186441</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1731228161019223</v>
+        <v>0.1731228161019222</v>
       </c>
       <c r="D4" t="n">
         <v>0.2730919500721075</v>
       </c>
       <c r="E4" t="n">
+        <v>0.1741668713375778</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.1741668713375777</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.1741668713375778</v>
-      </c>
       <c r="G4" t="n">
-        <v>0.2453621114530172</v>
+        <v>0.2453621114530156</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3493182385888094</v>
+        <v>0.3493182385888069</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1785799174251631</v>
+        <v>0.1785799174251629</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5029389276242135</v>
+        <v>0.5029389276242126</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2318799427724521</v>
+        <v>0.2318799427724505</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2788897714444103</v>
+        <v>0.2788897714444077</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.119962118866142</v>
+        <v>1.119962118866147</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9719453171276442</v>
+        <v>0.9719453171276436</v>
       </c>
       <c r="D5" t="n">
         <v>2.437065282605707</v>
       </c>
       <c r="E5" t="n">
-        <v>0.971945492996898</v>
+        <v>0.9719454929968976</v>
       </c>
       <c r="F5" t="n">
         <v>0.971945492996898</v>
       </c>
       <c r="G5" t="n">
-        <v>2.101541144753115</v>
+        <v>2.101541144753114</v>
       </c>
       <c r="H5" t="n">
         <v>4.091019723123632</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9719244705794469</v>
+        <v>0.9719244705794484</v>
       </c>
       <c r="J5" t="n">
-        <v>7.178677465882924</v>
+        <v>7.178677465882923</v>
       </c>
       <c r="K5" t="n">
-        <v>1.818430771329816</v>
+        <v>1.818430771329818</v>
       </c>
       <c r="L5" t="n">
-        <v>3.088316392894016</v>
+        <v>3.088316392894015</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2009013821731444</v>
+        <v>0.251803083404888</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1876818879055167</v>
+        <v>0.1876818879055172</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3394042173478161</v>
+        <v>0.3394042173478136</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1861722399222042</v>
+        <v>0.1861722399222044</v>
       </c>
       <c r="F6" t="n">
         <v>0.1904058967205206</v>
       </c>
       <c r="G6" t="n">
-        <v>0.257377101107516</v>
+        <v>0.3082788023392597</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4233576425058969</v>
+        <v>0.3625686094613783</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1905949070796631</v>
+        <v>0.2414966083114064</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5710854540727565</v>
+        <v>0.5710854540727539</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2444563223355649</v>
+        <v>0.2444563223355647</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2918138672139479</v>
+        <v>0.2918138672139485</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.263282057790092</v>
+        <v>0.2632820577900893</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2529964292448031</v>
+        <v>0.2529964292448028</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3471303139351389</v>
+        <v>0.3471303139351374</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2518763689884214</v>
+        <v>0.2518763689884211</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2518763689884214</v>
+        <v>0.2518763689884212</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3197577767244619</v>
+        <v>0.319757776724461</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4237139038602519</v>
+        <v>0.4237139038602521</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2529755826966085</v>
+        <v>0.2529755826966082</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5773345928956579</v>
+        <v>0.5773345928956573</v>
       </c>
       <c r="K7" t="n">
-        <v>0.306275608043898</v>
+        <v>0.3062756080438954</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3532854367158524</v>
+        <v>0.3532854367158522</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2878275765433436</v>
+        <v>0.2878275765433417</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3565661394168457</v>
+        <v>0.3565661394168456</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4681726547058942</v>
+        <v>0.4681726547058914</v>
       </c>
       <c r="E8" t="n">
-        <v>0.334754535001196</v>
+        <v>0.3347545350011957</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2796110845127713</v>
+        <v>0.279611084512771</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4239314081899944</v>
+        <v>0.4239314081899941</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5278875353259713</v>
+        <v>0.5278875353259703</v>
       </c>
       <c r="I8" t="n">
         <v>0.3571492141621417</v>
       </c>
       <c r="J8" t="n">
-        <v>0.68152387353497</v>
+        <v>0.6815238735349686</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3293419937238637</v>
+        <v>0.329341993723861</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5406372902766095</v>
+        <v>0.540637290276608</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4315307336556233</v>
+        <v>0.4315307336556208</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4956453501311408</v>
+        <v>0.4956453501311404</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5901365481642196</v>
+        <v>0.5901365481642187</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5815017513782195</v>
+        <v>0.5815017513782199</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4956454535007576</v>
+        <v>0.4956454535007577</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5624066976108004</v>
+        <v>0.5624066976107985</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6663628247465901</v>
+        <v>0.6663628247465898</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4956245035829454</v>
+        <v>0.4956245035829453</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8199835137819983</v>
+        <v>0.8199835137819952</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5058167397924022</v>
+        <v>0.5058167397924019</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5959343576021905</v>
+        <v>0.5959343576021898</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.519095717291455</v>
+        <v>2.565488797208919</v>
       </c>
       <c r="C2" t="n">
-        <v>1.832235047809663</v>
+        <v>2.711952897377849</v>
       </c>
       <c r="D2" t="n">
-        <v>1.719651655934331</v>
+        <v>2.576043657923516</v>
       </c>
       <c r="E2" t="n">
-        <v>1.907542236856705</v>
+        <v>2.774683120759037</v>
       </c>
       <c r="F2" t="n">
-        <v>1.644716614053522</v>
+        <v>2.555881313959418</v>
       </c>
       <c r="G2" t="n">
-        <v>1.630043710779226</v>
+        <v>2.571327769745714</v>
       </c>
       <c r="H2" t="n">
-        <v>1.674452200521798</v>
+        <v>2.573423982836053</v>
       </c>
       <c r="I2" t="n">
-        <v>1.665474923315409</v>
+        <v>2.573193451807608</v>
       </c>
       <c r="J2" t="n">
-        <v>2.145177251138701</v>
+        <v>2.921171896474612</v>
       </c>
       <c r="K2" t="n">
-        <v>1.765769333240115</v>
+        <v>2.705966347221687</v>
       </c>
       <c r="L2" t="n">
-        <v>1.691511040307103</v>
+        <v>2.574661464236309</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.219610083076058</v>
+        <v>1.596052918541801</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1154408798114985</v>
+        <v>1.879940384989424</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01107079140077928</v>
+        <v>1.671052939018044</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1908265159117861</v>
+        <v>1.983453536084574</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.07199910689139859</v>
+        <v>1.62230307920031</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.09199690775750866</v>
+        <v>1.637631685197211</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.04086266715133324</v>
+        <v>1.653983388170573</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05133121171338295</v>
+        <v>1.650868469125015</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4383428880126544</v>
+        <v>2.244137801552141</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03955528682125942</v>
+        <v>1.851925602182861</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.02130401606989039</v>
+        <v>1.660640978228293</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.000922669561065223</v>
+        <v>0.0009226695610638075</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08147991958212751</v>
+        <v>0.08147991958212752</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1201446768082451</v>
+        <v>0.1201446768082447</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08204629367968092</v>
+        <v>0.08204629367968114</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08204629367968092</v>
+        <v>0.082046293679681</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0666194653032092</v>
+        <v>0.06661946530320884</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09327122956840576</v>
+        <v>0.09327122956840574</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08623358279456379</v>
+        <v>0.08623358279456358</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1270566053384921</v>
+        <v>0.1270566053384913</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05035985302944828</v>
+        <v>0.05035985302944854</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1033807668192359</v>
+        <v>0.1033807668192343</v>
       </c>
     </row>
     <row r="5">
@@ -6575,34 +6575,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.573593086621444</v>
+        <v>-1.573593086621445</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1257105725584299</v>
+        <v>-0.1257105725584298</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3637474255214855</v>
+        <v>0.3637474255214833</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1257103848088172</v>
+        <v>-0.125710384808818</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1257103848088172</v>
+        <v>-0.1257103848088182</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4562007344557928</v>
+        <v>-0.4562007344557971</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03329837636192745</v>
+        <v>-0.03329837636192706</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1257114702240374</v>
+        <v>-0.1257114702240376</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5016982098905052</v>
+        <v>0.5016982098905021</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.711433755857187</v>
+        <v>-0.7114337558571859</v>
       </c>
       <c r="L5" t="n">
         <v>0.6209723335709769</v>
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03111513206489314</v>
+        <v>0.03111513206489445</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08500674815964866</v>
+        <v>0.0850067481596429</v>
       </c>
       <c r="D6" t="n">
-        <v>0.120804452639633</v>
+        <v>0.1208055306215472</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0845838520635659</v>
+        <v>0.0845838520635657</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08558647391762053</v>
+        <v>0.08558647391762067</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06525676672298215</v>
+        <v>0.0968119278070415</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0928365856388296</v>
+        <v>0.1312557122390564</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0848708842143356</v>
+        <v>0.116426045298394</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1616230025977938</v>
+        <v>0.1279521809906719</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04904389328749172</v>
+        <v>0.04904389328749212</v>
       </c>
       <c r="L6" t="n">
-        <v>0.103274008615345</v>
+        <v>0.1032740086153438</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05610846575527616</v>
+        <v>0.05610846575527598</v>
       </c>
       <c r="C7" t="n">
         <v>0.1414202766543824</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1749977445630113</v>
+        <v>0.1749977445630109</v>
       </c>
       <c r="E7" t="n">
         <v>0.1401014220501703</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1401014220501703</v>
+        <v>0.1401014220501704</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1218052614974231</v>
+        <v>0.1218052614974222</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1484570257626192</v>
+        <v>0.1484570257626184</v>
       </c>
       <c r="I7" t="n">
         <v>0.1414193789887774</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1822424015327052</v>
+        <v>0.1822424015327031</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1055456492236615</v>
+        <v>0.1055456492236611</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1585665630134485</v>
+        <v>0.1585665630134487</v>
       </c>
     </row>
     <row r="8">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06529047118904961</v>
+        <v>0.06529047118904796</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2018995030815409</v>
+        <v>0.2018995030815406</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2474493077055986</v>
+        <v>0.2474493077055972</v>
       </c>
       <c r="E8" t="n">
         <v>0.187639873597703</v>
@@ -6710,22 +6710,22 @@
         <v>0.1516664562162183</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1831150589446081</v>
+        <v>0.1831150589446079</v>
       </c>
       <c r="H8" t="n">
-        <v>0.209766823209737</v>
+        <v>0.2097668232097366</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2027291764359626</v>
+        <v>0.2027291764359629</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2435624436046921</v>
+        <v>0.2435624436046938</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1137593541553831</v>
+        <v>0.1137593541553832</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2743281980951089</v>
+        <v>0.2743281980951101</v>
       </c>
     </row>
     <row r="9">
@@ -6738,34 +6738,34 @@
         <v>0.1503730132372212</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2819036494401754</v>
+        <v>0.2819036494401762</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3158138363376357</v>
+        <v>0.3158138363376365</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3352393511064178</v>
+        <v>0.3352393511064179</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2819038196350271</v>
+        <v>0.2819038196350276</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2622886342832159</v>
+        <v>0.2622886342832179</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2889403985484118</v>
+        <v>0.2889403985484123</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2819027517745711</v>
+        <v>0.2819027517745715</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3227257743184989</v>
+        <v>0.3227257743184984</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2181631765368023</v>
+        <v>0.2192496491381782</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2990499357992429</v>
+        <v>0.2990499357992423</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.362783569984746</v>
+        <v>2.548945571170073</v>
       </c>
       <c r="C2" t="n">
-        <v>1.792990037009649</v>
+        <v>2.698828033744555</v>
       </c>
       <c r="D2" t="n">
-        <v>1.700613251676883</v>
+        <v>2.566724876333738</v>
       </c>
       <c r="E2" t="n">
-        <v>1.866876897582817</v>
+        <v>2.760337128337752</v>
       </c>
       <c r="F2" t="n">
-        <v>1.607958261903061</v>
+        <v>2.544787301843477</v>
       </c>
       <c r="G2" t="n">
-        <v>1.577247635959622</v>
+        <v>2.560232389002389</v>
       </c>
       <c r="H2" t="n">
-        <v>1.681789287415434</v>
+        <v>2.565545010319513</v>
       </c>
       <c r="I2" t="n">
-        <v>1.629805063883332</v>
+        <v>2.562998947161537</v>
       </c>
       <c r="J2" t="n">
-        <v>1.989858147862351</v>
+        <v>2.897105933806954</v>
       </c>
       <c r="K2" t="n">
-        <v>1.668732874590248</v>
+        <v>2.687283323610941</v>
       </c>
       <c r="L2" t="n">
-        <v>1.692734749032898</v>
+        <v>2.566459535630977</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.4005962305182142</v>
+        <v>1.533169861064446</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06963791728936415</v>
+        <v>1.857249733515256</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01202211536452219</v>
+        <v>1.659479052522106</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1436072474116285</v>
+        <v>1.958776727509421</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1153113882681275</v>
+        <v>1.602994309239379</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1539181285496789</v>
+        <v>1.613376427610021</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.03362486875098571</v>
+        <v>1.652251424544236</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09359207219989793</v>
+        <v>1.633044188840105</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2599581728259672</v>
+        <v>2.171750986073059</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.07223839190497791</v>
+        <v>1.804563468728552</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.02109422853115504</v>
+        <v>1.656675830220451</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09678223111199635</v>
+        <v>-0.09678223111199395</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05462178268385295</v>
+        <v>0.05462178268385265</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1040431995960576</v>
+        <v>0.1040431995960549</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05509741188138201</v>
+        <v>0.05509741188138177</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05509741188138204</v>
+        <v>0.05509741188138174</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03045506244566123</v>
+        <v>0.03045506244566158</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09283471149825803</v>
+        <v>0.09283471149825477</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0602708647416034</v>
+        <v>0.06027086474160308</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0357170384768434</v>
+        <v>0.03571703847684188</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.008098543332749855</v>
+        <v>-0.008098543332752242</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09930945585030278</v>
+        <v>0.09930945585030396</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-3.012740823100416</v>
+        <v>-3.012740823100415</v>
       </c>
       <c r="C5" t="n">
         <v>-0.4272711524536976</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2372727715506271</v>
+        <v>0.2372727715506292</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4272709357879455</v>
+        <v>-0.4272709357879438</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4272709357879455</v>
+        <v>-0.4272709357879438</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.938475806218015</v>
+        <v>-0.9384758062180154</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06081537467285045</v>
+        <v>0.06081537467285136</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4272696897278917</v>
+        <v>-0.4272696897278911</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9170280556762611</v>
+        <v>-0.9170280556762651</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.461385048771893</v>
+        <v>-1.461385048771889</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1711975005187633</v>
+        <v>-0.2799588131417932</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1012760660347557</v>
+        <v>-0.1012760660347574</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05620588224120782</v>
+        <v>0.05620588224118573</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1023632362030092</v>
+        <v>0.1023632362030083</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05611629270457829</v>
+        <v>0.05611629270457827</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05659522234460615</v>
+        <v>0.05659522234460636</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05362198439481435</v>
+        <v>0.02596122752289891</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1230607076643654</v>
+        <v>0.1230607076643598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05577702981884108</v>
+        <v>0.05577702981884092</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06319694825870642</v>
+        <v>0.03306329344312586</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01307083809949591</v>
+        <v>-0.01307083809949852</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09638560883679104</v>
+        <v>0.09638560883678793</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.04515094594151513</v>
+        <v>-0.04515094594151615</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1119006871862767</v>
+        <v>0.1119006871862762</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1553419673673523</v>
+        <v>0.1553419673673498</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1102640888518755</v>
+        <v>0.1102640888518752</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1102640888518755</v>
+        <v>0.1102640888518752</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08208634761614031</v>
+        <v>0.08208634761613987</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1444659966687329</v>
+        <v>0.1444659966687328</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1119021499120825</v>
+        <v>0.1119021499120822</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08734832364732328</v>
+        <v>0.0873483236473209</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04353274183772793</v>
+        <v>0.0435327418377275</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1509407410207854</v>
+        <v>0.1509407410207819</v>
       </c>
     </row>
     <row r="8">
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03946082708928343</v>
+        <v>-0.03946082708928367</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1626045188166483</v>
+        <v>0.1626045188166479</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2170836683629184</v>
+        <v>0.2170836683629194</v>
       </c>
       <c r="E8" t="n">
         <v>0.1500123867109583</v>
@@ -7106,22 +7106,22 @@
         <v>0.1182758180774035</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1339261033626204</v>
+        <v>0.1339261033626203</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1963057524150081</v>
+        <v>0.19630575241501</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1637419056585623</v>
+        <v>0.1637419056585622</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1391971491654806</v>
+        <v>0.1391971491654805</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04836560748617753</v>
+        <v>0.04836560748617769</v>
       </c>
       <c r="L8" t="n">
-        <v>0.250987651518836</v>
+        <v>0.250987651518837</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03468752440925457</v>
+        <v>0.03468752440925474</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2323320780174348</v>
+        <v>0.2323320780174341</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2761058517852116</v>
+        <v>0.27610585178521</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2791756193271743</v>
+        <v>0.2791756193271734</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2323322759988297</v>
+        <v>0.2323322759988292</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2025177384472989</v>
+        <v>0.2025177384472979</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2648973874998938</v>
+        <v>0.2648973874998922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2323335407432402</v>
+        <v>0.2323335407432399</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2077797144784785</v>
+        <v>0.2077797144784803</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1394902018268631</v>
+        <v>0.1394902018268619</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2713721318519406</v>
+        <v>0.2713721318519414</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.079799342961004</v>
+        <v>2.662268315676554</v>
       </c>
       <c r="C2" t="n">
-        <v>2.104895348232169</v>
+        <v>2.801718398659673</v>
       </c>
       <c r="D2" t="n">
-        <v>2.508896425263523</v>
+        <v>2.684850842862684</v>
       </c>
       <c r="E2" t="n">
-        <v>2.185719535513427</v>
+        <v>2.869421315191468</v>
       </c>
       <c r="F2" t="n">
-        <v>1.906930121259921</v>
+        <v>2.637332215575795</v>
       </c>
       <c r="G2" t="n">
-        <v>2.262949382451287</v>
+        <v>2.67190713848965</v>
       </c>
       <c r="H2" t="n">
-        <v>2.847546144232633</v>
+        <v>2.702566362392997</v>
       </c>
       <c r="I2" t="n">
-        <v>1.927256102815506</v>
+        <v>2.654238543242303</v>
       </c>
       <c r="J2" t="n">
-        <v>2.844993532639096</v>
+        <v>3.052848366266073</v>
       </c>
       <c r="K2" t="n">
-        <v>2.285185044286695</v>
+        <v>2.820070563393684</v>
       </c>
       <c r="L2" t="n">
-        <v>2.571451666785259</v>
+        <v>2.688304897749952</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4277724450772955</v>
+        <v>1.842966768494108</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4298555546453545</v>
+        <v>2.029699911544737</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9213229769180064</v>
+        <v>2.003219662782175</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5107746299094831</v>
+        <v>2.141069306126567</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2319852156559767</v>
+        <v>1.757985427715699</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6384329299075047</v>
+        <v>1.911698651310101</v>
       </c>
       <c r="H3" t="n">
-        <v>1.310909625344856</v>
+        <v>2.131289212625377</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2521485279496183</v>
+        <v>1.785882735165581</v>
       </c>
       <c r="J3" t="n">
-        <v>1.240421678524661</v>
+        <v>2.579545948448426</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6356921991299727</v>
+        <v>2.108348892508675</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9932598261398884</v>
+        <v>2.03003111814054</v>
       </c>
     </row>
     <row r="4">
@@ -7330,34 +7330,34 @@
         <v>0.3633650461324335</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2658766287739884</v>
+        <v>0.265876628773988</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6184450791755364</v>
+        <v>0.618445079175536</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2669966593109325</v>
+        <v>0.2669966593109321</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2669966593109326</v>
+        <v>0.266996659310932</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4718483975857544</v>
+        <v>0.471848397585754</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8196320543556742</v>
+        <v>0.8196320543556723</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2700439377806333</v>
+        <v>0.2700439377806327</v>
       </c>
       <c r="J4" t="n">
         <v>0.5511724361085956</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3733937762929457</v>
+        <v>0.3733937762929458</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6555658076823135</v>
+        <v>0.6555658076823134</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.659187682777365</v>
+        <v>3.659187682777363</v>
       </c>
       <c r="C5" t="n">
-        <v>2.066724512317081</v>
+        <v>2.066724512317076</v>
       </c>
       <c r="D5" t="n">
         <v>7.970707778380603</v>
       </c>
       <c r="E5" t="n">
-        <v>2.066724622528555</v>
+        <v>2.066724622528551</v>
       </c>
       <c r="F5" t="n">
-        <v>2.066724622528555</v>
+        <v>2.066724622528551</v>
       </c>
       <c r="G5" t="n">
-        <v>5.683536634090198</v>
+        <v>5.683536634090179</v>
       </c>
       <c r="H5" t="n">
         <v>12.35597430378459</v>
       </c>
       <c r="I5" t="n">
-        <v>2.066672520030282</v>
+        <v>2.06667252003028</v>
       </c>
       <c r="J5" t="n">
-        <v>7.563145309087061</v>
+        <v>7.563145309087066</v>
       </c>
       <c r="K5" t="n">
-        <v>3.865231663440279</v>
+        <v>3.865231663440274</v>
       </c>
       <c r="L5" t="n">
-        <v>10.44613279740828</v>
+        <v>4.030617546029122</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3852219786366321</v>
+        <v>0.3852219786366312</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2860568009602307</v>
+        <v>0.2860568009602439</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6472596784942232</v>
+        <v>0.6472596784942271</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2839129361905249</v>
+        <v>0.2839129361905141</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2915815670400552</v>
+        <v>0.2915815670400548</v>
       </c>
       <c r="G6" t="n">
-        <v>0.569113557855614</v>
+        <v>0.5691135578556137</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9268415202055329</v>
+        <v>0.9268415202055302</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3673090980504938</v>
+        <v>0.3673090980504931</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6532457284550185</v>
+        <v>0.6532457284550164</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3945262372730166</v>
+        <v>0.3945262372730129</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6799717178272987</v>
+        <v>0.6799717178272981</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4550768567253369</v>
+        <v>0.4550768567253364</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3618077406603352</v>
+        <v>0.3618077406603348</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7097986047723592</v>
+        <v>0.7097986047723596</v>
       </c>
       <c r="E7" t="n">
-        <v>0.361452802176502</v>
+        <v>0.3614528021765012</v>
       </c>
       <c r="F7" t="n">
-        <v>0.361452802176502</v>
+        <v>0.3614528021765012</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5635602081786564</v>
+        <v>0.5635602081786558</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9113438649485766</v>
+        <v>0.9113438649485759</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3617557483735362</v>
+        <v>0.3617557483735357</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6428842467014986</v>
+        <v>0.6428842467014987</v>
       </c>
       <c r="K7" t="n">
-        <v>0.465105586885849</v>
+        <v>0.4651055868858489</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7472776182752147</v>
+        <v>0.7472776182752141</v>
       </c>
     </row>
     <row r="8">
@@ -7487,34 +7487,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4947838630544741</v>
+        <v>0.4947838630544729</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5062380670507399</v>
+        <v>0.5062380670496637</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8761404776235472</v>
+        <v>0.8761404776235467</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4775210960867988</v>
+        <v>0.477521096086797</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4048321073952499</v>
+        <v>0.4048321073952488</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7078565218301056</v>
+        <v>0.7078565218301038</v>
       </c>
       <c r="H8" t="n">
-        <v>1.055640178600131</v>
+        <v>1.055640178600128</v>
       </c>
       <c r="I8" t="n">
-        <v>0.506052062024985</v>
+        <v>0.5060520620249833</v>
       </c>
       <c r="J8" t="n">
-        <v>0.787201115082373</v>
+        <v>0.7872011150823727</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5028697931403072</v>
+        <v>0.5028697931403069</v>
       </c>
       <c r="L8" t="n">
         <v>1.000826208980063</v>
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.696480926227648</v>
+        <v>0.6964809262276475</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7045150179206279</v>
+        <v>0.7045150179206263</v>
       </c>
       <c r="D9" t="n">
-        <v>1.05286417410998</v>
+        <v>1.052864174109979</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8214166656373596</v>
+        <v>0.8214166656373566</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7045149499930712</v>
+        <v>0.7045149499930697</v>
       </c>
       <c r="G9" t="n">
-        <v>0.906267485438949</v>
+        <v>0.9062674854389478</v>
       </c>
       <c r="H9" t="n">
         <v>1.254051142208869</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7044630256338282</v>
+        <v>0.7044630256338272</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9855915239617909</v>
+        <v>0.9855915239617891</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7491173907011202</v>
+        <v>0.7491173907011194</v>
       </c>
       <c r="L9" t="n">
-        <v>1.089984895535508</v>
+        <v>1.089984895535507</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.665841599340925</v>
+        <v>2.601722939906721</v>
       </c>
       <c r="C2" t="n">
-        <v>1.964205172574246</v>
+        <v>2.752163687214296</v>
       </c>
       <c r="D2" t="n">
-        <v>2.269276188458</v>
+        <v>2.633480503814324</v>
       </c>
       <c r="E2" t="n">
-        <v>2.042120147716313</v>
+        <v>2.817220378951921</v>
       </c>
       <c r="F2" t="n">
-        <v>1.77169122734203</v>
+        <v>2.592090010483835</v>
       </c>
       <c r="G2" t="n">
-        <v>1.884004147060415</v>
+        <v>2.613204401487478</v>
       </c>
       <c r="H2" t="n">
-        <v>1.742589633076878</v>
+        <v>2.605340560229346</v>
       </c>
       <c r="I2" t="n">
-        <v>1.791167147229218</v>
+        <v>2.608318646616644</v>
       </c>
       <c r="J2" t="n">
-        <v>2.420895623740377</v>
+        <v>2.977736328392976</v>
       </c>
       <c r="K2" t="n">
-        <v>2.009339366366796</v>
+        <v>2.757560308280562</v>
       </c>
       <c r="L2" t="n">
-        <v>2.216963490070399</v>
+        <v>2.630978387670485</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04949378088385099</v>
+        <v>1.666810865204983</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2676154364435694</v>
+        <v>1.951255243105482</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6445809976993456</v>
+        <v>1.891889493316432</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3456097663985519</v>
+        <v>2.058472069649765</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07518084602426967</v>
+        <v>1.686875038804722</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2014383412291763</v>
+        <v>1.748387653021136</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0388535675074867</v>
+        <v>1.695188893027198</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09459281890681341</v>
+        <v>1.71365274444311</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7541954397075498</v>
+        <v>2.380926375995154</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3190621624346058</v>
+        <v>1.971863075982986</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5843916319255029</v>
+        <v>1.874710982099931</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.100694943990486</v>
+        <v>0.1006949439904852</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1696588219899305</v>
+        <v>0.1696588219899307</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4594112375280323</v>
+        <v>0.4594112375280293</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1703894969714238</v>
+        <v>0.1703894969714243</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1703894969714239</v>
+        <v>0.1703894969714243</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2300803626196627</v>
+        <v>0.2300803626196634</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1463583515398396</v>
+        <v>0.1463583515398425</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1731713928260276</v>
+        <v>0.1731713928260277</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2931728880041513</v>
+        <v>0.2931728880041514</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1998648174807344</v>
+        <v>0.1998648174807359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4282264402944668</v>
+        <v>0.428226440294469</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3193136444043859</v>
+        <v>-0.3193136444043858</v>
       </c>
       <c r="C5" t="n">
-        <v>0.876130121798387</v>
+        <v>0.8761301217983866</v>
       </c>
       <c r="D5" t="n">
-        <v>5.208096955390201</v>
+        <v>5.208096955390205</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8761302547736752</v>
+        <v>0.8761302547736743</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8761302547736752</v>
+        <v>0.8761302547736743</v>
       </c>
       <c r="G5" t="n">
-        <v>1.783960622613748</v>
+        <v>1.783960622613804</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4626995115440451</v>
+        <v>0.4626995115440459</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8761115031551275</v>
+        <v>0.8761115031551285</v>
       </c>
       <c r="J5" t="n">
-        <v>3.057656101243097</v>
+        <v>3.057656101243099</v>
       </c>
       <c r="K5" t="n">
-        <v>1.251153727691565</v>
+        <v>1.251153727691566</v>
       </c>
       <c r="L5" t="n">
-        <v>1.022566157499854</v>
+        <v>5.831321620726573</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1577180478945755</v>
+        <v>0.1577180478945766</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1800431434387065</v>
+        <v>0.1800431434387035</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4761546040589429</v>
+        <v>0.4761556877391267</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1788320878804759</v>
+        <v>0.1788320878804756</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1821246204049355</v>
+        <v>0.1821246204049356</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2388639048632233</v>
+        <v>0.2871034665237508</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2105595035533632</v>
+        <v>0.2105595035533659</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2301944967301171</v>
+        <v>0.230194496730117</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3048118954955491</v>
+        <v>0.3048118954955479</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2088725481309613</v>
+        <v>0.2088725481309602</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4389857570384992</v>
+        <v>0.4389857570385</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1684980981368126</v>
+        <v>0.168498098136811</v>
       </c>
       <c r="C7" t="n">
         <v>0.240993165615615</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5268810586842482</v>
+        <v>0.5268810586842475</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2402876071994071</v>
+        <v>0.2402876071994074</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2402876071994071</v>
+        <v>0.2402876071994074</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2978835167659897</v>
+        <v>0.2978835167659906</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2141615056861665</v>
+        <v>0.2141615056861677</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2409745469723541</v>
+        <v>0.2409745469723543</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3609760421504773</v>
+        <v>0.3609760421504786</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2676679716270608</v>
+        <v>0.2676679716270606</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4960295944407935</v>
+        <v>0.4960295944407925</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1896374805716613</v>
+        <v>0.1896374805716607</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3333389692794477</v>
+        <v>0.3333389692794478</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6346143699083149</v>
+        <v>0.634614369908315</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3137330101877993</v>
+        <v>0.3137330101878004</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2641752738650841</v>
+        <v>0.264175273865084</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3904687354326865</v>
+        <v>0.3904687354326883</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3067467243530233</v>
+        <v>0.3067467243530239</v>
       </c>
       <c r="I8" t="n">
-        <v>0.333559765639051</v>
+        <v>0.3335597656390503</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4535753019514341</v>
+        <v>0.453575301951434</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2874802109745482</v>
+        <v>0.2874802109745472</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6632459632387164</v>
+        <v>0.6632459632387155</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3079649438204245</v>
+        <v>0.3079649438204226</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4442810748492687</v>
+        <v>0.4442810748492686</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7305023524059324</v>
+        <v>0.7305023524059341</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5179293831310607</v>
+        <v>0.5179293831310613</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4442811875380469</v>
+        <v>0.4442811875380465</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5011714259996428</v>
+        <v>0.5011714259996437</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4174494149198203</v>
+        <v>0.4174494149198207</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4442624562060075</v>
+        <v>0.4442624562060077</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5642639513841307</v>
+        <v>0.5642639513841322</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3905937564845108</v>
+        <v>0.4339777276549871</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6993175036744468</v>
+        <v>0.6993175036744469</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia climate change results.xlsx
+++ b/Results/Ammonia/ammonia climate change results.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.701627450228377</v>
+        <v>2.701627450228378</v>
       </c>
       <c r="C2" t="n">
         <v>2.83734037322328</v>
       </c>
       <c r="D2" t="n">
-        <v>2.710983548660236</v>
+        <v>2.710983548660237</v>
       </c>
       <c r="E2" t="n">
         <v>2.90669340249095</v>
@@ -530,19 +530,19 @@
         <v>2.669865718519153</v>
       </c>
       <c r="G2" t="n">
-        <v>2.70138576098771</v>
+        <v>2.701385760987711</v>
       </c>
       <c r="H2" t="n">
         <v>2.733005169467742</v>
       </c>
       <c r="I2" t="n">
-        <v>2.683598432065438</v>
+        <v>2.683598432065439</v>
       </c>
       <c r="J2" t="n">
-        <v>3.093802866594949</v>
+        <v>3.09380286659495</v>
       </c>
       <c r="K2" t="n">
-        <v>2.861758700790735</v>
+        <v>2.861758700790736</v>
       </c>
       <c r="L2" t="n">
         <v>2.718688840305117</v>
@@ -555,28 +555,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.981130591932112</v>
+        <v>1.981130591932113</v>
       </c>
       <c r="C3" t="n">
         <v>2.107255941103475</v>
       </c>
       <c r="D3" t="n">
-        <v>2.048096785600916</v>
+        <v>2.048096785600917</v>
       </c>
       <c r="E3" t="n">
-        <v>2.221278060133789</v>
+        <v>2.22127806013379</v>
       </c>
       <c r="F3" t="n">
         <v>1.830372206859595</v>
       </c>
       <c r="G3" t="n">
-        <v>1.980054957643558</v>
+        <v>1.980054957643559</v>
       </c>
       <c r="H3" t="n">
-        <v>2.208629862926373</v>
+        <v>2.208629862926374</v>
       </c>
       <c r="I3" t="n">
-        <v>1.853031476170677</v>
+        <v>1.853031476170678</v>
       </c>
       <c r="J3" t="n">
         <v>2.660203580568928</v>
@@ -595,25 +595,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5789019122578445</v>
+        <v>0.5789019122578448</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3688173603806959</v>
+        <v>0.3688173603806961</v>
       </c>
       <c r="D4" t="n">
         <v>0.6845833480636242</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3701854034321417</v>
+        <v>0.3701854034321418</v>
       </c>
       <c r="F4" t="n">
         <v>0.3701854034321417</v>
       </c>
       <c r="G4" t="n">
-        <v>0.575777878633384</v>
+        <v>0.5757778786333838</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9348078501230165</v>
+        <v>0.9348078501230161</v>
       </c>
       <c r="I4" t="n">
         <v>0.372620146307669</v>
@@ -622,10 +622,10 @@
         <v>0.642031052002125</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5029868746801486</v>
+        <v>0.5029868746801482</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7699010867731884</v>
+        <v>0.7699010867731882</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.529368491465479</v>
+        <v>7.529368491465484</v>
       </c>
       <c r="C5" t="n">
-        <v>3.767474817084591</v>
+        <v>3.767474817084603</v>
       </c>
       <c r="D5" t="n">
-        <v>9.771236304173216</v>
+        <v>9.771236304173213</v>
       </c>
       <c r="E5" t="n">
-        <v>3.767474913130348</v>
+        <v>3.767474913130352</v>
       </c>
       <c r="F5" t="n">
-        <v>3.767474913130348</v>
+        <v>3.767474913130352</v>
       </c>
       <c r="G5" t="n">
-        <v>7.859917809760037</v>
+        <v>7.859917809760016</v>
       </c>
       <c r="H5" t="n">
         <v>16.33143903885964</v>
       </c>
       <c r="I5" t="n">
-        <v>3.767422404730511</v>
+        <v>3.767422404730521</v>
       </c>
       <c r="J5" t="n">
-        <v>9.426468539986159</v>
+        <v>9.426468539986162</v>
       </c>
       <c r="K5" t="n">
-        <v>6.284672104273318</v>
+        <v>6.284672104273329</v>
       </c>
       <c r="L5" t="n">
-        <v>13.18871138282453</v>
+        <v>13.18871138282456</v>
       </c>
     </row>
     <row r="6">
@@ -675,34 +675,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6087508923831407</v>
+        <v>0.608750892383141</v>
       </c>
       <c r="C6" t="n">
-        <v>0.396390900333502</v>
+        <v>0.3963909003335085</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7213059152040134</v>
+        <v>0.7213059152040142</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3935506228635685</v>
+        <v>0.3935506228635614</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4023425306113482</v>
+        <v>0.4023425306113484</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6980526721738546</v>
+        <v>0.6980526721738547</v>
       </c>
       <c r="H6" t="n">
-        <v>1.06860622274435</v>
+        <v>1.068606222744351</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4948949398481409</v>
+        <v>0.4948949398481405</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7699466346340202</v>
+        <v>0.7699466346340205</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5330577704669706</v>
+        <v>0.5330577704669759</v>
       </c>
       <c r="L6" t="n">
         <v>0.8026676189336015</v>
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6906997894271558</v>
+        <v>0.6906997894271563</v>
       </c>
       <c r="C7" t="n">
         <v>0.4844704358310642</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7959977906679093</v>
+        <v>0.7959977906679091</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4843016067836914</v>
+        <v>0.4843016067836917</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4843016067836916</v>
+        <v>0.4843016067836917</v>
       </c>
       <c r="G7" t="n">
-        <v>0.687575755802694</v>
+        <v>0.6875757558026946</v>
       </c>
       <c r="H7" t="n">
         <v>1.04660572729233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4844180234769807</v>
+        <v>0.4844180234769805</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7538289291714363</v>
+        <v>0.7538289291714365</v>
       </c>
       <c r="K7" t="n">
         <v>0.6147847518494597</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8816989639425005</v>
+        <v>0.8816989639425001</v>
       </c>
     </row>
     <row r="8">
@@ -755,22 +755,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7441409269139324</v>
+        <v>0.7441409269139327</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6692650322057873</v>
+        <v>0.6692650322057879</v>
       </c>
       <c r="D8" t="n">
-        <v>1.007991400244779</v>
+        <v>1.00799140024478</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6332939619722314</v>
+        <v>0.633293961972232</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5421922725004458</v>
+        <v>0.5421922725004462</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8720213113269696</v>
+        <v>0.872021311326971</v>
       </c>
       <c r="H8" t="n">
         <v>1.231051282816647</v>
@@ -782,10 +782,10 @@
         <v>0.9383002307196416</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6657924150214991</v>
+        <v>0.6657924150214992</v>
       </c>
       <c r="L8" t="n">
-        <v>1.202989588427589</v>
+        <v>1.20298958842759</v>
       </c>
     </row>
     <row r="9">
@@ -807,7 +807,7 @@
         <v>1.111853972115888</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9558295311501767</v>
+        <v>0.9558295311501768</v>
       </c>
       <c r="G9" t="n">
         <v>1.158934965895111</v>
@@ -816,10 +816,10 @@
         <v>1.517964937384745</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9557772335693985</v>
+        <v>0.9557772335693986</v>
       </c>
       <c r="J9" t="n">
-        <v>1.225188139263854</v>
+        <v>1.225188139263853</v>
       </c>
       <c r="K9" t="n">
         <v>0.9158958867476189</v>
@@ -911,19 +911,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.578331691369865</v>
+        <v>2.578331691369866</v>
       </c>
       <c r="C2" t="n">
         <v>2.723217706734868</v>
       </c>
       <c r="D2" t="n">
-        <v>2.581591780971618</v>
+        <v>2.58159178097162</v>
       </c>
       <c r="E2" t="n">
-        <v>2.78672118936657</v>
+        <v>2.786721189366572</v>
       </c>
       <c r="F2" t="n">
-        <v>2.565572330135129</v>
+        <v>2.565572330135131</v>
       </c>
       <c r="G2" t="n">
         <v>2.578508735523657</v>
@@ -932,13 +932,13 @@
         <v>2.578518196931482</v>
       </c>
       <c r="I2" t="n">
-        <v>2.581392425257333</v>
+        <v>2.581392425257335</v>
       </c>
       <c r="J2" t="n">
-        <v>2.937585290835076</v>
+        <v>2.937585290835071</v>
       </c>
       <c r="K2" t="n">
-        <v>2.730147411103144</v>
+        <v>2.730147411103145</v>
       </c>
       <c r="L2" t="n">
         <v>2.582493617898285</v>
@@ -954,16 +954,16 @@
         <v>1.647006490459605</v>
       </c>
       <c r="C3" t="n">
-        <v>1.902889821489649</v>
+        <v>1.90288982148965</v>
       </c>
       <c r="D3" t="n">
-        <v>1.670163458160134</v>
+        <v>1.670163458160133</v>
       </c>
       <c r="E3" t="n">
         <v>2.007673725396782</v>
       </c>
       <c r="F3" t="n">
-        <v>1.642649009051314</v>
+        <v>1.642649009051319</v>
       </c>
       <c r="G3" t="n">
         <v>1.648261735304907</v>
@@ -972,13 +972,13 @@
         <v>1.64991286668676</v>
       </c>
       <c r="I3" t="n">
-        <v>1.668751814027777</v>
+        <v>1.668751814027778</v>
       </c>
       <c r="J3" t="n">
-        <v>2.285949270494085</v>
+        <v>2.285949270494098</v>
       </c>
       <c r="K3" t="n">
-        <v>1.936637905743854</v>
+        <v>1.936637905743855</v>
       </c>
       <c r="L3" t="n">
         <v>1.676008767377105</v>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08120478279237449</v>
+        <v>0.08120478279237708</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1102786302578023</v>
+        <v>0.1102786302578029</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1180289945594943</v>
+        <v>0.1180289945594928</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1108639206133957</v>
+        <v>0.1108639206133967</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1108639206133952</v>
+        <v>0.1108639206133967</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08295451059608216</v>
+        <v>0.08295451059608304</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08636150861579582</v>
+        <v>0.08636150861579631</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1141084124894318</v>
+        <v>0.1141084124894316</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1759798230353798</v>
+        <v>0.1759798230353774</v>
       </c>
       <c r="K4" t="n">
-        <v>0.162265963826986</v>
+        <v>0.1622659638269841</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1270102729236889</v>
+        <v>0.1270102729236887</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3483312367845479</v>
+        <v>-0.3483312367845478</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2100153496440141</v>
+        <v>0.2100153496440166</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2457255643541441</v>
+        <v>0.2457255643541459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2100155141881088</v>
+        <v>0.2100155141881118</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2100155141881088</v>
+        <v>0.2100155141881118</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3175274569935118</v>
+        <v>-0.3175274569935112</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2995592229228963</v>
+        <v>-0.2995592229228912</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2100170349753266</v>
+        <v>0.2100170349753288</v>
       </c>
       <c r="J5" t="n">
-        <v>1.27368979358496</v>
+        <v>1.273689793584992</v>
       </c>
       <c r="K5" t="n">
-        <v>0.908758454055278</v>
+        <v>0.9087584540552786</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4376182268273604</v>
+        <v>0.4376182268273623</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08332325809983081</v>
+        <v>0.08332325809983178</v>
       </c>
       <c r="C6" t="n">
-        <v>0.115790908032476</v>
+        <v>0.1157909080324811</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1569385484653934</v>
+        <v>0.1569385484653954</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1150725716950482</v>
+        <v>0.1150725716950626</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1162338461396996</v>
+        <v>0.1162338461396986</v>
       </c>
       <c r="G6" t="n">
         <v>0.1193962486728746</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1300144385249296</v>
+        <v>0.1300144385249265</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1162268877968851</v>
+        <v>0.1162268877968849</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1798658792216587</v>
+        <v>0.179865879221653</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1665790072628875</v>
+        <v>0.1665790072628879</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1295428918097128</v>
+        <v>0.1295428918097143</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1393207774839743</v>
+        <v>0.1393207774839762</v>
       </c>
       <c r="C7" t="n">
-        <v>0.172222721849716</v>
+        <v>0.172222721849718</v>
       </c>
       <c r="D7" t="n">
-        <v>0.175811980852138</v>
+        <v>0.1758119808521394</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1711469292301149</v>
+        <v>0.171146929230115</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1711469292301153</v>
+        <v>0.171146929230115</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1410705052876807</v>
+        <v>0.1410705052876811</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1444775033073948</v>
+        <v>0.1444775033073957</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1722244071810298</v>
+        <v>0.1722244071810295</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2340958177269747</v>
+        <v>0.2340958177269759</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2203819585185813</v>
+        <v>0.2203819585185823</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1851262676152872</v>
+        <v>0.1851262676152878</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.151283879019102</v>
+        <v>0.1512838790191045</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2404328493794221</v>
+        <v>0.2404328493794216</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2567388601898848</v>
+        <v>0.2567388601898836</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2248584884515349</v>
+        <v>0.2248584884515393</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1855446445889146</v>
+        <v>0.1855446445889163</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2098774376097486</v>
+        <v>0.2098774376097509</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2132844356296834</v>
+        <v>0.2132844356296842</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2410313395030986</v>
+        <v>0.2410313395030982</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3029139214940372</v>
+        <v>0.3029139214940366</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2312891567119136</v>
+        <v>0.2312891567119151</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3133113344035793</v>
+        <v>0.3133113344035794</v>
       </c>
     </row>
     <row r="9">
@@ -1191,34 +1191,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2316815550010083</v>
+        <v>0.2316815550010099</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3115593667671089</v>
+        <v>0.311559366767109</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3154816317776473</v>
+        <v>0.3154816317776468</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3657686682497909</v>
+        <v>0.3657686682497908</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3115595186465063</v>
+        <v>0.311559518646507</v>
       </c>
       <c r="G9" t="n">
-        <v>0.28040715020507</v>
+        <v>0.2804071502050723</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2838141482247857</v>
+        <v>0.2838141482247867</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3115610520984208</v>
+        <v>0.311561052098421</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3734324626443639</v>
+        <v>0.373432462644365</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3325006003701637</v>
+        <v>0.3325006003701649</v>
       </c>
       <c r="L9" t="n">
         <v>0.3244629125326788</v>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.732138720834095</v>
+        <v>2.732138720834096</v>
       </c>
       <c r="C2" t="n">
-        <v>2.579879115583296</v>
+        <v>2.579879115583297</v>
       </c>
       <c r="D2" t="n">
         <v>2.748630505395486</v>
@@ -1319,19 +1319,19 @@
         <v>2.614536725433025</v>
       </c>
       <c r="F2" t="n">
-        <v>2.614503434333101</v>
+        <v>2.614503434333102</v>
       </c>
       <c r="G2" t="n">
         <v>2.742852760949717</v>
       </c>
       <c r="H2" t="n">
-        <v>2.754931696360715</v>
+        <v>2.754931696360716</v>
       </c>
       <c r="I2" t="n">
         <v>2.733217563363371</v>
       </c>
       <c r="J2" t="n">
-        <v>2.917759407449681</v>
+        <v>2.917759407449683</v>
       </c>
       <c r="K2" t="n">
         <v>2.823405374087699</v>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.914155444096471</v>
+        <v>1.914155444096472</v>
       </c>
       <c r="C3" t="n">
         <v>1.681554793091684</v>
@@ -1362,19 +1362,19 @@
         <v>1.725809761719193</v>
       </c>
       <c r="G3" t="n">
-        <v>1.990557743927718</v>
+        <v>1.990557743927719</v>
       </c>
       <c r="H3" t="n">
         <v>2.079556259547428</v>
       </c>
       <c r="I3" t="n">
-        <v>1.92175985179727</v>
+        <v>1.921759851797271</v>
       </c>
       <c r="J3" t="n">
-        <v>2.333665725875396</v>
+        <v>2.333665725875397</v>
       </c>
       <c r="K3" t="n">
-        <v>2.101136684283349</v>
+        <v>2.10113668428335</v>
       </c>
       <c r="L3" t="n">
         <v>1.966477656876335</v>
@@ -1390,34 +1390,34 @@
         <v>0.2717088660387958</v>
       </c>
       <c r="C4" t="n">
-        <v>0.305984288661899</v>
+        <v>0.3059842886618994</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4579911592554218</v>
+        <v>0.4579911592554214</v>
       </c>
       <c r="E4" t="n">
         <v>0.279065276522311</v>
       </c>
       <c r="F4" t="n">
-        <v>0.279065276522311</v>
+        <v>0.2790652765223109</v>
       </c>
       <c r="G4" t="n">
         <v>0.3923234453086445</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5322399521988316</v>
+        <v>0.5322399521988311</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2811908101570385</v>
+        <v>0.2811908101570386</v>
       </c>
       <c r="J4" t="n">
         <v>0.5043073112760428</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3469015337476469</v>
+        <v>0.346901533747647</v>
       </c>
       <c r="L4" t="n">
-        <v>0.353570909376294</v>
+        <v>0.3535709093762938</v>
       </c>
     </row>
     <row r="5">
@@ -1430,34 +1430,34 @@
         <v>2.117174724905368</v>
       </c>
       <c r="C5" t="n">
-        <v>2.80319017907498</v>
+        <v>2.803190179074975</v>
       </c>
       <c r="D5" t="n">
-        <v>5.385715332933976</v>
+        <v>5.385715332933975</v>
       </c>
       <c r="E5" t="n">
-        <v>2.289206276250158</v>
+        <v>2.289206276250159</v>
       </c>
       <c r="F5" t="n">
-        <v>2.289206276250158</v>
+        <v>2.28920627625016</v>
       </c>
       <c r="G5" t="n">
-        <v>4.334627976681533</v>
+        <v>4.334627976681531</v>
       </c>
       <c r="H5" t="n">
-        <v>7.545355011832307</v>
+        <v>7.545355011832325</v>
       </c>
       <c r="I5" t="n">
-        <v>2.289175080594545</v>
+        <v>2.289175080594549</v>
       </c>
       <c r="J5" t="n">
-        <v>6.520263865221561</v>
+        <v>6.520263865221557</v>
       </c>
       <c r="K5" t="n">
-        <v>3.411331521851603</v>
+        <v>3.411331521851606</v>
       </c>
       <c r="L5" t="n">
-        <v>4.018025470065636</v>
+        <v>4.018025470065642</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3612541480944762</v>
+        <v>0.3612541480944771</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3261759827510846</v>
+        <v>0.3261759827510716</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4810473268733408</v>
+        <v>0.4810473268733406</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2947089586384519</v>
+        <v>0.294708958638452</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3005056299320087</v>
+        <v>0.3005056299320089</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4118491184928277</v>
+        <v>0.4118491184928281</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6357980130154178</v>
+        <v>0.6357980130154179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3007164833412229</v>
+        <v>0.3007164833412231</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5998412877150842</v>
+        <v>0.5998412877150848</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3663284947691113</v>
+        <v>0.3663284947691111</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3735833027833539</v>
+        <v>0.373583302783354</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.363924967705812</v>
+        <v>0.3639249677058117</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4018284287688952</v>
+        <v>0.4018284287688959</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5498550120070865</v>
+        <v>0.549855012007086</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3731975109773109</v>
+        <v>0.3731975109773111</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3731975109773109</v>
+        <v>0.3731975109773111</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4845395469756599</v>
+        <v>0.4845395469756608</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6244560538658481</v>
+        <v>0.6244560538658485</v>
       </c>
       <c r="I7" t="n">
         <v>0.3734069118240549</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5965234129430597</v>
+        <v>0.5965234129430599</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4391176354146629</v>
+        <v>0.439117635414663</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4457870110433106</v>
+        <v>0.4457870110433109</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4055633098254295</v>
+        <v>0.4055633098254289</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5515313344433046</v>
+        <v>0.5515313344433049</v>
       </c>
       <c r="D8" t="n">
         <v>0.7220322508348174</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4935287543915604</v>
+        <v>0.4935287543915602</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4185610318423714</v>
+        <v>0.4185610318423715</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6340057313660551</v>
+        <v>0.6340057313660546</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7739222382566925</v>
+        <v>0.7739222382566926</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5228730962144498</v>
+        <v>0.5228730962144496</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7460107884966761</v>
+        <v>0.7460107884966766</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4787530200132474</v>
+        <v>0.4787530200132471</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7078883930140452</v>
+        <v>0.7078883930140439</v>
       </c>
     </row>
     <row r="9">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5683150781329588</v>
+        <v>0.5683150781329589</v>
       </c>
       <c r="C9" t="n">
         <v>0.6981607832255401</v>
@@ -1596,28 +1596,28 @@
         <v>0.846539651032702</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7758697648747704</v>
+        <v>0.7758697648747703</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6697703584073291</v>
+        <v>0.6697703584073297</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7808719014323059</v>
+        <v>0.780871901432307</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9207884083224921</v>
+        <v>0.9207884083224922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6697392662807012</v>
+        <v>0.6697392662807014</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8928557673997042</v>
+        <v>0.8928557673997044</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6821783075913366</v>
+        <v>0.682178307591337</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7421193654999569</v>
+        <v>0.7421193654999566</v>
       </c>
     </row>
   </sheetData>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.716921612499278</v>
+        <v>2.716921612499277</v>
       </c>
       <c r="C2" t="n">
         <v>2.563798772351846</v>
       </c>
       <c r="D2" t="n">
-        <v>2.730192577177174</v>
+        <v>2.730192577177175</v>
       </c>
       <c r="E2" t="n">
         <v>2.596556914096581</v>
@@ -1718,7 +1718,7 @@
         <v>2.596523587250838</v>
       </c>
       <c r="G2" t="n">
-        <v>2.725303214842976</v>
+        <v>2.725303214842977</v>
       </c>
       <c r="H2" t="n">
         <v>2.72950479366677</v>
@@ -1730,10 +1730,10 @@
         <v>2.896953885475868</v>
       </c>
       <c r="K2" t="n">
-        <v>2.799735141695066</v>
+        <v>2.799735141695064</v>
       </c>
       <c r="L2" t="n">
-        <v>2.72079289732783</v>
+        <v>2.720792897327829</v>
       </c>
     </row>
     <row r="3">
@@ -1755,10 +1755,10 @@
         <v>1.680501563769299</v>
       </c>
       <c r="F3" t="n">
-        <v>1.680468236923556</v>
+        <v>1.680468236923557</v>
       </c>
       <c r="G3" t="n">
-        <v>1.933852614785587</v>
+        <v>1.933852614785586</v>
       </c>
       <c r="H3" t="n">
         <v>1.966442185616711</v>
@@ -1770,7 +1770,7 @@
         <v>2.27202109959656</v>
       </c>
       <c r="K3" t="n">
-        <v>2.026187510343072</v>
+        <v>2.026187510343071</v>
       </c>
       <c r="L3" t="n">
         <v>1.902559640250751</v>
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2056075355907861</v>
+        <v>0.2056075355907865</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2487437216041619</v>
+        <v>0.2487437216041616</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3555091865729861</v>
+        <v>0.3555091865729851</v>
       </c>
       <c r="E4" t="n">
         <v>0.2113487901267435</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2113487901267436</v>
+        <v>0.2113487901267435</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2998899496358422</v>
+        <v>0.2998899496358424</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3513843176250855</v>
+        <v>0.3513843176250854</v>
       </c>
       <c r="I4" t="n">
         <v>0.2136465520400437</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4128694858529288</v>
+        <v>0.4128694858529293</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2375229086411655</v>
+        <v>0.2375229086411659</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2502324833034467</v>
+        <v>0.2502324833034456</v>
       </c>
     </row>
     <row r="5">
@@ -1823,25 +1823,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.101849609528812</v>
+        <v>1.101849609528811</v>
       </c>
       <c r="C5" t="n">
-        <v>1.922818642851855</v>
+        <v>1.922818642851856</v>
       </c>
       <c r="D5" t="n">
-        <v>3.61523293147191</v>
+        <v>3.615232931471916</v>
       </c>
       <c r="E5" t="n">
-        <v>1.256559764499315</v>
+        <v>1.256559764499316</v>
       </c>
       <c r="F5" t="n">
-        <v>1.256559764499315</v>
+        <v>1.256559764499316</v>
       </c>
       <c r="G5" t="n">
-        <v>2.748987178081966</v>
+        <v>2.748987178081959</v>
       </c>
       <c r="H5" t="n">
-        <v>3.975994029891742</v>
+        <v>3.975994029891737</v>
       </c>
       <c r="I5" t="n">
         <v>1.256534299770539</v>
@@ -1853,7 +1853,7 @@
         <v>1.615635007428447</v>
       </c>
       <c r="L5" t="n">
-        <v>2.076663263989071</v>
+        <v>2.076663263989075</v>
       </c>
     </row>
     <row r="6">
@@ -1866,34 +1866,34 @@
         <v>0.2802593387844196</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2664395487582935</v>
+        <v>0.2664395487583139</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4348429162221993</v>
+        <v>0.4348429162221991</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2240011085477642</v>
+        <v>0.2240011085477645</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2288776795310205</v>
+        <v>0.2288776795310204</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3745417528294753</v>
+        <v>0.3745417528294755</v>
       </c>
       <c r="H6" t="n">
-        <v>0.43968286935135</v>
+        <v>0.4396828693513494</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2290589905664557</v>
+        <v>0.2290589905664553</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4319349025509759</v>
+        <v>0.4319349025509756</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2522264889767</v>
+        <v>0.2522264889767006</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2658614926783929</v>
+        <v>0.2658614926783928</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2854615836516433</v>
+        <v>0.2854615836516429</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3329244190101123</v>
+        <v>0.3329244190101121</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4350299712315485</v>
+        <v>0.4350299712315482</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2931631548269211</v>
+        <v>0.2931631548269215</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2931631548269211</v>
+        <v>0.2931631548269215</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3797439976966998</v>
+        <v>0.3797439976966993</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4312383656859424</v>
+        <v>0.4312383656859415</v>
       </c>
       <c r="I7" t="n">
         <v>0.2935006001009003</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4927235339137853</v>
+        <v>0.4927235339137851</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3173769567020222</v>
+        <v>0.3173769567020216</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3300865313643038</v>
+        <v>0.3300865313643036</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3200028256463495</v>
+        <v>0.3200028256463512</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4606697639162173</v>
+        <v>0.4606697639162169</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5823230832320376</v>
+        <v>0.5823230832320366</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3957045866758111</v>
+        <v>0.3957045866758112</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3310011075743795</v>
+        <v>0.3310011075743792</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5073965993184059</v>
+        <v>0.5073965993184061</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5588909673083331</v>
+        <v>0.5588909673083327</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4211532017226072</v>
+        <v>0.4211532017226069</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6203944344835987</v>
+        <v>0.6203944344835972</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3501886073968951</v>
+        <v>0.3501886073968952</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5550017338676919</v>
+        <v>0.5550017338676924</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4332300749808082</v>
+        <v>0.4332300749808074</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5525334949380806</v>
+        <v>0.5525334949380813</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6549723470800999</v>
+        <v>0.6549723470800993</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5960376045858423</v>
+        <v>0.5960376045858415</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5131350763223355</v>
+        <v>0.5131350763223349</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5993530736246684</v>
+        <v>0.5993530736246677</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6508474416139124</v>
+        <v>0.6508474416139114</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5131096760288697</v>
+        <v>0.5131096760288693</v>
       </c>
       <c r="J9" t="n">
         <v>0.7123326098417538</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4953613311331489</v>
+        <v>0.4953613311331481</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5496956072922733</v>
+        <v>0.5496956072922731</v>
       </c>
     </row>
   </sheetData>
@@ -2102,19 +2102,19 @@
         <v>2.710640647671781</v>
       </c>
       <c r="C2" t="n">
-        <v>2.553739862219772</v>
+        <v>2.553739862219771</v>
       </c>
       <c r="D2" t="n">
         <v>2.720771231262272</v>
       </c>
       <c r="E2" t="n">
-        <v>2.58719122723382</v>
+        <v>2.587191227233821</v>
       </c>
       <c r="F2" t="n">
-        <v>2.587157896465126</v>
+        <v>2.587157896465127</v>
       </c>
       <c r="G2" t="n">
-        <v>2.717002119291374</v>
+        <v>2.717002119291375</v>
       </c>
       <c r="H2" t="n">
         <v>2.71821109816561</v>
@@ -2126,10 +2126,10 @@
         <v>2.881851490222042</v>
       </c>
       <c r="K2" t="n">
-        <v>2.791879193920008</v>
+        <v>2.791879193920009</v>
       </c>
       <c r="L2" t="n">
-        <v>2.712842870157776</v>
+        <v>2.712842870157777</v>
       </c>
     </row>
     <row r="3">
@@ -2148,25 +2148,25 @@
         <v>1.925069907279844</v>
       </c>
       <c r="E3" t="n">
-        <v>1.649720473515041</v>
+        <v>1.64972047351504</v>
       </c>
       <c r="F3" t="n">
-        <v>1.649687142746346</v>
+        <v>1.649687142746345</v>
       </c>
       <c r="G3" t="n">
-        <v>1.898315518402883</v>
+        <v>1.898315518402884</v>
       </c>
       <c r="H3" t="n">
         <v>1.909322243866945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.853683463498561</v>
+        <v>1.85368346349856</v>
       </c>
       <c r="J3" t="n">
-        <v>2.214672903200109</v>
+        <v>2.21467290320011</v>
       </c>
       <c r="K3" t="n">
-        <v>1.993054620492243</v>
+        <v>1.993054620492244</v>
       </c>
       <c r="L3" t="n">
         <v>1.869189664433098</v>
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1648270122482856</v>
+        <v>0.1648270122482858</v>
       </c>
       <c r="C4" t="n">
-        <v>0.202609185564307</v>
+        <v>0.2026091855643073</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2792566142015632</v>
+        <v>0.2792566142015629</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1611185802171345</v>
+        <v>0.1611185802171347</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1611185802171346</v>
+        <v>0.1611185802171347</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2362988887080603</v>
+        <v>0.2362988887080601</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2540666778183353</v>
+        <v>0.2540666778183354</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1634668736156358</v>
+        <v>0.1634668736156361</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3275740279344935</v>
+        <v>0.3275740279344937</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1772784913405835</v>
+        <v>0.1772784913405834</v>
       </c>
       <c r="L4" t="n">
-        <v>0.190346718342442</v>
+        <v>0.1903467183424422</v>
       </c>
     </row>
     <row r="5">
@@ -2219,34 +2219,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5322587712122091</v>
+        <v>0.5322587712122095</v>
       </c>
       <c r="C5" t="n">
         <v>1.276386234215393</v>
       </c>
       <c r="D5" t="n">
-        <v>2.458851877558132</v>
+        <v>2.458851877558125</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5356923076614614</v>
+        <v>0.5356923076614621</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5356923076614614</v>
+        <v>0.5356923076614621</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7811146438136</v>
+        <v>1.781114643813601</v>
       </c>
       <c r="H5" t="n">
-        <v>2.271747863636937</v>
+        <v>2.271747863636943</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5356699525912094</v>
+        <v>0.5356699525912093</v>
       </c>
       <c r="J5" t="n">
-        <v>3.438876572210527</v>
+        <v>3.438876572210525</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7278755981733938</v>
+        <v>0.7278755981733954</v>
       </c>
       <c r="L5" t="n">
         <v>1.070120436663175</v>
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1781462586575106</v>
+        <v>0.1781462586575109</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2193451176565651</v>
+        <v>0.2193451176565535</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2949837465925787</v>
+        <v>0.2949837465925652</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1719984743296438</v>
+        <v>0.1719984743296442</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1765709810324999</v>
+        <v>0.1765709810325001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3043984448485126</v>
+        <v>0.3043984448485125</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3343851507296247</v>
+        <v>0.3343851507296242</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2315664297560885</v>
+        <v>0.2315664297560888</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4014313336007401</v>
+        <v>0.4014313336007402</v>
       </c>
       <c r="K6" t="n">
-        <v>0.189899922844478</v>
+        <v>0.1898999228444744</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2037360143231537</v>
+        <v>0.203736014323154</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.239589170911841</v>
+        <v>0.2395891709118414</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2825626585655373</v>
+        <v>0.2825626585655374</v>
       </c>
       <c r="D7" t="n">
         <v>0.353685641589742</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2378336675038976</v>
+        <v>0.2378336675038979</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2378336675038976</v>
+        <v>0.2378336675038979</v>
       </c>
       <c r="G7" t="n">
         <v>0.3110610473716157</v>
       </c>
       <c r="H7" t="n">
-        <v>0.328828836481891</v>
+        <v>0.3288288364818912</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2382290322791915</v>
+        <v>0.2382290322791918</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4023361865980492</v>
+        <v>0.4023361865980494</v>
       </c>
       <c r="K7" t="n">
-        <v>0.252040650004139</v>
+        <v>0.2520406500041392</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2651088770059976</v>
+        <v>0.2651088770059978</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2703992434979441</v>
+        <v>0.2703992434979444</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4004053568123031</v>
+        <v>0.4004053568123034</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4898613205207111</v>
+        <v>0.4898613205207105</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3322062046579313</v>
+        <v>0.3322062046579323</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2717685664780897</v>
+        <v>0.2717685664780901</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4288648735213333</v>
+        <v>0.428864873521334</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4466326626320772</v>
+        <v>0.4466326626320777</v>
       </c>
       <c r="I8" t="n">
         <v>0.3560328584289094</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5201571093946983</v>
+        <v>0.5201571093946986</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2812347689656903</v>
+        <v>0.2812347689656902</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4737849529418532</v>
+        <v>0.4737849529418534</v>
       </c>
     </row>
     <row r="9">
@@ -2382,34 +2382,34 @@
         <v>0.3573772632016988</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4622692729649849</v>
+        <v>0.4622692729649855</v>
       </c>
       <c r="D9" t="n">
-        <v>0.533725418754678</v>
+        <v>0.5337254187546782</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4894106312056536</v>
+        <v>0.4894106312056539</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4179579532374034</v>
+        <v>0.4179579532374036</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4907676617710631</v>
+        <v>0.490767661771063</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5085354508813392</v>
+        <v>0.5085354508813391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4179356466786392</v>
+        <v>0.4179356466786397</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5820428009974967</v>
+        <v>0.5820428009974969</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3944159140856938</v>
+        <v>0.3944159140856939</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4448154914054454</v>
+        <v>0.4448154914054458</v>
       </c>
     </row>
   </sheetData>
@@ -2498,34 +2498,34 @@
         <v>2.696351467626154</v>
       </c>
       <c r="C2" t="n">
-        <v>2.543904712413931</v>
+        <v>2.543904712413932</v>
       </c>
       <c r="D2" t="n">
         <v>2.708335702400564</v>
       </c>
       <c r="E2" t="n">
-        <v>2.583547873583396</v>
+        <v>2.583547873583397</v>
       </c>
       <c r="F2" t="n">
-        <v>2.583514484312825</v>
+        <v>2.583514484312826</v>
       </c>
       <c r="G2" t="n">
         <v>2.706568639069444</v>
       </c>
       <c r="H2" t="n">
-        <v>2.718713463937498</v>
+        <v>2.7187134639375</v>
       </c>
       <c r="I2" t="n">
-        <v>2.697847373797753</v>
+        <v>2.697847373797755</v>
       </c>
       <c r="J2" t="n">
         <v>2.890904825157736</v>
       </c>
       <c r="K2" t="n">
-        <v>2.790449178907025</v>
+        <v>2.790449178907026</v>
       </c>
       <c r="L2" t="n">
-        <v>2.706812412488986</v>
+        <v>2.706812412488988</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.836966938368599</v>
+        <v>1.8369669383686</v>
       </c>
       <c r="C3" t="n">
         <v>1.58186979864411</v>
       </c>
       <c r="D3" t="n">
-        <v>1.922279839620896</v>
+        <v>1.922279839620897</v>
       </c>
       <c r="E3" t="n">
-        <v>1.658911438163719</v>
+        <v>1.658911438163718</v>
       </c>
       <c r="F3" t="n">
-        <v>1.658878048893149</v>
+        <v>1.658878048893148</v>
       </c>
       <c r="G3" t="n">
         <v>1.909829097870338</v>
       </c>
       <c r="H3" t="n">
-        <v>1.998758432912308</v>
+        <v>1.998758432912309</v>
       </c>
       <c r="I3" t="n">
         <v>1.847595841741117</v>
       </c>
       <c r="J3" t="n">
-        <v>2.294479375410507</v>
+        <v>2.294479375410508</v>
       </c>
       <c r="K3" t="n">
-        <v>2.035843809923911</v>
+        <v>2.035843809923913</v>
       </c>
       <c r="L3" t="n">
-        <v>1.912185513679936</v>
+        <v>1.912185513679937</v>
       </c>
     </row>
     <row r="4">
@@ -2575,34 +2575,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1750228028066895</v>
+        <v>0.1750228028066896</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1636908799278193</v>
+        <v>0.1636908799278195</v>
       </c>
       <c r="D4" t="n">
-        <v>0.310390247604033</v>
+        <v>0.3103902476040328</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1873803975326692</v>
+        <v>0.1873803975326696</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1873803975326692</v>
+        <v>0.1873803975326696</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2900357809689784</v>
+        <v>0.2900357809689788</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4301907759912297</v>
+        <v>0.4301907759912303</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1892858367871116</v>
+        <v>0.189285836787112</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4555804375430818</v>
+        <v>0.4555804375430824</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2649827329183843</v>
+        <v>0.2649827329183845</v>
       </c>
       <c r="L4" t="n">
         <v>0.2932708596439262</v>
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6434410118693328</v>
+        <v>0.643441011869335</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4960944626985882</v>
+        <v>0.4960944626985883</v>
       </c>
       <c r="D5" t="n">
-        <v>3.043691879840273</v>
+        <v>3.043691879840272</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9294475058436402</v>
+        <v>0.9294475058436472</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9294475058436402</v>
+        <v>0.9294475058436472</v>
       </c>
       <c r="G5" t="n">
-        <v>2.759720836974957</v>
+        <v>2.759720836974962</v>
       </c>
       <c r="H5" t="n">
-        <v>5.827084812092125</v>
+        <v>5.827084812092123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9294187781524996</v>
+        <v>0.929418778152509</v>
       </c>
       <c r="J5" t="n">
-        <v>5.91898029924357</v>
+        <v>5.918980299243574</v>
       </c>
       <c r="K5" t="n">
-        <v>2.239760034886215</v>
+        <v>2.239760034886213</v>
       </c>
       <c r="L5" t="n">
-        <v>3.124525720100187</v>
+        <v>3.12452572010019</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1874121843723472</v>
+        <v>0.1874121843723477</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1753876265121798</v>
+        <v>0.175387626512198</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3247022374715754</v>
+        <v>0.3247022374715759</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1964600732656029</v>
+        <v>0.196460073265627</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2015255769990408</v>
+        <v>0.2015255769990412</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3024251625346357</v>
+        <v>0.3024251625346368</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5156439943273478</v>
+        <v>0.5156439943273493</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2621154874137155</v>
+        <v>0.2621154874137161</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4718404984803671</v>
+        <v>0.4718404984803679</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2776968964372155</v>
+        <v>0.2776968964372162</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3063641701635079</v>
+        <v>0.3063641701635078</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2584811491274653</v>
+        <v>0.2584811491274658</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2507370893893633</v>
+        <v>0.2507370893893638</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3934963395113206</v>
+        <v>0.3934963395113208</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2725707135124734</v>
+        <v>0.2725707135124741</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2725707135124734</v>
+        <v>0.2725707135124741</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3734941272897543</v>
+        <v>0.3734941272897547</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5136491223120049</v>
+        <v>0.5136491223120061</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2727441831078875</v>
+        <v>0.2727441831078882</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5390387838638576</v>
+        <v>0.5390387838638583</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3484410792391605</v>
+        <v>0.348441079239161</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3767292059647021</v>
+        <v>0.3767292059647027</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2935015661358948</v>
+        <v>0.2935015661358953</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3819058940562411</v>
+        <v>0.3819058940562423</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5446270433144847</v>
+        <v>0.5446270433144859</v>
       </c>
       <c r="E8" t="n">
-        <v>0.377594150824803</v>
+        <v>0.3775941508248036</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3109220052600994</v>
+        <v>0.3109220052601002</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5043918025945243</v>
+        <v>0.5043918025945258</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6445467976171464</v>
+        <v>0.6445467976171477</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4036418584126579</v>
+        <v>0.4036418584126588</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6699553017125448</v>
+        <v>0.6699553017125467</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3816805269583011</v>
+        <v>0.3816805269583015</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6077786946087351</v>
+        <v>0.6077786946087363</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4275645768024521</v>
+        <v>0.4275645768024532</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4986272200361259</v>
+        <v>0.4986272200361272</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6417387455272373</v>
+        <v>0.6417387455272396</v>
       </c>
       <c r="E9" t="n">
-        <v>0.611604217734708</v>
+        <v>0.61160421773471</v>
       </c>
       <c r="F9" t="n">
-        <v>0.52066295591621</v>
+        <v>0.5206629559162119</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6213842579365165</v>
+        <v>0.6213842579365181</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7615392529587673</v>
+        <v>0.7615392529587689</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5206343137546501</v>
+        <v>0.5206343137546516</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7869289145106205</v>
+        <v>0.7869289145106222</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5506703055001454</v>
+        <v>0.5506703055001461</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6246193366114648</v>
+        <v>0.624619336611466</v>
       </c>
     </row>
   </sheetData>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.668724763730048</v>
+        <v>2.66872476373005</v>
       </c>
       <c r="C2" t="n">
-        <v>2.523589258744617</v>
+        <v>2.523589258744616</v>
       </c>
       <c r="D2" t="n">
         <v>2.669335654386002</v>
       </c>
       <c r="E2" t="n">
-        <v>2.558850747757798</v>
+        <v>2.558850747757799</v>
       </c>
       <c r="F2" t="n">
         <v>2.558817225517998</v>
@@ -2909,19 +2909,19 @@
         <v>2.670441816574735</v>
       </c>
       <c r="H2" t="n">
-        <v>2.669707149480625</v>
+        <v>2.669707149480626</v>
       </c>
       <c r="I2" t="n">
-        <v>2.669273127317123</v>
+        <v>2.669273127317124</v>
       </c>
       <c r="J2" t="n">
-        <v>2.846697062373321</v>
+        <v>2.84669706237332</v>
       </c>
       <c r="K2" t="n">
-        <v>2.754174780407543</v>
+        <v>2.754174780407545</v>
       </c>
       <c r="L2" t="n">
-        <v>2.670742289686927</v>
+        <v>2.670742289686928</v>
       </c>
     </row>
     <row r="3">
@@ -2943,7 +2943,7 @@
         <v>1.623821234294428</v>
       </c>
       <c r="F3" t="n">
-        <v>1.623787712054628</v>
+        <v>1.623787712054627</v>
       </c>
       <c r="G3" t="n">
         <v>1.814452288503936</v>
@@ -2955,7 +2955,7 @@
         <v>1.806105349411575</v>
       </c>
       <c r="J3" t="n">
-        <v>2.14720773753771</v>
+        <v>2.147207737537709</v>
       </c>
       <c r="K3" t="n">
         <v>1.947581746445444</v>
@@ -2971,34 +2971,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1400994484985328</v>
+        <v>0.140099448498533</v>
       </c>
       <c r="C4" t="n">
         <v>0.1360083398021308</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1469997394810972</v>
+        <v>0.1469997394810973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1428170332287296</v>
+        <v>0.1428170332287295</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1428170332287296</v>
+        <v>0.1428170332287295</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1591525749069663</v>
+        <v>0.1591525749069659</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1547745356012862</v>
+        <v>0.1547745356012864</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1440147678201043</v>
+        <v>0.1440147678201044</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2454816983776131</v>
+        <v>0.2454816983776129</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1490465958850828</v>
+        <v>0.149046595885083</v>
       </c>
       <c r="L4" t="n">
         <v>0.1625339376320593</v>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3131941850741933</v>
+        <v>0.3131941850741924</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2772644332010148</v>
+        <v>0.2772644332010145</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4171550323596112</v>
+        <v>0.41715503235961</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4057426935909301</v>
+        <v>0.4057426935909307</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4057426935909301</v>
+        <v>0.4057426935909307</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6442311540433995</v>
+        <v>0.6442311540434075</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6047268654950828</v>
+        <v>0.604726865495083</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4057336775905366</v>
+        <v>0.4057336775905364</v>
       </c>
       <c r="J5" t="n">
-        <v>2.190592869347693</v>
+        <v>2.190592869347692</v>
       </c>
       <c r="K5" t="n">
-        <v>0.453307346643156</v>
+        <v>0.4533073466431559</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7656513185570049</v>
+        <v>0.7656513185570053</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1468883110529033</v>
+        <v>0.1468883110529018</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1436936700887354</v>
+        <v>0.1436936700887348</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2031087469644644</v>
+        <v>0.203108746964465</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1482369651291698</v>
+        <v>0.1482369651291743</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1507757100641955</v>
+        <v>0.1507757100641954</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1659414374613366</v>
+        <v>0.1659414374613364</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2174883001563769</v>
+        <v>0.2174883001563763</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1971140740804155</v>
+        <v>0.1971140740804154</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3029719014194364</v>
+        <v>0.3029719014194348</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1556357253264697</v>
+        <v>0.1556357253264675</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1694801175472095</v>
+        <v>0.1694801175472098</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2073500358250863</v>
+        <v>0.2073500358250845</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2056696406139912</v>
+        <v>0.2056696406139905</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2139168392875242</v>
+        <v>0.2139168392875238</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2110189397807544</v>
+        <v>0.2110189397807543</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2110189397807544</v>
+        <v>0.2110189397807543</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2264031622335205</v>
+        <v>0.2264031622335199</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2220251229278401</v>
+        <v>0.2220251229278384</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2112653551466585</v>
+        <v>0.2112653551466584</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3127322857041671</v>
+        <v>0.3127322857041649</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2162971832116367</v>
+        <v>0.2162971832116349</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2297845249586133</v>
+        <v>0.2297845249586147</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2310258984243551</v>
+        <v>0.2310258984243539</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3039378706779037</v>
+        <v>0.3039378706779031</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3277537282179132</v>
+        <v>0.3277537282179125</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2890824412472918</v>
+        <v>0.2890824412472922</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2373551688117279</v>
+        <v>0.237355168811728</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3244792021989104</v>
+        <v>0.3244792021989101</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3201011628934995</v>
+        <v>0.3201011628934986</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3093413951120489</v>
+        <v>0.3093413951120485</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4108229473682077</v>
+        <v>0.4108229473682057</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2385910243251597</v>
+        <v>0.2385910243251595</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4055777713621138</v>
+        <v>0.4055777713621134</v>
       </c>
     </row>
     <row r="9">
@@ -3171,34 +3171,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3181458019348795</v>
+        <v>0.3181458019348802</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3729417824720875</v>
+        <v>0.3729417824720876</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3815224863704527</v>
+        <v>0.3815224863704528</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4437190350704228</v>
+        <v>0.4437190350704229</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3785464857568716</v>
+        <v>0.3785464857568717</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3936753040916179</v>
+        <v>0.3936753040916177</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3892972647859373</v>
+        <v>0.3892972647859391</v>
       </c>
       <c r="I9" t="n">
         <v>0.3785374970047559</v>
       </c>
       <c r="J9" t="n">
-        <v>0.480004427562264</v>
+        <v>0.4800044275622652</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3508466986078541</v>
+        <v>0.3508466986078542</v>
       </c>
       <c r="L9" t="n">
         <v>0.3970566668167109</v>
@@ -3293,13 +3293,13 @@
         <v>2.516551516923005</v>
       </c>
       <c r="D2" t="n">
-        <v>2.659405027091219</v>
+        <v>2.65940502709122</v>
       </c>
       <c r="E2" t="n">
         <v>2.551693935410417</v>
       </c>
       <c r="F2" t="n">
-        <v>2.551660309154605</v>
+        <v>2.551660309154606</v>
       </c>
       <c r="G2" t="n">
         <v>2.659524488409336</v>
@@ -3311,13 +3311,13 @@
         <v>2.659510547208884</v>
       </c>
       <c r="J2" t="n">
-        <v>2.824283759730192</v>
+        <v>2.824283759730193</v>
       </c>
       <c r="K2" t="n">
         <v>2.749259719553034</v>
       </c>
       <c r="L2" t="n">
-        <v>2.659333790657549</v>
+        <v>2.659333790657548</v>
       </c>
     </row>
     <row r="3">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.791375412062975</v>
+        <v>1.791375412062976</v>
       </c>
       <c r="C3" t="n">
         <v>1.55564660732573</v>
@@ -3351,13 +3351,13 @@
         <v>1.793692252413304</v>
       </c>
       <c r="J3" t="n">
-        <v>2.072060711516901</v>
+        <v>2.072060711516902</v>
       </c>
       <c r="K3" t="n">
         <v>1.939029102648854</v>
       </c>
       <c r="L3" t="n">
-        <v>1.792280203675552</v>
+        <v>1.792280203675553</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1286422355170527</v>
+        <v>0.1286422355170547</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1259803665249627</v>
+        <v>0.1259803665249616</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1311570392220613</v>
+        <v>0.1311570392220623</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1285452497021863</v>
+        <v>0.1285452497021862</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1285452497021863</v>
+        <v>0.1285452497021862</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1321729714578227</v>
+        <v>0.1321729714578045</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1319368169715807</v>
+        <v>0.1319368169715791</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1301239485388715</v>
+        <v>0.1301239485388749</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1454409547785495</v>
+        <v>0.1454409547785502</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1265530479923536</v>
+        <v>0.1265530479923537</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1299839611283968</v>
+        <v>0.1299839611283952</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2704106943178555</v>
+        <v>0.270410694317851</v>
       </c>
       <c r="C5" t="n">
         <v>0.2493538995606449</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3005252504432027</v>
+        <v>0.3005252504432026</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3206689176762603</v>
+        <v>0.3206689176762604</v>
       </c>
       <c r="F5" t="n">
         <v>0.3206689176762603</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3296199230942624</v>
+        <v>0.3296199230942509</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3402647878850544</v>
+        <v>0.3402647878850564</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3206629361503473</v>
+        <v>0.3206629361503498</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5653900855831347</v>
+        <v>0.5653900855831352</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2227398533017923</v>
+        <v>0.2227398533017906</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3067876542152243</v>
+        <v>0.3067876542152247</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1738739347221765</v>
+        <v>0.173873934722175</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1307836704066637</v>
+        <v>0.1307836704066642</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1352684032285383</v>
+        <v>0.1352684032285355</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1322541498876076</v>
+        <v>0.1322541498876165</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1340410764734633</v>
+        <v>0.1340410764734631</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1774046706629271</v>
+        <v>0.1774046706629247</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1360070952518803</v>
+        <v>0.1360070952518814</v>
       </c>
       <c r="I6" t="n">
         <v>0.1753556477439951</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1508532520459896</v>
+        <v>0.1508532520459909</v>
       </c>
       <c r="K6" t="n">
-        <v>0.130170571895827</v>
+        <v>0.1301705718958275</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1340368778523599</v>
+        <v>0.1340368778523592</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1906229166991071</v>
+        <v>0.1906229166991066</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1898188970708866</v>
+        <v>0.189818897070886</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1928041923666527</v>
+        <v>0.1928041923666513</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1916808321567146</v>
+        <v>0.1916808321567144</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1916808321567146</v>
+        <v>0.1916808321567144</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1941536526398556</v>
+        <v>0.1941536526398553</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1939174981536319</v>
+        <v>0.193917498153631</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1921046297209266</v>
+        <v>0.1921046297209265</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2074216359606023</v>
+        <v>0.2074216359606017</v>
       </c>
       <c r="K7" t="n">
-        <v>0.188533729174408</v>
+        <v>0.1885337291744054</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1919646423104479</v>
+        <v>0.191964642310447</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2091956852254691</v>
+        <v>0.2091956852254686</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2737054368000653</v>
+        <v>0.273705436800065</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2905388857120154</v>
+        <v>0.2905388857120155</v>
       </c>
       <c r="E8" t="n">
         <v>0.2580464194287915</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2126955559131645</v>
+        <v>0.2126955559131646</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2780164956745606</v>
+        <v>0.2780164956745603</v>
       </c>
       <c r="H8" t="n">
-        <v>0.277780341188487</v>
+        <v>0.2777803411884868</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2759674727556306</v>
+        <v>0.2759674727556304</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2912973103358228</v>
+        <v>0.2912973103358196</v>
       </c>
       <c r="K8" t="n">
-        <v>0.205893701049385</v>
+        <v>0.2058937010493823</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3440284276089851</v>
+        <v>0.3440284276089847</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2870114225428326</v>
+        <v>0.2870114225428329</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3361454687683438</v>
+        <v>0.3361454687683439</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3394643006332719</v>
+        <v>0.3394643006332694</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3960646285802478</v>
+        <v>0.3960646285802487</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3384371579733424</v>
+        <v>0.3384371579733428</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3404802243373147</v>
+        <v>0.3404802243373136</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3402440698510879</v>
+        <v>0.3402440698510875</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3384312014183837</v>
+        <v>0.3384312014183838</v>
       </c>
       <c r="J9" t="n">
-        <v>0.35374820765806</v>
+        <v>0.3537482076580594</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3059259929826915</v>
+        <v>0.3059259929826916</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3382912140079049</v>
+        <v>0.3382912140079036</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.669537695904298</v>
+        <v>2.669537695904292</v>
       </c>
       <c r="C2" t="n">
-        <v>2.524600626140154</v>
+        <v>2.524600626140147</v>
       </c>
       <c r="D2" t="n">
-        <v>2.671951836849842</v>
+        <v>2.671951836849844</v>
       </c>
       <c r="E2" t="n">
-        <v>2.56610622995118</v>
+        <v>2.56610622995117</v>
       </c>
       <c r="F2" t="n">
-        <v>2.566072758248604</v>
+        <v>2.566072758248595</v>
       </c>
       <c r="G2" t="n">
-        <v>2.674253781160294</v>
+        <v>2.674253781160293</v>
       </c>
       <c r="H2" t="n">
-        <v>2.688589290427755</v>
+        <v>2.688589290427749</v>
       </c>
       <c r="I2" t="n">
-        <v>2.670095353790204</v>
+        <v>2.670095353790202</v>
       </c>
       <c r="J2" t="n">
-        <v>2.854739493578245</v>
+        <v>2.854739493578241</v>
       </c>
       <c r="K2" t="n">
-        <v>2.76210978975725</v>
+        <v>2.762109789757243</v>
       </c>
       <c r="L2" t="n">
-        <v>2.678432662390561</v>
+        <v>2.678432662390559</v>
       </c>
     </row>
     <row r="3">
@@ -3729,16 +3729,16 @@
         <v>1.559462189149482</v>
       </c>
       <c r="D3" t="n">
-        <v>1.818233045078902</v>
+        <v>1.818233045078901</v>
       </c>
       <c r="E3" t="n">
-        <v>1.633353015954029</v>
+        <v>1.633353015954027</v>
       </c>
       <c r="F3" t="n">
-        <v>1.633319544251456</v>
+        <v>1.633319544251454</v>
       </c>
       <c r="G3" t="n">
-        <v>1.834692530302356</v>
+        <v>1.834692530302357</v>
       </c>
       <c r="H3" t="n">
         <v>1.938706018553496</v>
@@ -3750,7 +3750,7 @@
         <v>2.15191779992142</v>
       </c>
       <c r="K3" t="n">
-        <v>1.966860737958236</v>
+        <v>1.966860737958237</v>
       </c>
       <c r="L3" t="n">
         <v>1.864499820629071</v>
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.153527377394995</v>
+        <v>0.1535273773949944</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1455026109928975</v>
+        <v>0.1455026109928972</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1807962099347094</v>
+        <v>0.1807962099347086</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1559868670216271</v>
+        <v>0.1559868670216272</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1559868670216271</v>
+        <v>0.155986867021627</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2064362148770183</v>
+        <v>0.2064362148770181</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3706019781861548</v>
+        <v>0.370601978186154</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1574153857486677</v>
+        <v>0.1574153857486676</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2464080168926493</v>
+        <v>0.2464080168926495</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1803831723370181</v>
+        <v>0.1803831723370183</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2531721347034626</v>
+        <v>0.2531721347034638</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4136350695088464</v>
+        <v>0.4136350695088463</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3106036098669467</v>
+        <v>0.3106036098669476</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8854484816432826</v>
+        <v>0.8854484816432805</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5117424848435472</v>
+        <v>0.5117424848435471</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5117424848435473</v>
+        <v>0.5117424848435471</v>
       </c>
       <c r="G5" t="n">
-        <v>1.385793093835999</v>
+        <v>1.385793093835989</v>
       </c>
       <c r="H5" t="n">
-        <v>4.807701402125008</v>
+        <v>4.807701402125002</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5117256691925196</v>
+        <v>0.5117256691925206</v>
       </c>
       <c r="J5" t="n">
-        <v>2.157114830456456</v>
+        <v>2.157114830456464</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8810988773225937</v>
+        <v>0.8810988773225941</v>
       </c>
       <c r="L5" t="n">
-        <v>2.486022026966982</v>
+        <v>2.48602202696698</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1615823968789442</v>
+        <v>0.161582396878944</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1537597000280754</v>
+        <v>0.1537597000280699</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1886260645674199</v>
+        <v>0.1886260645674197</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1618142497890046</v>
+        <v>0.1618142497890002</v>
       </c>
       <c r="F6" t="n">
         <v>0.1653765647152101</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2144912343609672</v>
+        <v>0.2144912343609676</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4454835680499867</v>
+        <v>0.4454835680499866</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1654704052326175</v>
+        <v>0.1654704052326173</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2569214303532773</v>
+        <v>0.2569214303532763</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1880724675943885</v>
+        <v>0.1880724675943898</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2618298578780888</v>
+        <v>0.2618298578780897</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2301418430300917</v>
+        <v>0.2301418430300913</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2248695029806621</v>
+        <v>0.2248695029806631</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2570584626459488</v>
+        <v>0.2570584626459485</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2338394047308199</v>
+        <v>0.2338394047308198</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2338394047308199</v>
+        <v>0.2338394047308198</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2830506805121155</v>
+        <v>0.2830506805121148</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4472164438212524</v>
+        <v>0.447216443821251</v>
       </c>
       <c r="I7" t="n">
         <v>0.2340298513837646</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3230224825277474</v>
+        <v>0.3230224825277464</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2569976379721145</v>
+        <v>0.2569976379721153</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3297866003385604</v>
+        <v>0.3297866003385608</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2600245062453864</v>
+        <v>0.2600245062453862</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3418143243757924</v>
+        <v>0.3418143243757922</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3920890913636658</v>
+        <v>0.3920890913636657</v>
       </c>
       <c r="E8" t="n">
         <v>0.3271278006460832</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2667671530236577</v>
+        <v>0.2667671530236579</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3997310305199762</v>
+        <v>0.3997310305199759</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5638967938295143</v>
+        <v>0.5638967938295144</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3507102013916258</v>
+        <v>0.3507102013916256</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4397198906884744</v>
+        <v>0.4397198906884722</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2852679895998313</v>
+        <v>0.2852679895998314</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5371343920331867</v>
+        <v>0.5371343920331856</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3729792854711616</v>
+        <v>0.3729792854711615</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4367241757354599</v>
+        <v>0.4367241757354592</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4692653375776836</v>
+        <v>0.4692653375776832</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5255456504781444</v>
+        <v>0.5255456504781446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4459012598081255</v>
+        <v>0.4459012598081254</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4949053532669138</v>
+        <v>0.4949053532669124</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6590711165760509</v>
+        <v>0.6590711165760491</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4458845241385628</v>
+        <v>0.4458845241385626</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5348771552825453</v>
+        <v>0.5348771552825449</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4288634519114504</v>
+        <v>0.4288634519114494</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5416412730933594</v>
+        <v>0.5416412730933592</v>
       </c>
     </row>
   </sheetData>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.623976826307904</v>
+        <v>2.623976826307903</v>
       </c>
       <c r="C2" t="n">
-        <v>2.495638970720225</v>
+        <v>2.495638970720224</v>
       </c>
       <c r="D2" t="n">
         <v>2.62465892328168</v>
@@ -4094,22 +4094,22 @@
         <v>2.531062768403281</v>
       </c>
       <c r="G2" t="n">
-        <v>2.624396549169136</v>
+        <v>2.624396549169135</v>
       </c>
       <c r="H2" t="n">
-        <v>2.62437993448968</v>
+        <v>2.624379934489681</v>
       </c>
       <c r="I2" t="n">
-        <v>2.62393274197334</v>
+        <v>2.623932741973339</v>
       </c>
       <c r="J2" t="n">
-        <v>2.813001260517243</v>
+        <v>2.813001260517242</v>
       </c>
       <c r="K2" t="n">
         <v>2.714610463502833</v>
       </c>
       <c r="L2" t="n">
-        <v>2.624806481536969</v>
+        <v>2.62480648153697</v>
       </c>
     </row>
     <row r="3">
@@ -4122,16 +4122,16 @@
         <v>1.748976218939165</v>
       </c>
       <c r="C3" t="n">
-        <v>1.538685459937586</v>
+        <v>1.538685459937585</v>
       </c>
       <c r="D3" t="n">
-        <v>1.753814379315137</v>
+        <v>1.753814379315136</v>
       </c>
       <c r="E3" t="n">
         <v>1.59538882768105</v>
       </c>
       <c r="F3" t="n">
-        <v>1.595355223734528</v>
+        <v>1.595355223734529</v>
       </c>
       <c r="G3" t="n">
         <v>1.751954677230468</v>
@@ -4143,7 +4143,7 @@
         <v>1.748643713153985</v>
       </c>
       <c r="J3" t="n">
-        <v>2.063287558116062</v>
+        <v>2.063287558116061</v>
       </c>
       <c r="K3" t="n">
         <v>1.894173893574779</v>
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1244740123583563</v>
+        <v>0.1244740123583567</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1254650350560515</v>
+        <v>0.1254650350560543</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1321786114572533</v>
+        <v>0.132178611457254</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1204905861108784</v>
+        <v>0.1204905861108787</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1204905861108784</v>
+        <v>0.1204905861108787</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1288846349984648</v>
+        <v>0.128884634998466</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1323379779286728</v>
+        <v>0.1323379779286734</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1217716247888579</v>
+        <v>0.1217716247888582</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1292155087643806</v>
+        <v>0.1292155087643811</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1154122811744709</v>
+        <v>0.1154122811744699</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1333717678062634</v>
+        <v>0.1333717678062631</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1875106296531441</v>
+        <v>0.1875106296531447</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2332325810992492</v>
+        <v>0.233232581099252</v>
       </c>
       <c r="D5" t="n">
-        <v>0.308232578036173</v>
+        <v>0.3082325780361736</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1672436530379453</v>
+        <v>0.1672436530379456</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1672436530379453</v>
+        <v>0.1672436530379456</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2621576011392783</v>
+        <v>0.2621576011392896</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3370885757969852</v>
+        <v>0.3370885757969854</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1672364885158375</v>
+        <v>0.1672364885158377</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2656159303055378</v>
+        <v>0.2656159303055361</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0229256850107275</v>
+        <v>0.02292568501072864</v>
       </c>
       <c r="L5" t="n">
-        <v>0.361812485225479</v>
+        <v>0.3618124852254782</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1696744098142167</v>
+        <v>0.1696744098142179</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1300686827367908</v>
+        <v>0.1300686827367665</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1359682383637946</v>
+        <v>0.1359682383637941</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1233410273280624</v>
+        <v>0.1233410273280627</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1252472893110385</v>
+        <v>0.1252472893110389</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1324197333952042</v>
+        <v>0.1324197333952045</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1871520484470276</v>
+        <v>0.1871520484470289</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1669720222447185</v>
+        <v>0.1669720222447192</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1341339658613367</v>
+        <v>0.1341339658613368</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1182224407780675</v>
+        <v>0.1182224407780686</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1370430101235675</v>
+        <v>0.1370430101235673</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.186676370293731</v>
+        <v>0.1866763702937305</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1896805379325171</v>
+        <v>0.1896805379325195</v>
       </c>
       <c r="D7" t="n">
         <v>0.1940475211910541</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1836603863923269</v>
+        <v>0.1836603863923272</v>
       </c>
       <c r="F7" t="n">
-        <v>0.183660386392327</v>
+        <v>0.1836603863923272</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1910869929338398</v>
+        <v>0.1910869929338399</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1945403358640475</v>
+        <v>0.194540335864047</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1839739827242328</v>
+        <v>0.1839739827242332</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1914178666997556</v>
+        <v>0.1914178666997564</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1776146391098456</v>
+        <v>0.1776146391098457</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1955741257416377</v>
+        <v>0.1955741257416385</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.205551788493343</v>
+        <v>0.205551788493344</v>
       </c>
       <c r="C8" t="n">
-        <v>0.274790077266022</v>
+        <v>0.2747900772660242</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2930700802934285</v>
+        <v>0.2930700802934294</v>
       </c>
       <c r="E8" t="n">
         <v>0.2509057538172546</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2049595970174451</v>
+        <v>0.204959597017445</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2760685626734925</v>
+        <v>0.276068562673492</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2795219056042218</v>
+        <v>0.2795219056042213</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2689555524638846</v>
+        <v>0.2689555524638861</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2764124281524773</v>
+        <v>0.2764124281524762</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1952621016093671</v>
+        <v>0.1952621016093667</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3496090984348156</v>
+        <v>0.3496090984348163</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2905110045444019</v>
+        <v>0.2905110045444024</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3457840051751468</v>
+        <v>0.3457840051751491</v>
       </c>
       <c r="D9" t="n">
-        <v>0.350484443767783</v>
+        <v>0.3504844437677824</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4004017129336608</v>
+        <v>0.4004017129336615</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3400845880910521</v>
+        <v>0.3400845880910528</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3471904601764692</v>
+        <v>0.3471904601764706</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3506438031066773</v>
+        <v>0.3506438031066774</v>
       </c>
       <c r="I9" t="n">
-        <v>0.340077449966863</v>
+        <v>0.3400774499668635</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3475213339423853</v>
+        <v>0.3475213339423863</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2679023138133176</v>
+        <v>0.2679023138133164</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3516775929842679</v>
+        <v>0.351677592984269</v>
       </c>
     </row>
   </sheetData>
@@ -4478,16 +4478,16 @@
         <v>2.595464378300613</v>
       </c>
       <c r="C2" t="n">
-        <v>2.463530286422067</v>
+        <v>2.463530286422068</v>
       </c>
       <c r="D2" t="n">
         <v>2.595820095469023</v>
       </c>
       <c r="E2" t="n">
-        <v>2.505922112338837</v>
+        <v>2.505922112338838</v>
       </c>
       <c r="F2" t="n">
-        <v>2.505888334286863</v>
+        <v>2.505888334286864</v>
       </c>
       <c r="G2" t="n">
         <v>2.595619021271621</v>
@@ -4502,7 +4502,7 @@
         <v>2.77553257435705</v>
       </c>
       <c r="K2" t="n">
-        <v>2.695147488922819</v>
+        <v>2.69514748892282</v>
       </c>
       <c r="L2" t="n">
         <v>2.596016148526422</v>
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1129621639317344</v>
+        <v>0.1129621639317356</v>
       </c>
       <c r="C4" t="n">
         <v>0.114325784635968</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1169801529868915</v>
+        <v>0.1169801529868931</v>
       </c>
       <c r="E4" t="n">
-        <v>0.108548053788013</v>
+        <v>0.1085480537880131</v>
       </c>
       <c r="F4" t="n">
-        <v>0.108548053788013</v>
+        <v>0.1085480537880131</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1144088943564471</v>
+        <v>0.1144088943564477</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1177395288265596</v>
+        <v>0.11773952882656</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1091228778900011</v>
+        <v>0.1091228778900013</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1124957391994071</v>
+        <v>0.1124957391994087</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1041848311448697</v>
+        <v>0.1041848311448715</v>
       </c>
       <c r="L4" t="n">
-        <v>0.118669477450708</v>
+        <v>0.1186694774507095</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1759383609957674</v>
+        <v>0.1759383609957696</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2148917187865158</v>
+        <v>0.2148917187865172</v>
       </c>
       <c r="D5" t="n">
-        <v>0.233915660295884</v>
+        <v>0.2339156602958861</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1328323214504421</v>
+        <v>0.1328323214504422</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1328323214504421</v>
+        <v>0.1328323214504422</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1980439786905346</v>
+        <v>0.1980439786905429</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2656792801083386</v>
+        <v>0.2656792801083411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1328256200137016</v>
+        <v>0.1328256200137018</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1607262630706824</v>
+        <v>0.1607262630706838</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01610444955151166</v>
+        <v>0.0161044495515125</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2871259101135135</v>
+        <v>0.2871259101135219</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.14859322302457</v>
+        <v>0.1485932230245733</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1152804550181281</v>
+        <v>0.1152804550181283</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1174485903465446</v>
+        <v>0.1174485903465471</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1084231193739385</v>
+        <v>0.1084231193739386</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1095404142890824</v>
+        <v>0.1095404142890825</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1148519685385911</v>
+        <v>0.1148519685385936</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1610596694790183</v>
+        <v>0.1610596694790197</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1095659520721471</v>
+        <v>0.1095659520721473</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1515213000345344</v>
+        <v>0.1515213000345362</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1038512755750512</v>
+        <v>0.1038512755750543</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1192607688333735</v>
+        <v>0.1192607688333747</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1700762607627879</v>
+        <v>0.1700762607627903</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1727092706700977</v>
+        <v>0.1727092706700958</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1737605885906801</v>
+        <v>0.1737605885906811</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1660827134473562</v>
+        <v>0.1660827134473564</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1660827134473562</v>
+        <v>0.1660827134473564</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1715229911875009</v>
+        <v>0.1715229911875021</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1748536256576125</v>
+        <v>0.1748536256576146</v>
       </c>
       <c r="I7" t="n">
-        <v>0.166236974721056</v>
+        <v>0.1662369747210561</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1696098360304623</v>
+        <v>0.1696098360304634</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1612989279759236</v>
+        <v>0.1612989279759262</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1757835742817626</v>
+        <v>0.1757835742817641</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1828942473684801</v>
+        <v>0.182894247368482</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2413006242601293</v>
+        <v>0.2413006242601284</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2539138710113827</v>
+        <v>0.2539138710113842</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2195362906674805</v>
+        <v>0.2195362906674806</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1809237754539006</v>
+        <v>0.1809237754539007</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2398354682662806</v>
+        <v>0.2398354682662816</v>
       </c>
       <c r="H8" t="n">
-        <v>0.243166102736896</v>
+        <v>0.2431661027368971</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2345494517998349</v>
+        <v>0.2345494517998351</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2379332193939876</v>
+        <v>0.2379332193939898</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1730860759276742</v>
+        <v>0.1730860759276762</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3020646870598013</v>
+        <v>0.3020646870598037</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2632651780267195</v>
+        <v>0.2632651780267212</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3122793495400629</v>
+        <v>0.3122793495400635</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3136643303664507</v>
+        <v>0.3136643303664532</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3593366014807443</v>
+        <v>0.3593366014807451</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3058137293331527</v>
+        <v>0.3058137293331534</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3110930700574659</v>
+        <v>0.3110930700574679</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3144237045275786</v>
+        <v>0.3144237045275804</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3058070535910206</v>
+        <v>0.3058070535910216</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3091799149004276</v>
+        <v>0.3091799149004297</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2729052914377898</v>
+        <v>0.2729052914377929</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3153536531517276</v>
+        <v>0.3153536531517301</v>
       </c>
     </row>
   </sheetData>
@@ -4877,28 +4877,28 @@
         <v>2.820058017619532</v>
       </c>
       <c r="D2" t="n">
-        <v>2.701388335764315</v>
+        <v>2.701388335764316</v>
       </c>
       <c r="E2" t="n">
-        <v>2.88904484284104</v>
+        <v>2.889044842841042</v>
       </c>
       <c r="F2" t="n">
-        <v>2.653419851931613</v>
+        <v>2.653419851931614</v>
       </c>
       <c r="G2" t="n">
-        <v>2.691875379548547</v>
+        <v>2.691875379548548</v>
       </c>
       <c r="H2" t="n">
-        <v>2.720065743901251</v>
+        <v>2.720065743901252</v>
       </c>
       <c r="I2" t="n">
-        <v>2.67009510891313</v>
+        <v>2.670095108913131</v>
       </c>
       <c r="J2" t="n">
-        <v>3.081275331464451</v>
+        <v>3.081275331464456</v>
       </c>
       <c r="K2" t="n">
-        <v>2.843723727670013</v>
+        <v>2.843723727670014</v>
       </c>
       <c r="L2" t="n">
         <v>2.70905385912181</v>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.9276678363416</v>
+        <v>1.927667836341599</v>
       </c>
       <c r="C3" t="n">
         <v>2.055931996598146</v>
@@ -4920,10 +4920,10 @@
         <v>2.030773507954851</v>
       </c>
       <c r="E3" t="n">
-        <v>2.169348997388225</v>
+        <v>2.169348997388226</v>
       </c>
       <c r="F3" t="n">
-        <v>1.780428422930139</v>
+        <v>1.78042842293014</v>
       </c>
       <c r="G3" t="n">
         <v>1.963363919298775</v>
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4916564766964483</v>
+        <v>0.4916564766964467</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2947445849697746</v>
+        <v>0.2947445849697752</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6549216004820012</v>
+        <v>0.6549216004820027</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2959416176569434</v>
+        <v>0.295941617656944</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2959416176569434</v>
+        <v>0.295941617656944</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5470483593641623</v>
+        <v>0.547048359364162</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8676864313792811</v>
+        <v>0.8676864313792824</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2986375842659497</v>
+        <v>0.2986375842659508</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6337162787028884</v>
+        <v>0.6337162787028893</v>
       </c>
       <c r="K4" t="n">
-        <v>0.435415987428618</v>
+        <v>0.4354159874286196</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7397389342536564</v>
+        <v>0.7397389342536577</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.728838108406091</v>
+        <v>5.728838108406075</v>
       </c>
       <c r="C5" t="n">
-        <v>2.384922802844441</v>
+        <v>2.384922802844447</v>
       </c>
       <c r="D5" t="n">
-        <v>8.786034687389414</v>
+        <v>8.786034687389424</v>
       </c>
       <c r="E5" t="n">
-        <v>2.38492289498226</v>
+        <v>2.384922894982267</v>
       </c>
       <c r="F5" t="n">
-        <v>2.38492289498226</v>
+        <v>2.384922894982267</v>
       </c>
       <c r="G5" t="n">
-        <v>7.023552200776319</v>
+        <v>7.023552200776328</v>
       </c>
       <c r="H5" t="n">
-        <v>14.1527850301928</v>
+        <v>14.15278503019279</v>
       </c>
       <c r="I5" t="n">
-        <v>2.384860095512413</v>
+        <v>2.384860095512418</v>
       </c>
       <c r="J5" t="n">
-        <v>8.932356134929107</v>
+        <v>8.932356134929112</v>
       </c>
       <c r="K5" t="n">
-        <v>4.875393762942671</v>
+        <v>4.875393762942672</v>
       </c>
       <c r="L5" t="n">
-        <v>5.31457371078608</v>
+        <v>5.314573710786083</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5170055327739945</v>
+        <v>0.5170055327739935</v>
       </c>
       <c r="C6" t="n">
-        <v>0.316908790958003</v>
+        <v>0.3169087909580147</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6865597953073743</v>
+        <v>0.6865597953073755</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3144623158867499</v>
+        <v>0.3144623158867503</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3234367595999892</v>
+        <v>0.3234367595999899</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5723974154417073</v>
+        <v>0.5723974154417079</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9865198639182891</v>
+        <v>0.9865198639182894</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4071838208116552</v>
+        <v>0.4071838208116556</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6641570341248252</v>
+        <v>0.6641570341248251</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4599266719199459</v>
+        <v>0.4599266719199538</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7677585618056791</v>
+        <v>0.7677585618056798</v>
       </c>
     </row>
     <row r="7">
@@ -5071,34 +5071,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5914483547037391</v>
+        <v>0.5914483547037365</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3984921696052691</v>
+        <v>0.3984921696052693</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7543548608662141</v>
+        <v>0.7543548608662149</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3983653552295674</v>
+        <v>0.3983653552295684</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3983653552295674</v>
+        <v>0.3983653552295683</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6468402373714527</v>
+        <v>0.6468402373714519</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9674783093865733</v>
+        <v>0.9674783093865732</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3984294622732415</v>
+        <v>0.3984294622732423</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7335081567101804</v>
+        <v>0.7335081567101802</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5352078654359101</v>
+        <v>0.53520786543591</v>
       </c>
       <c r="L7" t="n">
         <v>0.8395308122609484</v>
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6382075083552815</v>
+        <v>0.6382075083552817</v>
       </c>
       <c r="C8" t="n">
-        <v>0.561892059002426</v>
+        <v>0.561892059002427</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9418710674008735</v>
+        <v>0.9418710674008743</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5299526240438871</v>
+        <v>0.5299526240438879</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4490757231180468</v>
+        <v>0.4490757231180475</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8098852051901169</v>
+        <v>0.8098852051901173</v>
       </c>
       <c r="H8" t="n">
-        <v>1.130523277205336</v>
+        <v>1.13052327720534</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5614744300919056</v>
+        <v>0.5614744300919068</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8965759779416537</v>
+        <v>0.8965759779416548</v>
       </c>
       <c r="K8" t="n">
-        <v>0.579806950394729</v>
+        <v>0.5798069503947291</v>
       </c>
       <c r="L8" t="n">
-        <v>1.124046036563535</v>
+        <v>1.124046036563538</v>
       </c>
     </row>
     <row r="9">
@@ -5151,28 +5151,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8557071490601948</v>
+        <v>0.8557071490601953</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7735153749328118</v>
+        <v>0.7735153749328125</v>
       </c>
       <c r="D9" t="n">
-        <v>1.129736716936857</v>
+        <v>1.129736716936858</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9013350445950572</v>
+        <v>0.9013350445950578</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7735152797977251</v>
+        <v>0.7735152797977262</v>
       </c>
       <c r="G9" t="n">
         <v>1.021863442698996</v>
       </c>
       <c r="H9" t="n">
-        <v>1.342501514714119</v>
+        <v>1.342501514714117</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7734526676007849</v>
+        <v>0.773452667600785</v>
       </c>
       <c r="J9" t="n">
         <v>1.108531362037725</v>
@@ -5181,7 +5181,7 @@
         <v>0.8460537499715547</v>
       </c>
       <c r="L9" t="n">
-        <v>1.214554017588491</v>
+        <v>1.214554017588492</v>
       </c>
     </row>
   </sheetData>
@@ -5267,22 +5267,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.677540858698026</v>
+        <v>2.677540858698027</v>
       </c>
       <c r="C2" t="n">
         <v>2.819396791007936</v>
       </c>
       <c r="D2" t="n">
-        <v>2.695523990548602</v>
+        <v>2.695523990548603</v>
       </c>
       <c r="E2" t="n">
         <v>2.887268655880266</v>
       </c>
       <c r="F2" t="n">
-        <v>2.654747326578678</v>
+        <v>2.654747326578679</v>
       </c>
       <c r="G2" t="n">
-        <v>2.687453749981444</v>
+        <v>2.687453749981445</v>
       </c>
       <c r="H2" t="n">
         <v>2.709515283955625</v>
@@ -5291,7 +5291,7 @@
         <v>2.670210905841658</v>
       </c>
       <c r="J2" t="n">
-        <v>3.065216687523667</v>
+        <v>3.065216687523668</v>
       </c>
       <c r="K2" t="n">
         <v>2.837975227838602</v>
@@ -5307,16 +5307,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.884687346343044</v>
+        <v>1.884687346343045</v>
       </c>
       <c r="C3" t="n">
-        <v>2.078975347896578</v>
+        <v>2.078975347896579</v>
       </c>
       <c r="D3" t="n">
         <v>2.012484857946837</v>
       </c>
       <c r="E3" t="n">
-        <v>2.19058547580215</v>
+        <v>2.190585475802151</v>
       </c>
       <c r="F3" t="n">
         <v>1.806788096225939</v>
@@ -5325,10 +5325,10 @@
         <v>1.955416864035832</v>
       </c>
       <c r="H3" t="n">
-        <v>2.11617221818801</v>
+        <v>2.116172218188011</v>
       </c>
       <c r="I3" t="n">
-        <v>1.83230383694076</v>
+        <v>1.832303836940761</v>
       </c>
       <c r="J3" t="n">
         <v>2.594502932221465</v>
@@ -5337,7 +5337,7 @@
         <v>2.154860181778954</v>
       </c>
       <c r="L3" t="n">
-        <v>2.063877953950011</v>
+        <v>2.063877953950012</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4219466610678299</v>
+        <v>0.4219466610678301</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3324338785751926</v>
+        <v>0.3324338785751924</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6250744079694351</v>
+        <v>0.6250744079694366</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3334988150736709</v>
+        <v>0.3334988150736706</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3334988150736707</v>
+        <v>0.3334988150736705</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5335270260214586</v>
+        <v>0.5335270260214592</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7856031488249061</v>
+        <v>0.7856031488249076</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3365401903084098</v>
+        <v>0.3365401903084094</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5645587158780025</v>
+        <v>0.5645587158780035</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4338626438574468</v>
+        <v>0.4338626438574478</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7013377485805973</v>
+        <v>0.7013377485805984</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.38987792213342</v>
+        <v>4.389877922133425</v>
       </c>
       <c r="C5" t="n">
-        <v>2.887050333414725</v>
+        <v>2.887050333414735</v>
       </c>
       <c r="D5" t="n">
-        <v>7.698023567541529</v>
+        <v>7.698023567541533</v>
       </c>
       <c r="E5" t="n">
-        <v>2.887050452145104</v>
+        <v>2.887050452145109</v>
       </c>
       <c r="F5" t="n">
-        <v>2.887050452145103</v>
+        <v>2.887050452145109</v>
       </c>
       <c r="G5" t="n">
-        <v>6.35988144810227</v>
+        <v>6.359881448102273</v>
       </c>
       <c r="H5" t="n">
-        <v>11.82118444979241</v>
+        <v>11.82118444979244</v>
       </c>
       <c r="I5" t="n">
-        <v>2.886999433696298</v>
+        <v>2.886999433696308</v>
       </c>
       <c r="J5" t="n">
-        <v>7.231921036045616</v>
+        <v>7.231921036045617</v>
       </c>
       <c r="K5" t="n">
-        <v>4.371977988238946</v>
+        <v>4.371977988238933</v>
       </c>
       <c r="L5" t="n">
-        <v>5.587291825869785</v>
+        <v>5.587291825869772</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.446034477052856</v>
+        <v>0.4460344770528559</v>
       </c>
       <c r="C6" t="n">
-        <v>0.355297759168289</v>
+        <v>0.3552977591682928</v>
       </c>
       <c r="D6" t="n">
-        <v>0.654205087451611</v>
+        <v>0.6542050874516143</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3531437576738701</v>
+        <v>0.35314375767387</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3603633798062495</v>
+        <v>0.3603633798062491</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5576148420064871</v>
+        <v>0.557614842006488</v>
       </c>
       <c r="H6" t="n">
-        <v>0.893247042555579</v>
+        <v>0.8932470425555807</v>
       </c>
       <c r="I6" t="n">
-        <v>0.435067529276765</v>
+        <v>0.4350675292767656</v>
       </c>
       <c r="J6" t="n">
-        <v>0.592960921276532</v>
+        <v>0.5929609212765331</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4572936894565061</v>
+        <v>0.4572936894565083</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7277390964332219</v>
+        <v>0.7277390964332229</v>
       </c>
     </row>
     <row r="7">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5109763248700067</v>
+        <v>0.5109763248700084</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4256207538290192</v>
+        <v>0.4256207538290186</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7137702256939359</v>
+        <v>0.7137702256939367</v>
       </c>
       <c r="E7" t="n">
         <v>0.4251998930850299</v>
@@ -5482,22 +5482,22 @@
         <v>0.4251998930850299</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6225566898236359</v>
+        <v>0.6225566898236368</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8746328126270811</v>
+        <v>0.8746328126270841</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4255698541105862</v>
+        <v>0.4255698541105861</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6535883796801799</v>
+        <v>0.6535883796801808</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5228923076596242</v>
+        <v>0.522892307659626</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7903674123827746</v>
+        <v>0.7903674123827751</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5512509774683513</v>
+        <v>0.5512509774683527</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5682660202380381</v>
+        <v>0.5682660202380374</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8779287689764238</v>
+        <v>0.8779287689764255</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5401834675545383</v>
+        <v>0.5401834675545382</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4690872817672977</v>
+        <v>0.4690872817672976</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7651623798065263</v>
+        <v>0.7651623798065256</v>
       </c>
       <c r="H8" t="n">
-        <v>1.017238502610156</v>
+        <v>1.017238502610158</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5681755440934765</v>
+        <v>0.5681755440934761</v>
       </c>
       <c r="J8" t="n">
-        <v>0.796214180584885</v>
+        <v>0.7962141805848855</v>
       </c>
       <c r="K8" t="n">
-        <v>0.561266108706569</v>
+        <v>0.5612661087065711</v>
       </c>
       <c r="L8" t="n">
-        <v>1.039866427641616</v>
+        <v>1.039866427641617</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7319606823625547</v>
+        <v>0.7319606823625571</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7411212066714417</v>
+        <v>0.7411212066714414</v>
       </c>
       <c r="D9" t="n">
-        <v>1.029604563601112</v>
+        <v>1.029604563601115</v>
       </c>
       <c r="E9" t="n">
-        <v>0.850190741793734</v>
+        <v>0.8501907417937346</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7411211743454943</v>
+        <v>0.7411211743454948</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9380571426660567</v>
+        <v>0.9380571426660571</v>
       </c>
       <c r="H9" t="n">
         <v>1.190133265469504</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7410703069530085</v>
+        <v>0.7410703069530096</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9690888325226015</v>
+        <v>0.9690888325226032</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7836297800607964</v>
+        <v>0.7836297800607985</v>
       </c>
       <c r="L9" t="n">
-        <v>1.105867865225196</v>
+        <v>1.105867865225198</v>
       </c>
     </row>
   </sheetData>
@@ -5663,22 +5663,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.672548747768353</v>
+        <v>2.672548747768352</v>
       </c>
       <c r="C2" t="n">
         <v>2.827513501778669</v>
       </c>
       <c r="D2" t="n">
-        <v>2.68862121940728</v>
+        <v>2.688621219407279</v>
       </c>
       <c r="E2" t="n">
         <v>2.894454818326931</v>
       </c>
       <c r="F2" t="n">
-        <v>2.664376071892174</v>
+        <v>2.664376071892175</v>
       </c>
       <c r="G2" t="n">
-        <v>2.682707270890122</v>
+        <v>2.682707270890123</v>
       </c>
       <c r="H2" t="n">
         <v>2.69918973442744</v>
@@ -5693,7 +5693,7 @@
         <v>2.830913448587098</v>
       </c>
       <c r="L2" t="n">
-        <v>2.696057071397113</v>
+        <v>2.696057071397114</v>
       </c>
     </row>
     <row r="3">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.866038690783476</v>
+        <v>1.866038690783477</v>
       </c>
       <c r="C3" t="n">
         <v>2.139324185681286</v>
@@ -5721,16 +5721,16 @@
         <v>1.938457941471321</v>
       </c>
       <c r="H3" t="n">
-        <v>2.058928911812995</v>
+        <v>2.058928911812996</v>
       </c>
       <c r="I3" t="n">
-        <v>1.888441991925283</v>
+        <v>1.888441991925282</v>
       </c>
       <c r="J3" t="n">
-        <v>2.586091474321867</v>
+        <v>2.586091474321868</v>
       </c>
       <c r="K3" t="n">
-        <v>2.133177685119538</v>
+        <v>2.133177685119539</v>
       </c>
       <c r="L3" t="n">
         <v>2.035382309228057</v>
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3970507846149934</v>
+        <v>0.3970507846149965</v>
       </c>
       <c r="C4" t="n">
         <v>0.426916652633236</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5785967454789107</v>
+        <v>0.5785967454789132</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4279569152472154</v>
+        <v>0.427956915247215</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4279569152472151</v>
+        <v>0.427956915247215</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5114754334070675</v>
+        <v>0.5114754334070667</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7010181582157634</v>
+        <v>0.7010181582157662</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4309110758789668</v>
+        <v>0.430911075878967</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5618410266077306</v>
+        <v>0.5618410266077326</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4099924724719875</v>
+        <v>0.4099924724719908</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6612949274582871</v>
+        <v>0.6612949274582899</v>
       </c>
     </row>
     <row r="5">
@@ -5783,22 +5783,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.820312444557182</v>
+        <v>3.820312444557185</v>
       </c>
       <c r="C5" t="n">
-        <v>4.277255714809653</v>
+        <v>4.27725571480966</v>
       </c>
       <c r="D5" t="n">
-        <v>6.67153172463721</v>
+        <v>6.671531724637204</v>
       </c>
       <c r="E5" t="n">
-        <v>4.27725586027763</v>
+        <v>4.277255860277633</v>
       </c>
       <c r="F5" t="n">
-        <v>4.27725586027763</v>
+        <v>4.277255860277633</v>
       </c>
       <c r="G5" t="n">
-        <v>5.806626335143803</v>
+        <v>5.80662633514381</v>
       </c>
       <c r="H5" t="n">
         <v>9.765315241160584</v>
@@ -5807,13 +5807,13 @@
         <v>4.277231438423386</v>
       </c>
       <c r="J5" t="n">
-        <v>7.148757153270935</v>
+        <v>7.148757153270937</v>
       </c>
       <c r="K5" t="n">
-        <v>3.760608526331235</v>
+        <v>3.760608526331244</v>
       </c>
       <c r="L5" t="n">
-        <v>4.00228524828069</v>
+        <v>4.0022852482807</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4225407264533855</v>
+        <v>0.4225407264533841</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4544236407453739</v>
+        <v>0.4544236407453662</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6079309347244696</v>
+        <v>0.6079309347244712</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4522293915342204</v>
+        <v>0.4522293915342277</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4570325559594756</v>
+        <v>0.4570325559594767</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6081882909468859</v>
+        <v>0.6081882909468932</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8068171500765629</v>
+        <v>0.8068171500765653</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4564010177173597</v>
+        <v>0.4564010177173592</v>
       </c>
       <c r="J6" t="n">
         <v>0.6632478143737033</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4343344329980637</v>
+        <v>0.4343344329980643</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6891055658541316</v>
+        <v>0.689105565854133</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4841028675641504</v>
+        <v>0.4841028675641507</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5179874352143817</v>
+        <v>0.517987435214382</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6653151134927544</v>
+        <v>0.6653151134927622</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5172556046463987</v>
+        <v>0.5172556046463984</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5172556046463987</v>
+        <v>0.5172556046463984</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5985275163562236</v>
+        <v>0.5985275163562274</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7880702411649186</v>
+        <v>0.7880702411649193</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5179631588281248</v>
+        <v>0.5179631588281253</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6488931095568851</v>
+        <v>0.6488931095568859</v>
       </c>
       <c r="K7" t="n">
-        <v>0.497044555421143</v>
+        <v>0.4970445554211444</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7483470104074414</v>
+        <v>0.7483470104074427</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5214805868969483</v>
+        <v>0.5214805868969453</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6534825590270589</v>
+        <v>0.6534825590270594</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8218017063805098</v>
+        <v>0.8218017063805106</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6265133851027097</v>
+        <v>0.6265133851027099</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5582460919360646</v>
+        <v>0.5582460919360652</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7342814462012486</v>
+        <v>0.7342814462012479</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9238241710101559</v>
+        <v>0.923824171010158</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6537170886731474</v>
+        <v>0.6537170886731475</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7846663730972091</v>
+        <v>0.7846663730972094</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5325948861410987</v>
+        <v>0.532594886141102</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9868631181729003</v>
+        <v>0.9868631181729032</v>
       </c>
     </row>
     <row r="9">
@@ -5943,34 +5943,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6849126401768031</v>
+        <v>0.6849126401768085</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8068137322802473</v>
+        <v>0.806813732280248</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9544751606464131</v>
+        <v>0.9544751606464129</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9083829598066009</v>
+        <v>0.9083829598066019</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8068137555994548</v>
+        <v>0.8068137555994549</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8873538134220893</v>
+        <v>0.8873538134220929</v>
       </c>
       <c r="H9" t="n">
-        <v>1.076896538230787</v>
+        <v>1.076896538230788</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8067894558939899</v>
+        <v>0.8067894558939909</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9377194066227555</v>
+        <v>0.9377194066227564</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7348737473362572</v>
+        <v>0.7348737473362627</v>
       </c>
       <c r="L9" t="n">
         <v>1.037173307473312</v>
@@ -6059,22 +6059,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.612336578531737</v>
+        <v>2.612336578531738</v>
       </c>
       <c r="C2" t="n">
         <v>2.756445728322899</v>
       </c>
       <c r="D2" t="n">
-        <v>2.619791392889366</v>
+        <v>2.619791392889367</v>
       </c>
       <c r="E2" t="n">
-        <v>2.82224259191282</v>
+        <v>2.822242591912819</v>
       </c>
       <c r="F2" t="n">
         <v>2.595228696526114</v>
       </c>
       <c r="G2" t="n">
-        <v>2.617363805126579</v>
+        <v>2.61736380512658</v>
       </c>
       <c r="H2" t="n">
         <v>2.626298110720708</v>
@@ -6089,7 +6089,7 @@
         <v>2.764442878837718</v>
       </c>
       <c r="L2" t="n">
-        <v>2.620348954304859</v>
+        <v>2.620348954304858</v>
       </c>
     </row>
     <row r="3">
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.722541234510321</v>
+        <v>1.72254123451032</v>
       </c>
       <c r="C3" t="n">
         <v>1.956610200816029</v>
@@ -6111,19 +6111,19 @@
         <v>2.065032871177562</v>
       </c>
       <c r="F3" t="n">
-        <v>1.690326701835006</v>
+        <v>1.690326701835005</v>
       </c>
       <c r="G3" t="n">
-        <v>1.758255749172082</v>
+        <v>1.758255749172081</v>
       </c>
       <c r="H3" t="n">
         <v>1.823556454680994</v>
       </c>
       <c r="I3" t="n">
-        <v>1.717351100470953</v>
+        <v>1.717351100470952</v>
       </c>
       <c r="J3" t="n">
-        <v>2.52262153675077</v>
+        <v>2.522621536750772</v>
       </c>
       <c r="K3" t="n">
         <v>1.994297324970364</v>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1888863925186441</v>
+        <v>0.1888863925186439</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1731228161019222</v>
+        <v>0.1731228161019221</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2730919500721075</v>
+        <v>0.2730919500721077</v>
       </c>
       <c r="E4" t="n">
+        <v>0.1741668713375777</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.1741668713375778</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.1741668713375777</v>
       </c>
       <c r="G4" t="n">
         <v>0.2453621114530156</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3493182385888069</v>
+        <v>0.3493182385888066</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1785799174251629</v>
+        <v>0.1785799174251627</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5029389276242126</v>
+        <v>0.5029389276242127</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2318799427724505</v>
+        <v>0.2318799427724506</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2788897714444077</v>
+        <v>0.2788897714444076</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.119962118866147</v>
+        <v>1.11996211886614</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9719453171276436</v>
+        <v>0.971945317127642</v>
       </c>
       <c r="D5" t="n">
-        <v>2.437065282605707</v>
+        <v>2.437065282605703</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9719454929968976</v>
+        <v>0.9719454929968971</v>
       </c>
       <c r="F5" t="n">
-        <v>0.971945492996898</v>
+        <v>0.9719454929968971</v>
       </c>
       <c r="G5" t="n">
-        <v>2.101541144753114</v>
+        <v>2.101541144753121</v>
       </c>
       <c r="H5" t="n">
-        <v>4.091019723123632</v>
+        <v>4.09101972312363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9719244705794484</v>
+        <v>0.9719244705794458</v>
       </c>
       <c r="J5" t="n">
-        <v>7.178677465882923</v>
+        <v>7.178677465882927</v>
       </c>
       <c r="K5" t="n">
-        <v>1.818430771329818</v>
+        <v>1.818430771329817</v>
       </c>
       <c r="L5" t="n">
-        <v>3.088316392894015</v>
+        <v>3.088316392894013</v>
       </c>
     </row>
     <row r="6">
@@ -6219,13 +6219,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.251803083404888</v>
+        <v>0.2518030834048871</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1876818879055172</v>
+        <v>0.187681887905524</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3394042173478136</v>
+        <v>0.3394042173478139</v>
       </c>
       <c r="E6" t="n">
         <v>0.1861722399222044</v>
@@ -6234,19 +6234,19 @@
         <v>0.1904058967205206</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3082788023392597</v>
+        <v>0.3082788023392593</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3625686094613783</v>
+        <v>0.3625686094613778</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2414966083114064</v>
+        <v>0.2414966083114062</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5710854540727539</v>
+        <v>0.5710854540727541</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2444563223355647</v>
+        <v>0.2444563223355648</v>
       </c>
       <c r="L6" t="n">
         <v>0.2918138672139485</v>
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2632820577900893</v>
+        <v>0.2632820577900895</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2529964292448028</v>
+        <v>0.2529964292448033</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3471303139351374</v>
+        <v>0.3471303139351376</v>
       </c>
       <c r="E7" t="n">
         <v>0.2518763689884211</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2518763689884212</v>
+        <v>0.2518763689884211</v>
       </c>
       <c r="G7" t="n">
-        <v>0.319757776724461</v>
+        <v>0.3197577767244609</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4237139038602521</v>
+        <v>0.4237139038602519</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2529755826966082</v>
+        <v>0.2529755826966084</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5773345928956573</v>
+        <v>0.5773345928956577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3062756080438954</v>
+        <v>0.3062756080438958</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3532854367158522</v>
+        <v>0.3532854367158524</v>
       </c>
     </row>
     <row r="8">
@@ -6302,34 +6302,34 @@
         <v>0.2878275765433417</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3565661394168456</v>
+        <v>0.3565661394168457</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4681726547058914</v>
+        <v>0.4681726547058916</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3347545350011957</v>
+        <v>0.3347545350011959</v>
       </c>
       <c r="F8" t="n">
-        <v>0.279611084512771</v>
+        <v>0.2796110845127709</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4239314081899941</v>
+        <v>0.4239314081899944</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5278875353259703</v>
+        <v>0.5278875353259709</v>
       </c>
       <c r="I8" t="n">
         <v>0.3571492141621417</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6815238735349686</v>
+        <v>0.6815238735349695</v>
       </c>
       <c r="K8" t="n">
         <v>0.329341993723861</v>
       </c>
       <c r="L8" t="n">
-        <v>0.540637290276608</v>
+        <v>0.5406372902766087</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4315307336556208</v>
+        <v>0.4315307336556207</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4956453501311404</v>
+        <v>0.4956453501311405</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5901365481642187</v>
+        <v>0.5901365481642185</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5815017513782199</v>
+        <v>0.581501751378219</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4956454535007577</v>
+        <v>0.4956454535007574</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5624066976107985</v>
+        <v>0.5624066976107984</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6663628247465898</v>
+        <v>0.6663628247465893</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4956245035829453</v>
+        <v>0.495624503582945</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8199835137819952</v>
+        <v>0.8199835137819947</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5058167397924019</v>
+        <v>0.5058167397924015</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5959343576021898</v>
+        <v>0.5959343576021893</v>
       </c>
     </row>
   </sheetData>
@@ -6473,16 +6473,16 @@
         <v>2.571327769745714</v>
       </c>
       <c r="H2" t="n">
-        <v>2.573423982836053</v>
+        <v>2.573423982836052</v>
       </c>
       <c r="I2" t="n">
-        <v>2.573193451807608</v>
+        <v>2.573193451807607</v>
       </c>
       <c r="J2" t="n">
         <v>2.921171896474612</v>
       </c>
       <c r="K2" t="n">
-        <v>2.705966347221687</v>
+        <v>2.705966347221686</v>
       </c>
       <c r="L2" t="n">
         <v>2.574661464236309</v>
@@ -6504,7 +6504,7 @@
         <v>1.671052939018044</v>
       </c>
       <c r="E3" t="n">
-        <v>1.983453536084574</v>
+        <v>1.983453536084575</v>
       </c>
       <c r="F3" t="n">
         <v>1.62230307920031</v>
@@ -6513,13 +6513,13 @@
         <v>1.637631685197211</v>
       </c>
       <c r="H3" t="n">
-        <v>1.653983388170573</v>
+        <v>1.653983388170572</v>
       </c>
       <c r="I3" t="n">
         <v>1.650868469125015</v>
       </c>
       <c r="J3" t="n">
-        <v>2.244137801552141</v>
+        <v>2.24413780155214</v>
       </c>
       <c r="K3" t="n">
         <v>1.851925602182861</v>
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009226695610638075</v>
+        <v>0.0009226695610621144</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08147991958212752</v>
+        <v>0.08147991958212747</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1201446768082447</v>
+        <v>0.1201446768082425</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08204629367968114</v>
+        <v>0.08204629367968073</v>
       </c>
       <c r="F4" t="n">
-        <v>0.082046293679681</v>
+        <v>0.08204629367968073</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06661946530320884</v>
+        <v>0.0666194653032087</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09327122956840574</v>
+        <v>0.09327122956840452</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08623358279456358</v>
+        <v>0.08623358279456371</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1270566053384913</v>
+        <v>0.1270566053384902</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05035985302944854</v>
+        <v>0.05035985302944639</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1033807668192343</v>
+        <v>0.103380766819234</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.573593086621445</v>
+        <v>-1.573593086621448</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1257105725584298</v>
+        <v>-0.1257105725584313</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3637474255214833</v>
+        <v>0.3637474255214832</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.125710384808818</v>
+        <v>-0.1257103848088199</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1257103848088182</v>
+        <v>-0.1257103848088199</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4562007344557971</v>
+        <v>-0.4562007344557893</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03329837636192706</v>
+        <v>-0.03329837636192889</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1257114702240376</v>
+        <v>-0.1257114702240381</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5016982098905021</v>
+        <v>0.5016982098904996</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7114337558571859</v>
+        <v>-0.7114337558571873</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6209723335709769</v>
+        <v>0.6209723335709751</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03111513206489445</v>
+        <v>0.03111513206489233</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0850067481596429</v>
+        <v>0.085006748159625</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1208055306215472</v>
+        <v>0.120805530621547</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0845838520635657</v>
+        <v>0.08458385206356561</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08558647391762067</v>
+        <v>0.08558647391762042</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0968119278070415</v>
+        <v>0.09681192780703829</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1312557122390564</v>
+        <v>0.1312557122390554</v>
       </c>
       <c r="I6" t="n">
-        <v>0.116426045298394</v>
+        <v>0.1164260452983936</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1279521809906719</v>
+        <v>0.127952180990671</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04904389328749212</v>
+        <v>0.04904389328749123</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1032740086153438</v>
+        <v>0.1032740086153433</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05610846575527598</v>
+        <v>0.05610846575527408</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1414202766543824</v>
+        <v>0.1414202766543823</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1749977445630109</v>
+        <v>0.1749977445630101</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1401014220501703</v>
+        <v>0.1401014220501702</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1401014220501704</v>
+        <v>0.1401014220501702</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1218052614974222</v>
+        <v>0.1218052614974221</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1484570257626184</v>
+        <v>0.1484570257626182</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1414193789887774</v>
+        <v>0.1414193789887773</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1822424015327031</v>
+        <v>0.1822424015327034</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1055456492236611</v>
+        <v>0.1055456492236601</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1585665630134487</v>
+        <v>0.1585665630134473</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06529047118904796</v>
+        <v>0.06529047118904874</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2018995030815406</v>
+        <v>0.2018995030815405</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2474493077055972</v>
+        <v>0.2474493077055958</v>
       </c>
       <c r="E8" t="n">
-        <v>0.187639873597703</v>
+        <v>0.1876398735977029</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1516664562162183</v>
+        <v>0.1516664562162181</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1831150589446079</v>
+        <v>0.1831150589446065</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2097668232097366</v>
+        <v>0.2097668232097354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2027291764359629</v>
+        <v>0.2027291764359624</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2435624436046938</v>
+        <v>0.2435624436046901</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1137593541553832</v>
+        <v>0.1137593541553817</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2743281980951101</v>
+        <v>0.2743281980951084</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1503730132372212</v>
+        <v>0.1503730132372199</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2819036494401762</v>
+        <v>0.2819036494401752</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3158138363376365</v>
+        <v>0.3158138363376342</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3352393511064179</v>
+        <v>0.3352393511064172</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2819038196350276</v>
+        <v>0.281903819635027</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2622886342832179</v>
+        <v>0.2622886342832155</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2889403985484123</v>
+        <v>0.288940398548411</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2819027517745715</v>
+        <v>0.2819027517745708</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3227257743184984</v>
+        <v>0.322725774318497</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2192496491381782</v>
+        <v>0.219249649138178</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2990499357992423</v>
+        <v>0.2990499357992397</v>
       </c>
     </row>
   </sheetData>
@@ -6857,10 +6857,10 @@
         <v>2.698828033744555</v>
       </c>
       <c r="D2" t="n">
-        <v>2.566724876333738</v>
+        <v>2.566724876333739</v>
       </c>
       <c r="E2" t="n">
-        <v>2.760337128337752</v>
+        <v>2.760337128337753</v>
       </c>
       <c r="F2" t="n">
         <v>2.544787301843477</v>
@@ -6869,13 +6869,13 @@
         <v>2.560232389002389</v>
       </c>
       <c r="H2" t="n">
-        <v>2.565545010319513</v>
+        <v>2.565545010319512</v>
       </c>
       <c r="I2" t="n">
         <v>2.562998947161537</v>
       </c>
       <c r="J2" t="n">
-        <v>2.897105933806954</v>
+        <v>2.897105933806953</v>
       </c>
       <c r="K2" t="n">
         <v>2.687283323610941</v>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.533169861064446</v>
+        <v>1.533169861064445</v>
       </c>
       <c r="C3" t="n">
         <v>1.857249733515256</v>
@@ -6903,7 +6903,7 @@
         <v>1.958776727509421</v>
       </c>
       <c r="F3" t="n">
-        <v>1.602994309239379</v>
+        <v>1.60299430923938</v>
       </c>
       <c r="G3" t="n">
         <v>1.613376427610021</v>
@@ -6921,7 +6921,7 @@
         <v>1.804563468728552</v>
       </c>
       <c r="L3" t="n">
-        <v>1.656675830220451</v>
+        <v>1.65667583022045</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09678223111199395</v>
+        <v>-0.09678223111199137</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05462178268385265</v>
+        <v>0.05462178268385286</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1040431995960549</v>
+        <v>0.104043199596057</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05509741188138177</v>
+        <v>0.05509741188138184</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05509741188138174</v>
+        <v>0.05509741188138187</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03045506244566158</v>
+        <v>0.03045506244566307</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09283471149825477</v>
+        <v>0.09283471149825696</v>
       </c>
       <c r="I4" t="n">
         <v>0.06027086474160308</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03571703847684188</v>
+        <v>0.03571703847684424</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.008098543332752242</v>
+        <v>-0.0080985433327493</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09930945585030396</v>
+        <v>0.09930945585030607</v>
       </c>
     </row>
     <row r="5">
@@ -6971,34 +6971,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-3.012740823100415</v>
+        <v>-3.012740823100417</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4272711524536976</v>
+        <v>-0.4272711524536978</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2372727715506292</v>
+        <v>0.2372727715506303</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4272709357879438</v>
+        <v>-0.4272709357879473</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4272709357879438</v>
+        <v>-0.4272709357879473</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9384758062180154</v>
+        <v>-0.9384758062180089</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06081537467285136</v>
+        <v>0.06081537467285503</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4272696897278911</v>
+        <v>-0.4272696897278933</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9170280556762651</v>
+        <v>-0.917028055676262</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.461385048771889</v>
+        <v>-1.46138504877189</v>
       </c>
       <c r="L5" t="n">
         <v>-0.2799588131417932</v>
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1012760660347574</v>
+        <v>-0.1012760660347555</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05620588224118573</v>
+        <v>0.05620588224118641</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1023632362030083</v>
+        <v>0.1023632362030106</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05611629270457827</v>
+        <v>0.05611629270458861</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05659522234460636</v>
+        <v>0.05659522234460603</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02596122752289891</v>
+        <v>0.02596122752290098</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1230607076643598</v>
+        <v>0.1230607076643647</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05577702981884092</v>
+        <v>0.05577702981884107</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03306329344312586</v>
+        <v>0.03306329344312903</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01307083809949852</v>
+        <v>-0.01307083809949458</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09638560883678793</v>
+        <v>0.09638560883679094</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.04515094594151615</v>
+        <v>-0.04515094594151194</v>
       </c>
       <c r="C7" t="n">
         <v>0.1119006871862762</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1553419673673498</v>
+        <v>0.1553419673673513</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1102640888518752</v>
+        <v>0.1102640888518751</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1102640888518752</v>
+        <v>0.1102640888518751</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08208634761613987</v>
+        <v>0.08208634761614225</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1444659966687328</v>
+        <v>0.1444659966687355</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1119021499120822</v>
+        <v>0.1119021499120823</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0873483236473209</v>
+        <v>0.08734832364732356</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0435327418377275</v>
+        <v>0.04353274183772862</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1509407410207819</v>
+        <v>0.1509407410207867</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03946082708928367</v>
+        <v>-0.03946082708928217</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1626045188166479</v>
+        <v>0.1626045188166482</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2170836683629194</v>
+        <v>0.2170836683629215</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1500123867109583</v>
+        <v>0.1500123867109582</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1182758180774035</v>
+        <v>0.1182758180774034</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1339261033626203</v>
+        <v>0.1339261033626221</v>
       </c>
       <c r="H8" t="n">
-        <v>0.19630575241501</v>
+        <v>0.1963057524150119</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1637419056585622</v>
+        <v>0.1637419056585618</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1391971491654805</v>
+        <v>0.1391971491654823</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04836560748617769</v>
+        <v>0.04836560748617884</v>
       </c>
       <c r="L8" t="n">
-        <v>0.250987651518837</v>
+        <v>0.2509876515188383</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03468752440925474</v>
+        <v>0.03468752440925763</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2323320780174341</v>
+        <v>0.232332078017434</v>
       </c>
       <c r="D9" t="n">
-        <v>0.27610585178521</v>
+        <v>0.2761058517852106</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2791756193271734</v>
+        <v>0.2791756193271743</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2323322759988292</v>
+        <v>0.2323322759988289</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2025177384472979</v>
+        <v>0.2025177384473005</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2648973874998922</v>
+        <v>0.2648973874998938</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2323335407432399</v>
+        <v>0.23233354074324</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2077797144784803</v>
+        <v>0.2077797144784815</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1394902018268619</v>
+        <v>0.139490201826864</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2713721318519414</v>
+        <v>0.2713721318519436</v>
       </c>
     </row>
   </sheetData>
@@ -7256,10 +7256,10 @@
         <v>2.684850842862684</v>
       </c>
       <c r="E2" t="n">
-        <v>2.869421315191468</v>
+        <v>2.869421315191467</v>
       </c>
       <c r="F2" t="n">
-        <v>2.637332215575795</v>
+        <v>2.637332215575794</v>
       </c>
       <c r="G2" t="n">
         <v>2.67190713848965</v>
@@ -7268,16 +7268,16 @@
         <v>2.702566362392997</v>
       </c>
       <c r="I2" t="n">
-        <v>2.654238543242303</v>
+        <v>2.654238543242302</v>
       </c>
       <c r="J2" t="n">
-        <v>3.052848366266073</v>
+        <v>3.052848366266072</v>
       </c>
       <c r="K2" t="n">
         <v>2.820070563393684</v>
       </c>
       <c r="L2" t="n">
-        <v>2.688304897749952</v>
+        <v>2.68830489774995</v>
       </c>
     </row>
     <row r="3">
@@ -7296,10 +7296,10 @@
         <v>2.003219662782175</v>
       </c>
       <c r="E3" t="n">
-        <v>2.141069306126567</v>
+        <v>2.141069306126568</v>
       </c>
       <c r="F3" t="n">
-        <v>1.757985427715699</v>
+        <v>1.7579854277157</v>
       </c>
       <c r="G3" t="n">
         <v>1.911698651310101</v>
@@ -7314,7 +7314,7 @@
         <v>2.579545948448426</v>
       </c>
       <c r="K3" t="n">
-        <v>2.108348892508675</v>
+        <v>2.108348892508674</v>
       </c>
       <c r="L3" t="n">
         <v>2.03003111814054</v>
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3633650461324335</v>
+        <v>0.363365046132433</v>
       </c>
       <c r="C4" t="n">
         <v>0.265876628773988</v>
       </c>
       <c r="D4" t="n">
-        <v>0.618445079175536</v>
+        <v>0.6184450791755356</v>
       </c>
       <c r="E4" t="n">
         <v>0.2669966593109321</v>
       </c>
       <c r="F4" t="n">
-        <v>0.266996659310932</v>
+        <v>0.2669966593109322</v>
       </c>
       <c r="G4" t="n">
-        <v>0.471848397585754</v>
+        <v>0.4718483975857544</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8196320543556723</v>
+        <v>0.8196320543556729</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2700439377806327</v>
+        <v>0.270043937780633</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5511724361085956</v>
+        <v>0.551172436108595</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3733937762929458</v>
+        <v>0.3733937762929456</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6555658076823134</v>
+        <v>0.6555658076823127</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.659187682777363</v>
+        <v>3.659187682777358</v>
       </c>
       <c r="C5" t="n">
-        <v>2.066724512317076</v>
+        <v>2.066724512317073</v>
       </c>
       <c r="D5" t="n">
-        <v>7.970707778380603</v>
+        <v>7.970707778380616</v>
       </c>
       <c r="E5" t="n">
-        <v>2.066724622528551</v>
+        <v>2.066724622528548</v>
       </c>
       <c r="F5" t="n">
-        <v>2.066724622528551</v>
+        <v>2.066724622528548</v>
       </c>
       <c r="G5" t="n">
-        <v>5.683536634090179</v>
+        <v>5.683536634090187</v>
       </c>
       <c r="H5" t="n">
-        <v>12.35597430378459</v>
+        <v>12.35597430378458</v>
       </c>
       <c r="I5" t="n">
-        <v>2.06667252003028</v>
+        <v>2.066672520030276</v>
       </c>
       <c r="J5" t="n">
-        <v>7.563145309087066</v>
+        <v>7.563145309087063</v>
       </c>
       <c r="K5" t="n">
-        <v>3.865231663440274</v>
+        <v>3.865231663440273</v>
       </c>
       <c r="L5" t="n">
-        <v>4.030617546029122</v>
+        <v>4.030617546029139</v>
       </c>
     </row>
     <row r="6">
@@ -7407,16 +7407,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3852219786366312</v>
+        <v>0.3852219786366315</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2860568009602439</v>
+        <v>0.2860568009602229</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6472596784942271</v>
+        <v>0.6472596784942274</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2839129361905141</v>
+        <v>0.2839129361905246</v>
       </c>
       <c r="F6" t="n">
         <v>0.2915815670400548</v>
@@ -7425,16 +7425,16 @@
         <v>0.5691135578556137</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9268415202055302</v>
+        <v>0.9268415202055328</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3673090980504931</v>
+        <v>0.3673090980504927</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6532457284550164</v>
+        <v>0.6532457284550173</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3945262372730129</v>
+        <v>0.3945262372730164</v>
       </c>
       <c r="L6" t="n">
         <v>0.6799717178272981</v>
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4550768567253364</v>
+        <v>0.4550768567253363</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3618077406603348</v>
+        <v>0.3618077406603351</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7097986047723596</v>
+        <v>0.7097986047723598</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3614528021765012</v>
+        <v>0.3614528021765014</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3614528021765012</v>
+        <v>0.3614528021765014</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5635602081786558</v>
+        <v>0.5635602081786565</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9113438649485759</v>
+        <v>0.9113438649485756</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3617557483735357</v>
+        <v>0.3617557483735359</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6428842467014987</v>
+        <v>0.6428842467014981</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4651055868858489</v>
+        <v>0.4651055868858486</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7472776182752141</v>
+        <v>0.7472776182752143</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4947838630544729</v>
+        <v>0.4947838630544742</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5062380670496637</v>
+        <v>0.5062380670496635</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8761404776235467</v>
+        <v>0.8761404776235454</v>
       </c>
       <c r="E8" t="n">
-        <v>0.477521096086797</v>
+        <v>0.4775210960867979</v>
       </c>
       <c r="F8" t="n">
         <v>0.4048321073952488</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7078565218301038</v>
+        <v>0.7078565218301044</v>
       </c>
       <c r="H8" t="n">
-        <v>1.055640178600128</v>
+        <v>1.055640178600129</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5060520620249833</v>
+        <v>0.5060520620249832</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7872011150823727</v>
+        <v>0.7872011150823721</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5028697931403069</v>
+        <v>0.5028697931403067</v>
       </c>
       <c r="L8" t="n">
-        <v>1.000826208980063</v>
+        <v>1.000826208980062</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6964809262276475</v>
+        <v>0.6964809262276469</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7045150179206263</v>
+        <v>0.7045150179206273</v>
       </c>
       <c r="D9" t="n">
         <v>1.052864174109979</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8214166656373566</v>
+        <v>0.8214166656373585</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7045149499930697</v>
+        <v>0.7045149499930704</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9062674854389478</v>
+        <v>0.9062674854389485</v>
       </c>
       <c r="H9" t="n">
-        <v>1.254051142208869</v>
+        <v>1.254051142208867</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7044630256338272</v>
+        <v>0.704463025633827</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9855915239617891</v>
+        <v>0.9855915239617905</v>
       </c>
       <c r="K9" t="n">
         <v>0.7491173907011194</v>
       </c>
       <c r="L9" t="n">
-        <v>1.089984895535507</v>
+        <v>1.089984895535508</v>
       </c>
     </row>
   </sheetData>
@@ -7649,16 +7649,16 @@
         <v>2.752163687214296</v>
       </c>
       <c r="D2" t="n">
-        <v>2.633480503814324</v>
+        <v>2.633480503814325</v>
       </c>
       <c r="E2" t="n">
-        <v>2.817220378951921</v>
+        <v>2.81722037895192</v>
       </c>
       <c r="F2" t="n">
         <v>2.592090010483835</v>
       </c>
       <c r="G2" t="n">
-        <v>2.613204401487478</v>
+        <v>2.613204401487479</v>
       </c>
       <c r="H2" t="n">
         <v>2.605340560229346</v>
@@ -7667,13 +7667,13 @@
         <v>2.608318646616644</v>
       </c>
       <c r="J2" t="n">
-        <v>2.977736328392976</v>
+        <v>2.977736328392977</v>
       </c>
       <c r="K2" t="n">
-        <v>2.757560308280562</v>
+        <v>2.757560308280563</v>
       </c>
       <c r="L2" t="n">
-        <v>2.630978387670485</v>
+        <v>2.630978387670486</v>
       </c>
     </row>
     <row r="3">
@@ -7686,13 +7686,13 @@
         <v>1.666810865204983</v>
       </c>
       <c r="C3" t="n">
-        <v>1.951255243105482</v>
+        <v>1.951255243105483</v>
       </c>
       <c r="D3" t="n">
         <v>1.891889493316432</v>
       </c>
       <c r="E3" t="n">
-        <v>2.058472069649765</v>
+        <v>2.058472069649764</v>
       </c>
       <c r="F3" t="n">
         <v>1.686875038804722</v>
@@ -7701,13 +7701,13 @@
         <v>1.748387653021136</v>
       </c>
       <c r="H3" t="n">
-        <v>1.695188893027198</v>
+        <v>1.695188893027199</v>
       </c>
       <c r="I3" t="n">
-        <v>1.71365274444311</v>
+        <v>1.713652744443111</v>
       </c>
       <c r="J3" t="n">
-        <v>2.380926375995154</v>
+        <v>2.380926375995155</v>
       </c>
       <c r="K3" t="n">
         <v>1.971863075982986</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1006949439904852</v>
+        <v>0.1006949439904849</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1696588219899307</v>
+        <v>0.1696588219899306</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4594112375280293</v>
+        <v>0.4594112375280323</v>
       </c>
       <c r="E4" t="n">
         <v>0.1703894969714243</v>
@@ -7738,22 +7738,22 @@
         <v>0.1703894969714243</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2300803626196634</v>
+        <v>0.2300803626196626</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1463583515398425</v>
+        <v>0.146358351539839</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1731713928260277</v>
+        <v>0.1731713928260278</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2931728880041514</v>
+        <v>0.2931728880041505</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1998648174807359</v>
+        <v>0.1998648174807336</v>
       </c>
       <c r="L4" t="n">
-        <v>0.428226440294469</v>
+        <v>0.4282264402944652</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3193136444043858</v>
+        <v>-0.3193136444043846</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8761301217983866</v>
+        <v>0.8761301217983877</v>
       </c>
       <c r="D5" t="n">
-        <v>5.208096955390205</v>
+        <v>5.208096955390206</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8761302547736743</v>
+        <v>0.8761302547736756</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8761302547736743</v>
+        <v>0.8761302547736756</v>
       </c>
       <c r="G5" t="n">
-        <v>1.783960622613804</v>
+        <v>1.7839606226138</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4626995115440459</v>
+        <v>0.462699511544047</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8761115031551285</v>
+        <v>0.8761115031551279</v>
       </c>
       <c r="J5" t="n">
-        <v>3.057656101243099</v>
+        <v>3.057656101243102</v>
       </c>
       <c r="K5" t="n">
         <v>1.251153727691566</v>
       </c>
       <c r="L5" t="n">
-        <v>5.831321620726573</v>
+        <v>5.831321620726557</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1577180478945766</v>
+        <v>0.1577180478945759</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1800431434387035</v>
+        <v>0.1800431434386904</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4761556877391267</v>
+        <v>0.4761556877391268</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1788320878804756</v>
+        <v>0.1788320878804759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1821246204049356</v>
+        <v>0.1821246204049358</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2871034665237508</v>
+        <v>0.2871034665237531</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2105595035533659</v>
+        <v>0.2105595035533642</v>
       </c>
       <c r="I6" t="n">
-        <v>0.230194496730117</v>
+        <v>0.2301944967301172</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3048118954955479</v>
+        <v>0.3048118954955488</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2088725481309602</v>
+        <v>0.2088725481309616</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4389857570385</v>
+        <v>0.4389857570384992</v>
       </c>
     </row>
     <row r="7">
@@ -7843,13 +7843,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.168498098136811</v>
+        <v>0.1684980981368126</v>
       </c>
       <c r="C7" t="n">
         <v>0.240993165615615</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5268810586842475</v>
+        <v>0.5268810586842489</v>
       </c>
       <c r="E7" t="n">
         <v>0.2402876071994074</v>
@@ -7858,22 +7858,22 @@
         <v>0.2402876071994074</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2978835167659906</v>
+        <v>0.2978835167659898</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2141615056861677</v>
+        <v>0.2141615056861663</v>
       </c>
       <c r="I7" t="n">
         <v>0.2409745469723543</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3609760421504786</v>
+        <v>0.3609760421504773</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2676679716270606</v>
+        <v>0.2676679716270608</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4960295944407925</v>
+        <v>0.4960295944407934</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1896374805716607</v>
+        <v>0.1896374805716622</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3333389692794478</v>
+        <v>0.3333389692794482</v>
       </c>
       <c r="D8" t="n">
-        <v>0.634614369908315</v>
+        <v>0.6346143699083175</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3137330101878004</v>
+        <v>0.3137330101877998</v>
       </c>
       <c r="F8" t="n">
-        <v>0.264175273865084</v>
+        <v>0.2641752738650849</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3904687354326883</v>
+        <v>0.3904687354326873</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3067467243530239</v>
+        <v>0.306746724353024</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3335597656390503</v>
+        <v>0.3335597656390519</v>
       </c>
       <c r="J8" t="n">
-        <v>0.453575301951434</v>
+        <v>0.4535753019514348</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2874802109745472</v>
+        <v>0.2874802109745482</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6632459632387155</v>
+        <v>0.6632459632387169</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3079649438204226</v>
+        <v>0.3079649438204239</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4442810748492686</v>
+        <v>0.4442810748492685</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7305023524059341</v>
+        <v>0.7305023524059338</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5179293831310613</v>
+        <v>0.517929383131061</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4442811875380465</v>
+        <v>0.4442811875380467</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5011714259996437</v>
+        <v>0.5011714259996424</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4174494149198207</v>
+        <v>0.4174494149198194</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4442624562060077</v>
+        <v>0.4442624562060078</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5642639513841322</v>
+        <v>0.5642639513841299</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4339777276549871</v>
+        <v>0.4339777276549875</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6993175036744469</v>
+        <v>0.6993175036744461</v>
       </c>
     </row>
   </sheetData>
